--- a/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
+++ b/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
@@ -22,6 +22,9 @@
     <sheet name="FECHAMENTO EM ALVENARIA" sheetId="9" r:id="rId6"/>
     <sheet name="TABELAS LÍBANO" sheetId="10" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CONTENÇÃO RÁPIDA'!$K$1:$T$255</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="1000"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1097,7 +1100,7 @@
     <numFmt numFmtId="167" formatCode="0.000%"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1334,55 +1337,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFC00000"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1457,31 +1446,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFD1D1D1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2010,16 +1981,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2030,7 +2001,7 @@
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2482,59 +2453,68 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="left"/>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="left"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="34" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="38" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="40" fillId="16" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2543,7 +2523,7 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
     <dxf>
       <font>
         <color theme="0"/>
@@ -2594,6 +2574,21 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2605,6 +2600,2979 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1100" b="1">
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>PILAR – CARGA TRAPEZOIDAL (kN/m)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Pilar</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="76200" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$141:$L$142</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$141:$M$142</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Carga (kN/m)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$143:$L$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.247957670388743</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>172.47957670388743</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$143:$M$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Sc | solo</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$147:$L$148</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>17.247957670388743</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.247957670388743</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$147:$M$148</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>seta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$149:$L$150</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>146.60764019830432</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$149:$M$150</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.4166666666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4166666666666667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>seta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$151:$L$152</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>120.73570369272119</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$151:$M$152</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.8333333333333334</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8333333333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>seta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$153:$L$154</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>94.86376718713808</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$153:$M$154</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>seta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$155:$L$156</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>68.99183068155496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$155:$M$156</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.6666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6666666666666667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>seta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$157:$L$158</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>43.119894175971865</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$157:$M$158</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.0833333333333335</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0833333333333335</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:v>E</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="2F5597"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$159:$L$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>198.35151320947054</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$159:$M$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.9090909090909092</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9090909090909092</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:v>R,topo</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$161:$L$162</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-60.367851846360594</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$161:$M$162</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:v>R,base</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$163:$L$164</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-60.367851846360594</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$163:$M$164</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$165</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>p,topo = 17,25 kN/m</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$165:$L$165</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>17.247957670388743</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$165:$M$165</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$166</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>p,base = 172,48 kN/m</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$166:$L$166</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>172.47957670388743</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$166:$M$166</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$167</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>E = 237,2 kN (y = 0,91 m)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$167:$L$167</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>198.35151320947054</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$167:$M$167</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.9090909090909092</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$168</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>R,topo = 55,0 kN → laje</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$168:$L$168</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>-60.367851846360594</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$168:$M$168</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$169</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>R,base = 182,2 kN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$169:$L$169</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>-60.367851846360594</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$169:$M$169</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="51"/>
+        <c:axId val="52"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="51"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="900" b="0"/>
+                  <a:t>carga (kN/m)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:ln w="6350">
+            <a:solidFill>
+              <a:srgbClr val="A6A6A6"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="52"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="52"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:solidFill>
+                <a:srgbClr val="E7E6E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="900" b="0"/>
+                  <a:t>altura a partir da base (m)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:ln w="6350">
+            <a:solidFill>
+              <a:srgbClr val="A6A6A6"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="51"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900" b="0">
+          <a:solidFill>
+            <a:srgbClr val="404040"/>
+          </a:solidFill>
+          <a:latin typeface="Aptos Narrow"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1100" b="1">
+                <a:latin typeface="Aptos Narrow"/>
+              </a:rPr>
+              <a:t>LAJE ALVEOLAR – PRESSÃO NOS PAINÉIS (kN/m²)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Placas</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="76200" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$170:$L$171</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$170:$M$171</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Pressão real</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$172:$L$175</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.639320225002103</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>26.39320225002103</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$172:$M$175</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Sc | solo</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$176:$L$177</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.639320225002103</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.639320225002103</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$176:$M$177</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>seta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$178:$L$179</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20.4547317437663</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$178:$M$179</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.625</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>seta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$180:$L$181</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>14.516261237511566</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$180:$M$181</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>seta</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$182:$L$183</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>8.577790731256833</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$182:$M$183</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.875</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.875</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>Pressão adotada por painel</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="2F5597"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$184:$L$203</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>26.393202250021027</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26.393202250021027</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$184:$M$203</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>junta 1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$204:$L$205</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27.71286236252208</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$204:$M$205</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:v>junta 2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$206:$L$207</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$206:$M$207</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:v>junta 3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$208:$L$209</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$208:$M$209</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:v>junta 4</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$210:$L$211</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$210:$M$211</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:v>junta 5</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$212:$L$213</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$212:$M$213</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>6.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:v>junta 6</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$214:$L$215</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$214:$M$215</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:v>junta 7</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$216:$L$217</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$216:$M$217</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:v>junta 8</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$218:$L$219</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$218:$M$219</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:v>junta 9</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$220:$L$221</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$220:$M$221</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>11.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="16"/>
+          <c:order val="16"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$222</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>σ,topo = 2,64 kN/m²</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$222:$L$222</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.639320225002103</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$222:$M$222</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="17"/>
+          <c:order val="17"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$223</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>σ,base = 26,39 kN/m²</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$223:$L$223</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>26.39320225002103</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$223:$M$223</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="18"/>
+          <c:order val="18"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$224</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P1: 26,4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$224:$L$224</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>26.393202250021027</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$224:$M$224</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.625</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="19"/>
+          <c:order val="19"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$225</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P2: 14,5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$225:$L$225</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$225:$M$225</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.875</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="20"/>
+          <c:order val="20"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$226</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$226:$L$226</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$226:$M$226</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="21"/>
+          <c:order val="21"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$227</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$227:$L$227</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$227:$M$227</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="22"/>
+          <c:order val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$228</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$228:$L$228</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$228:$M$228</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="23"/>
+          <c:order val="23"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$229</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$229:$L$229</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$229:$M$229</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="24"/>
+          <c:order val="24"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$230</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$230:$L$230</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$230:$M$230</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="25"/>
+          <c:order val="25"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$231</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$231:$L$231</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$231:$M$231</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="26"/>
+          <c:order val="26"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$232</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$232:$L$232</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$232:$M$232</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="27"/>
+          <c:order val="27"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$233</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$233:$L$233</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$233:$M$233</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:axId val="61"/>
+        <c:axId val="62"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="61"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="900" b="0"/>
+                  <a:t>pressão (kN/m²)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:ln w="6350">
+            <a:solidFill>
+              <a:srgbClr val="A6A6A6"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="62"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="62"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:solidFill>
+                <a:srgbClr val="E7E6E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="900" b="0"/>
+                  <a:t>altura a partir da base (m)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:ln w="6350">
+            <a:solidFill>
+              <a:srgbClr val="A6A6A6"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="404040"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Narrow"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="61"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="000000"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900" b="0">
+          <a:solidFill>
+            <a:srgbClr val="404040"/>
+          </a:solidFill>
+          <a:latin typeface="Aptos Narrow"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3535,6 +6503,71 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagrama 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagrama 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -10121,1246 +13154,3293 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
-    <tabColor rgb="FF2F75B5"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="K1:T255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONTENÇÃO – CARGAS NO PILAR E NA LAJE ALVEOLAR (cálculo rápido)</t>
-        </is>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preencha só as células AMARELAS (texto azul). Empuxo de Rankine, solo sem coesão (a favor da segurança). Valores característicos (sem γf). Convenção: 1 tf = 10 kN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. DADOS DE ENTRADA</t>
-        </is>
-      </c>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sobrecarga no terreno (Sc)</t>
-        </is>
-      </c>
-      <c r="B5" s="224">
+    <row r="1">
+      <c r="K1" s="219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EMPUXO EM CONTENÇÃO – CARGAS NO PILAR E NA LAJE ALVEOLAR</t>
+        </is>
+      </c>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="K2" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Como usar: células CINZA são entradas (preencha/edite). As demais são calculadas. Empuxo de Rankine, solo sem coesão (a favor da segurança); valores característicos (sem γf); 1 tf = 10 kN. A coluna Status fica verde quando está Ok. O RESUMO abaixo traz o que lançar no modelo (Eberick/TQS) e na tabela do fabricante da laje alveolar.</t>
+        </is>
+      </c>
+      <c r="L2" s="220"/>
+      <c r="M2" s="220"/>
+      <c r="N2" s="220"/>
+      <c r="O2" s="220"/>
+      <c r="P2" s="220"/>
+      <c r="Q2" s="220"/>
+      <c r="R2" s="220"/>
+      <c r="S2" s="220"/>
+      <c r="T2" s="220"/>
+    </row>
+    <row r="4">
+      <c r="K4" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESUMO – VALORES PARA LANÇAR</t>
+        </is>
+      </c>
+      <c r="L4" s="221"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="221"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="221"/>
+      <c r="T4" s="221"/>
+    </row>
+    <row r="6">
+      <c r="K6" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="L6" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultado</t>
+        </is>
+      </c>
+      <c r="M6" s="235"/>
+      <c r="N6" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="O6" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O que é</t>
+        </is>
+      </c>
+      <c r="P6" s="235"/>
+      <c r="Q6" s="235"/>
+      <c r="R6" s="235"/>
+      <c r="S6" s="235"/>
+      <c r="T6" s="235"/>
+    </row>
+    <row r="7">
+      <c r="K7" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empuxo</t>
+        </is>
+      </c>
+      <c r="L7" s="236">
+        <f>$L$34&amp;" – K = "&amp;FIXED($L$44,3)</f>
+      </c>
+      <c r="M7" s="236"/>
+      <c r="N7" s="232">
+        <f>"Ok"</f>
+      </c>
+      <c r="O7" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coeficiente adotado – item 2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="K8" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aviso</t>
+        </is>
+      </c>
+      <c r="L8" s="234">
+        <f>IF(AND($L$35&lt;&gt;"Balanço",$L$34="Ativo"),"⚠ Topo do pilar travado pela laje com empuxo ATIVO: se a estrutura for rígida (sem deslocamento), use REPOUSO – K0 = "&amp;FIXED($L$43,2)&amp;" contra Ka = "&amp;FIXED($L$42,2)&amp;" (+"&amp;FIXED(($L$43/$L$42-1)*100,0)&amp;"% de carga).",IF(AND($L$35="Balanço",$L$34="Repouso"),"⚠ Balanço com empuxo em REPOUSO: pilar livre no topo se desloca – ATIVO costuma bastar.","Sem avisos."))</f>
+      </c>
+      <c r="M8" s="234"/>
+      <c r="N8" s="234"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="234"/>
+      <c r="R8" s="234"/>
+      <c r="S8" s="234"/>
+      <c r="T8" s="234"/>
+    </row>
+    <row r="9">
+      <c r="K9" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar p,topo</t>
+        </is>
+      </c>
+      <c r="L9" s="236">
+        <f>FIXED($L$55,2)&amp;" kN/m"</f>
+      </c>
+      <c r="M9" s="236"/>
+      <c r="N9" s="232"/>
+      <c r="O9" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga trapezoidal no pilar: valor no topo – item 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="K10" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar p,base</t>
+        </is>
+      </c>
+      <c r="L10" s="236">
+        <f>FIXED($L$56,2)&amp;" kN/m"</f>
+      </c>
+      <c r="M10" s="236"/>
+      <c r="N10" s="232"/>
+      <c r="O10" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga trapezoidal no pilar: valor na base – item 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="K11" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultante</t>
+        </is>
+      </c>
+      <c r="L11" s="236">
+        <f>FIXED($L$59,2)&amp;" kN ("&amp;FIXED($L$60,2)&amp;" tf)"</f>
+      </c>
+      <c r="M11" s="236"/>
+      <c r="N11" s="232"/>
+      <c r="O11" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solo + Sc, aplicada a y,E da base – item 3.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="K12" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelo pilar</t>
+        </is>
+      </c>
+      <c r="L12" s="236">
+        <f>$L$35</f>
+      </c>
+      <c r="M12" s="236"/>
+      <c r="N12" s="232">
+        <f>IF(ISNA(MATCH($L$35,$K$70:$K$72,0)),"Rever: modelo inválido","Ok")</f>
+      </c>
+      <c r="O12" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelo estrutural do pilar – item 4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="K13" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,topo</t>
+        </is>
+      </c>
+      <c r="L13" s="236">
+        <f>FIXED($L$74,2)&amp;" kN"</f>
+      </c>
+      <c r="M13" s="236"/>
+      <c r="N13" s="232"/>
+      <c r="O13" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Força que o pilar entrega à laje/viga do topo – item 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="K14" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M,base</t>
+        </is>
+      </c>
+      <c r="L14" s="236">
+        <f>FIXED($L$76,2)&amp;" kN·m"</f>
+      </c>
+      <c r="M14" s="236"/>
+      <c r="N14" s="232"/>
+      <c r="O14" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento na base do pilar – item 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="K15" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M,vão</t>
+        </is>
+      </c>
+      <c r="L15" s="236">
+        <f>IF($L$35="Balanço","-",FIXED($L$77,2)&amp;" kN·m a "&amp;FIXED($L$78,2)&amp;" m")</f>
+      </c>
+      <c r="M15" s="236"/>
+      <c r="N15" s="232"/>
+      <c r="O15" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maior momento positivo e altura a partir da base – item 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="K16" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M(x)</t>
+        </is>
+      </c>
+      <c r="L16" s="236">
+        <f>FIXED($L$79,2)&amp;" kN·m"</f>
+      </c>
+      <c r="M16" s="236"/>
+      <c r="N16" s="232">
+        <f>IF($L$36&gt;$L$29,"Rever: x maior que H",IF($L$36&lt;0,"Rever: x negativo","Ok"))</f>
+      </c>
+      <c r="O16" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento na cota x – item 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="K17" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laje p,total</t>
+        </is>
+      </c>
+      <c r="L17" s="236">
+        <f>FIXED($L$88,2)&amp;" kN/m²"</f>
+      </c>
+      <c r="M17" s="236"/>
+      <c r="N17" s="232">
+        <f>IF($L$85&gt;10,"Rever: mais de 10 painéis","Ok")</f>
+      </c>
+      <c r="O17" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Painel inferior: comparar com a tabela do fabricante – item 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="K18" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laje g / q</t>
+        </is>
+      </c>
+      <c r="L18" s="236">
+        <f>FIXED($L$89,2)&amp;" / "&amp;FIXED($L$90,2)&amp;" kN/m"</f>
+      </c>
+      <c r="M18" s="236"/>
+      <c r="N18" s="232"/>
+      <c r="O18" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cargas lineares no painel inferior – item 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="K19" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laje Mk / Vk</t>
+        </is>
+      </c>
+      <c r="L19" s="236">
+        <f>FIXED($L$91,2)&amp;" kN·m / "&amp;FIXED($L$92,2)&amp;" kN"</f>
+      </c>
+      <c r="M19" s="236"/>
+      <c r="N19" s="232"/>
+      <c r="O19" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esforços no painel inferior, vão L – item 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="K22" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 . DADOS DE ENTRADA</t>
+        </is>
+      </c>
+      <c r="L22" s="221"/>
+      <c r="M22" s="221"/>
+      <c r="N22" s="221"/>
+      <c r="O22" s="221"/>
+      <c r="P22" s="221"/>
+      <c r="Q22" s="221"/>
+      <c r="R22" s="221"/>
+      <c r="S22" s="221"/>
+      <c r="T22" s="221"/>
+    </row>
+    <row r="24">
+      <c r="K24" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1 Solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="K25" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">γ</t>
+        </is>
+      </c>
+      <c r="L25" s="224">
+        <v>18</v>
+      </c>
+      <c r="M25" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m³</t>
+        </is>
+      </c>
+      <c r="O25" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peso específico do solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="K26" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">φ</t>
+        </is>
+      </c>
+      <c r="L26" s="224">
+        <v>18</v>
+      </c>
+      <c r="M26" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">°</t>
+        </is>
+      </c>
+      <c r="O26" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ângulo de atrito do solo (ver aba DADOS DO SOLO, col. G).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="K27" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sc</t>
+        </is>
+      </c>
+      <c r="L27" s="224">
         <v>5</v>
       </c>
-      <c r="C5" s="223" t="inlineStr">
+      <c r="M27" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN/m²</t>
         </is>
       </c>
-      <c r="D5" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Veículos leves ≈ 5 a 10 kN/m²; só pedestres ≈ 2,5 a 5 kN/m².</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peso específico do solo (γ)</t>
-        </is>
-      </c>
-      <c r="B6" s="224">
-        <v>18</v>
-      </c>
-      <c r="C6" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ângulo de atrito do solo (φ)</t>
-        </is>
-      </c>
-      <c r="B7" s="224">
-        <v>18</v>
-      </c>
-      <c r="C7" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">°</t>
-        </is>
-      </c>
-      <c r="D7" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ver aba DADOS DO SOLO (col. G) conforme tipo de solo e SPT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Altura da contenção (H)</t>
-        </is>
-      </c>
-      <c r="B8" s="224">
+      <c r="O27" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sobrecarga no terreno (veículos leves ≈ 5 a 10; só pedestres ≈ 2,5 a 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="K28" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2 Geometria</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="K29" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="L29" s="224">
         <v>2.5</v>
       </c>
-      <c r="C8" s="223" t="inlineStr">
+      <c r="M29" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">m</t>
         </is>
       </c>
-      <c r="D8" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Do nível de apoio (base) até o topo do terreno contido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Largura de influência no pilar (D)</t>
-        </is>
-      </c>
-      <c r="B9" s="225">
+      <c r="O29" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura da contenção: da base até o topo do terreno contido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="K30" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="L30" s="226">
         <f>13.07/2</f>
       </c>
-      <c r="C9" s="223" t="inlineStr">
+      <c r="M30" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">m</t>
         </is>
       </c>
-      <c r="D9" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pilar intermediário: (vão esq. + vão dir.)/2.  Pilar de extremidade: vão/2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tipo de empuxo</t>
-        </is>
-      </c>
-      <c r="B10" s="226" t="inlineStr">
+      <c r="O30" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Largura de influência no pilar: intermediário = (vão esq. + vão dir.)/2; extremidade = vão/2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="K31" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bw</t>
+        </is>
+      </c>
+      <c r="L31" s="224">
+        <v>1.25</v>
+      </c>
+      <c r="M31" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="O31" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Largura da placa de laje alveolar = altura de cada painel deitado na contenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="K32" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
+      <c r="L32" s="226">
+        <f>L30</f>
+      </c>
+      <c r="M32" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="O32" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vão que a placa vence entre pilares (padrão = D; altere se for diferente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="K33" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="K34" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empuxo</t>
+        </is>
+      </c>
+      <c r="L34" s="224" t="inlineStr">
         <is>
           <t xml:space="preserve">Ativo</t>
         </is>
       </c>
-      <c r="C10" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D10" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ativo (Ka): parede pode se deslocar.  Repouso (K0): topo travado por laje/viga, estrutura rígida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Largura da placa de laje alveolar (bw)</t>
-        </is>
-      </c>
-      <c r="B11" s="224">
-        <v>1.25</v>
-      </c>
-      <c r="C11" s="223" t="inlineStr">
+      <c r="M34" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O34" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ativo (Ka): parede pode se deslocar. Repouso (K0): topo travado, estrutura rígida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="K35" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar</t>
+        </is>
+      </c>
+      <c r="L35" s="224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engaste-apoio</t>
+        </is>
+      </c>
+      <c r="M35" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O35" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelo do pilar: escolha na tabela do item 4.1 (define o resumo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="K36" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="L36" s="224">
+        <v>0</v>
+      </c>
+      <c r="M36" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">m</t>
         </is>
       </c>
-      <c r="D11" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Altura de cada painel na contenção (placas deitadas, uma sobre a outra).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vão da laje alveolar (L)</t>
-        </is>
-      </c>
-      <c r="B12" s="225">
-        <f>B9</f>
-      </c>
-      <c r="C12" s="223" t="inlineStr">
+      <c r="O36" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cota de verificação do momento, medida a partir da base (x = 0 → base).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="K38" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 . COEFICIENTE DE EMPUXO E PRESSÕES</t>
+        </is>
+      </c>
+      <c r="L38" s="221"/>
+      <c r="M38" s="221"/>
+      <c r="N38" s="221"/>
+      <c r="O38" s="221"/>
+      <c r="P38" s="221"/>
+      <c r="Q38" s="221"/>
+      <c r="R38" s="221"/>
+      <c r="S38" s="221"/>
+      <c r="T38" s="221"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="K40" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rankine, parede vertical e terreno horizontal. A sobrecarga Sc vira uma pressão constante K·Sc em toda a altura; o solo dá uma pressão triangular K·γ·z (zero no topo, máxima na base).</t>
+        </is>
+      </c>
+      <c r="L40" s="220"/>
+      <c r="M40" s="220"/>
+      <c r="N40" s="220"/>
+      <c r="O40" s="220"/>
+      <c r="P40" s="220"/>
+      <c r="Q40" s="220"/>
+      <c r="R40" s="220"/>
+      <c r="S40" s="220"/>
+      <c r="T40" s="220"/>
+    </row>
+    <row r="41">
+      <c r="K41" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1 Coeficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="K42" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ka</t>
+        </is>
+      </c>
+      <c r="L42" s="228">
+        <f>TAN(RADIANS(45-$L$26/2))^2</f>
+      </c>
+      <c r="M42" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O42" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empuxo ativo: tan²(45° − φ/2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="K43" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K0</t>
+        </is>
+      </c>
+      <c r="L43" s="228">
+        <f>1-SIN(RADIANS($L$26))</f>
+      </c>
+      <c r="M43" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O43" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empuxo em repouso: 1 − sen φ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="K44" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="L44" s="228">
+        <f>IF($L$34="Repouso",$L$43,$L$42)</f>
+      </c>
+      <c r="M44" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O44" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coeficiente adotado (item 1.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="K45" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Pressões</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="K46" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h,eq</t>
+        </is>
+      </c>
+      <c r="L46" s="228">
+        <f>IF($L$25=0,0,$L$27/$L$25)</f>
+      </c>
+      <c r="M46" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">m</t>
         </is>
       </c>
-      <c r="D12" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vão horizontal que a placa vence entre pilares (padrão = D; altere se for diferente).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cota de verificação (x, medida da base)</t>
-        </is>
-      </c>
-      <c r="B13" s="224">
-        <v>0</v>
-      </c>
-      <c r="C13" s="223" t="inlineStr">
+      <c r="O46" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura de solo equivalente à sobrecarga (Sc/γ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="K47" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σ,topo</t>
+        </is>
+      </c>
+      <c r="L47" s="227">
+        <f>$L$44*$L$27</f>
+      </c>
+      <c r="M47" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m²</t>
+        </is>
+      </c>
+      <c r="O47" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão no topo: K·Sc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="K48" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σ,base</t>
+        </is>
+      </c>
+      <c r="L48" s="227">
+        <f>$L$44*($L$27+$L$25*$L$29)</f>
+      </c>
+      <c r="M48" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m²</t>
+        </is>
+      </c>
+      <c r="O48" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão na base: K·(Sc + γ·H).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="K49" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σ,solo</t>
+        </is>
+      </c>
+      <c r="L49" s="227">
+        <f>$L$44*$L$25*$L$29</f>
+      </c>
+      <c r="M49" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m²</t>
+        </is>
+      </c>
+      <c r="O49" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão na base só do solo: K·γ·H (sem Sc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="K51" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 . PILAR – CARGA PARA LANÇAR NO MODELO</t>
+        </is>
+      </c>
+      <c r="L51" s="221"/>
+      <c r="M51" s="221"/>
+      <c r="N51" s="221"/>
+      <c r="O51" s="221"/>
+      <c r="P51" s="221"/>
+      <c r="Q51" s="221"/>
+      <c r="R51" s="221"/>
+      <c r="S51" s="221"/>
+      <c r="T51" s="221"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="K53" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lançar no pilar como carga horizontal TRAPEZOIDAL: p,topo no topo e p,base na base (pressão × largura de influência D). Se preferir carga concentrada, use a resultante E no ponto de aplicação y,E.</t>
+        </is>
+      </c>
+      <c r="L53" s="220"/>
+      <c r="M53" s="220"/>
+      <c r="N53" s="220"/>
+      <c r="O53" s="220"/>
+      <c r="P53" s="220"/>
+      <c r="Q53" s="220"/>
+      <c r="R53" s="220"/>
+      <c r="S53" s="220"/>
+      <c r="T53" s="220"/>
+    </row>
+    <row r="54">
+      <c r="K54" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1 Carga distribuída</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="K55" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p,topo</t>
+        </is>
+      </c>
+      <c r="L55" s="227">
+        <f>$L$47*$L$30</f>
+      </c>
+      <c r="M55" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m</t>
+        </is>
+      </c>
+      <c r="O55" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga no topo do pilar: σ,topo·D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="K56" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p,base</t>
+        </is>
+      </c>
+      <c r="L56" s="227">
+        <f>$L$48*$L$30</f>
+      </c>
+      <c r="M56" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m</t>
+        </is>
+      </c>
+      <c r="O56" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga na base do pilar: σ,base·D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="K57" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Δp</t>
+        </is>
+      </c>
+      <c r="L57" s="227">
+        <f>$L$56-$L$55</f>
+      </c>
+      <c r="M57" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m</t>
+        </is>
+      </c>
+      <c r="O57" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcela triangular (p,base − p,topo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="K58" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2 Resultante</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="K59" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="L59" s="227">
+        <f>($L$55+$L$56)*$L$29/2</f>
+      </c>
+      <c r="M59" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O59" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultante total (solo + Sc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="K60" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="L60" s="227">
+        <f>$L$59/10</f>
+      </c>
+      <c r="M60" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="O60" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultante total em tf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="K61" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y,E</t>
+        </is>
+      </c>
+      <c r="L61" s="228">
+        <f>IF($L$59=0,0,($L$55*$L$29^2/2+$L$57*$L$29^2/6)/$L$59)</f>
+      </c>
+      <c r="M61" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">m</t>
         </is>
       </c>
-      <c r="D13" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Usada só na coluna 'M na cota x' da seção 4. x = 0 → base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. COEFICIENTE DE EMPUXO E PRESSÕES</t>
-        </is>
-      </c>
-      <c r="B15" s="220"/>
-      <c r="C15" s="220"/>
-      <c r="D15" s="220"/>
-      <c r="E15" s="220"/>
-      <c r="F15" s="220"/>
-      <c r="G15" s="220"/>
-      <c r="H15" s="220"/>
-      <c r="I15" s="220"/>
-      <c r="J15" s="220"/>
-      <c r="K15" s="220"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ka = tan²(45° − φ/2)  (ativo)</t>
-        </is>
-      </c>
-      <c r="B16" s="228">
-        <f>TAN(RADIANS(45-B7/2))^2</f>
-      </c>
-      <c r="C16" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K0 = 1 − sen φ  (repouso)</t>
-        </is>
-      </c>
-      <c r="B17" s="228">
-        <f>1-SIN(RADIANS(B7))</f>
-      </c>
-      <c r="C17" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K adotado</t>
-        </is>
-      </c>
-      <c r="B18" s="229">
-        <f>IF(B10="Repouso",B17,B16)</f>
-      </c>
-      <c r="C18" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Altura equivalente da sobrecarga (heq = Sc/γ)</t>
-        </is>
-      </c>
-      <c r="B19" s="228">
-        <f>IF(B6=0,0,B5/B6)</f>
-      </c>
-      <c r="C19" s="223" t="inlineStr">
+      <c r="O61" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ponto de aplicação de E, medido a partir da base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="K62" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E,solo</t>
+        </is>
+      </c>
+      <c r="L62" s="227">
+        <f>$L$44*$L$25*$L$29^2/2*$L$30</f>
+      </c>
+      <c r="M62" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O62" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultante só do solo, a H/3 da base (= M23 da aba MURO DE ARRIMO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="K63" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E,solo</t>
+        </is>
+      </c>
+      <c r="L63" s="227">
+        <f>$L$62/10</f>
+      </c>
+      <c r="M63" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="O63" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idem em tf (= M24 da aba MURO DE ARRIMO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="K65" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 . PILAR – ESFORÇOS (característicos)</t>
+        </is>
+      </c>
+      <c r="L65" s="221"/>
+      <c r="M65" s="221"/>
+      <c r="N65" s="221"/>
+      <c r="O65" s="221"/>
+      <c r="P65" s="221"/>
+      <c r="Q65" s="221"/>
+      <c r="R65" s="221"/>
+      <c r="S65" s="221"/>
+      <c r="T65" s="221"/>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="K67" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sinal: M negativo = tração na face do pilar em contato com o solo; M positivo = tração na face externa. R,topo é a força horizontal que o pilar entrega à laje/viga do topo. Com laje ou viga travando o topo use Engaste-apoio; Balanço só se nada travar o topo.</t>
+        </is>
+      </c>
+      <c r="L67" s="220"/>
+      <c r="M67" s="220"/>
+      <c r="N67" s="220"/>
+      <c r="O67" s="220"/>
+      <c r="P67" s="220"/>
+      <c r="Q67" s="220"/>
+      <c r="R67" s="220"/>
+      <c r="S67" s="220"/>
+      <c r="T67" s="220"/>
+    </row>
+    <row r="68">
+      <c r="K68" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 Comparação dos modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="K69" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelo</t>
+        </is>
+      </c>
+      <c r="L69" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,topo (kN)</t>
+        </is>
+      </c>
+      <c r="M69" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,base (kN)</t>
+        </is>
+      </c>
+      <c r="N69" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M,base (kN·m)</t>
+        </is>
+      </c>
+      <c r="O69" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M,vão (kN·m)</t>
+        </is>
+      </c>
+      <c r="P69" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y,M (m)</t>
+        </is>
+      </c>
+      <c r="Q69" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M(x) (kN·m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="K70" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balanço</t>
+        </is>
+      </c>
+      <c r="L70" s="227">
+        <f>0</f>
+      </c>
+      <c r="M70" s="227">
+        <f>$L$59-L70</f>
+      </c>
+      <c r="N70" s="227">
+        <f>-($L$55*$L$29^2/2+$L$57*$L$29^2/6)</f>
+      </c>
+      <c r="O70" s="227">
+        <v>0</v>
+      </c>
+      <c r="P70" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="Q70" s="227">
+        <f>L70*($L$29-$L$36)-$L$55*($L$29-$L$36)^2/2-$L$57*($L$29-$L$36)^3/(6*$L$29)</f>
+      </c>
+    </row>
+    <row r="71">
+      <c r="K71" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engaste-apoio</t>
+        </is>
+      </c>
+      <c r="L71" s="227">
+        <f>3*$L$55*$L$29/8+$L$57*$L$29/10</f>
+      </c>
+      <c r="M71" s="227">
+        <f>$L$59-L71</f>
+      </c>
+      <c r="N71" s="227">
+        <f>-($L$55*$L$29^2/8+$L$57*$L$29^2/15)</f>
+      </c>
+      <c r="O71" s="227">
+        <f>L71*($L$29-P71)-$L$55*($L$29-P71)^2/2-$L$57*($L$29-P71)^3/(6*$L$29)</f>
+      </c>
+      <c r="P71" s="227">
+        <f>$L$29-IFERROR(IF($L$57=0,L71/$L$55,(-$L$55+SQRT($L$55^2+2*$L$57*L71/$L$29))/($L$57/$L$29)),0)</f>
+      </c>
+      <c r="Q71" s="227">
+        <f>L71*($L$29-$L$36)-$L$55*($L$29-$L$36)^2/2-$L$57*($L$29-$L$36)^3/(6*$L$29)</f>
+      </c>
+    </row>
+    <row r="72">
+      <c r="K72" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biapoiado</t>
+        </is>
+      </c>
+      <c r="L72" s="227">
+        <f>$L$55*$L$29/2+$L$57*$L$29/6</f>
+      </c>
+      <c r="M72" s="227">
+        <f>$L$59-L72</f>
+      </c>
+      <c r="N72" s="227">
+        <f>0</f>
+      </c>
+      <c r="O72" s="227">
+        <f>L72*($L$29-P72)-$L$55*($L$29-P72)^2/2-$L$57*($L$29-P72)^3/(6*$L$29)</f>
+      </c>
+      <c r="P72" s="227">
+        <f>$L$29-IFERROR(IF($L$57=0,L72/$L$55,(-$L$55+SQRT($L$55^2+2*$L$57*L72/$L$29))/($L$57/$L$29)),0)</f>
+      </c>
+      <c r="Q72" s="227">
+        <f>L72*($L$29-$L$36)-$L$55*($L$29-$L$36)^2/2-$L$57*($L$29-$L$36)^3/(6*$L$29)</f>
+      </c>
+    </row>
+    <row r="73">
+      <c r="K73" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 Modelo adotado (item 1.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="K74" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,topo</t>
+        </is>
+      </c>
+      <c r="L74" s="227">
+        <f>IFERROR(INDEX($L$70:$L$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
+      </c>
+      <c r="M74" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O74" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Força horizontal que vai para a laje/viga do topo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="K75" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,base</t>
+        </is>
+      </c>
+      <c r="L75" s="227">
+        <f>IFERROR(INDEX($M$70:$M$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
+      </c>
+      <c r="M75" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O75" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Força horizontal que vai para a fundação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="K76" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M,base</t>
+        </is>
+      </c>
+      <c r="L76" s="227">
+        <f>IFERROR(INDEX($N$70:$N$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
+      </c>
+      <c r="M76" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O76" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento na base do pilar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="K77" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M,vão</t>
+        </is>
+      </c>
+      <c r="L77" s="227">
+        <f>IFERROR(INDEX($O$70:$O$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
+      </c>
+      <c r="M77" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O77" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maior momento positivo ao longo do pilar (0 no balanço).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="K78" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y,M</t>
+        </is>
+      </c>
+      <c r="L78" s="227">
+        <f>IF($L$35="Balanço","-",IFERROR(INDEX($P$70:$P$72,MATCH($L$35,$K$70:$K$72,0)),0))</f>
+      </c>
+      <c r="M78" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">m</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pressão no topo  σ,topo = K·Sc</t>
-        </is>
-      </c>
-      <c r="B20" s="227">
-        <f>B18*B5</f>
-      </c>
-      <c r="C20" s="223" t="inlineStr">
+      <c r="O78" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura do M,vão a partir da base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="K79" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M(x)</t>
+        </is>
+      </c>
+      <c r="L79" s="227">
+        <f>IFERROR(INDEX($Q$70:$Q$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
+      </c>
+      <c r="M79" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="N79" s="232">
+        <f>IF($L$36&gt;$L$29,"Rever: x maior que H",IF($L$36&lt;0,"Rever: x negativo","Ok"))</f>
+      </c>
+      <c r="O79" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento na cota x (item 1.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="K81" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 . LAJE ALVEOLAR – CARGA EM CADA PAINEL</t>
+        </is>
+      </c>
+      <c r="L81" s="221"/>
+      <c r="M81" s="221"/>
+      <c r="N81" s="221"/>
+      <c r="O81" s="221"/>
+      <c r="P81" s="221"/>
+      <c r="Q81" s="221"/>
+      <c r="R81" s="221"/>
+      <c r="S81" s="221"/>
+      <c r="T81" s="221"/>
+    </row>
+    <row r="83" ht="45" customHeight="1">
+      <c r="K83" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placas deitadas, uma sobre a outra, vencendo o vão L entre pilares. Painel 1 = inferior (mais carregado). Cada painel usa a pressão da sua borda inferior (a favor da segurança). g = solo (permanente); q = sobrecarga (variável). p,total é o valor a comparar com a sobrecarga da tabela do fabricante.</t>
+        </is>
+      </c>
+      <c r="L83" s="220"/>
+      <c r="M83" s="220"/>
+      <c r="N83" s="220"/>
+      <c r="O83" s="220"/>
+      <c r="P83" s="220"/>
+      <c r="Q83" s="220"/>
+      <c r="R83" s="220"/>
+      <c r="S83" s="220"/>
+      <c r="T83" s="220"/>
+    </row>
+    <row r="84">
+      <c r="K84" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.1 Painel inferior (o mais carregado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="K85" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n</t>
+        </is>
+      </c>
+      <c r="L85" s="229">
+        <f>IF($L$31=0,0,ROUNDUP($L$29/$L$31,0))</f>
+      </c>
+      <c r="M85" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">un</t>
+        </is>
+      </c>
+      <c r="N85" s="232">
+        <f>IF($L$85&gt;10,"Rever: mais de 10 painéis",IF($L$85&lt;1,"Rever: H ou bw","Ok"))</f>
+      </c>
+      <c r="O85" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Número de painéis na altura H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="K86" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σg</t>
+        </is>
+      </c>
+      <c r="L86" s="227">
+        <f>$L$44*$L$25*$L$29</f>
+      </c>
+      <c r="M86" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN/m²</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pressão na base  σ,base = K·(Sc + γ·H)</t>
-        </is>
-      </c>
-      <c r="B21" s="227">
-        <f>B18*(B5+B6*B8)</f>
-      </c>
-      <c r="C21" s="223" t="inlineStr">
+      <c r="O86" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão do solo na borda inferior do painel 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="K87" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σq</t>
+        </is>
+      </c>
+      <c r="L87" s="227">
+        <f>$L$44*$L$27</f>
+      </c>
+      <c r="M87" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN/m²</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pressão na base só do solo  K·γ·H</t>
-        </is>
-      </c>
-      <c r="B22" s="227">
-        <f>B18*B6*B8</f>
-      </c>
-      <c r="C22" s="223" t="inlineStr">
+      <c r="O87" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão da sobrecarga (constante na altura).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="K88" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p,total</t>
+        </is>
+      </c>
+      <c r="L88" s="227">
+        <f>$L$86+$L$87</f>
+      </c>
+      <c r="M88" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN/m²</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. PILAR – CARGA PARA LANÇAR NO MODELO (Eberick/TQS)</t>
-        </is>
-      </c>
-      <c r="B24" s="220"/>
-      <c r="C24" s="220"/>
-      <c r="D24" s="220"/>
-      <c r="E24" s="220"/>
-      <c r="F24" s="220"/>
-      <c r="G24" s="220"/>
-      <c r="H24" s="220"/>
-      <c r="I24" s="220"/>
-      <c r="J24" s="220"/>
-      <c r="K24" s="220"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga distribuída no topo  p,topo = σ,topo·D</t>
-        </is>
-      </c>
-      <c r="B25" s="229">
-        <f>B20*B9</f>
-      </c>
-      <c r="C25" s="223" t="inlineStr">
+      <c r="O88" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão total no painel 1 → comparar com a tabela do fabricante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="K89" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g</t>
+        </is>
+      </c>
+      <c r="L89" s="227">
+        <f>$L$86*MIN($L$31,$L$29)</f>
+      </c>
+      <c r="M89" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN/m</t>
         </is>
       </c>
-      <c r="D25" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lançar no pilar como carga horizontal TRAPEZOIDAL: p,topo no topo → p,base na base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga distribuída na base  p,base = σ,base·D</t>
-        </is>
-      </c>
-      <c r="B26" s="229">
-        <f>B21*B9</f>
-      </c>
-      <c r="C26" s="223" t="inlineStr">
+      <c r="O89" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga permanente linear no painel 1 (σg × largura).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="K90" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q</t>
+        </is>
+      </c>
+      <c r="L90" s="227">
+        <f>$L$87*MIN($L$31,$L$29)</f>
+      </c>
+      <c r="M90" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN/m</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parcela triangular  Δp = p,base − p,topo</t>
-        </is>
-      </c>
-      <c r="B27" s="227">
-        <f>B26-B25</f>
-      </c>
-      <c r="C27" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resultante total (solo + Sc)  E = (p,topo + p,base)·H/2</t>
-        </is>
-      </c>
-      <c r="B28" s="229">
-        <f>(B25+B26)*B8/2</f>
-      </c>
-      <c r="C28" s="223" t="inlineStr">
+      <c r="O90" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga variável linear no painel 1 (σq × largura).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="K91" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mk</t>
+        </is>
+      </c>
+      <c r="L91" s="227">
+        <f>($L$89+$L$90)*$L$32^2/8</f>
+      </c>
+      <c r="M91" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O91" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento no painel 1, biapoiado nos pilares: (g+q)·L²/8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="K92" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vk</t>
+        </is>
+      </c>
+      <c r="L92" s="227">
+        <f>($L$89+$L$90)*$L$32/2</f>
+      </c>
+      <c r="M92" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN</t>
         </is>
       </c>
-      <c r="D28" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se preferir carga concentrada, lançar E no ponto de aplicação abaixo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resultante total em tf</t>
-        </is>
-      </c>
-      <c r="B29" s="227">
-        <f>B28/10</f>
-      </c>
-      <c r="C29" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tf</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ponto de aplicação de E (altura a partir da base)</t>
-        </is>
-      </c>
-      <c r="B30" s="228">
-        <f>IF(B28=0,0,(B25*B8^2/2+B27*B8^2/6)/B28)</f>
-      </c>
-      <c r="C30" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">m</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resultante só do solo (sem Sc)  K·γ·H²/2·D</t>
-        </is>
-      </c>
-      <c r="B31" s="227">
-        <f>B18*B6*B8^2/2*B9</f>
-      </c>
-      <c r="C31" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN</t>
-        </is>
-      </c>
-      <c r="D31" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Equivale ao 'Ea(total)' / 'Carga no pilar' da aba original (M23/M24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resultante só do solo em tf  (aplicada a H/3)</t>
-        </is>
-      </c>
-      <c r="B32" s="227">
-        <f>B31/10</f>
-      </c>
-      <c r="C32" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tf</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. PILAR – ESFORÇOS POR MODELO ESTRUTURAL (característicos)</t>
-        </is>
-      </c>
-      <c r="B34" s="220"/>
-      <c r="C34" s="220"/>
-      <c r="D34" s="220"/>
-      <c r="E34" s="220"/>
-      <c r="F34" s="220"/>
-      <c r="G34" s="220"/>
-      <c r="H34" s="220"/>
-      <c r="I34" s="220"/>
-      <c r="J34" s="220"/>
-      <c r="K34" s="220"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modelo do pilar</t>
-        </is>
-      </c>
-      <c r="B35" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R topo → laje/viga (kN)</t>
-        </is>
-      </c>
-      <c r="C35" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R base → fundação (kN)</t>
-        </is>
-      </c>
-      <c r="D35" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M na base (kN·m)</t>
-        </is>
-      </c>
-      <c r="E35" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M máx. no vão (kN·m)</t>
-        </is>
-      </c>
-      <c r="F35" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Posição M máx. (m da base)</t>
-        </is>
-      </c>
-      <c r="G35" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M na cota x (kN·m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engastado na base / livre no topo (balanço)</t>
-        </is>
-      </c>
-      <c r="B36" s="227">
-        <f>0</f>
-      </c>
-      <c r="C36" s="227">
-        <f>$B$28-B36</f>
-      </c>
-      <c r="D36" s="229">
-        <f>-($B$25*$B$8^2/2+$B$27*$B$8^2/6)</f>
-      </c>
-      <c r="E36" s="234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F36" s="234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G36" s="227">
-        <f>B36*($B$8-$B$13)-$B$25*($B$8-$B$13)^2/2-$B$27*($B$8-$B$13)^3/(6*$B$8)</f>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engastado na base / apoiado no topo (laje) – RECOMENDADO</t>
-        </is>
-      </c>
-      <c r="B37" s="227">
-        <f>3*$B$25*$B$8/8+$B$27*$B$8/10</f>
-      </c>
-      <c r="C37" s="227">
-        <f>$B$28-B37</f>
-      </c>
-      <c r="D37" s="229">
-        <f>-($B$25*$B$8^2/8+$B$27*$B$8^2/15)</f>
-      </c>
-      <c r="E37" s="229">
-        <f>B37*($B$8-F37)-$B$25*($B$8-F37)^2/2-$B$27*($B$8-F37)^3/(6*$B$8)</f>
-      </c>
-      <c r="F37" s="227">
-        <f>$B$8-IFERROR(IF($B$27=0,B37/$B$25,(-$B$25+SQRT($B$25^2+2*$B$27*B37/$B$8))/($B$27/$B$8)),0)</f>
-      </c>
-      <c r="G37" s="227">
-        <f>B37*($B$8-$B$13)-$B$25*($B$8-$B$13)^2/2-$B$27*($B$8-$B$13)^3/(6*$B$8)</f>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biapoiado (rotulado na base e no topo)</t>
-        </is>
-      </c>
-      <c r="B38" s="227">
-        <f>$B$25*$B$8/2+$B$27*$B$8/6</f>
-      </c>
-      <c r="C38" s="227">
-        <f>$B$28-B38</f>
-      </c>
-      <c r="D38" s="229">
-        <v>0</v>
-      </c>
-      <c r="E38" s="229">
-        <f>B38*($B$8-F38)-$B$25*($B$8-F38)^2/2-$B$27*($B$8-F38)^3/(6*$B$8)</f>
-      </c>
-      <c r="F38" s="227">
-        <f>$B$8-IFERROR(IF($B$27=0,B38/$B$25,(-$B$25+SQRT($B$25^2+2*$B$27*B38/$B$8))/($B$27/$B$8)),0)</f>
-      </c>
-      <c r="G38" s="227">
-        <f>B38*($B$8-$B$13)-$B$25*($B$8-$B$13)^2/2-$B$27*($B$8-$B$13)^3/(6*$B$8)</f>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sinal: M negativo = tração na face do pilar em contato com o solo; M positivo = tração na face externa. R topo é a força horizontal que o pilar transmite à laje/viga do topo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Com laje ou viga travando o topo, use 'engastado/apoiado'. O balanço só vale se nada travar o topo do pilar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5. LAJE ALVEOLAR – CARGA EM CADA PAINEL (placas deitadas vencendo o vão L entre pilares)</t>
-        </is>
-      </c>
-      <c r="B42" s="220"/>
-      <c r="C42" s="220"/>
-      <c r="D42" s="220"/>
-      <c r="E42" s="220"/>
-      <c r="F42" s="220"/>
-      <c r="G42" s="220"/>
-      <c r="H42" s="220"/>
-      <c r="I42" s="220"/>
-      <c r="J42" s="220"/>
-      <c r="K42" s="220"/>
-    </row>
-    <row r="43" ht="38" customHeight="1">
-      <c r="A43" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Painel 1 = inferior (mais carregado). Carga de cada painel com a pressão da borda inferior do painel (a favor da segurança). g = parcela do solo (permanente); q = parcela da sobrecarga (variável). 'p total' é o valor a comparar com a tabela do fabricante (kN/m²).</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="231" t="inlineStr">
+      <c r="O92" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cortante / reação de cada lado no pilar: (g+q)·L/2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="K93" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Todos os painéis</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="K94" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Painel</t>
         </is>
       </c>
-      <c r="B44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">z topo (m, prof.)</t>
-        </is>
-      </c>
-      <c r="C44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">z base (m, prof.)</t>
-        </is>
-      </c>
-      <c r="D44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Altura carregada (m)</t>
-        </is>
-      </c>
-      <c r="E44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">σg solo (kN/m²)</t>
-        </is>
-      </c>
-      <c r="F44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">σq sobrecarga (kN/m²)</t>
-        </is>
-      </c>
-      <c r="G44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p total (kN/m²)</t>
-        </is>
-      </c>
-      <c r="H44" s="231" t="inlineStr">
+      <c r="L94" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z,topo (m)</t>
+        </is>
+      </c>
+      <c r="M94" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z,base (m)</t>
+        </is>
+      </c>
+      <c r="N94" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σg (kN/m²)</t>
+        </is>
+      </c>
+      <c r="O94" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σq (kN/m²)</t>
+        </is>
+      </c>
+      <c r="P94" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p,total (kN/m²)</t>
+        </is>
+      </c>
+      <c r="Q94" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">g (kN/m)</t>
         </is>
       </c>
-      <c r="I44" s="231" t="inlineStr">
+      <c r="R94" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">q (kN/m)</t>
         </is>
       </c>
-      <c r="J44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mk = (g+q)·L²/8 (kN·m)</t>
-        </is>
-      </c>
-      <c r="K44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vk = (g+q)·L/2 (kN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="233">
+      <c r="S94" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mk (kN·m)</t>
+        </is>
+      </c>
+      <c r="T94" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vk (kN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="K95" s="237">
         <v>1</v>
       </c>
-      <c r="B45" s="227">
-        <f>IF((A45-1)*$B$11&gt;=$B$8,"",MAX($B$8-A45*$B$11,0))</f>
-      </c>
-      <c r="C45" s="227">
-        <f>IF(B45="","",$B$8-(A45-1)*$B$11)</f>
-      </c>
-      <c r="D45" s="227">
-        <f>IF(B45="","",C45-B45)</f>
-      </c>
-      <c r="E45" s="227">
-        <f>IF(B45="","",$B$18*$B$6*C45)</f>
-      </c>
-      <c r="F45" s="227">
-        <f>IF(B45="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G45" s="229">
-        <f>IF(B45="","",E45+F45)</f>
-      </c>
-      <c r="H45" s="229">
-        <f>IF(B45="","",E45*D45)</f>
-      </c>
-      <c r="I45" s="229">
-        <f>IF(B45="","",F45*D45)</f>
-      </c>
-      <c r="J45" s="229">
-        <f>IF(B45="","",(H45+I45)*$B$12^2/8)</f>
-      </c>
-      <c r="K45" s="229">
-        <f>IF(B45="","",(H45+I45)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="233">
+      <c r="L95" s="227">
+        <f>IF((K95-1)*$L$31&gt;=$L$29,"",MAX($L$29-K95*$L$31,0))</f>
+      </c>
+      <c r="M95" s="227">
+        <f>IF(L95="","",$L$29-(K95-1)*$L$31)</f>
+      </c>
+      <c r="N95" s="227">
+        <f>IF(L95="","",$L$44*$L$25*M95)</f>
+      </c>
+      <c r="O95" s="227">
+        <f>IF(L95="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P95" s="227">
+        <f>IF(L95="","",N95+O95)</f>
+      </c>
+      <c r="Q95" s="227">
+        <f>IF(L95="","",N95*(M95-L95))</f>
+      </c>
+      <c r="R95" s="227">
+        <f>IF(L95="","",O95*(M95-L95))</f>
+      </c>
+      <c r="S95" s="227">
+        <f>IF(L95="","",(Q95+R95)*$L$32^2/8)</f>
+      </c>
+      <c r="T95" s="227">
+        <f>IF(L95="","",(Q95+R95)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="96">
+      <c r="K96" s="237">
         <v>2</v>
       </c>
-      <c r="B46" s="227">
-        <f>IF((A46-1)*$B$11&gt;=$B$8,"",MAX($B$8-A46*$B$11,0))</f>
-      </c>
-      <c r="C46" s="227">
-        <f>IF(B46="","",$B$8-(A46-1)*$B$11)</f>
-      </c>
-      <c r="D46" s="227">
-        <f>IF(B46="","",C46-B46)</f>
-      </c>
-      <c r="E46" s="227">
-        <f>IF(B46="","",$B$18*$B$6*C46)</f>
-      </c>
-      <c r="F46" s="227">
-        <f>IF(B46="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G46" s="227">
-        <f>IF(B46="","",E46+F46)</f>
-      </c>
-      <c r="H46" s="227">
-        <f>IF(B46="","",E46*D46)</f>
-      </c>
-      <c r="I46" s="227">
-        <f>IF(B46="","",F46*D46)</f>
-      </c>
-      <c r="J46" s="227">
-        <f>IF(B46="","",(H46+I46)*$B$12^2/8)</f>
-      </c>
-      <c r="K46" s="227">
-        <f>IF(B46="","",(H46+I46)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="233">
+      <c r="L96" s="227">
+        <f>IF((K96-1)*$L$31&gt;=$L$29,"",MAX($L$29-K96*$L$31,0))</f>
+      </c>
+      <c r="M96" s="227">
+        <f>IF(L96="","",$L$29-(K96-1)*$L$31)</f>
+      </c>
+      <c r="N96" s="227">
+        <f>IF(L96="","",$L$44*$L$25*M96)</f>
+      </c>
+      <c r="O96" s="227">
+        <f>IF(L96="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P96" s="227">
+        <f>IF(L96="","",N96+O96)</f>
+      </c>
+      <c r="Q96" s="227">
+        <f>IF(L96="","",N96*(M96-L96))</f>
+      </c>
+      <c r="R96" s="227">
+        <f>IF(L96="","",O96*(M96-L96))</f>
+      </c>
+      <c r="S96" s="227">
+        <f>IF(L96="","",(Q96+R96)*$L$32^2/8)</f>
+      </c>
+      <c r="T96" s="227">
+        <f>IF(L96="","",(Q96+R96)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="97">
+      <c r="K97" s="237">
         <v>3</v>
       </c>
-      <c r="B47" s="227">
-        <f>IF((A47-1)*$B$11&gt;=$B$8,"",MAX($B$8-A47*$B$11,0))</f>
-      </c>
-      <c r="C47" s="227">
-        <f>IF(B47="","",$B$8-(A47-1)*$B$11)</f>
-      </c>
-      <c r="D47" s="227">
-        <f>IF(B47="","",C47-B47)</f>
-      </c>
-      <c r="E47" s="227">
-        <f>IF(B47="","",$B$18*$B$6*C47)</f>
-      </c>
-      <c r="F47" s="227">
-        <f>IF(B47="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G47" s="227">
-        <f>IF(B47="","",E47+F47)</f>
-      </c>
-      <c r="H47" s="227">
-        <f>IF(B47="","",E47*D47)</f>
-      </c>
-      <c r="I47" s="227">
-        <f>IF(B47="","",F47*D47)</f>
-      </c>
-      <c r="J47" s="227">
-        <f>IF(B47="","",(H47+I47)*$B$12^2/8)</f>
-      </c>
-      <c r="K47" s="227">
-        <f>IF(B47="","",(H47+I47)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="233">
+      <c r="L97" s="227">
+        <f>IF((K97-1)*$L$31&gt;=$L$29,"",MAX($L$29-K97*$L$31,0))</f>
+      </c>
+      <c r="M97" s="227">
+        <f>IF(L97="","",$L$29-(K97-1)*$L$31)</f>
+      </c>
+      <c r="N97" s="227">
+        <f>IF(L97="","",$L$44*$L$25*M97)</f>
+      </c>
+      <c r="O97" s="227">
+        <f>IF(L97="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P97" s="227">
+        <f>IF(L97="","",N97+O97)</f>
+      </c>
+      <c r="Q97" s="227">
+        <f>IF(L97="","",N97*(M97-L97))</f>
+      </c>
+      <c r="R97" s="227">
+        <f>IF(L97="","",O97*(M97-L97))</f>
+      </c>
+      <c r="S97" s="227">
+        <f>IF(L97="","",(Q97+R97)*$L$32^2/8)</f>
+      </c>
+      <c r="T97" s="227">
+        <f>IF(L97="","",(Q97+R97)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="98">
+      <c r="K98" s="237">
         <v>4</v>
       </c>
-      <c r="B48" s="227">
-        <f>IF((A48-1)*$B$11&gt;=$B$8,"",MAX($B$8-A48*$B$11,0))</f>
-      </c>
-      <c r="C48" s="227">
-        <f>IF(B48="","",$B$8-(A48-1)*$B$11)</f>
-      </c>
-      <c r="D48" s="227">
-        <f>IF(B48="","",C48-B48)</f>
-      </c>
-      <c r="E48" s="227">
-        <f>IF(B48="","",$B$18*$B$6*C48)</f>
-      </c>
-      <c r="F48" s="227">
-        <f>IF(B48="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G48" s="227">
-        <f>IF(B48="","",E48+F48)</f>
-      </c>
-      <c r="H48" s="227">
-        <f>IF(B48="","",E48*D48)</f>
-      </c>
-      <c r="I48" s="227">
-        <f>IF(B48="","",F48*D48)</f>
-      </c>
-      <c r="J48" s="227">
-        <f>IF(B48="","",(H48+I48)*$B$12^2/8)</f>
-      </c>
-      <c r="K48" s="227">
-        <f>IF(B48="","",(H48+I48)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="233">
+      <c r="L98" s="227">
+        <f>IF((K98-1)*$L$31&gt;=$L$29,"",MAX($L$29-K98*$L$31,0))</f>
+      </c>
+      <c r="M98" s="227">
+        <f>IF(L98="","",$L$29-(K98-1)*$L$31)</f>
+      </c>
+      <c r="N98" s="227">
+        <f>IF(L98="","",$L$44*$L$25*M98)</f>
+      </c>
+      <c r="O98" s="227">
+        <f>IF(L98="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P98" s="227">
+        <f>IF(L98="","",N98+O98)</f>
+      </c>
+      <c r="Q98" s="227">
+        <f>IF(L98="","",N98*(M98-L98))</f>
+      </c>
+      <c r="R98" s="227">
+        <f>IF(L98="","",O98*(M98-L98))</f>
+      </c>
+      <c r="S98" s="227">
+        <f>IF(L98="","",(Q98+R98)*$L$32^2/8)</f>
+      </c>
+      <c r="T98" s="227">
+        <f>IF(L98="","",(Q98+R98)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="99">
+      <c r="K99" s="237">
         <v>5</v>
       </c>
-      <c r="B49" s="227">
-        <f>IF((A49-1)*$B$11&gt;=$B$8,"",MAX($B$8-A49*$B$11,0))</f>
-      </c>
-      <c r="C49" s="227">
-        <f>IF(B49="","",$B$8-(A49-1)*$B$11)</f>
-      </c>
-      <c r="D49" s="227">
-        <f>IF(B49="","",C49-B49)</f>
-      </c>
-      <c r="E49" s="227">
-        <f>IF(B49="","",$B$18*$B$6*C49)</f>
-      </c>
-      <c r="F49" s="227">
-        <f>IF(B49="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G49" s="227">
-        <f>IF(B49="","",E49+F49)</f>
-      </c>
-      <c r="H49" s="227">
-        <f>IF(B49="","",E49*D49)</f>
-      </c>
-      <c r="I49" s="227">
-        <f>IF(B49="","",F49*D49)</f>
-      </c>
-      <c r="J49" s="227">
-        <f>IF(B49="","",(H49+I49)*$B$12^2/8)</f>
-      </c>
-      <c r="K49" s="227">
-        <f>IF(B49="","",(H49+I49)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="233">
+      <c r="L99" s="227">
+        <f>IF((K99-1)*$L$31&gt;=$L$29,"",MAX($L$29-K99*$L$31,0))</f>
+      </c>
+      <c r="M99" s="227">
+        <f>IF(L99="","",$L$29-(K99-1)*$L$31)</f>
+      </c>
+      <c r="N99" s="227">
+        <f>IF(L99="","",$L$44*$L$25*M99)</f>
+      </c>
+      <c r="O99" s="227">
+        <f>IF(L99="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P99" s="227">
+        <f>IF(L99="","",N99+O99)</f>
+      </c>
+      <c r="Q99" s="227">
+        <f>IF(L99="","",N99*(M99-L99))</f>
+      </c>
+      <c r="R99" s="227">
+        <f>IF(L99="","",O99*(M99-L99))</f>
+      </c>
+      <c r="S99" s="227">
+        <f>IF(L99="","",(Q99+R99)*$L$32^2/8)</f>
+      </c>
+      <c r="T99" s="227">
+        <f>IF(L99="","",(Q99+R99)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="100">
+      <c r="K100" s="237">
         <v>6</v>
       </c>
-      <c r="B50" s="227">
-        <f>IF((A50-1)*$B$11&gt;=$B$8,"",MAX($B$8-A50*$B$11,0))</f>
-      </c>
-      <c r="C50" s="227">
-        <f>IF(B50="","",$B$8-(A50-1)*$B$11)</f>
-      </c>
-      <c r="D50" s="227">
-        <f>IF(B50="","",C50-B50)</f>
-      </c>
-      <c r="E50" s="227">
-        <f>IF(B50="","",$B$18*$B$6*C50)</f>
-      </c>
-      <c r="F50" s="227">
-        <f>IF(B50="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G50" s="227">
-        <f>IF(B50="","",E50+F50)</f>
-      </c>
-      <c r="H50" s="227">
-        <f>IF(B50="","",E50*D50)</f>
-      </c>
-      <c r="I50" s="227">
-        <f>IF(B50="","",F50*D50)</f>
-      </c>
-      <c r="J50" s="227">
-        <f>IF(B50="","",(H50+I50)*$B$12^2/8)</f>
-      </c>
-      <c r="K50" s="227">
-        <f>IF(B50="","",(H50+I50)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="233">
+      <c r="L100" s="227">
+        <f>IF((K100-1)*$L$31&gt;=$L$29,"",MAX($L$29-K100*$L$31,0))</f>
+      </c>
+      <c r="M100" s="227">
+        <f>IF(L100="","",$L$29-(K100-1)*$L$31)</f>
+      </c>
+      <c r="N100" s="227">
+        <f>IF(L100="","",$L$44*$L$25*M100)</f>
+      </c>
+      <c r="O100" s="227">
+        <f>IF(L100="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P100" s="227">
+        <f>IF(L100="","",N100+O100)</f>
+      </c>
+      <c r="Q100" s="227">
+        <f>IF(L100="","",N100*(M100-L100))</f>
+      </c>
+      <c r="R100" s="227">
+        <f>IF(L100="","",O100*(M100-L100))</f>
+      </c>
+      <c r="S100" s="227">
+        <f>IF(L100="","",(Q100+R100)*$L$32^2/8)</f>
+      </c>
+      <c r="T100" s="227">
+        <f>IF(L100="","",(Q100+R100)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="101">
+      <c r="K101" s="237">
         <v>7</v>
       </c>
-      <c r="B51" s="227">
-        <f>IF((A51-1)*$B$11&gt;=$B$8,"",MAX($B$8-A51*$B$11,0))</f>
-      </c>
-      <c r="C51" s="227">
-        <f>IF(B51="","",$B$8-(A51-1)*$B$11)</f>
-      </c>
-      <c r="D51" s="227">
-        <f>IF(B51="","",C51-B51)</f>
-      </c>
-      <c r="E51" s="227">
-        <f>IF(B51="","",$B$18*$B$6*C51)</f>
-      </c>
-      <c r="F51" s="227">
-        <f>IF(B51="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G51" s="227">
-        <f>IF(B51="","",E51+F51)</f>
-      </c>
-      <c r="H51" s="227">
-        <f>IF(B51="","",E51*D51)</f>
-      </c>
-      <c r="I51" s="227">
-        <f>IF(B51="","",F51*D51)</f>
-      </c>
-      <c r="J51" s="227">
-        <f>IF(B51="","",(H51+I51)*$B$12^2/8)</f>
-      </c>
-      <c r="K51" s="227">
-        <f>IF(B51="","",(H51+I51)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="233">
+      <c r="L101" s="227">
+        <f>IF((K101-1)*$L$31&gt;=$L$29,"",MAX($L$29-K101*$L$31,0))</f>
+      </c>
+      <c r="M101" s="227">
+        <f>IF(L101="","",$L$29-(K101-1)*$L$31)</f>
+      </c>
+      <c r="N101" s="227">
+        <f>IF(L101="","",$L$44*$L$25*M101)</f>
+      </c>
+      <c r="O101" s="227">
+        <f>IF(L101="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P101" s="227">
+        <f>IF(L101="","",N101+O101)</f>
+      </c>
+      <c r="Q101" s="227">
+        <f>IF(L101="","",N101*(M101-L101))</f>
+      </c>
+      <c r="R101" s="227">
+        <f>IF(L101="","",O101*(M101-L101))</f>
+      </c>
+      <c r="S101" s="227">
+        <f>IF(L101="","",(Q101+R101)*$L$32^2/8)</f>
+      </c>
+      <c r="T101" s="227">
+        <f>IF(L101="","",(Q101+R101)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="102">
+      <c r="K102" s="237">
         <v>8</v>
       </c>
-      <c r="B52" s="227">
-        <f>IF((A52-1)*$B$11&gt;=$B$8,"",MAX($B$8-A52*$B$11,0))</f>
-      </c>
-      <c r="C52" s="227">
-        <f>IF(B52="","",$B$8-(A52-1)*$B$11)</f>
-      </c>
-      <c r="D52" s="227">
-        <f>IF(B52="","",C52-B52)</f>
-      </c>
-      <c r="E52" s="227">
-        <f>IF(B52="","",$B$18*$B$6*C52)</f>
-      </c>
-      <c r="F52" s="227">
-        <f>IF(B52="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G52" s="227">
-        <f>IF(B52="","",E52+F52)</f>
-      </c>
-      <c r="H52" s="227">
-        <f>IF(B52="","",E52*D52)</f>
-      </c>
-      <c r="I52" s="227">
-        <f>IF(B52="","",F52*D52)</f>
-      </c>
-      <c r="J52" s="227">
-        <f>IF(B52="","",(H52+I52)*$B$12^2/8)</f>
-      </c>
-      <c r="K52" s="227">
-        <f>IF(B52="","",(H52+I52)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="233">
+      <c r="L102" s="227">
+        <f>IF((K102-1)*$L$31&gt;=$L$29,"",MAX($L$29-K102*$L$31,0))</f>
+      </c>
+      <c r="M102" s="227">
+        <f>IF(L102="","",$L$29-(K102-1)*$L$31)</f>
+      </c>
+      <c r="N102" s="227">
+        <f>IF(L102="","",$L$44*$L$25*M102)</f>
+      </c>
+      <c r="O102" s="227">
+        <f>IF(L102="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P102" s="227">
+        <f>IF(L102="","",N102+O102)</f>
+      </c>
+      <c r="Q102" s="227">
+        <f>IF(L102="","",N102*(M102-L102))</f>
+      </c>
+      <c r="R102" s="227">
+        <f>IF(L102="","",O102*(M102-L102))</f>
+      </c>
+      <c r="S102" s="227">
+        <f>IF(L102="","",(Q102+R102)*$L$32^2/8)</f>
+      </c>
+      <c r="T102" s="227">
+        <f>IF(L102="","",(Q102+R102)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="103">
+      <c r="K103" s="237">
         <v>9</v>
       </c>
-      <c r="B53" s="227">
-        <f>IF((A53-1)*$B$11&gt;=$B$8,"",MAX($B$8-A53*$B$11,0))</f>
-      </c>
-      <c r="C53" s="227">
-        <f>IF(B53="","",$B$8-(A53-1)*$B$11)</f>
-      </c>
-      <c r="D53" s="227">
-        <f>IF(B53="","",C53-B53)</f>
-      </c>
-      <c r="E53" s="227">
-        <f>IF(B53="","",$B$18*$B$6*C53)</f>
-      </c>
-      <c r="F53" s="227">
-        <f>IF(B53="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G53" s="227">
-        <f>IF(B53="","",E53+F53)</f>
-      </c>
-      <c r="H53" s="227">
-        <f>IF(B53="","",E53*D53)</f>
-      </c>
-      <c r="I53" s="227">
-        <f>IF(B53="","",F53*D53)</f>
-      </c>
-      <c r="J53" s="227">
-        <f>IF(B53="","",(H53+I53)*$B$12^2/8)</f>
-      </c>
-      <c r="K53" s="227">
-        <f>IF(B53="","",(H53+I53)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="233">
+      <c r="L103" s="227">
+        <f>IF((K103-1)*$L$31&gt;=$L$29,"",MAX($L$29-K103*$L$31,0))</f>
+      </c>
+      <c r="M103" s="227">
+        <f>IF(L103="","",$L$29-(K103-1)*$L$31)</f>
+      </c>
+      <c r="N103" s="227">
+        <f>IF(L103="","",$L$44*$L$25*M103)</f>
+      </c>
+      <c r="O103" s="227">
+        <f>IF(L103="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P103" s="227">
+        <f>IF(L103="","",N103+O103)</f>
+      </c>
+      <c r="Q103" s="227">
+        <f>IF(L103="","",N103*(M103-L103))</f>
+      </c>
+      <c r="R103" s="227">
+        <f>IF(L103="","",O103*(M103-L103))</f>
+      </c>
+      <c r="S103" s="227">
+        <f>IF(L103="","",(Q103+R103)*$L$32^2/8)</f>
+      </c>
+      <c r="T103" s="227">
+        <f>IF(L103="","",(Q103+R103)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="104">
+      <c r="K104" s="237">
         <v>10</v>
       </c>
-      <c r="B54" s="227">
-        <f>IF((A54-1)*$B$11&gt;=$B$8,"",MAX($B$8-A54*$B$11,0))</f>
-      </c>
-      <c r="C54" s="227">
-        <f>IF(B54="","",$B$8-(A54-1)*$B$11)</f>
-      </c>
-      <c r="D54" s="227">
-        <f>IF(B54="","",C54-B54)</f>
-      </c>
-      <c r="E54" s="227">
-        <f>IF(B54="","",$B$18*$B$6*C54)</f>
-      </c>
-      <c r="F54" s="227">
-        <f>IF(B54="","",$B$18*$B$5)</f>
-      </c>
-      <c r="G54" s="227">
-        <f>IF(B54="","",E54+F54)</f>
-      </c>
-      <c r="H54" s="227">
-        <f>IF(B54="","",E54*D54)</f>
-      </c>
-      <c r="I54" s="227">
-        <f>IF(B54="","",F54*D54)</f>
-      </c>
-      <c r="J54" s="227">
-        <f>IF(B54="","",(H54+I54)*$B$12^2/8)</f>
-      </c>
-      <c r="K54" s="227">
-        <f>IF(B54="","",(H54+I54)*$B$12/2)</f>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nº de painéis necessários</t>
-        </is>
-      </c>
-      <c r="B55" s="227">
-        <f>IF(B11=0,0,ROUNDUP(B8/B11,0))</f>
-      </c>
-      <c r="C55" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">un</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A tabela mostra até 10 painéis (H até 10·bw). Se precisar de mais, copie a última linha para baixo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6. CONFERÊNCIA DA ABA 'MURO DE ARRIMO' (região L2:X40)</t>
-        </is>
-      </c>
-      <c r="B58" s="220"/>
-      <c r="C58" s="220"/>
-      <c r="D58" s="220"/>
-      <c r="E58" s="220"/>
-      <c r="F58" s="220"/>
-      <c r="G58" s="220"/>
-      <c r="H58" s="220"/>
-      <c r="I58" s="220"/>
-      <c r="J58" s="220"/>
-      <c r="K58" s="220"/>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1) M11 e M12 dão #REF! (referência apagada). São cópias antigas de M22/M23, que estão corretas – podem ser apagadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2) M22 a M26 (carga no pilar) consideram só o solo, sem a sobrecarga Sc. M30/M31 (Pa,sup/Pa,inf) já incluem Sc. Nesta aba: B28 = com Sc, B31 = sem Sc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3) M26 (momento no pilar) está sem unidade: o resultado é em tf·m (base de pilar em balanço, sem Sc).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4) M28 = M25·M24/M27 com M27 = M25 → sempre igual a M24 (linha redundante, não é erro).</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5) M34 só vale na cota 0 (usa H² na parcela uniforme). M36 é a fórmula correta para qualquer cota.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6) M40 ('biapoiado', 'em ajuste'): o modelo é na verdade ENGASTADO na base e APOIADO no topo. Na cota 0 está certo (−78,15 kN·m), mas para cota ≠ 0 os termos em x estão com sinal trocado e o termo x²·Δp/2 aparece duplicado. Corrigido na seção 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7) P22:R27 (laje alveolar) estão corretos para o painel inferior (pressão na base × bw). A seção 5 detalha todos os painéis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8) Conversão kN → tf por ×0,1 (1 tf = 9,81 kN) fica ~2% abaixo do exato; mantida por ser a convenção usual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9) L10 cita '− 2·c·√Ka', mas a coesão não é usada (a favor da segurança) – ok.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10) Pilar com laje/viga travando o topo quase não se desloca: o empuxo em repouso (K0 = 1 − sen φ) é mais realista que o ativo. Para φ = 18°: Ka = 0,53 e K0 = 0,69 (+31%). Use o seletor em B10.</t>
-        </is>
-      </c>
+      <c r="L104" s="227">
+        <f>IF((K104-1)*$L$31&gt;=$L$29,"",MAX($L$29-K104*$L$31,0))</f>
+      </c>
+      <c r="M104" s="227">
+        <f>IF(L104="","",$L$29-(K104-1)*$L$31)</f>
+      </c>
+      <c r="N104" s="227">
+        <f>IF(L104="","",$L$44*$L$25*M104)</f>
+      </c>
+      <c r="O104" s="227">
+        <f>IF(L104="","",$L$44*$L$27)</f>
+      </c>
+      <c r="P104" s="227">
+        <f>IF(L104="","",N104+O104)</f>
+      </c>
+      <c r="Q104" s="227">
+        <f>IF(L104="","",N104*(M104-L104))</f>
+      </c>
+      <c r="R104" s="227">
+        <f>IF(L104="","",O104*(M104-L104))</f>
+      </c>
+      <c r="S104" s="227">
+        <f>IF(L104="","",(Q104+R104)*$L$32^2/8)</f>
+      </c>
+      <c r="T104" s="227">
+        <f>IF(L104="","",(Q104+R104)*$L$32/2)</f>
+      </c>
+    </row>
+    <row r="106">
+      <c r="K106" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 . DIAGRAMAS DE CARGA (atualizam automaticamente)</t>
+        </is>
+      </c>
+      <c r="L106" s="221"/>
+      <c r="M106" s="221"/>
+      <c r="N106" s="221"/>
+      <c r="O106" s="221"/>
+      <c r="P106" s="221"/>
+      <c r="Q106" s="221"/>
+      <c r="R106" s="221"/>
+      <c r="S106" s="221"/>
+      <c r="T106" s="221"/>
+    </row>
+    <row r="108" ht="45" customHeight="1">
+      <c r="K108" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gráficos de dispersão desenhados a partir da tabela de coordenadas do item 6.1. À esquerda: pilar com a carga trapezoidal (kN/m), a resultante E e as reações. À direita: parede de placas alveolares com a pressão real (vermelho) e a pressão adotada em cada painel (azul, constante = valor da borda inferior).</t>
+        </is>
+      </c>
+      <c r="L108" s="220"/>
+      <c r="M108" s="220"/>
+      <c r="N108" s="220"/>
+      <c r="O108" s="220"/>
+      <c r="P108" s="220"/>
+      <c r="Q108" s="220"/>
+      <c r="R108" s="220"/>
+      <c r="S108" s="220"/>
+      <c r="T108" s="220"/>
+    </row>
+    <row r="139">
+      <c r="K139" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 Coordenadas do desenho (não editar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="K140" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Série</t>
+        </is>
+      </c>
+      <c r="L140" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="M140" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="K141" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar</t>
+        </is>
+      </c>
+      <c r="L141" s="227">
+        <v>0</v>
+      </c>
+      <c r="M141" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="K142" s="237"/>
+      <c r="L142" s="227">
+        <v>0</v>
+      </c>
+      <c r="M142" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="143">
+      <c r="K143" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga (kN/m)</t>
+        </is>
+      </c>
+      <c r="L143" s="227">
+        <v>0</v>
+      </c>
+      <c r="M143" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="144">
+      <c r="K144" s="237"/>
+      <c r="L144" s="227">
+        <f>$L$55</f>
+      </c>
+      <c r="M144" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="145">
+      <c r="K145" s="237"/>
+      <c r="L145" s="227">
+        <f>$L$56</f>
+      </c>
+      <c r="M145" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="K146" s="237"/>
+      <c r="L146" s="227">
+        <v>0</v>
+      </c>
+      <c r="M146" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="K147" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sc | solo</t>
+        </is>
+      </c>
+      <c r="L147" s="227">
+        <f>$L$55</f>
+      </c>
+      <c r="M147" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="148">
+      <c r="K148" s="237"/>
+      <c r="L148" s="227">
+        <f>$L$55</f>
+      </c>
+      <c r="M148" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="K149" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
+      <c r="L149" s="227">
+        <f>$L$56-$L$57*1/6</f>
+      </c>
+      <c r="M149" s="227">
+        <f>$L$29*1/6</f>
+      </c>
+    </row>
+    <row r="150">
+      <c r="K150" s="237"/>
+      <c r="L150" s="227">
+        <v>0</v>
+      </c>
+      <c r="M150" s="227">
+        <f>$L$29*1/6</f>
+      </c>
+    </row>
+    <row r="151">
+      <c r="K151" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
+      <c r="L151" s="227">
+        <f>$L$56-$L$57*2/6</f>
+      </c>
+      <c r="M151" s="227">
+        <f>$L$29*2/6</f>
+      </c>
+    </row>
+    <row r="152">
+      <c r="K152" s="237"/>
+      <c r="L152" s="227">
+        <v>0</v>
+      </c>
+      <c r="M152" s="227">
+        <f>$L$29*2/6</f>
+      </c>
+    </row>
+    <row r="153">
+      <c r="K153" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
+      <c r="L153" s="227">
+        <f>$L$56-$L$57*3/6</f>
+      </c>
+      <c r="M153" s="227">
+        <f>$L$29*3/6</f>
+      </c>
+    </row>
+    <row r="154">
+      <c r="K154" s="237"/>
+      <c r="L154" s="227">
+        <v>0</v>
+      </c>
+      <c r="M154" s="227">
+        <f>$L$29*3/6</f>
+      </c>
+    </row>
+    <row r="155">
+      <c r="K155" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
+      <c r="L155" s="227">
+        <f>$L$56-$L$57*4/6</f>
+      </c>
+      <c r="M155" s="227">
+        <f>$L$29*4/6</f>
+      </c>
+    </row>
+    <row r="156">
+      <c r="K156" s="237"/>
+      <c r="L156" s="227">
+        <v>0</v>
+      </c>
+      <c r="M156" s="227">
+        <f>$L$29*4/6</f>
+      </c>
+    </row>
+    <row r="157">
+      <c r="K157" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
+      <c r="L157" s="227">
+        <f>$L$56-$L$57*5/6</f>
+      </c>
+      <c r="M157" s="227">
+        <f>$L$29*5/6</f>
+      </c>
+    </row>
+    <row r="158">
+      <c r="K158" s="237"/>
+      <c r="L158" s="227">
+        <v>0</v>
+      </c>
+      <c r="M158" s="227">
+        <f>$L$29*5/6</f>
+      </c>
+    </row>
+    <row r="159">
+      <c r="K159" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="L159" s="227">
+        <f>MAX($L$55,$L$56)*1.15</f>
+      </c>
+      <c r="M159" s="227">
+        <f>$L$61</f>
+      </c>
+    </row>
+    <row r="160">
+      <c r="K160" s="237"/>
+      <c r="L160" s="227">
+        <v>0</v>
+      </c>
+      <c r="M160" s="227">
+        <f>$L$61</f>
+      </c>
+    </row>
+    <row r="161">
+      <c r="K161" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,topo</t>
+        </is>
+      </c>
+      <c r="L161" s="227">
+        <f>IF($L$35="Balanço",NA(),0)</f>
+      </c>
+      <c r="M161" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="162">
+      <c r="K162" s="237"/>
+      <c r="L162" s="227">
+        <f>IF($L$35="Balanço",NA(),-0.35*$L$56)</f>
+      </c>
+      <c r="M162" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="163">
+      <c r="K163" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,base</t>
+        </is>
+      </c>
+      <c r="L163" s="227">
+        <v>0</v>
+      </c>
+      <c r="M163" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="K164" s="237"/>
+      <c r="L164" s="227">
+        <f>-0.35*$L$56</f>
+      </c>
+      <c r="M164" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="K165" s="237">
+        <f>"p,topo = "&amp;FIXED($L$55,2)&amp;" kN/m"</f>
+      </c>
+      <c r="L165" s="227">
+        <f>$L$55</f>
+      </c>
+      <c r="M165" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="166">
+      <c r="K166" s="237">
+        <f>"p,base = "&amp;FIXED($L$56,2)&amp;" kN/m"</f>
+      </c>
+      <c r="L166" s="227">
+        <f>$L$56</f>
+      </c>
+      <c r="M166" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="K167" s="237">
+        <f>"E = "&amp;FIXED($L$59,1)&amp;" kN (y = "&amp;FIXED($L$61,2)&amp;" m)"</f>
+      </c>
+      <c r="L167" s="227">
+        <f>MAX($L$55,$L$56)*1.15</f>
+      </c>
+      <c r="M167" s="227">
+        <f>$L$61</f>
+      </c>
+    </row>
+    <row r="168">
+      <c r="K168" s="237">
+        <f>"R,topo = "&amp;FIXED($L$74,1)&amp;" kN → laje"</f>
+      </c>
+      <c r="L168" s="227">
+        <f>IF($L$35="Balanço",NA(),-0.35*$L$56)</f>
+      </c>
+      <c r="M168" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="169">
+      <c r="K169" s="237">
+        <f>"R,base = "&amp;FIXED($L$75,1)&amp;" kN"</f>
+      </c>
+      <c r="L169" s="227">
+        <f>-0.35*$L$56</f>
+      </c>
+      <c r="M169" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="K170" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placas</t>
+        </is>
+      </c>
+      <c r="L170" s="227">
+        <v>0</v>
+      </c>
+      <c r="M170" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="K171" s="237"/>
+      <c r="L171" s="227">
+        <v>0</v>
+      </c>
+      <c r="M171" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="172">
+      <c r="K172" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão real</t>
+        </is>
+      </c>
+      <c r="L172" s="227">
+        <v>0</v>
+      </c>
+      <c r="M172" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="173">
+      <c r="K173" s="237"/>
+      <c r="L173" s="227">
+        <f>$L$47</f>
+      </c>
+      <c r="M173" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="174">
+      <c r="K174" s="237"/>
+      <c r="L174" s="227">
+        <f>$L$48</f>
+      </c>
+      <c r="M174" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="K175" s="237"/>
+      <c r="L175" s="227">
+        <v>0</v>
+      </c>
+      <c r="M175" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="K176" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sc | solo</t>
+        </is>
+      </c>
+      <c r="L176" s="227">
+        <f>$L$47</f>
+      </c>
+      <c r="M176" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="177">
+      <c r="K177" s="237"/>
+      <c r="L177" s="227">
+        <f>$L$47</f>
+      </c>
+      <c r="M177" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="K178" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
+      <c r="L178" s="227">
+        <f>$L$48-($L$48-$L$47)*1/4</f>
+      </c>
+      <c r="M178" s="227">
+        <f>$L$29*1/4</f>
+      </c>
+    </row>
+    <row r="179">
+      <c r="K179" s="237"/>
+      <c r="L179" s="227">
+        <v>0</v>
+      </c>
+      <c r="M179" s="227">
+        <f>$L$29*1/4</f>
+      </c>
+    </row>
+    <row r="180">
+      <c r="K180" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
+      <c r="L180" s="227">
+        <f>$L$48-($L$48-$L$47)*2/4</f>
+      </c>
+      <c r="M180" s="227">
+        <f>$L$29*2/4</f>
+      </c>
+    </row>
+    <row r="181">
+      <c r="K181" s="237"/>
+      <c r="L181" s="227">
+        <v>0</v>
+      </c>
+      <c r="M181" s="227">
+        <f>$L$29*2/4</f>
+      </c>
+    </row>
+    <row r="182">
+      <c r="K182" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
+      <c r="L182" s="227">
+        <f>$L$48-($L$48-$L$47)*3/4</f>
+      </c>
+      <c r="M182" s="227">
+        <f>$L$29*3/4</f>
+      </c>
+    </row>
+    <row r="183">
+      <c r="K183" s="237"/>
+      <c r="L183" s="227">
+        <v>0</v>
+      </c>
+      <c r="M183" s="227">
+        <f>$L$29*3/4</f>
+      </c>
+    </row>
+    <row r="184">
+      <c r="K184" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão adotada por painel</t>
+        </is>
+      </c>
+      <c r="L184" s="227">
+        <f>P95</f>
+      </c>
+      <c r="M184" s="227">
+        <f>$L$29-M95</f>
+      </c>
+    </row>
+    <row r="185">
+      <c r="K185" s="237"/>
+      <c r="L185" s="227">
+        <f>P95</f>
+      </c>
+      <c r="M185" s="227">
+        <f>$L$29-L95</f>
+      </c>
+    </row>
+    <row r="186">
+      <c r="K186" s="237"/>
+      <c r="L186" s="227">
+        <f>IF(L96="",L185,P96)</f>
+      </c>
+      <c r="M186" s="227">
+        <f>IF(L96="",M185,$L$29-M96)</f>
+      </c>
+    </row>
+    <row r="187">
+      <c r="K187" s="237"/>
+      <c r="L187" s="227">
+        <f>IF(L96="",L186,P96)</f>
+      </c>
+      <c r="M187" s="227">
+        <f>IF(L96="",M186,$L$29-L96)</f>
+      </c>
+    </row>
+    <row r="188">
+      <c r="K188" s="237"/>
+      <c r="L188" s="227">
+        <f>IF(L97="",L187,P97)</f>
+      </c>
+      <c r="M188" s="227">
+        <f>IF(L97="",M187,$L$29-M97)</f>
+      </c>
+    </row>
+    <row r="189">
+      <c r="K189" s="237"/>
+      <c r="L189" s="227">
+        <f>IF(L97="",L188,P97)</f>
+      </c>
+      <c r="M189" s="227">
+        <f>IF(L97="",M188,$L$29-L97)</f>
+      </c>
+    </row>
+    <row r="190">
+      <c r="K190" s="237"/>
+      <c r="L190" s="227">
+        <f>IF(L98="",L189,P98)</f>
+      </c>
+      <c r="M190" s="227">
+        <f>IF(L98="",M189,$L$29-M98)</f>
+      </c>
+    </row>
+    <row r="191">
+      <c r="K191" s="237"/>
+      <c r="L191" s="227">
+        <f>IF(L98="",L190,P98)</f>
+      </c>
+      <c r="M191" s="227">
+        <f>IF(L98="",M190,$L$29-L98)</f>
+      </c>
+    </row>
+    <row r="192">
+      <c r="K192" s="237"/>
+      <c r="L192" s="227">
+        <f>IF(L99="",L191,P99)</f>
+      </c>
+      <c r="M192" s="227">
+        <f>IF(L99="",M191,$L$29-M99)</f>
+      </c>
+    </row>
+    <row r="193">
+      <c r="K193" s="237"/>
+      <c r="L193" s="227">
+        <f>IF(L99="",L192,P99)</f>
+      </c>
+      <c r="M193" s="227">
+        <f>IF(L99="",M192,$L$29-L99)</f>
+      </c>
+    </row>
+    <row r="194">
+      <c r="K194" s="237"/>
+      <c r="L194" s="227">
+        <f>IF(L100="",L193,P100)</f>
+      </c>
+      <c r="M194" s="227">
+        <f>IF(L100="",M193,$L$29-M100)</f>
+      </c>
+    </row>
+    <row r="195">
+      <c r="K195" s="237"/>
+      <c r="L195" s="227">
+        <f>IF(L100="",L194,P100)</f>
+      </c>
+      <c r="M195" s="227">
+        <f>IF(L100="",M194,$L$29-L100)</f>
+      </c>
+    </row>
+    <row r="196">
+      <c r="K196" s="237"/>
+      <c r="L196" s="227">
+        <f>IF(L101="",L195,P101)</f>
+      </c>
+      <c r="M196" s="227">
+        <f>IF(L101="",M195,$L$29-M101)</f>
+      </c>
+    </row>
+    <row r="197">
+      <c r="K197" s="237"/>
+      <c r="L197" s="227">
+        <f>IF(L101="",L196,P101)</f>
+      </c>
+      <c r="M197" s="227">
+        <f>IF(L101="",M196,$L$29-L101)</f>
+      </c>
+    </row>
+    <row r="198">
+      <c r="K198" s="237"/>
+      <c r="L198" s="227">
+        <f>IF(L102="",L197,P102)</f>
+      </c>
+      <c r="M198" s="227">
+        <f>IF(L102="",M197,$L$29-M102)</f>
+      </c>
+    </row>
+    <row r="199">
+      <c r="K199" s="237"/>
+      <c r="L199" s="227">
+        <f>IF(L102="",L198,P102)</f>
+      </c>
+      <c r="M199" s="227">
+        <f>IF(L102="",M198,$L$29-L102)</f>
+      </c>
+    </row>
+    <row r="200">
+      <c r="K200" s="237"/>
+      <c r="L200" s="227">
+        <f>IF(L103="",L199,P103)</f>
+      </c>
+      <c r="M200" s="227">
+        <f>IF(L103="",M199,$L$29-M103)</f>
+      </c>
+    </row>
+    <row r="201">
+      <c r="K201" s="237"/>
+      <c r="L201" s="227">
+        <f>IF(L103="",L200,P103)</f>
+      </c>
+      <c r="M201" s="227">
+        <f>IF(L103="",M200,$L$29-L103)</f>
+      </c>
+    </row>
+    <row r="202">
+      <c r="K202" s="237"/>
+      <c r="L202" s="227">
+        <f>IF(L104="",L201,P104)</f>
+      </c>
+      <c r="M202" s="227">
+        <f>IF(L104="",M201,$L$29-M104)</f>
+      </c>
+    </row>
+    <row r="203">
+      <c r="K203" s="237"/>
+      <c r="L203" s="227">
+        <f>IF(L104="",L202,P104)</f>
+      </c>
+      <c r="M203" s="227">
+        <f>IF(L104="",M202,$L$29-L104)</f>
+      </c>
+    </row>
+    <row r="204">
+      <c r="K204" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 1</t>
+        </is>
+      </c>
+      <c r="L204" s="227">
+        <f>IF($L$31*1&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M204" s="227">
+        <f>$L$31*1</f>
+      </c>
+    </row>
+    <row r="205">
+      <c r="K205" s="237"/>
+      <c r="L205" s="227">
+        <f>IF($L$31*1&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M205" s="227">
+        <f>$L$31*1</f>
+      </c>
+    </row>
+    <row r="206">
+      <c r="K206" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 2</t>
+        </is>
+      </c>
+      <c r="L206" s="227">
+        <f>IF($L$31*2&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M206" s="227">
+        <f>$L$31*2</f>
+      </c>
+    </row>
+    <row r="207">
+      <c r="K207" s="237"/>
+      <c r="L207" s="227">
+        <f>IF($L$31*2&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M207" s="227">
+        <f>$L$31*2</f>
+      </c>
+    </row>
+    <row r="208">
+      <c r="K208" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 3</t>
+        </is>
+      </c>
+      <c r="L208" s="227">
+        <f>IF($L$31*3&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M208" s="227">
+        <f>$L$31*3</f>
+      </c>
+    </row>
+    <row r="209">
+      <c r="K209" s="237"/>
+      <c r="L209" s="227">
+        <f>IF($L$31*3&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M209" s="227">
+        <f>$L$31*3</f>
+      </c>
+    </row>
+    <row r="210">
+      <c r="K210" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 4</t>
+        </is>
+      </c>
+      <c r="L210" s="227">
+        <f>IF($L$31*4&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M210" s="227">
+        <f>$L$31*4</f>
+      </c>
+    </row>
+    <row r="211">
+      <c r="K211" s="237"/>
+      <c r="L211" s="227">
+        <f>IF($L$31*4&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M211" s="227">
+        <f>$L$31*4</f>
+      </c>
+    </row>
+    <row r="212">
+      <c r="K212" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 5</t>
+        </is>
+      </c>
+      <c r="L212" s="227">
+        <f>IF($L$31*5&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M212" s="227">
+        <f>$L$31*5</f>
+      </c>
+    </row>
+    <row r="213">
+      <c r="K213" s="237"/>
+      <c r="L213" s="227">
+        <f>IF($L$31*5&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M213" s="227">
+        <f>$L$31*5</f>
+      </c>
+    </row>
+    <row r="214">
+      <c r="K214" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 6</t>
+        </is>
+      </c>
+      <c r="L214" s="227">
+        <f>IF($L$31*6&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M214" s="227">
+        <f>$L$31*6</f>
+      </c>
+    </row>
+    <row r="215">
+      <c r="K215" s="237"/>
+      <c r="L215" s="227">
+        <f>IF($L$31*6&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M215" s="227">
+        <f>$L$31*6</f>
+      </c>
+    </row>
+    <row r="216">
+      <c r="K216" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 7</t>
+        </is>
+      </c>
+      <c r="L216" s="227">
+        <f>IF($L$31*7&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M216" s="227">
+        <f>$L$31*7</f>
+      </c>
+    </row>
+    <row r="217">
+      <c r="K217" s="237"/>
+      <c r="L217" s="227">
+        <f>IF($L$31*7&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M217" s="227">
+        <f>$L$31*7</f>
+      </c>
+    </row>
+    <row r="218">
+      <c r="K218" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 8</t>
+        </is>
+      </c>
+      <c r="L218" s="227">
+        <f>IF($L$31*8&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M218" s="227">
+        <f>$L$31*8</f>
+      </c>
+    </row>
+    <row r="219">
+      <c r="K219" s="237"/>
+      <c r="L219" s="227">
+        <f>IF($L$31*8&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M219" s="227">
+        <f>$L$31*8</f>
+      </c>
+    </row>
+    <row r="220">
+      <c r="K220" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 9</t>
+        </is>
+      </c>
+      <c r="L220" s="227">
+        <f>IF($L$31*9&lt;$L$29,0,NA())</f>
+      </c>
+      <c r="M220" s="227">
+        <f>$L$31*9</f>
+      </c>
+    </row>
+    <row r="221">
+      <c r="K221" s="237"/>
+      <c r="L221" s="227">
+        <f>IF($L$31*9&lt;$L$29,$L$48*1.05,NA())</f>
+      </c>
+      <c r="M221" s="227">
+        <f>$L$31*9</f>
+      </c>
+    </row>
+    <row r="222">
+      <c r="K222" s="237">
+        <f>"σ,topo = "&amp;FIXED($L$47,2)&amp;" kN/m²"</f>
+      </c>
+      <c r="L222" s="227">
+        <f>$L$47</f>
+      </c>
+      <c r="M222" s="227">
+        <f>$L$29</f>
+      </c>
+    </row>
+    <row r="223">
+      <c r="K223" s="237">
+        <f>"σ,base = "&amp;FIXED($L$48,2)&amp;" kN/m²"</f>
+      </c>
+      <c r="L223" s="227">
+        <f>$L$48</f>
+      </c>
+      <c r="M223" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="K224" s="237">
+        <f>IF(L95="","","P1: "&amp;FIXED(P95,1))</f>
+      </c>
+      <c r="L224" s="227">
+        <f>IF(L95="",NA(),P95)</f>
+      </c>
+      <c r="M224" s="227">
+        <f>IF(L95="",NA(),$L$29-(L95+M95)/2)</f>
+      </c>
+    </row>
+    <row r="225">
+      <c r="K225" s="237">
+        <f>IF(L96="","","P2: "&amp;FIXED(P96,1))</f>
+      </c>
+      <c r="L225" s="227">
+        <f>IF(L96="",NA(),P96)</f>
+      </c>
+      <c r="M225" s="227">
+        <f>IF(L96="",NA(),$L$29-(L96+M96)/2)</f>
+      </c>
+    </row>
+    <row r="226">
+      <c r="K226" s="237">
+        <f>IF(L97="","","P3: "&amp;FIXED(P97,1))</f>
+      </c>
+      <c r="L226" s="227">
+        <f>IF(L97="",NA(),P97)</f>
+      </c>
+      <c r="M226" s="227">
+        <f>IF(L97="",NA(),$L$29-(L97+M97)/2)</f>
+      </c>
+    </row>
+    <row r="227">
+      <c r="K227" s="237">
+        <f>IF(L98="","","P4: "&amp;FIXED(P98,1))</f>
+      </c>
+      <c r="L227" s="227">
+        <f>IF(L98="",NA(),P98)</f>
+      </c>
+      <c r="M227" s="227">
+        <f>IF(L98="",NA(),$L$29-(L98+M98)/2)</f>
+      </c>
+    </row>
+    <row r="228">
+      <c r="K228" s="237">
+        <f>IF(L99="","","P5: "&amp;FIXED(P99,1))</f>
+      </c>
+      <c r="L228" s="227">
+        <f>IF(L99="",NA(),P99)</f>
+      </c>
+      <c r="M228" s="227">
+        <f>IF(L99="",NA(),$L$29-(L99+M99)/2)</f>
+      </c>
+    </row>
+    <row r="229">
+      <c r="K229" s="237">
+        <f>IF(L100="","","P6: "&amp;FIXED(P100,1))</f>
+      </c>
+      <c r="L229" s="227">
+        <f>IF(L100="",NA(),P100)</f>
+      </c>
+      <c r="M229" s="227">
+        <f>IF(L100="",NA(),$L$29-(L100+M100)/2)</f>
+      </c>
+    </row>
+    <row r="230">
+      <c r="K230" s="237">
+        <f>IF(L101="","","P7: "&amp;FIXED(P101,1))</f>
+      </c>
+      <c r="L230" s="227">
+        <f>IF(L101="",NA(),P101)</f>
+      </c>
+      <c r="M230" s="227">
+        <f>IF(L101="",NA(),$L$29-(L101+M101)/2)</f>
+      </c>
+    </row>
+    <row r="231">
+      <c r="K231" s="237">
+        <f>IF(L102="","","P8: "&amp;FIXED(P102,1))</f>
+      </c>
+      <c r="L231" s="227">
+        <f>IF(L102="",NA(),P102)</f>
+      </c>
+      <c r="M231" s="227">
+        <f>IF(L102="",NA(),$L$29-(L102+M102)/2)</f>
+      </c>
+    </row>
+    <row r="232">
+      <c r="K232" s="237">
+        <f>IF(L103="","","P9: "&amp;FIXED(P103,1))</f>
+      </c>
+      <c r="L232" s="227">
+        <f>IF(L103="",NA(),P103)</f>
+      </c>
+      <c r="M232" s="227">
+        <f>IF(L103="",NA(),$L$29-(L103+M103)/2)</f>
+      </c>
+    </row>
+    <row r="233">
+      <c r="K233" s="237">
+        <f>IF(L104="","","P10: "&amp;FIXED(P104,1))</f>
+      </c>
+      <c r="L233" s="227">
+        <f>IF(L104="",NA(),P104)</f>
+      </c>
+      <c r="M233" s="227">
+        <f>IF(L104="",NA(),$L$29-(L104+M104)/2)</f>
+      </c>
+    </row>
+    <row r="235">
+      <c r="K235" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 . CONFERÊNCIA DA ABA MURO DE ARRIMO</t>
+        </is>
+      </c>
+      <c r="L235" s="221"/>
+      <c r="M235" s="221"/>
+      <c r="N235" s="221"/>
+      <c r="O235" s="221"/>
+      <c r="P235" s="221"/>
+      <c r="Q235" s="221"/>
+      <c r="R235" s="221"/>
+      <c r="S235" s="221"/>
+      <c r="T235" s="221"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="K237" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pontos encontrados na aba original (nada foi alterado nela). Esta aba já calcula tudo corrigido.</t>
+        </is>
+      </c>
+      <c r="L237" s="220"/>
+      <c r="M237" s="220"/>
+      <c r="N237" s="220"/>
+      <c r="O237" s="220"/>
+      <c r="P237" s="220"/>
+      <c r="Q237" s="220"/>
+      <c r="R237" s="220"/>
+      <c r="S237" s="220"/>
+      <c r="T237" s="220"/>
+    </row>
+    <row r="238">
+      <c r="K238" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 Região L2:X40 (a que você usa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="17" customHeight="1">
+      <c r="K239" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11:M12</t>
+        </is>
+      </c>
+      <c r="L239" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#REF! – referência apagada. São cópias antigas de M22/M23 (corretas). Podem ser apagadas.</t>
+        </is>
+      </c>
+      <c r="M239" s="239"/>
+      <c r="N239" s="239"/>
+      <c r="O239" s="239"/>
+      <c r="P239" s="239"/>
+      <c r="Q239" s="239"/>
+      <c r="R239" s="239"/>
+      <c r="S239" s="239"/>
+      <c r="T239" s="239"/>
+    </row>
+    <row r="240" ht="32" customHeight="1">
+      <c r="K240" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M22:M26</t>
+        </is>
+      </c>
+      <c r="L240" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga no pilar só com o solo, sem a sobrecarga Sc (M30/M31 já incluem). Aqui: E (com Sc) e E,solo (sem Sc) – item 3.2.</t>
+        </is>
+      </c>
+      <c r="M240" s="239"/>
+      <c r="N240" s="239"/>
+      <c r="O240" s="239"/>
+      <c r="P240" s="239"/>
+      <c r="Q240" s="239"/>
+      <c r="R240" s="239"/>
+      <c r="S240" s="239"/>
+      <c r="T240" s="239"/>
+    </row>
+    <row r="241" ht="17" customHeight="1">
+      <c r="K241" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26</t>
+        </is>
+      </c>
+      <c r="L241" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento sem unidade: o resultado é em tf·m (base do pilar em balanço, sem Sc).</t>
+        </is>
+      </c>
+      <c r="M241" s="239"/>
+      <c r="N241" s="239"/>
+      <c r="O241" s="239"/>
+      <c r="P241" s="239"/>
+      <c r="Q241" s="239"/>
+      <c r="R241" s="239"/>
+      <c r="S241" s="239"/>
+      <c r="T241" s="239"/>
+    </row>
+    <row r="242" ht="17" customHeight="1">
+      <c r="K242" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M28</t>
+        </is>
+      </c>
+      <c r="L242" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M25·M24/M27 com M27 = M25 → sempre igual a M24 (redundante, não é erro).</t>
+        </is>
+      </c>
+      <c r="M242" s="239"/>
+      <c r="N242" s="239"/>
+      <c r="O242" s="239"/>
+      <c r="P242" s="239"/>
+      <c r="Q242" s="239"/>
+      <c r="R242" s="239"/>
+      <c r="S242" s="239"/>
+      <c r="T242" s="239"/>
+    </row>
+    <row r="243" ht="17" customHeight="1">
+      <c r="K243" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M34</t>
+        </is>
+      </c>
+      <c r="L243" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Só vale na cota 0 (usa H² na parcela uniforme). M36 é a fórmula certa para qualquer cota.</t>
+        </is>
+      </c>
+      <c r="M243" s="239"/>
+      <c r="N243" s="239"/>
+      <c r="O243" s="239"/>
+      <c r="P243" s="239"/>
+      <c r="Q243" s="239"/>
+      <c r="R243" s="239"/>
+      <c r="S243" s="239"/>
+      <c r="T243" s="239"/>
+    </row>
+    <row r="244" ht="32" customHeight="1">
+      <c r="K244" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M40</t>
+        </is>
+      </c>
+      <c r="L244" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Biapoiado' é na verdade engastado na base e apoiado no topo. Certo na cota 0 (−78,15 kN·m); para cota ≠ 0 os termos em x estão com sinal trocado e x²·Δp/2 aparece duplicado. Corrigido no item 4.1.</t>
+        </is>
+      </c>
+      <c r="M244" s="239"/>
+      <c r="N244" s="239"/>
+      <c r="O244" s="239"/>
+      <c r="P244" s="239"/>
+      <c r="Q244" s="239"/>
+      <c r="R244" s="239"/>
+      <c r="S244" s="239"/>
+      <c r="T244" s="239"/>
+    </row>
+    <row r="245" ht="17" customHeight="1">
+      <c r="K245" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P22:R27</t>
+        </is>
+      </c>
+      <c r="L245" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laje alveolar correta para o painel inferior (pressão na base × bw). O item 5 detalha todos os painéis.</t>
+        </is>
+      </c>
+      <c r="M245" s="239"/>
+      <c r="N245" s="239"/>
+      <c r="O245" s="239"/>
+      <c r="P245" s="239"/>
+      <c r="Q245" s="239"/>
+      <c r="R245" s="239"/>
+      <c r="S245" s="239"/>
+      <c r="T245" s="239"/>
+    </row>
+    <row r="246" ht="17" customHeight="1">
+      <c r="K246" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M24</t>
+        </is>
+      </c>
+      <c r="L246" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN → tf por ×0,1 (1 tf = 9,81 kN) fica ~2% abaixo do exato; mantido por ser a convenção usual.</t>
+        </is>
+      </c>
+      <c r="M246" s="239"/>
+      <c r="N246" s="239"/>
+      <c r="O246" s="239"/>
+      <c r="P246" s="239"/>
+      <c r="Q246" s="239"/>
+      <c r="R246" s="239"/>
+      <c r="S246" s="239"/>
+      <c r="T246" s="239"/>
+    </row>
+    <row r="247" ht="32" customHeight="1">
+      <c r="K247" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M8</t>
+        </is>
+      </c>
+      <c r="L247" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar travado no topo quase não se desloca: empuxo em repouso (K0) é mais realista que o ativo. Para φ = 18°: Ka = 0,53 e K0 = 0,69 (+31%). Use a entrada Empuxo (item 1.3).</t>
+        </is>
+      </c>
+      <c r="M247" s="239"/>
+      <c r="N247" s="239"/>
+      <c r="O247" s="239"/>
+      <c r="P247" s="239"/>
+      <c r="Q247" s="239"/>
+      <c r="R247" s="239"/>
+      <c r="S247" s="239"/>
+      <c r="T247" s="239"/>
+    </row>
+    <row r="248">
+      <c r="K248" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 Restante da aba (colunas A–C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="32" customHeight="1">
+      <c r="K249" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B20 / B28</t>
+        </is>
+      </c>
+      <c r="L249" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#NUM! e #DIV/0!: a alvenaria pede 3,43 cm²/m e Ø8 em todo furo dá só 2,51 cm²/m → espaçamento '0 furos' e divisão por zero. Na prática: Ø8 não basta, usar Ø10 em todo furo (3,93 cm²/m).</t>
+        </is>
+      </c>
+      <c r="M249" s="239"/>
+      <c r="N249" s="239"/>
+      <c r="O249" s="239"/>
+      <c r="P249" s="239"/>
+      <c r="Q249" s="239"/>
+      <c r="R249" s="239"/>
+      <c r="S249" s="239"/>
+      <c r="T249" s="239"/>
+    </row>
+    <row r="250" ht="17" customHeight="1">
+      <c r="K250" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B8 / B9</t>
+        </is>
+      </c>
+      <c r="L250" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coesão e φ dão 0: NSPT (B4) = 0 não existe na tabela DADOS DO SOLO. Sem efeito, pois o Ka de B33 é digitado.</t>
+        </is>
+      </c>
+      <c r="M250" s="239"/>
+      <c r="N250" s="239"/>
+      <c r="O250" s="239"/>
+      <c r="P250" s="239"/>
+      <c r="Q250" s="239"/>
+      <c r="R250" s="239"/>
+      <c r="S250" s="239"/>
+      <c r="T250" s="239"/>
+    </row>
+    <row r="251" ht="32" customHeight="1">
+      <c r="K251" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B33</t>
+        </is>
+      </c>
+      <c r="L251" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ka = 0,36 digitado, sem ligação com φ. A aba usa 3 valores diferentes: 0,36 (B33), 0,528 (M8) e 0,75 (CÁLCULO FECHAMENTO).</t>
+        </is>
+      </c>
+      <c r="M251" s="239"/>
+      <c r="N251" s="239"/>
+      <c r="O251" s="239"/>
+      <c r="P251" s="239"/>
+      <c r="Q251" s="239"/>
+      <c r="R251" s="239"/>
+      <c r="S251" s="239"/>
+      <c r="T251" s="239"/>
+    </row>
+    <row r="252" ht="32" customHeight="1">
+      <c r="K252" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B24</t>
+        </is>
+      </c>
+      <c r="L252" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esbeltez do pilar usa a altura da alvenaria (1,75 m) em vez da do pilar (3,85 m). Com 3,85 m dá ≈ 25,7 &lt; 30 → segue 'Sim', por acaso.</t>
+        </is>
+      </c>
+      <c r="M252" s="239"/>
+      <c r="N252" s="239"/>
+      <c r="O252" s="239"/>
+      <c r="P252" s="239"/>
+      <c r="Q252" s="239"/>
+      <c r="R252" s="239"/>
+      <c r="S252" s="239"/>
+      <c r="T252" s="239"/>
+    </row>
+    <row r="253" ht="32" customHeight="1">
+      <c r="K253" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B52:B66</t>
+        </is>
+      </c>
+      <c r="L253" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar 20×30 não passa: Kc = 0,25 fora de tabela, Ks = 0,028 digitado não corresponde, As = 58 cm² (48 barras). Momento com (H/3 + 0,6) sem origem clara e sem Sc.</t>
+        </is>
+      </c>
+      <c r="M253" s="239"/>
+      <c r="N253" s="239"/>
+      <c r="O253" s="239"/>
+      <c r="P253" s="239"/>
+      <c r="Q253" s="239"/>
+      <c r="R253" s="239"/>
+      <c r="S253" s="239"/>
+      <c r="T253" s="239"/>
+    </row>
+    <row r="254" ht="17" customHeight="1">
+      <c r="K254" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B15</t>
+        </is>
+      </c>
+      <c r="L254" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TABELAS LÍBANO com μ digitados para La/Lb = 0,91: se mudar H ou D, os coeficientes não se atualizam.</t>
+        </is>
+      </c>
+      <c r="M254" s="239"/>
+      <c r="N254" s="239"/>
+      <c r="O254" s="239"/>
+      <c r="P254" s="239"/>
+      <c r="Q254" s="239"/>
+      <c r="R254" s="239"/>
+      <c r="S254" s="239"/>
+      <c r="T254" s="239"/>
+    </row>
+    <row r="255" ht="17" customHeight="1">
+      <c r="K255" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B90</t>
+        </is>
+      </c>
+      <c r="L255" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peso da sapata fixo (1,2 × 1,0 × 0,5 m).</t>
+        </is>
+      </c>
+      <c r="M255" s="239"/>
+      <c r="N255" s="239"/>
+      <c r="O255" s="239"/>
+      <c r="P255" s="239"/>
+      <c r="Q255" s="239"/>
+      <c r="R255" s="239"/>
+      <c r="S255" s="239"/>
+      <c r="T255" s="239"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="D28:K28"/>
-    <mergeCell ref="D31:K31"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A63:K63"/>
-    <mergeCell ref="A64:K64"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A66:K66"/>
-    <mergeCell ref="A67:K67"/>
-    <mergeCell ref="A68:K68"/>
+  <mergeCells count="47">
+    <mergeCell ref="K1:T1"/>
+    <mergeCell ref="K2:T2"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K22:T22"/>
+    <mergeCell ref="K38:T38"/>
+    <mergeCell ref="K40:T40"/>
+    <mergeCell ref="K51:T51"/>
+    <mergeCell ref="K53:T53"/>
+    <mergeCell ref="K65:T65"/>
+    <mergeCell ref="K67:T67"/>
+    <mergeCell ref="K81:T81"/>
+    <mergeCell ref="K83:T83"/>
+    <mergeCell ref="K106:T106"/>
+    <mergeCell ref="K108:T108"/>
+    <mergeCell ref="K235:T235"/>
+    <mergeCell ref="K237:T237"/>
+    <mergeCell ref="L239:T239"/>
+    <mergeCell ref="L240:T240"/>
+    <mergeCell ref="L241:T241"/>
+    <mergeCell ref="L242:T242"/>
+    <mergeCell ref="L243:T243"/>
+    <mergeCell ref="L244:T244"/>
+    <mergeCell ref="L245:T245"/>
+    <mergeCell ref="L246:T246"/>
+    <mergeCell ref="L247:T247"/>
+    <mergeCell ref="L249:T249"/>
+    <mergeCell ref="L250:T250"/>
+    <mergeCell ref="L251:T251"/>
+    <mergeCell ref="L252:T252"/>
+    <mergeCell ref="L253:T253"/>
+    <mergeCell ref="L254:T254"/>
+    <mergeCell ref="L255:T255"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:T8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="B10">
+  <conditionalFormatting sqref="N79 N85 N7 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19">
+    <cfRule type="beginsWith" dxfId="6" priority="1" operator="beginsWith" text="Ok">
+      <formula>LEFT(N79,2)="Ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N79 N85 N7 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19">
+    <cfRule type="beginsWith" dxfId="5" priority="2" operator="beginsWith" text="Não se aplica">
+      <formula>LEFT(N79,13)="Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L34">
       <formula1>"Ativo,Repouso"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L35">
+      <formula1>$K$70:$K$72</formula1>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToHeight="0"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
+++ b/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
@@ -3723,7 +3723,7 @@
               <a:rPr lang="pt-BR" sz="1100" b="1">
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
-              <a:t>LAJE ALVEOLAR – PRESSÃO NOS PAINÉIS (kN/m²)</a:t>
+              <a:t>LAJE ALVEOLAR – PRESSÃO (kN/m²) E CARGA NA PLACA (kN/m)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4614,7 +4614,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>σ,topo = 2,64 kN/m²</c:v>
+                  <c:v>σq = 2,64 kN/m² (Sc)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4686,7 +4686,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>σ,base = 26,39 kN/m²</c:v>
+                  <c:v>σ,base = 26,39 kN/m² = solo 23,75 + Sc 2,64</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4758,7 +4758,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>P1: 26,4</c:v>
+                  <c:v>P1: g = 29,69 | q = 3,30 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4830,7 +4830,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>P2: 14,5</c:v>
+                  <c:v>P2: g = 14,85 | q = 3,30 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -14986,10 +14986,10 @@
       <c r="S106" s="221"/>
       <c r="T106" s="221"/>
     </row>
-    <row r="108" ht="45" customHeight="1">
+    <row r="108" ht="75" customHeight="1">
       <c r="K108" s="220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gráficos de dispersão desenhados a partir da tabela de coordenadas do item 6.1. À esquerda: pilar com a carga trapezoidal (kN/m), a resultante E e as reações. À direita: parede de placas alveolares com a pressão real (vermelho) e a pressão adotada em cada painel (azul, constante = valor da borda inferior).</t>
+          <t xml:space="preserve">Gráficos de dispersão desenhados a partir da tabela de coordenadas do item 6.1. À esquerda: pilar com a carga trapezoidal (kN/m), a resultante E e as reações. À direita: parede de placas alveolares com a pressão real (vermelho) e a pressão adotada em cada painel (azul, constante = valor da borda inferior). O eixo está em PRESSÃO (kN/m²); os rótulos P1, P2… trazem a CARGA NA PLACA (kN/m) = pressão × bw, a mesma da tabela 5.2 (ex.: 23,75 × 1,25 = 29,69 kN/m de solo e 2,64 × 1,25 = 3,30 kN/m de sobrecarga).</t>
         </is>
       </c>
       <c r="L108" s="220"/>
@@ -15875,7 +15875,7 @@
     </row>
     <row r="222">
       <c r="K222" s="237">
-        <f>"σ,topo = "&amp;FIXED($L$47,2)&amp;" kN/m²"</f>
+        <f>"σq = "&amp;FIXED($L$47,2)&amp;" kN/m² (Sc)"</f>
       </c>
       <c r="L222" s="227">
         <f>$L$47</f>
@@ -15886,7 +15886,7 @@
     </row>
     <row r="223">
       <c r="K223" s="237">
-        <f>"σ,base = "&amp;FIXED($L$48,2)&amp;" kN/m²"</f>
+        <f>"σ,base = "&amp;FIXED($L$48,2)&amp;" kN/m² = solo "&amp;FIXED($L$49,2)&amp;" + Sc "&amp;FIXED($L$47,2)</f>
       </c>
       <c r="L223" s="227">
         <f>$L$48</f>
@@ -15897,7 +15897,7 @@
     </row>
     <row r="224">
       <c r="K224" s="237">
-        <f>IF(L95="","","P1: "&amp;FIXED(P95,1))</f>
+        <f>IF(L95="","","P1: g = "&amp;FIXED(Q95,2)&amp;" | q = "&amp;FIXED(R95,2)&amp;" kN/m")</f>
       </c>
       <c r="L224" s="227">
         <f>IF(L95="",NA(),P95)</f>
@@ -15908,7 +15908,7 @@
     </row>
     <row r="225">
       <c r="K225" s="237">
-        <f>IF(L96="","","P2: "&amp;FIXED(P96,1))</f>
+        <f>IF(L96="","","P2: g = "&amp;FIXED(Q96,2)&amp;" | q = "&amp;FIXED(R96,2)&amp;" kN/m")</f>
       </c>
       <c r="L225" s="227">
         <f>IF(L96="",NA(),P96)</f>
@@ -15919,7 +15919,7 @@
     </row>
     <row r="226">
       <c r="K226" s="237">
-        <f>IF(L97="","","P3: "&amp;FIXED(P97,1))</f>
+        <f>IF(L97="","","P3: g = "&amp;FIXED(Q97,2)&amp;" | q = "&amp;FIXED(R97,2)&amp;" kN/m")</f>
       </c>
       <c r="L226" s="227">
         <f>IF(L97="",NA(),P97)</f>
@@ -15930,7 +15930,7 @@
     </row>
     <row r="227">
       <c r="K227" s="237">
-        <f>IF(L98="","","P4: "&amp;FIXED(P98,1))</f>
+        <f>IF(L98="","","P4: g = "&amp;FIXED(Q98,2)&amp;" | q = "&amp;FIXED(R98,2)&amp;" kN/m")</f>
       </c>
       <c r="L227" s="227">
         <f>IF(L98="",NA(),P98)</f>
@@ -15941,7 +15941,7 @@
     </row>
     <row r="228">
       <c r="K228" s="237">
-        <f>IF(L99="","","P5: "&amp;FIXED(P99,1))</f>
+        <f>IF(L99="","","P5: g = "&amp;FIXED(Q99,2)&amp;" | q = "&amp;FIXED(R99,2)&amp;" kN/m")</f>
       </c>
       <c r="L228" s="227">
         <f>IF(L99="",NA(),P99)</f>
@@ -15952,7 +15952,7 @@
     </row>
     <row r="229">
       <c r="K229" s="237">
-        <f>IF(L100="","","P6: "&amp;FIXED(P100,1))</f>
+        <f>IF(L100="","","P6: g = "&amp;FIXED(Q100,2)&amp;" | q = "&amp;FIXED(R100,2)&amp;" kN/m")</f>
       </c>
       <c r="L229" s="227">
         <f>IF(L100="",NA(),P100)</f>
@@ -15963,7 +15963,7 @@
     </row>
     <row r="230">
       <c r="K230" s="237">
-        <f>IF(L101="","","P7: "&amp;FIXED(P101,1))</f>
+        <f>IF(L101="","","P7: g = "&amp;FIXED(Q101,2)&amp;" | q = "&amp;FIXED(R101,2)&amp;" kN/m")</f>
       </c>
       <c r="L230" s="227">
         <f>IF(L101="",NA(),P101)</f>
@@ -15974,7 +15974,7 @@
     </row>
     <row r="231">
       <c r="K231" s="237">
-        <f>IF(L102="","","P8: "&amp;FIXED(P102,1))</f>
+        <f>IF(L102="","","P8: g = "&amp;FIXED(Q102,2)&amp;" | q = "&amp;FIXED(R102,2)&amp;" kN/m")</f>
       </c>
       <c r="L231" s="227">
         <f>IF(L102="",NA(),P102)</f>
@@ -15985,7 +15985,7 @@
     </row>
     <row r="232">
       <c r="K232" s="237">
-        <f>IF(L103="","","P9: "&amp;FIXED(P103,1))</f>
+        <f>IF(L103="","","P9: g = "&amp;FIXED(Q103,2)&amp;" | q = "&amp;FIXED(R103,2)&amp;" kN/m")</f>
       </c>
       <c r="L232" s="227">
         <f>IF(L103="",NA(),P103)</f>
@@ -15996,7 +15996,7 @@
     </row>
     <row r="233">
       <c r="K233" s="237">
-        <f>IF(L104="","","P10: "&amp;FIXED(P104,1))</f>
+        <f>IF(L104="","","P10: g = "&amp;FIXED(Q104,2)&amp;" | q = "&amp;FIXED(R104,2)&amp;" kN/m")</f>
       </c>
       <c r="L233" s="227">
         <f>IF(L104="",NA(),P104)</f>

--- a/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
+++ b/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
@@ -23,7 +23,7 @@
     <sheet name="TABELAS LÍBANO" sheetId="10" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'CONTENÇÃO RÁPIDA'!$K$1:$T$255</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CONTENÇÃO RÁPIDA'!$K$1:$T$259</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="1000"/>
   <extLst>
@@ -2001,7 +2001,7 @@
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2513,6 +2513,12 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2651,7 +2657,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$141:$L$142</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$145:$L$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2666,7 +2672,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$141:$M$142</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$145:$M$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2700,7 +2706,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$143:$L$146</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$147:$L$150</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2721,7 +2727,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$143:$M$146</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$147:$M$150</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2762,7 +2768,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$147:$L$148</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$151:$L$152</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2777,7 +2783,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$147:$M$148</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$151:$M$152</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2812,7 +2818,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$149:$L$150</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$153:$L$154</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2827,7 +2833,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$149:$M$150</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$153:$M$154</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2862,7 +2868,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$151:$L$152</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$155:$L$156</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2877,7 +2883,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$151:$M$152</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$155:$M$156</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2912,7 +2918,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$153:$L$154</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$157:$L$158</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2927,7 +2933,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$153:$M$154</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$157:$M$158</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2962,7 +2968,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$155:$L$156</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$159:$L$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2977,7 +2983,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$155:$M$156</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$159:$M$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3012,7 +3018,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$157:$L$158</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$161:$L$162</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3027,7 +3033,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$157:$M$158</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$161:$M$162</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3062,7 +3068,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$159:$L$160</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$163:$L$164</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3077,7 +3083,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$159:$M$160</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$163:$M$164</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3112,7 +3118,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$161:$L$162</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$165:$L$166</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3127,7 +3133,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$161:$M$162</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$165:$M$166</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3162,7 +3168,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$163:$L$164</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$167:$L$168</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3177,7 +3183,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$163:$M$164</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$167:$M$168</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3197,7 +3203,7 @@
           <c:order val="11"/>
           <c:tx>
             <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$165</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$169</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3240,7 +3246,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$165:$L$165</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$169:$L$169</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3252,7 +3258,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$165:$M$165</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$169:$M$169</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3269,7 +3275,7 @@
           <c:order val="12"/>
           <c:tx>
             <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$166</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$170</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3312,7 +3318,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$166:$L$166</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$170:$L$170</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3324,7 +3330,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$166:$M$166</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$170:$M$170</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3341,7 +3347,7 @@
           <c:order val="13"/>
           <c:tx>
             <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$167</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$171</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3384,7 +3390,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$167:$L$167</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$171:$L$171</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3396,7 +3402,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$167:$M$167</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$171:$M$171</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3413,7 +3419,7 @@
           <c:order val="14"/>
           <c:tx>
             <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$168</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$172</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3456,7 +3462,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$168:$L$168</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$172:$L$172</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3468,7 +3474,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$168:$M$168</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$172:$M$172</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3485,7 +3491,7 @@
           <c:order val="15"/>
           <c:tx>
             <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$169</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$173</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3528,7 +3534,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$169:$L$169</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$173:$L$173</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3540,7 +3546,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$169:$M$169</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$173:$M$173</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -3755,7 +3761,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$170:$L$171</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$174:$L$175</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3770,7 +3776,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$170:$M$171</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$174:$M$175</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3804,7 +3810,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$172:$L$175</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$176:$L$179</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3825,7 +3831,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$172:$M$175</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$176:$M$179</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3866,7 +3872,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$176:$L$177</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$180:$L$181</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3881,7 +3887,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$176:$M$177</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$180:$M$181</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3916,7 +3922,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$178:$L$179</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$182:$L$183</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3931,7 +3937,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$178:$M$179</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$182:$M$183</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3966,7 +3972,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$180:$L$181</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$184:$L$185</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3981,7 +3987,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$180:$M$181</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$184:$M$185</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4016,7 +4022,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$182:$L$183</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$186:$L$187</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4031,7 +4037,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$182:$M$183</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$186:$M$187</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4065,7 +4071,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$184:$L$203</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$188:$L$207</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -4134,7 +4140,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$184:$M$203</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$188:$M$207</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -4223,7 +4229,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$204:$L$205</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$208:$L$209</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4238,7 +4244,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$204:$M$205</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$208:$M$209</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4258,94 +4264,6 @@
           <c:order val="8"/>
           <c:tx>
             <c:v>junta 2</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="9525" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="7F7F7F"/>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$206:$L$207</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$206:$M$207</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="9"/>
-          <c:order val="9"/>
-          <c:tx>
-            <c:v>junta 3</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="9525" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="7F7F7F"/>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$208:$L$209</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$208:$M$209</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>3.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.75</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="10"/>
-          <c:order val="10"/>
-          <c:tx>
-            <c:v>junta 4</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="9525" cap="rnd">
@@ -4375,10 +4293,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>5.0</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.0</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4386,10 +4304,10 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="11"/>
-          <c:order val="11"/>
+          <c:idx val="9"/>
+          <c:order val="9"/>
           <c:tx>
-            <c:v>junta 5</c:v>
+            <c:v>junta 3</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="9525" cap="rnd">
@@ -4419,10 +4337,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6.25</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.25</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4430,10 +4348,10 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="12"/>
-          <c:order val="12"/>
+          <c:idx val="10"/>
+          <c:order val="10"/>
           <c:tx>
-            <c:v>junta 6</c:v>
+            <c:v>junta 4</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="9525" cap="rnd">
@@ -4463,10 +4381,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7.5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4474,10 +4392,10 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="13"/>
-          <c:order val="13"/>
+          <c:idx val="11"/>
+          <c:order val="11"/>
           <c:tx>
-            <c:v>junta 7</c:v>
+            <c:v>junta 5</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="9525" cap="rnd">
@@ -4507,10 +4425,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>8.75</c:v>
+                  <c:v>6.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.75</c:v>
+                  <c:v>6.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4518,10 +4436,10 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="14"/>
-          <c:order val="14"/>
+          <c:idx val="12"/>
+          <c:order val="12"/>
           <c:tx>
-            <c:v>junta 8</c:v>
+            <c:v>junta 6</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="9525" cap="rnd">
@@ -4551,10 +4469,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>10.0</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.0</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4562,10 +4480,10 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="15"/>
-          <c:order val="15"/>
+          <c:idx val="13"/>
+          <c:order val="13"/>
           <c:tx>
-            <c:v>junta 9</c:v>
+            <c:v>junta 7</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="9525" cap="rnd">
@@ -4595,6 +4513,94 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
+                  <c:v>8.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:v>junta 8</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$222:$L$223</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$222:$M$223</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>10.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:v>junta 9</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$224:$L$225</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$224:$M$225</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
                   <c:v>11.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -4610,299 +4616,11 @@
           <c:order val="16"/>
           <c:tx>
             <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$222</c:f>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$226</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>σq = 2,64 kN/m² (Sc)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="pt-BR"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="r"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$222:$L$222</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2.639320225002103</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$222:$M$222</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>2.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="17"/>
-          <c:order val="17"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$223</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>σ,base = 26,39 kN/m² = solo 23,75 + Sc 2,64</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="pt-BR"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="r"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$223:$L$223</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>26.39320225002103</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$223:$M$223</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="18"/>
-          <c:order val="18"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$224</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>P1: g = 29,69 | q = 3,30 kN/m</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="pt-BR"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="r"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$224:$L$224</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>26.393202250021027</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$224:$M$224</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.625</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="19"/>
-          <c:order val="19"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$225</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>P2: g = 14,85 | q = 3,30 kN/m</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="pt-BR"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="r"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="1"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$L$225:$L$225</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>14.516261237511564</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$M$225:$M$225</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1.875</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="20"/>
-          <c:order val="20"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'CONTENÇÃO RÁPIDA'!$K$226</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v/>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4945,6 +4663,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.639320225002103</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4954,21 +4675,24 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="21"/>
-          <c:order val="21"/>
+          <c:idx val="17"/>
+          <c:order val="17"/>
           <c:tx>
             <c:strRef>
               <c:f>'CONTENÇÃO RÁPIDA'!$K$227</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v/>
+                  <c:v>σ,base = 26,39 kN/m² = solo 23,75 + Sc 2,64</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5011,6 +4735,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>26.39320225002103</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -5020,21 +4747,24 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="22"/>
-          <c:order val="22"/>
+          <c:idx val="18"/>
+          <c:order val="18"/>
           <c:tx>
             <c:strRef>
               <c:f>'CONTENÇÃO RÁPIDA'!$K$228</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v/>
+                  <c:v>P1: g = 29,69 | q = 3,30 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5077,6 +4807,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>26.393202250021027</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -5086,21 +4819,24 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.625</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="23"/>
-          <c:order val="23"/>
+          <c:idx val="19"/>
+          <c:order val="19"/>
           <c:tx>
             <c:strRef>
               <c:f>'CONTENÇÃO RÁPIDA'!$K$229</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v/>
+                  <c:v>P2: g = 14,85 | q = 3,30 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5143,6 +4879,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>14.516261237511564</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -5152,14 +4891,17 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.875</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="24"/>
-          <c:order val="24"/>
+          <c:idx val="20"/>
+          <c:order val="20"/>
           <c:tx>
             <c:strRef>
               <c:f>'CONTENÇÃO RÁPIDA'!$K$230</c:f>
@@ -5224,8 +4966,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="25"/>
-          <c:order val="25"/>
+          <c:idx val="21"/>
+          <c:order val="21"/>
           <c:tx>
             <c:strRef>
               <c:f>'CONTENÇÃO RÁPIDA'!$K$231</c:f>
@@ -5290,8 +5032,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="26"/>
-          <c:order val="26"/>
+          <c:idx val="22"/>
+          <c:order val="22"/>
           <c:tx>
             <c:strRef>
               <c:f>'CONTENÇÃO RÁPIDA'!$K$232</c:f>
@@ -5356,8 +5098,8 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="27"/>
-          <c:order val="27"/>
+          <c:idx val="23"/>
+          <c:order val="23"/>
           <c:tx>
             <c:strRef>
               <c:f>'CONTENÇÃO RÁPIDA'!$K$233</c:f>
@@ -5413,6 +5155,270 @@
           <c:yVal>
             <c:numRef>
               <c:f>'CONTENÇÃO RÁPIDA'!$M$233:$M$233</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="24"/>
+          <c:order val="24"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$234</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$234:$L$234</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$234:$M$234</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="25"/>
+          <c:order val="25"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$235</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$235:$L$235</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$235:$M$235</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="26"/>
+          <c:order val="26"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$236</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$236:$L$236</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$236:$M$236</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="27"/>
+          <c:order val="27"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$K$237</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Aptos Narrow"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$L$237:$L$237</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CONTENÇÃO RÁPIDA'!$M$237:$M$237</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -6509,13 +6515,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>138</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6539,13 +6545,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>138</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -13156,7 +13162,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="K1:T255"/>
+  <dimension ref="K1:T259"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="2.7109375" customWidth="1"/>
@@ -13183,1616 +13189,1554 @@
       <c r="S1" s="219"/>
       <c r="T1" s="219"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="K2" s="220" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="K2" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PILAR – CARGA TRAPEZOIDAL</t>
+        </is>
+      </c>
+      <c r="L2" s="239"/>
+      <c r="M2" s="240">
+        <f>"p,topo = "&amp;FIXED($L$59,2)&amp;" kN/m"</f>
+      </c>
+      <c r="N2" s="240"/>
+      <c r="O2" s="240">
+        <f>"p,base = "&amp;FIXED($L$60,2)&amp;" kN/m"</f>
+      </c>
+      <c r="P2" s="240"/>
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240">
+        <f>"E = "&amp;FIXED($L$63,2)&amp;" kN a "&amp;FIXED($L$65,2)&amp;" m da base"</f>
+      </c>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="K3" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PILAR – MOMENTOS</t>
+        </is>
+      </c>
+      <c r="L3" s="239"/>
+      <c r="M3" s="240">
+        <f>"M,base = "&amp;FIXED($L$80,2)&amp;" kN·m ("&amp;$L$39&amp;")"</f>
+      </c>
+      <c r="N3" s="240"/>
+      <c r="O3" s="240">
+        <f>"M,vão = "&amp;IF($L$39="Balanço","-",FIXED($L$81,2)&amp;" kN·m a "&amp;FIXED($L$82,2)&amp;" m")</f>
+      </c>
+      <c r="P3" s="240"/>
+      <c r="Q3" s="240"/>
+      <c r="R3" s="240">
+        <f>"R,topo = "&amp;FIXED($L$78,2)&amp;" kN → laje"</f>
+      </c>
+      <c r="S3" s="240"/>
+      <c r="T3" s="240"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="K4" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAJE – PAINEL MAIS CARREGADO (P1)</t>
+        </is>
+      </c>
+      <c r="L4" s="239"/>
+      <c r="M4" s="240">
+        <f>"g = "&amp;FIXED($L$93,2)&amp;" | q = "&amp;FIXED($L$94,2)&amp;" kN/m"</f>
+      </c>
+      <c r="N4" s="240"/>
+      <c r="O4" s="240">
+        <f>"p,total = "&amp;FIXED($L$92,2)&amp;" kN/m²"</f>
+      </c>
+      <c r="P4" s="240"/>
+      <c r="Q4" s="240"/>
+      <c r="R4" s="240">
+        <f>"Mk = "&amp;FIXED($L$95,2)&amp;" kN·m | Vk = "&amp;FIXED($L$96,2)&amp;" kN"</f>
+      </c>
+      <c r="S4" s="240"/>
+      <c r="T4" s="240"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="K6" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Como usar: células CINZA são entradas (preencha/edite). As demais são calculadas. Empuxo de Rankine, solo sem coesão (a favor da segurança); valores característicos (sem γf); 1 tf = 10 kN. A coluna Status fica verde quando está Ok. O RESUMO abaixo traz o que lançar no modelo (Eberick/TQS) e na tabela do fabricante da laje alveolar.</t>
         </is>
       </c>
-      <c r="L2" s="220"/>
-      <c r="M2" s="220"/>
-      <c r="N2" s="220"/>
-      <c r="O2" s="220"/>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="220"/>
-      <c r="R2" s="220"/>
-      <c r="S2" s="220"/>
-      <c r="T2" s="220"/>
-    </row>
-    <row r="4">
-      <c r="K4" s="221" t="inlineStr">
+      <c r="L6" s="220"/>
+      <c r="M6" s="220"/>
+      <c r="N6" s="220"/>
+      <c r="O6" s="220"/>
+      <c r="P6" s="220"/>
+      <c r="Q6" s="220"/>
+      <c r="R6" s="220"/>
+      <c r="S6" s="220"/>
+      <c r="T6" s="220"/>
+    </row>
+    <row r="8">
+      <c r="K8" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">RESUMO – VALORES PARA LANÇAR</t>
         </is>
       </c>
-      <c r="L4" s="221"/>
-      <c r="M4" s="221"/>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="221"/>
-      <c r="R4" s="221"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="221"/>
-    </row>
-    <row r="6">
-      <c r="K6" s="235" t="inlineStr">
+      <c r="L8" s="221"/>
+      <c r="M8" s="221"/>
+      <c r="N8" s="221"/>
+      <c r="O8" s="221"/>
+      <c r="P8" s="221"/>
+      <c r="Q8" s="221"/>
+      <c r="R8" s="221"/>
+      <c r="S8" s="221"/>
+      <c r="T8" s="221"/>
+    </row>
+    <row r="10">
+      <c r="K10" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Item</t>
         </is>
       </c>
-      <c r="L6" s="235" t="inlineStr">
+      <c r="L10" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Resultado</t>
         </is>
       </c>
-      <c r="M6" s="235"/>
-      <c r="N6" s="235" t="inlineStr">
+      <c r="M10" s="235"/>
+      <c r="N10" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="O6" s="235" t="inlineStr">
+      <c r="O10" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">O que é</t>
         </is>
       </c>
-      <c r="P6" s="235"/>
-      <c r="Q6" s="235"/>
-      <c r="R6" s="235"/>
-      <c r="S6" s="235"/>
-      <c r="T6" s="235"/>
-    </row>
-    <row r="7">
-      <c r="K7" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Empuxo</t>
-        </is>
-      </c>
-      <c r="L7" s="236">
-        <f>$L$34&amp;" – K = "&amp;FIXED($L$44,3)</f>
-      </c>
-      <c r="M7" s="236"/>
-      <c r="N7" s="232">
-        <f>"Ok"</f>
-      </c>
-      <c r="O7" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coeficiente adotado – item 2.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="K8" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aviso</t>
-        </is>
-      </c>
-      <c r="L8" s="234">
-        <f>IF(AND($L$35&lt;&gt;"Balanço",$L$34="Ativo"),"⚠ Topo do pilar travado pela laje com empuxo ATIVO: se a estrutura for rígida (sem deslocamento), use REPOUSO – K0 = "&amp;FIXED($L$43,2)&amp;" contra Ka = "&amp;FIXED($L$42,2)&amp;" (+"&amp;FIXED(($L$43/$L$42-1)*100,0)&amp;"% de carga).",IF(AND($L$35="Balanço",$L$34="Repouso"),"⚠ Balanço com empuxo em REPOUSO: pilar livre no topo se desloca – ATIVO costuma bastar.","Sem avisos."))</f>
-      </c>
-      <c r="M8" s="234"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="234"/>
-      <c r="Q8" s="234"/>
-      <c r="R8" s="234"/>
-      <c r="S8" s="234"/>
-      <c r="T8" s="234"/>
-    </row>
-    <row r="9">
-      <c r="K9" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pilar p,topo</t>
-        </is>
-      </c>
-      <c r="L9" s="236">
-        <f>FIXED($L$55,2)&amp;" kN/m"</f>
-      </c>
-      <c r="M9" s="236"/>
-      <c r="N9" s="232"/>
-      <c r="O9" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga trapezoidal no pilar: valor no topo – item 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="K10" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pilar p,base</t>
-        </is>
-      </c>
-      <c r="L10" s="236">
-        <f>FIXED($L$56,2)&amp;" kN/m"</f>
-      </c>
-      <c r="M10" s="236"/>
-      <c r="N10" s="232"/>
-      <c r="O10" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga trapezoidal no pilar: valor na base – item 3.1</t>
-        </is>
-      </c>
+      <c r="P10" s="235"/>
+      <c r="Q10" s="235"/>
+      <c r="R10" s="235"/>
+      <c r="S10" s="235"/>
+      <c r="T10" s="235"/>
     </row>
     <row r="11">
       <c r="K11" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resultante</t>
+          <t xml:space="preserve">Empuxo</t>
         </is>
       </c>
       <c r="L11" s="236">
-        <f>FIXED($L$59,2)&amp;" kN ("&amp;FIXED($L$60,2)&amp;" tf)"</f>
+        <f>$L$38&amp;" – K = "&amp;FIXED($L$48,3)</f>
       </c>
       <c r="M11" s="236"/>
-      <c r="N11" s="232"/>
+      <c r="N11" s="232">
+        <f>"Ok"</f>
+      </c>
       <c r="O11" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solo + Sc, aplicada a y,E da base – item 3.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t xml:space="preserve">Coeficiente adotado – item 2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
       <c r="K12" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modelo pilar</t>
-        </is>
-      </c>
-      <c r="L12" s="236">
-        <f>$L$35</f>
-      </c>
-      <c r="M12" s="236"/>
-      <c r="N12" s="232">
-        <f>IF(ISNA(MATCH($L$35,$K$70:$K$72,0)),"Rever: modelo inválido","Ok")</f>
-      </c>
-      <c r="O12" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modelo estrutural do pilar – item 4.1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Aviso</t>
+        </is>
+      </c>
+      <c r="L12" s="234">
+        <f>IF(AND($L$39&lt;&gt;"Balanço",$L$38="Ativo"),"⚠ Topo do pilar travado pela laje com empuxo ATIVO: se a estrutura for rígida (sem deslocamento), use REPOUSO – K0 = "&amp;FIXED($L$47,2)&amp;" contra Ka = "&amp;FIXED($L$46,2)&amp;" (+"&amp;FIXED(($L$47/$L$46-1)*100,0)&amp;"% de carga).",IF(AND($L$39="Balanço",$L$38="Repouso"),"⚠ Balanço com empuxo em REPOUSO: pilar livre no topo se desloca – ATIVO costuma bastar.","Sem avisos."))</f>
+      </c>
+      <c r="M12" s="234"/>
+      <c r="N12" s="234"/>
+      <c r="O12" s="234"/>
+      <c r="P12" s="234"/>
+      <c r="Q12" s="234"/>
+      <c r="R12" s="234"/>
+      <c r="S12" s="234"/>
+      <c r="T12" s="234"/>
     </row>
     <row r="13">
       <c r="K13" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">R,topo</t>
+          <t xml:space="preserve">Pilar p,topo</t>
         </is>
       </c>
       <c r="L13" s="236">
-        <f>FIXED($L$74,2)&amp;" kN"</f>
+        <f>FIXED($L$59,2)&amp;" kN/m"</f>
       </c>
       <c r="M13" s="236"/>
       <c r="N13" s="232"/>
       <c r="O13" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Força que o pilar entrega à laje/viga do topo – item 4.2</t>
+          <t xml:space="preserve">Carga trapezoidal no pilar: valor no topo – item 3.1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="K14" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">M,base</t>
+          <t xml:space="preserve">Pilar p,base</t>
         </is>
       </c>
       <c r="L14" s="236">
-        <f>FIXED($L$76,2)&amp;" kN·m"</f>
+        <f>FIXED($L$60,2)&amp;" kN/m"</f>
       </c>
       <c r="M14" s="236"/>
       <c r="N14" s="232"/>
       <c r="O14" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Momento na base do pilar – item 4.2</t>
+          <t xml:space="preserve">Carga trapezoidal no pilar: valor na base – item 3.1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="K15" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">M,vão</t>
+          <t xml:space="preserve">Resultante</t>
         </is>
       </c>
       <c r="L15" s="236">
-        <f>IF($L$35="Balanço","-",FIXED($L$77,2)&amp;" kN·m a "&amp;FIXED($L$78,2)&amp;" m")</f>
+        <f>FIXED($L$63,2)&amp;" kN ("&amp;FIXED($L$64,2)&amp;" tf)"</f>
       </c>
       <c r="M15" s="236"/>
       <c r="N15" s="232"/>
       <c r="O15" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maior momento positivo e altura a partir da base – item 4.2</t>
+          <t xml:space="preserve">Solo + Sc, aplicada a y,E da base – item 3.2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="K16" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">M(x)</t>
+          <t xml:space="preserve">Modelo pilar</t>
         </is>
       </c>
       <c r="L16" s="236">
-        <f>FIXED($L$79,2)&amp;" kN·m"</f>
+        <f>$L$39</f>
       </c>
       <c r="M16" s="236"/>
       <c r="N16" s="232">
-        <f>IF($L$36&gt;$L$29,"Rever: x maior que H",IF($L$36&lt;0,"Rever: x negativo","Ok"))</f>
+        <f>IF(ISNA(MATCH($L$39,$K$74:$K$76,0)),"Rever: modelo inválido","Ok")</f>
       </c>
       <c r="O16" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Momento na cota x – item 4.2</t>
+          <t xml:space="preserve">Modelo estrutural do pilar – item 4.1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="K17" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laje p,total</t>
+          <t xml:space="preserve">R,topo</t>
         </is>
       </c>
       <c r="L17" s="236">
-        <f>FIXED($L$88,2)&amp;" kN/m²"</f>
+        <f>FIXED($L$78,2)&amp;" kN"</f>
       </c>
       <c r="M17" s="236"/>
-      <c r="N17" s="232">
-        <f>IF($L$85&gt;10,"Rever: mais de 10 painéis","Ok")</f>
-      </c>
+      <c r="N17" s="232"/>
       <c r="O17" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Painel inferior: comparar com a tabela do fabricante – item 5.1</t>
+          <t xml:space="preserve">Força que o pilar entrega à laje/viga do topo – item 4.2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="K18" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laje g / q</t>
+          <t xml:space="preserve">M,base</t>
         </is>
       </c>
       <c r="L18" s="236">
-        <f>FIXED($L$89,2)&amp;" / "&amp;FIXED($L$90,2)&amp;" kN/m"</f>
+        <f>FIXED($L$80,2)&amp;" kN·m"</f>
       </c>
       <c r="M18" s="236"/>
       <c r="N18" s="232"/>
       <c r="O18" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cargas lineares no painel inferior – item 5.1</t>
+          <t xml:space="preserve">Momento na base do pilar – item 4.2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="K19" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laje Mk / Vk</t>
+          <t xml:space="preserve">M,vão</t>
         </is>
       </c>
       <c r="L19" s="236">
-        <f>FIXED($L$91,2)&amp;" kN·m / "&amp;FIXED($L$92,2)&amp;" kN"</f>
+        <f>IF($L$39="Balanço","-",FIXED($L$81,2)&amp;" kN·m a "&amp;FIXED($L$82,2)&amp;" m")</f>
       </c>
       <c r="M19" s="236"/>
       <c r="N19" s="232"/>
       <c r="O19" s="233" t="inlineStr">
         <is>
+          <t xml:space="preserve">Maior momento positivo e altura a partir da base – item 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="K20" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M(x)</t>
+        </is>
+      </c>
+      <c r="L20" s="236">
+        <f>FIXED($L$83,2)&amp;" kN·m"</f>
+      </c>
+      <c r="M20" s="236"/>
+      <c r="N20" s="232">
+        <f>IF($L$40&gt;$L$33,"Rever: x maior que H",IF($L$40&lt;0,"Rever: x negativo","Ok"))</f>
+      </c>
+      <c r="O20" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento na cota x – item 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="K21" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laje p,total</t>
+        </is>
+      </c>
+      <c r="L21" s="236">
+        <f>FIXED($L$92,2)&amp;" kN/m²"</f>
+      </c>
+      <c r="M21" s="236"/>
+      <c r="N21" s="232">
+        <f>IF($L$89&gt;10,"Rever: mais de 10 painéis","Ok")</f>
+      </c>
+      <c r="O21" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Painel inferior: comparar com a tabela do fabricante – item 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="K22" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laje g / q</t>
+        </is>
+      </c>
+      <c r="L22" s="236">
+        <f>FIXED($L$93,2)&amp;" / "&amp;FIXED($L$94,2)&amp;" kN/m"</f>
+      </c>
+      <c r="M22" s="236"/>
+      <c r="N22" s="232"/>
+      <c r="O22" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cargas lineares no painel inferior – item 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="K23" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laje Mk / Vk</t>
+        </is>
+      </c>
+      <c r="L23" s="236">
+        <f>FIXED($L$95,2)&amp;" kN·m / "&amp;FIXED($L$96,2)&amp;" kN"</f>
+      </c>
+      <c r="M23" s="236"/>
+      <c r="N23" s="232"/>
+      <c r="O23" s="233" t="inlineStr">
+        <is>
           <t xml:space="preserve">Esforços no painel inferior, vão L – item 5.1</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="K22" s="221" t="inlineStr">
+    <row r="26">
+      <c r="K26" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">1 . DADOS DE ENTRADA</t>
         </is>
       </c>
-      <c r="L22" s="221"/>
-      <c r="M22" s="221"/>
-      <c r="N22" s="221"/>
-      <c r="O22" s="221"/>
-      <c r="P22" s="221"/>
-      <c r="Q22" s="221"/>
-      <c r="R22" s="221"/>
-      <c r="S22" s="221"/>
-      <c r="T22" s="221"/>
-    </row>
-    <row r="24">
-      <c r="K24" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.1 Solo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="K25" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">γ</t>
-        </is>
-      </c>
-      <c r="L25" s="224">
-        <v>18</v>
-      </c>
-      <c r="M25" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m³</t>
-        </is>
-      </c>
-      <c r="O25" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peso específico do solo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="K26" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">φ</t>
-        </is>
-      </c>
-      <c r="L26" s="224">
-        <v>18</v>
-      </c>
-      <c r="M26" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">°</t>
-        </is>
-      </c>
-      <c r="O26" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ângulo de atrito do solo (ver aba DADOS DO SOLO, col. G).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="K27" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sc</t>
-        </is>
-      </c>
-      <c r="L27" s="224">
-        <v>5</v>
-      </c>
-      <c r="M27" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m²</t>
-        </is>
-      </c>
-      <c r="O27" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sobrecarga no terreno (veículos leves ≈ 5 a 10; só pedestres ≈ 2,5 a 5).</t>
-        </is>
-      </c>
+      <c r="L26" s="221"/>
+      <c r="M26" s="221"/>
+      <c r="N26" s="221"/>
+      <c r="O26" s="221"/>
+      <c r="P26" s="221"/>
+      <c r="Q26" s="221"/>
+      <c r="R26" s="221"/>
+      <c r="S26" s="221"/>
+      <c r="T26" s="221"/>
     </row>
     <row r="28">
       <c r="K28" s="222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.2 Geometria</t>
+          <t xml:space="preserve">1.1 Solo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="K29" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">H</t>
+          <t xml:space="preserve">γ</t>
         </is>
       </c>
       <c r="L29" s="224">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="M29" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">kN/m³</t>
         </is>
       </c>
       <c r="O29" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Altura da contenção: da base até o topo do terreno contido.</t>
+          <t xml:space="preserve">Peso específico do solo.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="K30" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
-        </is>
-      </c>
-      <c r="L30" s="226">
-        <f>13.07/2</f>
+          <t xml:space="preserve">φ</t>
+        </is>
+      </c>
+      <c r="L30" s="224">
+        <v>18</v>
       </c>
       <c r="M30" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">°</t>
         </is>
       </c>
       <c r="O30" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Largura de influência no pilar: intermediário = (vão esq. + vão dir.)/2; extremidade = vão/2.</t>
+          <t xml:space="preserve">Ângulo de atrito do solo (ver aba DADOS DO SOLO, col. G).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="K31" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">bw</t>
+          <t xml:space="preserve">Sc</t>
         </is>
       </c>
       <c r="L31" s="224">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="M31" s="231" t="inlineStr">
         <is>
+          <t xml:space="preserve">kN/m²</t>
+        </is>
+      </c>
+      <c r="O31" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sobrecarga no terreno (veículos leves ≈ 5 a 10; só pedestres ≈ 2,5 a 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="K32" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2 Geometria</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="K33" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="L33" s="224">
+        <v>2.5</v>
+      </c>
+      <c r="M33" s="231" t="inlineStr">
+        <is>
           <t xml:space="preserve">m</t>
         </is>
       </c>
-      <c r="O31" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Largura da placa de laje alveolar = altura de cada painel deitado na contenção.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="K32" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L</t>
-        </is>
-      </c>
-      <c r="L32" s="226">
-        <f>L30</f>
-      </c>
-      <c r="M32" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">m</t>
-        </is>
-      </c>
-      <c r="O32" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vão que a placa vence entre pilares (padrão = D; altere se for diferente).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="K33" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.3 Modelo</t>
+      <c r="O33" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura da contenção: da base até o topo do terreno contido.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="K34" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empuxo</t>
-        </is>
-      </c>
-      <c r="L34" s="224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ativo</t>
-        </is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="L34" s="226">
+        <f>13.07/2</f>
       </c>
       <c r="M34" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">m</t>
         </is>
       </c>
       <c r="O34" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ativo (Ka): parede pode se deslocar. Repouso (K0): topo travado, estrutura rígida.</t>
+          <t xml:space="preserve">Largura de influência no pilar: intermediário = (vão esq. + vão dir.)/2; extremidade = vão/2.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="K35" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilar</t>
-        </is>
-      </c>
-      <c r="L35" s="224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engaste-apoio</t>
-        </is>
+          <t xml:space="preserve">bw</t>
+        </is>
+      </c>
+      <c r="L35" s="224">
+        <v>1.25</v>
       </c>
       <c r="M35" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">m</t>
         </is>
       </c>
       <c r="O35" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modelo do pilar: escolha na tabela do item 4.1 (define o resumo).</t>
+          <t xml:space="preserve">Largura da placa de laje alveolar = altura de cada painel deitado na contenção.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="K36" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
+      <c r="L36" s="226">
+        <f>L34</f>
+      </c>
+      <c r="M36" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="O36" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vão que a placa vence entre pilares (padrão = D; altere se for diferente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="K37" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="K38" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empuxo</t>
+        </is>
+      </c>
+      <c r="L38" s="224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ativo</t>
+        </is>
+      </c>
+      <c r="M38" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O38" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ativo (Ka): parede pode se deslocar. Repouso (K0): topo travado, estrutura rígida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="K39" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar</t>
+        </is>
+      </c>
+      <c r="L39" s="224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engaste-apoio</t>
+        </is>
+      </c>
+      <c r="M39" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O39" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelo do pilar: escolha na tabela do item 4.1 (define o resumo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="K40" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">x</t>
         </is>
       </c>
-      <c r="L36" s="224">
-        <v>0</v>
-      </c>
-      <c r="M36" s="231" t="inlineStr">
+      <c r="L40" s="224">
+        <v>0</v>
+      </c>
+      <c r="M40" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">m</t>
         </is>
       </c>
-      <c r="O36" s="233" t="inlineStr">
+      <c r="O40" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Cota de verificação do momento, medida a partir da base (x = 0 → base).</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="K38" s="221" t="inlineStr">
+    <row r="42">
+      <c r="K42" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">2 . COEFICIENTE DE EMPUXO E PRESSÕES</t>
         </is>
       </c>
-      <c r="L38" s="221"/>
-      <c r="M38" s="221"/>
-      <c r="N38" s="221"/>
-      <c r="O38" s="221"/>
-      <c r="P38" s="221"/>
-      <c r="Q38" s="221"/>
-      <c r="R38" s="221"/>
-      <c r="S38" s="221"/>
-      <c r="T38" s="221"/>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="K40" s="220" t="inlineStr">
+      <c r="L42" s="221"/>
+      <c r="M42" s="221"/>
+      <c r="N42" s="221"/>
+      <c r="O42" s="221"/>
+      <c r="P42" s="221"/>
+      <c r="Q42" s="221"/>
+      <c r="R42" s="221"/>
+      <c r="S42" s="221"/>
+      <c r="T42" s="221"/>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="K44" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Rankine, parede vertical e terreno horizontal. A sobrecarga Sc vira uma pressão constante K·Sc em toda a altura; o solo dá uma pressão triangular K·γ·z (zero no topo, máxima na base).</t>
         </is>
       </c>
-      <c r="L40" s="220"/>
-      <c r="M40" s="220"/>
-      <c r="N40" s="220"/>
-      <c r="O40" s="220"/>
-      <c r="P40" s="220"/>
-      <c r="Q40" s="220"/>
-      <c r="R40" s="220"/>
-      <c r="S40" s="220"/>
-      <c r="T40" s="220"/>
-    </row>
-    <row r="41">
-      <c r="K41" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1 Coeficiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="K42" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ka</t>
-        </is>
-      </c>
-      <c r="L42" s="228">
-        <f>TAN(RADIANS(45-$L$26/2))^2</f>
-      </c>
-      <c r="M42" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O42" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Empuxo ativo: tan²(45° − φ/2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="K43" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K0</t>
-        </is>
-      </c>
-      <c r="L43" s="228">
-        <f>1-SIN(RADIANS($L$26))</f>
-      </c>
-      <c r="M43" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O43" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Empuxo em repouso: 1 − sen φ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="K44" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K</t>
-        </is>
-      </c>
-      <c r="L44" s="228">
-        <f>IF($L$34="Repouso",$L$43,$L$42)</f>
-      </c>
-      <c r="M44" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O44" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coeficiente adotado (item 1.3).</t>
-        </is>
-      </c>
+      <c r="L44" s="220"/>
+      <c r="M44" s="220"/>
+      <c r="N44" s="220"/>
+      <c r="O44" s="220"/>
+      <c r="P44" s="220"/>
+      <c r="Q44" s="220"/>
+      <c r="R44" s="220"/>
+      <c r="S44" s="220"/>
+      <c r="T44" s="220"/>
     </row>
     <row r="45">
       <c r="K45" s="222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Pressões</t>
+          <t xml:space="preserve">2.1 Coeficiente</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="K46" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">h,eq</t>
+          <t xml:space="preserve">Ka</t>
         </is>
       </c>
       <c r="L46" s="228">
-        <f>IF($L$25=0,0,$L$27/$L$25)</f>
+        <f>TAN(RADIANS(45-$L$30/2))^2</f>
       </c>
       <c r="M46" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O46" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Altura de solo equivalente à sobrecarga (Sc/γ).</t>
+          <t xml:space="preserve">Empuxo ativo: tan²(45° − φ/2).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="K47" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">σ,topo</t>
-        </is>
-      </c>
-      <c r="L47" s="227">
-        <f>$L$44*$L$27</f>
+          <t xml:space="preserve">K0</t>
+        </is>
+      </c>
+      <c r="L47" s="228">
+        <f>1-SIN(RADIANS($L$30))</f>
       </c>
       <c r="M47" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN/m²</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O47" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressão no topo: K·Sc.</t>
+          <t xml:space="preserve">Empuxo em repouso: 1 − sen φ.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="K48" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="L48" s="228">
+        <f>IF($L$38="Repouso",$L$47,$L$46)</f>
+      </c>
+      <c r="M48" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O48" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coeficiente adotado (item 1.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="K49" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Pressões</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="K50" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h,eq</t>
+        </is>
+      </c>
+      <c r="L50" s="228">
+        <f>IF($L$29=0,0,$L$31/$L$29)</f>
+      </c>
+      <c r="M50" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="O50" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura de solo equivalente à sobrecarga (Sc/γ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="K51" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σ,topo</t>
+        </is>
+      </c>
+      <c r="L51" s="227">
+        <f>$L$48*$L$31</f>
+      </c>
+      <c r="M51" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m²</t>
+        </is>
+      </c>
+      <c r="O51" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão no topo: K·Sc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="K52" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">σ,base</t>
         </is>
       </c>
-      <c r="L48" s="227">
-        <f>$L$44*($L$27+$L$25*$L$29)</f>
-      </c>
-      <c r="M48" s="231" t="inlineStr">
+      <c r="L52" s="227">
+        <f>$L$48*($L$31+$L$29*$L$33)</f>
+      </c>
+      <c r="M52" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN/m²</t>
         </is>
       </c>
-      <c r="O48" s="233" t="inlineStr">
+      <c r="O52" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Pressão na base: K·(Sc + γ·H).</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="K49" s="223" t="inlineStr">
+    <row r="53">
+      <c r="K53" s="223" t="inlineStr">
         <is>
           <t xml:space="preserve">σ,solo</t>
         </is>
       </c>
-      <c r="L49" s="227">
-        <f>$L$44*$L$25*$L$29</f>
-      </c>
-      <c r="M49" s="231" t="inlineStr">
+      <c r="L53" s="227">
+        <f>$L$48*$L$29*$L$33</f>
+      </c>
+      <c r="M53" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN/m²</t>
         </is>
       </c>
-      <c r="O49" s="233" t="inlineStr">
+      <c r="O53" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Pressão na base só do solo: K·γ·H (sem Sc).</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="K51" s="221" t="inlineStr">
+    <row r="55">
+      <c r="K55" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">3 . PILAR – CARGA PARA LANÇAR NO MODELO</t>
         </is>
       </c>
-      <c r="L51" s="221"/>
-      <c r="M51" s="221"/>
-      <c r="N51" s="221"/>
-      <c r="O51" s="221"/>
-      <c r="P51" s="221"/>
-      <c r="Q51" s="221"/>
-      <c r="R51" s="221"/>
-      <c r="S51" s="221"/>
-      <c r="T51" s="221"/>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="K53" s="220" t="inlineStr">
+      <c r="L55" s="221"/>
+      <c r="M55" s="221"/>
+      <c r="N55" s="221"/>
+      <c r="O55" s="221"/>
+      <c r="P55" s="221"/>
+      <c r="Q55" s="221"/>
+      <c r="R55" s="221"/>
+      <c r="S55" s="221"/>
+      <c r="T55" s="221"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="K57" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Lançar no pilar como carga horizontal TRAPEZOIDAL: p,topo no topo e p,base na base (pressão × largura de influência D). Se preferir carga concentrada, use a resultante E no ponto de aplicação y,E.</t>
         </is>
       </c>
-      <c r="L53" s="220"/>
-      <c r="M53" s="220"/>
-      <c r="N53" s="220"/>
-      <c r="O53" s="220"/>
-      <c r="P53" s="220"/>
-      <c r="Q53" s="220"/>
-      <c r="R53" s="220"/>
-      <c r="S53" s="220"/>
-      <c r="T53" s="220"/>
-    </row>
-    <row r="54">
-      <c r="K54" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1 Carga distribuída</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="K55" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p,topo</t>
-        </is>
-      </c>
-      <c r="L55" s="227">
-        <f>$L$47*$L$30</f>
-      </c>
-      <c r="M55" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m</t>
-        </is>
-      </c>
-      <c r="O55" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga no topo do pilar: σ,topo·D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="K56" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p,base</t>
-        </is>
-      </c>
-      <c r="L56" s="227">
-        <f>$L$48*$L$30</f>
-      </c>
-      <c r="M56" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m</t>
-        </is>
-      </c>
-      <c r="O56" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga na base do pilar: σ,base·D.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="K57" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Δp</t>
-        </is>
-      </c>
-      <c r="L57" s="227">
-        <f>$L$56-$L$55</f>
-      </c>
-      <c r="M57" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m</t>
-        </is>
-      </c>
-      <c r="O57" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parcela triangular (p,base − p,topo).</t>
-        </is>
-      </c>
+      <c r="L57" s="220"/>
+      <c r="M57" s="220"/>
+      <c r="N57" s="220"/>
+      <c r="O57" s="220"/>
+      <c r="P57" s="220"/>
+      <c r="Q57" s="220"/>
+      <c r="R57" s="220"/>
+      <c r="S57" s="220"/>
+      <c r="T57" s="220"/>
     </row>
     <row r="58">
       <c r="K58" s="222" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2 Resultante</t>
+          <t xml:space="preserve">3.1 Carga distribuída</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="K59" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">p,topo</t>
         </is>
       </c>
       <c r="L59" s="227">
-        <f>($L$55+$L$56)*$L$29/2</f>
+        <f>$L$51*$L$34</f>
       </c>
       <c r="M59" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN</t>
+          <t xml:space="preserve">kN/m</t>
         </is>
       </c>
       <c r="O59" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resultante total (solo + Sc).</t>
+          <t xml:space="preserve">Carga no topo do pilar: σ,topo·D.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="K60" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">p,base</t>
         </is>
       </c>
       <c r="L60" s="227">
-        <f>$L$59/10</f>
+        <f>$L$52*$L$34</f>
       </c>
       <c r="M60" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">kN/m</t>
         </is>
       </c>
       <c r="O60" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resultante total em tf.</t>
+          <t xml:space="preserve">Carga na base do pilar: σ,base·D.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="K61" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">y,E</t>
-        </is>
-      </c>
-      <c r="L61" s="228">
-        <f>IF($L$59=0,0,($L$55*$L$29^2/2+$L$57*$L$29^2/6)/$L$59)</f>
+          <t xml:space="preserve">Δp</t>
+        </is>
+      </c>
+      <c r="L61" s="227">
+        <f>$L$60-$L$59</f>
       </c>
       <c r="M61" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">kN/m</t>
         </is>
       </c>
       <c r="O61" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ponto de aplicação de E, medido a partir da base.</t>
+          <t xml:space="preserve">Parcela triangular (p,base − p,topo).</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="K62" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E,solo</t>
-        </is>
-      </c>
-      <c r="L62" s="227">
-        <f>$L$44*$L$25*$L$29^2/2*$L$30</f>
-      </c>
-      <c r="M62" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN</t>
-        </is>
-      </c>
-      <c r="O62" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resultante só do solo, a H/3 da base (= M23 da aba MURO DE ARRIMO).</t>
+      <c r="K62" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2 Resultante</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="K63" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="L63" s="227">
+        <f>($L$59+$L$60)*$L$33/2</f>
+      </c>
+      <c r="M63" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O63" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultante total (solo + Sc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="K64" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="L64" s="227">
+        <f>$L$63/10</f>
+      </c>
+      <c r="M64" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="O64" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultante total em tf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="K65" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y,E</t>
+        </is>
+      </c>
+      <c r="L65" s="228">
+        <f>IF($L$63=0,0,($L$59*$L$33^2/2+$L$61*$L$33^2/6)/$L$63)</f>
+      </c>
+      <c r="M65" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="O65" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ponto de aplicação de E, medido a partir da base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="K66" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">E,solo</t>
         </is>
       </c>
-      <c r="L63" s="227">
-        <f>$L$62/10</f>
-      </c>
-      <c r="M63" s="231" t="inlineStr">
+      <c r="L66" s="227">
+        <f>$L$48*$L$29*$L$33^2/2*$L$34</f>
+      </c>
+      <c r="M66" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O66" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultante só do solo, a H/3 da base (= M23 da aba MURO DE ARRIMO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="K67" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E,solo</t>
+        </is>
+      </c>
+      <c r="L67" s="227">
+        <f>$L$66/10</f>
+      </c>
+      <c r="M67" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="O63" s="233" t="inlineStr">
+      <c r="O67" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Idem em tf (= M24 da aba MURO DE ARRIMO).</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="K65" s="221" t="inlineStr">
+    <row r="69">
+      <c r="K69" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">4 . PILAR – ESFORÇOS (característicos)</t>
         </is>
       </c>
-      <c r="L65" s="221"/>
-      <c r="M65" s="221"/>
-      <c r="N65" s="221"/>
-      <c r="O65" s="221"/>
-      <c r="P65" s="221"/>
-      <c r="Q65" s="221"/>
-      <c r="R65" s="221"/>
-      <c r="S65" s="221"/>
-      <c r="T65" s="221"/>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="K67" s="220" t="inlineStr">
+      <c r="L69" s="221"/>
+      <c r="M69" s="221"/>
+      <c r="N69" s="221"/>
+      <c r="O69" s="221"/>
+      <c r="P69" s="221"/>
+      <c r="Q69" s="221"/>
+      <c r="R69" s="221"/>
+      <c r="S69" s="221"/>
+      <c r="T69" s="221"/>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="K71" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Sinal: M negativo = tração na face do pilar em contato com o solo; M positivo = tração na face externa. R,topo é a força horizontal que o pilar entrega à laje/viga do topo. Com laje ou viga travando o topo use Engaste-apoio; Balanço só se nada travar o topo.</t>
         </is>
       </c>
-      <c r="L67" s="220"/>
-      <c r="M67" s="220"/>
-      <c r="N67" s="220"/>
-      <c r="O67" s="220"/>
-      <c r="P67" s="220"/>
-      <c r="Q67" s="220"/>
-      <c r="R67" s="220"/>
-      <c r="S67" s="220"/>
-      <c r="T67" s="220"/>
-    </row>
-    <row r="68">
-      <c r="K68" s="222" t="inlineStr">
+      <c r="L71" s="220"/>
+      <c r="M71" s="220"/>
+      <c r="N71" s="220"/>
+      <c r="O71" s="220"/>
+      <c r="P71" s="220"/>
+      <c r="Q71" s="220"/>
+      <c r="R71" s="220"/>
+      <c r="S71" s="220"/>
+      <c r="T71" s="220"/>
+    </row>
+    <row r="72">
+      <c r="K72" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1 Comparação dos modelos</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="K69" s="235" t="inlineStr">
+    <row r="73" ht="30" customHeight="1">
+      <c r="K73" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Modelo</t>
         </is>
       </c>
-      <c r="L69" s="235" t="inlineStr">
+      <c r="L73" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">R,topo (kN)</t>
         </is>
       </c>
-      <c r="M69" s="235" t="inlineStr">
+      <c r="M73" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">R,base (kN)</t>
         </is>
       </c>
-      <c r="N69" s="235" t="inlineStr">
+      <c r="N73" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">M,base (kN·m)</t>
         </is>
       </c>
-      <c r="O69" s="235" t="inlineStr">
+      <c r="O73" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">M,vão (kN·m)</t>
         </is>
       </c>
-      <c r="P69" s="235" t="inlineStr">
+      <c r="P73" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">y,M (m)</t>
         </is>
       </c>
-      <c r="Q69" s="235" t="inlineStr">
+      <c r="Q73" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">M(x) (kN·m)</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="K70" s="237" t="inlineStr">
+    <row r="74">
+      <c r="K74" s="237" t="inlineStr">
         <is>
           <t xml:space="preserve">Balanço</t>
         </is>
       </c>
-      <c r="L70" s="227">
+      <c r="L74" s="227">
         <f>0</f>
       </c>
-      <c r="M70" s="227">
-        <f>$L$59-L70</f>
-      </c>
-      <c r="N70" s="227">
-        <f>-($L$55*$L$29^2/2+$L$57*$L$29^2/6)</f>
-      </c>
-      <c r="O70" s="227">
-        <v>0</v>
-      </c>
-      <c r="P70" s="237" t="inlineStr">
+      <c r="M74" s="227">
+        <f>$L$63-L74</f>
+      </c>
+      <c r="N74" s="227">
+        <f>-($L$59*$L$33^2/2+$L$61*$L$33^2/6)</f>
+      </c>
+      <c r="O74" s="227">
+        <v>0</v>
+      </c>
+      <c r="P74" s="237" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="Q70" s="227">
-        <f>L70*($L$29-$L$36)-$L$55*($L$29-$L$36)^2/2-$L$57*($L$29-$L$36)^3/(6*$L$29)</f>
-      </c>
-    </row>
-    <row r="71">
-      <c r="K71" s="237" t="inlineStr">
+      <c r="Q74" s="227">
+        <f>L74*($L$33-$L$40)-$L$59*($L$33-$L$40)^2/2-$L$61*($L$33-$L$40)^3/(6*$L$33)</f>
+      </c>
+    </row>
+    <row r="75">
+      <c r="K75" s="237" t="inlineStr">
         <is>
           <t xml:space="preserve">Engaste-apoio</t>
         </is>
       </c>
-      <c r="L71" s="227">
-        <f>3*$L$55*$L$29/8+$L$57*$L$29/10</f>
-      </c>
-      <c r="M71" s="227">
-        <f>$L$59-L71</f>
-      </c>
-      <c r="N71" s="227">
-        <f>-($L$55*$L$29^2/8+$L$57*$L$29^2/15)</f>
-      </c>
-      <c r="O71" s="227">
-        <f>L71*($L$29-P71)-$L$55*($L$29-P71)^2/2-$L$57*($L$29-P71)^3/(6*$L$29)</f>
-      </c>
-      <c r="P71" s="227">
-        <f>$L$29-IFERROR(IF($L$57=0,L71/$L$55,(-$L$55+SQRT($L$55^2+2*$L$57*L71/$L$29))/($L$57/$L$29)),0)</f>
-      </c>
-      <c r="Q71" s="227">
-        <f>L71*($L$29-$L$36)-$L$55*($L$29-$L$36)^2/2-$L$57*($L$29-$L$36)^3/(6*$L$29)</f>
-      </c>
-    </row>
-    <row r="72">
-      <c r="K72" s="237" t="inlineStr">
+      <c r="L75" s="227">
+        <f>3*$L$59*$L$33/8+$L$61*$L$33/10</f>
+      </c>
+      <c r="M75" s="227">
+        <f>$L$63-L75</f>
+      </c>
+      <c r="N75" s="227">
+        <f>-($L$59*$L$33^2/8+$L$61*$L$33^2/15)</f>
+      </c>
+      <c r="O75" s="227">
+        <f>L75*($L$33-P75)-$L$59*($L$33-P75)^2/2-$L$61*($L$33-P75)^3/(6*$L$33)</f>
+      </c>
+      <c r="P75" s="227">
+        <f>$L$33-IFERROR(IF($L$61=0,L75/$L$59,(-$L$59+SQRT($L$59^2+2*$L$61*L75/$L$33))/($L$61/$L$33)),0)</f>
+      </c>
+      <c r="Q75" s="227">
+        <f>L75*($L$33-$L$40)-$L$59*($L$33-$L$40)^2/2-$L$61*($L$33-$L$40)^3/(6*$L$33)</f>
+      </c>
+    </row>
+    <row r="76">
+      <c r="K76" s="237" t="inlineStr">
         <is>
           <t xml:space="preserve">Biapoiado</t>
         </is>
       </c>
-      <c r="L72" s="227">
-        <f>$L$55*$L$29/2+$L$57*$L$29/6</f>
-      </c>
-      <c r="M72" s="227">
-        <f>$L$59-L72</f>
-      </c>
-      <c r="N72" s="227">
+      <c r="L76" s="227">
+        <f>$L$59*$L$33/2+$L$61*$L$33/6</f>
+      </c>
+      <c r="M76" s="227">
+        <f>$L$63-L76</f>
+      </c>
+      <c r="N76" s="227">
         <f>0</f>
       </c>
-      <c r="O72" s="227">
-        <f>L72*($L$29-P72)-$L$55*($L$29-P72)^2/2-$L$57*($L$29-P72)^3/(6*$L$29)</f>
-      </c>
-      <c r="P72" s="227">
-        <f>$L$29-IFERROR(IF($L$57=0,L72/$L$55,(-$L$55+SQRT($L$55^2+2*$L$57*L72/$L$29))/($L$57/$L$29)),0)</f>
-      </c>
-      <c r="Q72" s="227">
-        <f>L72*($L$29-$L$36)-$L$55*($L$29-$L$36)^2/2-$L$57*($L$29-$L$36)^3/(6*$L$29)</f>
-      </c>
-    </row>
-    <row r="73">
-      <c r="K73" s="222" t="inlineStr">
+      <c r="O76" s="227">
+        <f>L76*($L$33-P76)-$L$59*($L$33-P76)^2/2-$L$61*($L$33-P76)^3/(6*$L$33)</f>
+      </c>
+      <c r="P76" s="227">
+        <f>$L$33-IFERROR(IF($L$61=0,L76/$L$59,(-$L$59+SQRT($L$59^2+2*$L$61*L76/$L$33))/($L$61/$L$33)),0)</f>
+      </c>
+      <c r="Q76" s="227">
+        <f>L76*($L$33-$L$40)-$L$59*($L$33-$L$40)^2/2-$L$61*($L$33-$L$40)^3/(6*$L$33)</f>
+      </c>
+    </row>
+    <row r="77">
+      <c r="K77" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">4.2 Modelo adotado (item 1.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="K74" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R,topo</t>
-        </is>
-      </c>
-      <c r="L74" s="227">
-        <f>IFERROR(INDEX($L$70:$L$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
-      </c>
-      <c r="M74" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN</t>
-        </is>
-      </c>
-      <c r="O74" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Força horizontal que vai para a laje/viga do topo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="K75" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R,base</t>
-        </is>
-      </c>
-      <c r="L75" s="227">
-        <f>IFERROR(INDEX($M$70:$M$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
-      </c>
-      <c r="M75" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN</t>
-        </is>
-      </c>
-      <c r="O75" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Força horizontal que vai para a fundação.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="K76" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M,base</t>
-        </is>
-      </c>
-      <c r="L76" s="227">
-        <f>IFERROR(INDEX($N$70:$N$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
-      </c>
-      <c r="M76" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN·m</t>
-        </is>
-      </c>
-      <c r="O76" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Momento na base do pilar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="K77" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M,vão</t>
-        </is>
-      </c>
-      <c r="L77" s="227">
-        <f>IFERROR(INDEX($O$70:$O$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
-      </c>
-      <c r="M77" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN·m</t>
-        </is>
-      </c>
-      <c r="O77" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Maior momento positivo ao longo do pilar (0 no balanço).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="K78" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">y,M</t>
+          <t xml:space="preserve">R,topo</t>
         </is>
       </c>
       <c r="L78" s="227">
-        <f>IF($L$35="Balanço","-",IFERROR(INDEX($P$70:$P$72,MATCH($L$35,$K$70:$K$72,0)),0))</f>
+        <f>IFERROR(INDEX($L$74:$L$76,MATCH($L$39,$K$74:$K$76,0)),0)</f>
       </c>
       <c r="M78" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">kN</t>
         </is>
       </c>
       <c r="O78" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Altura do M,vão a partir da base.</t>
+          <t xml:space="preserve">Força horizontal que vai para a laje/viga do topo.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="K79" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">R,base</t>
+        </is>
+      </c>
+      <c r="L79" s="227">
+        <f>IFERROR(INDEX($M$74:$M$76,MATCH($L$39,$K$74:$K$76,0)),0)</f>
+      </c>
+      <c r="M79" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O79" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Força horizontal que vai para a fundação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="K80" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M,base</t>
+        </is>
+      </c>
+      <c r="L80" s="227">
+        <f>IFERROR(INDEX($N$74:$N$76,MATCH($L$39,$K$74:$K$76,0)),0)</f>
+      </c>
+      <c r="M80" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O80" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento na base do pilar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="K81" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M,vão</t>
+        </is>
+      </c>
+      <c r="L81" s="227">
+        <f>IFERROR(INDEX($O$74:$O$76,MATCH($L$39,$K$74:$K$76,0)),0)</f>
+      </c>
+      <c r="M81" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O81" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maior momento positivo ao longo do pilar (0 no balanço).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="K82" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y,M</t>
+        </is>
+      </c>
+      <c r="L82" s="227">
+        <f>IF($L$39="Balanço","-",IFERROR(INDEX($P$74:$P$76,MATCH($L$39,$K$74:$K$76,0)),0))</f>
+      </c>
+      <c r="M82" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="O82" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura do M,vão a partir da base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="K83" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">M(x)</t>
         </is>
       </c>
-      <c r="L79" s="227">
-        <f>IFERROR(INDEX($Q$70:$Q$72,MATCH($L$35,$K$70:$K$72,0)),0)</f>
-      </c>
-      <c r="M79" s="231" t="inlineStr">
+      <c r="L83" s="227">
+        <f>IFERROR(INDEX($Q$74:$Q$76,MATCH($L$39,$K$74:$K$76,0)),0)</f>
+      </c>
+      <c r="M83" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN·m</t>
         </is>
       </c>
-      <c r="N79" s="232">
-        <f>IF($L$36&gt;$L$29,"Rever: x maior que H",IF($L$36&lt;0,"Rever: x negativo","Ok"))</f>
-      </c>
-      <c r="O79" s="233" t="inlineStr">
+      <c r="N83" s="232">
+        <f>IF($L$40&gt;$L$33,"Rever: x maior que H",IF($L$40&lt;0,"Rever: x negativo","Ok"))</f>
+      </c>
+      <c r="O83" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Momento na cota x (item 1.3).</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="K81" s="221" t="inlineStr">
+    <row r="85">
+      <c r="K85" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">5 . LAJE ALVEOLAR – CARGA EM CADA PAINEL</t>
         </is>
       </c>
-      <c r="L81" s="221"/>
-      <c r="M81" s="221"/>
-      <c r="N81" s="221"/>
-      <c r="O81" s="221"/>
-      <c r="P81" s="221"/>
-      <c r="Q81" s="221"/>
-      <c r="R81" s="221"/>
-      <c r="S81" s="221"/>
-      <c r="T81" s="221"/>
-    </row>
-    <row r="83" ht="45" customHeight="1">
-      <c r="K83" s="220" t="inlineStr">
+      <c r="L85" s="221"/>
+      <c r="M85" s="221"/>
+      <c r="N85" s="221"/>
+      <c r="O85" s="221"/>
+      <c r="P85" s="221"/>
+      <c r="Q85" s="221"/>
+      <c r="R85" s="221"/>
+      <c r="S85" s="221"/>
+      <c r="T85" s="221"/>
+    </row>
+    <row r="87" ht="45" customHeight="1">
+      <c r="K87" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Placas deitadas, uma sobre a outra, vencendo o vão L entre pilares. Painel 1 = inferior (mais carregado). Cada painel usa a pressão da sua borda inferior (a favor da segurança). g = solo (permanente); q = sobrecarga (variável). p,total é o valor a comparar com a sobrecarga da tabela do fabricante.</t>
         </is>
       </c>
-      <c r="L83" s="220"/>
-      <c r="M83" s="220"/>
-      <c r="N83" s="220"/>
-      <c r="O83" s="220"/>
-      <c r="P83" s="220"/>
-      <c r="Q83" s="220"/>
-      <c r="R83" s="220"/>
-      <c r="S83" s="220"/>
-      <c r="T83" s="220"/>
-    </row>
-    <row r="84">
-      <c r="K84" s="222" t="inlineStr">
+      <c r="L87" s="220"/>
+      <c r="M87" s="220"/>
+      <c r="N87" s="220"/>
+      <c r="O87" s="220"/>
+      <c r="P87" s="220"/>
+      <c r="Q87" s="220"/>
+      <c r="R87" s="220"/>
+      <c r="S87" s="220"/>
+      <c r="T87" s="220"/>
+    </row>
+    <row r="88">
+      <c r="K88" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">5.1 Painel inferior (o mais carregado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="K85" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n</t>
-        </is>
-      </c>
-      <c r="L85" s="229">
-        <f>IF($L$31=0,0,ROUNDUP($L$29/$L$31,0))</f>
-      </c>
-      <c r="M85" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">un</t>
-        </is>
-      </c>
-      <c r="N85" s="232">
-        <f>IF($L$85&gt;10,"Rever: mais de 10 painéis",IF($L$85&lt;1,"Rever: H ou bw","Ok"))</f>
-      </c>
-      <c r="O85" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Número de painéis na altura H.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="K86" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">σg</t>
-        </is>
-      </c>
-      <c r="L86" s="227">
-        <f>$L$44*$L$25*$L$29</f>
-      </c>
-      <c r="M86" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m²</t>
-        </is>
-      </c>
-      <c r="O86" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pressão do solo na borda inferior do painel 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="K87" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">σq</t>
-        </is>
-      </c>
-      <c r="L87" s="227">
-        <f>$L$44*$L$27</f>
-      </c>
-      <c r="M87" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m²</t>
-        </is>
-      </c>
-      <c r="O87" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pressão da sobrecarga (constante na altura).</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="K88" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p,total</t>
-        </is>
-      </c>
-      <c r="L88" s="227">
-        <f>$L$86+$L$87</f>
-      </c>
-      <c r="M88" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN/m²</t>
-        </is>
-      </c>
-      <c r="O88" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pressão total no painel 1 → comparar com a tabela do fabricante.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="K89" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">g</t>
-        </is>
-      </c>
-      <c r="L89" s="227">
-        <f>$L$86*MIN($L$31,$L$29)</f>
+          <t xml:space="preserve">n</t>
+        </is>
+      </c>
+      <c r="L89" s="229">
+        <f>IF($L$35=0,0,ROUNDUP($L$33/$L$35,0))</f>
       </c>
       <c r="M89" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN/m</t>
-        </is>
+          <t xml:space="preserve">un</t>
+        </is>
+      </c>
+      <c r="N89" s="232">
+        <f>IF($L$89&gt;10,"Rever: mais de 10 painéis",IF($L$89&lt;1,"Rever: H ou bw","Ok"))</f>
       </c>
       <c r="O89" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carga permanente linear no painel 1 (σg × largura).</t>
+          <t xml:space="preserve">Número de painéis na altura H.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="K90" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">q</t>
+          <t xml:space="preserve">σg</t>
         </is>
       </c>
       <c r="L90" s="227">
-        <f>$L$87*MIN($L$31,$L$29)</f>
+        <f>$L$48*$L$29*$L$33</f>
       </c>
       <c r="M90" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN/m</t>
+          <t xml:space="preserve">kN/m²</t>
         </is>
       </c>
       <c r="O90" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carga variável linear no painel 1 (σq × largura).</t>
+          <t xml:space="preserve">Pressão do solo na borda inferior do painel 1.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="K91" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mk</t>
+          <t xml:space="preserve">σq</t>
         </is>
       </c>
       <c r="L91" s="227">
-        <f>($L$89+$L$90)*$L$32^2/8</f>
+        <f>$L$48*$L$31</f>
       </c>
       <c r="M91" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN·m</t>
+          <t xml:space="preserve">kN/m²</t>
         </is>
       </c>
       <c r="O91" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Momento no painel 1, biapoiado nos pilares: (g+q)·L²/8.</t>
+          <t xml:space="preserve">Pressão da sobrecarga (constante na altura).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="K92" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">p,total</t>
+        </is>
+      </c>
+      <c r="L92" s="227">
+        <f>$L$90+$L$91</f>
+      </c>
+      <c r="M92" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m²</t>
+        </is>
+      </c>
+      <c r="O92" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão total no painel 1 → comparar com a tabela do fabricante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="K93" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g</t>
+        </is>
+      </c>
+      <c r="L93" s="227">
+        <f>$L$90*MIN($L$35,$L$33)</f>
+      </c>
+      <c r="M93" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m</t>
+        </is>
+      </c>
+      <c r="O93" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga permanente linear no painel 1 (σg × largura).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="K94" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q</t>
+        </is>
+      </c>
+      <c r="L94" s="227">
+        <f>$L$91*MIN($L$35,$L$33)</f>
+      </c>
+      <c r="M94" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN/m</t>
+        </is>
+      </c>
+      <c r="O94" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga variável linear no painel 1 (σq × largura).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="K95" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mk</t>
+        </is>
+      </c>
+      <c r="L95" s="227">
+        <f>($L$93+$L$94)*$L$36^2/8</f>
+      </c>
+      <c r="M95" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O95" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento no painel 1, biapoiado nos pilares: (g+q)·L²/8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="K96" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vk</t>
         </is>
       </c>
-      <c r="L92" s="227">
-        <f>($L$89+$L$90)*$L$32/2</f>
-      </c>
-      <c r="M92" s="231" t="inlineStr">
+      <c r="L96" s="227">
+        <f>($L$93+$L$94)*$L$36/2</f>
+      </c>
+      <c r="M96" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN</t>
         </is>
       </c>
-      <c r="O92" s="233" t="inlineStr">
+      <c r="O96" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Cortante / reação de cada lado no pilar: (g+q)·L/2.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="K93" s="222" t="inlineStr">
+    <row r="97">
+      <c r="K97" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">5.2 Todos os painéis</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="K94" s="235" t="inlineStr">
+    <row r="98" ht="30" customHeight="1">
+      <c r="K98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Painel</t>
         </is>
       </c>
-      <c r="L94" s="235" t="inlineStr">
+      <c r="L98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">z,topo (m)</t>
         </is>
       </c>
-      <c r="M94" s="235" t="inlineStr">
+      <c r="M98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">z,base (m)</t>
         </is>
       </c>
-      <c r="N94" s="235" t="inlineStr">
+      <c r="N98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">σg (kN/m²)</t>
         </is>
       </c>
-      <c r="O94" s="235" t="inlineStr">
+      <c r="O98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">σq (kN/m²)</t>
         </is>
       </c>
-      <c r="P94" s="235" t="inlineStr">
+      <c r="P98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">p,total (kN/m²)</t>
         </is>
       </c>
-      <c r="Q94" s="235" t="inlineStr">
+      <c r="Q98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">g (kN/m)</t>
         </is>
       </c>
-      <c r="R94" s="235" t="inlineStr">
+      <c r="R98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">q (kN/m)</t>
         </is>
       </c>
-      <c r="S94" s="235" t="inlineStr">
+      <c r="S98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Mk (kN·m)</t>
         </is>
       </c>
-      <c r="T94" s="235" t="inlineStr">
+      <c r="T98" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Vk (kN)</t>
         </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="K95" s="237">
-        <v>1</v>
-      </c>
-      <c r="L95" s="227">
-        <f>IF((K95-1)*$L$31&gt;=$L$29,"",MAX($L$29-K95*$L$31,0))</f>
-      </c>
-      <c r="M95" s="227">
-        <f>IF(L95="","",$L$29-(K95-1)*$L$31)</f>
-      </c>
-      <c r="N95" s="227">
-        <f>IF(L95="","",$L$44*$L$25*M95)</f>
-      </c>
-      <c r="O95" s="227">
-        <f>IF(L95="","",$L$44*$L$27)</f>
-      </c>
-      <c r="P95" s="227">
-        <f>IF(L95="","",N95+O95)</f>
-      </c>
-      <c r="Q95" s="227">
-        <f>IF(L95="","",N95*(M95-L95))</f>
-      </c>
-      <c r="R95" s="227">
-        <f>IF(L95="","",O95*(M95-L95))</f>
-      </c>
-      <c r="S95" s="227">
-        <f>IF(L95="","",(Q95+R95)*$L$32^2/8)</f>
-      </c>
-      <c r="T95" s="227">
-        <f>IF(L95="","",(Q95+R95)*$L$32/2)</f>
-      </c>
-    </row>
-    <row r="96">
-      <c r="K96" s="237">
-        <v>2</v>
-      </c>
-      <c r="L96" s="227">
-        <f>IF((K96-1)*$L$31&gt;=$L$29,"",MAX($L$29-K96*$L$31,0))</f>
-      </c>
-      <c r="M96" s="227">
-        <f>IF(L96="","",$L$29-(K96-1)*$L$31)</f>
-      </c>
-      <c r="N96" s="227">
-        <f>IF(L96="","",$L$44*$L$25*M96)</f>
-      </c>
-      <c r="O96" s="227">
-        <f>IF(L96="","",$L$44*$L$27)</f>
-      </c>
-      <c r="P96" s="227">
-        <f>IF(L96="","",N96+O96)</f>
-      </c>
-      <c r="Q96" s="227">
-        <f>IF(L96="","",N96*(M96-L96))</f>
-      </c>
-      <c r="R96" s="227">
-        <f>IF(L96="","",O96*(M96-L96))</f>
-      </c>
-      <c r="S96" s="227">
-        <f>IF(L96="","",(Q96+R96)*$L$32^2/8)</f>
-      </c>
-      <c r="T96" s="227">
-        <f>IF(L96="","",(Q96+R96)*$L$32/2)</f>
-      </c>
-    </row>
-    <row r="97">
-      <c r="K97" s="237">
-        <v>3</v>
-      </c>
-      <c r="L97" s="227">
-        <f>IF((K97-1)*$L$31&gt;=$L$29,"",MAX($L$29-K97*$L$31,0))</f>
-      </c>
-      <c r="M97" s="227">
-        <f>IF(L97="","",$L$29-(K97-1)*$L$31)</f>
-      </c>
-      <c r="N97" s="227">
-        <f>IF(L97="","",$L$44*$L$25*M97)</f>
-      </c>
-      <c r="O97" s="227">
-        <f>IF(L97="","",$L$44*$L$27)</f>
-      </c>
-      <c r="P97" s="227">
-        <f>IF(L97="","",N97+O97)</f>
-      </c>
-      <c r="Q97" s="227">
-        <f>IF(L97="","",N97*(M97-L97))</f>
-      </c>
-      <c r="R97" s="227">
-        <f>IF(L97="","",O97*(M97-L97))</f>
-      </c>
-      <c r="S97" s="227">
-        <f>IF(L97="","",(Q97+R97)*$L$32^2/8)</f>
-      </c>
-      <c r="T97" s="227">
-        <f>IF(L97="","",(Q97+R97)*$L$32/2)</f>
-      </c>
-    </row>
-    <row r="98">
-      <c r="K98" s="237">
-        <v>4</v>
-      </c>
-      <c r="L98" s="227">
-        <f>IF((K98-1)*$L$31&gt;=$L$29,"",MAX($L$29-K98*$L$31,0))</f>
-      </c>
-      <c r="M98" s="227">
-        <f>IF(L98="","",$L$29-(K98-1)*$L$31)</f>
-      </c>
-      <c r="N98" s="227">
-        <f>IF(L98="","",$L$44*$L$25*M98)</f>
-      </c>
-      <c r="O98" s="227">
-        <f>IF(L98="","",$L$44*$L$27)</f>
-      </c>
-      <c r="P98" s="227">
-        <f>IF(L98="","",N98+O98)</f>
-      </c>
-      <c r="Q98" s="227">
-        <f>IF(L98="","",N98*(M98-L98))</f>
-      </c>
-      <c r="R98" s="227">
-        <f>IF(L98="","",O98*(M98-L98))</f>
-      </c>
-      <c r="S98" s="227">
-        <f>IF(L98="","",(Q98+R98)*$L$32^2/8)</f>
-      </c>
-      <c r="T98" s="227">
-        <f>IF(L98="","",(Q98+R98)*$L$32/2)</f>
       </c>
     </row>
     <row r="99">
       <c r="K99" s="237">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L99" s="227">
-        <f>IF((K99-1)*$L$31&gt;=$L$29,"",MAX($L$29-K99*$L$31,0))</f>
+        <f>IF((K99-1)*$L$35&gt;=$L$33,"",MAX($L$33-K99*$L$35,0))</f>
       </c>
       <c r="M99" s="227">
-        <f>IF(L99="","",$L$29-(K99-1)*$L$31)</f>
+        <f>IF(L99="","",$L$33-(K99-1)*$L$35)</f>
       </c>
       <c r="N99" s="227">
-        <f>IF(L99="","",$L$44*$L$25*M99)</f>
+        <f>IF(L99="","",$L$48*$L$29*M99)</f>
       </c>
       <c r="O99" s="227">
-        <f>IF(L99="","",$L$44*$L$27)</f>
+        <f>IF(L99="","",$L$48*$L$31)</f>
       </c>
       <c r="P99" s="227">
         <f>IF(L99="","",N99+O99)</f>
@@ -14804,27 +14748,27 @@
         <f>IF(L99="","",O99*(M99-L99))</f>
       </c>
       <c r="S99" s="227">
-        <f>IF(L99="","",(Q99+R99)*$L$32^2/8)</f>
+        <f>IF(L99="","",(Q99+R99)*$L$36^2/8)</f>
       </c>
       <c r="T99" s="227">
-        <f>IF(L99="","",(Q99+R99)*$L$32/2)</f>
+        <f>IF(L99="","",(Q99+R99)*$L$36/2)</f>
       </c>
     </row>
     <row r="100">
       <c r="K100" s="237">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L100" s="227">
-        <f>IF((K100-1)*$L$31&gt;=$L$29,"",MAX($L$29-K100*$L$31,0))</f>
+        <f>IF((K100-1)*$L$35&gt;=$L$33,"",MAX($L$33-K100*$L$35,0))</f>
       </c>
       <c r="M100" s="227">
-        <f>IF(L100="","",$L$29-(K100-1)*$L$31)</f>
+        <f>IF(L100="","",$L$33-(K100-1)*$L$35)</f>
       </c>
       <c r="N100" s="227">
-        <f>IF(L100="","",$L$44*$L$25*M100)</f>
+        <f>IF(L100="","",$L$48*$L$29*M100)</f>
       </c>
       <c r="O100" s="227">
-        <f>IF(L100="","",$L$44*$L$27)</f>
+        <f>IF(L100="","",$L$48*$L$31)</f>
       </c>
       <c r="P100" s="227">
         <f>IF(L100="","",N100+O100)</f>
@@ -14836,27 +14780,27 @@
         <f>IF(L100="","",O100*(M100-L100))</f>
       </c>
       <c r="S100" s="227">
-        <f>IF(L100="","",(Q100+R100)*$L$32^2/8)</f>
+        <f>IF(L100="","",(Q100+R100)*$L$36^2/8)</f>
       </c>
       <c r="T100" s="227">
-        <f>IF(L100="","",(Q100+R100)*$L$32/2)</f>
+        <f>IF(L100="","",(Q100+R100)*$L$36/2)</f>
       </c>
     </row>
     <row r="101">
       <c r="K101" s="237">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L101" s="227">
-        <f>IF((K101-1)*$L$31&gt;=$L$29,"",MAX($L$29-K101*$L$31,0))</f>
+        <f>IF((K101-1)*$L$35&gt;=$L$33,"",MAX($L$33-K101*$L$35,0))</f>
       </c>
       <c r="M101" s="227">
-        <f>IF(L101="","",$L$29-(K101-1)*$L$31)</f>
+        <f>IF(L101="","",$L$33-(K101-1)*$L$35)</f>
       </c>
       <c r="N101" s="227">
-        <f>IF(L101="","",$L$44*$L$25*M101)</f>
+        <f>IF(L101="","",$L$48*$L$29*M101)</f>
       </c>
       <c r="O101" s="227">
-        <f>IF(L101="","",$L$44*$L$27)</f>
+        <f>IF(L101="","",$L$48*$L$31)</f>
       </c>
       <c r="P101" s="227">
         <f>IF(L101="","",N101+O101)</f>
@@ -14868,27 +14812,27 @@
         <f>IF(L101="","",O101*(M101-L101))</f>
       </c>
       <c r="S101" s="227">
-        <f>IF(L101="","",(Q101+R101)*$L$32^2/8)</f>
+        <f>IF(L101="","",(Q101+R101)*$L$36^2/8)</f>
       </c>
       <c r="T101" s="227">
-        <f>IF(L101="","",(Q101+R101)*$L$32/2)</f>
+        <f>IF(L101="","",(Q101+R101)*$L$36/2)</f>
       </c>
     </row>
     <row r="102">
       <c r="K102" s="237">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L102" s="227">
-        <f>IF((K102-1)*$L$31&gt;=$L$29,"",MAX($L$29-K102*$L$31,0))</f>
+        <f>IF((K102-1)*$L$35&gt;=$L$33,"",MAX($L$33-K102*$L$35,0))</f>
       </c>
       <c r="M102" s="227">
-        <f>IF(L102="","",$L$29-(K102-1)*$L$31)</f>
+        <f>IF(L102="","",$L$33-(K102-1)*$L$35)</f>
       </c>
       <c r="N102" s="227">
-        <f>IF(L102="","",$L$44*$L$25*M102)</f>
+        <f>IF(L102="","",$L$48*$L$29*M102)</f>
       </c>
       <c r="O102" s="227">
-        <f>IF(L102="","",$L$44*$L$27)</f>
+        <f>IF(L102="","",$L$48*$L$31)</f>
       </c>
       <c r="P102" s="227">
         <f>IF(L102="","",N102+O102)</f>
@@ -14900,27 +14844,27 @@
         <f>IF(L102="","",O102*(M102-L102))</f>
       </c>
       <c r="S102" s="227">
-        <f>IF(L102="","",(Q102+R102)*$L$32^2/8)</f>
+        <f>IF(L102="","",(Q102+R102)*$L$36^2/8)</f>
       </c>
       <c r="T102" s="227">
-        <f>IF(L102="","",(Q102+R102)*$L$32/2)</f>
+        <f>IF(L102="","",(Q102+R102)*$L$36/2)</f>
       </c>
     </row>
     <row r="103">
       <c r="K103" s="237">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L103" s="227">
-        <f>IF((K103-1)*$L$31&gt;=$L$29,"",MAX($L$29-K103*$L$31,0))</f>
+        <f>IF((K103-1)*$L$35&gt;=$L$33,"",MAX($L$33-K103*$L$35,0))</f>
       </c>
       <c r="M103" s="227">
-        <f>IF(L103="","",$L$29-(K103-1)*$L$31)</f>
+        <f>IF(L103="","",$L$33-(K103-1)*$L$35)</f>
       </c>
       <c r="N103" s="227">
-        <f>IF(L103="","",$L$44*$L$25*M103)</f>
+        <f>IF(L103="","",$L$48*$L$29*M103)</f>
       </c>
       <c r="O103" s="227">
-        <f>IF(L103="","",$L$44*$L$27)</f>
+        <f>IF(L103="","",$L$48*$L$31)</f>
       </c>
       <c r="P103" s="227">
         <f>IF(L103="","",N103+O103)</f>
@@ -14932,27 +14876,27 @@
         <f>IF(L103="","",O103*(M103-L103))</f>
       </c>
       <c r="S103" s="227">
-        <f>IF(L103="","",(Q103+R103)*$L$32^2/8)</f>
+        <f>IF(L103="","",(Q103+R103)*$L$36^2/8)</f>
       </c>
       <c r="T103" s="227">
-        <f>IF(L103="","",(Q103+R103)*$L$32/2)</f>
+        <f>IF(L103="","",(Q103+R103)*$L$36/2)</f>
       </c>
     </row>
     <row r="104">
       <c r="K104" s="237">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L104" s="227">
-        <f>IF((K104-1)*$L$31&gt;=$L$29,"",MAX($L$29-K104*$L$31,0))</f>
+        <f>IF((K104-1)*$L$35&gt;=$L$33,"",MAX($L$33-K104*$L$35,0))</f>
       </c>
       <c r="M104" s="227">
-        <f>IF(L104="","",$L$29-(K104-1)*$L$31)</f>
+        <f>IF(L104="","",$L$33-(K104-1)*$L$35)</f>
       </c>
       <c r="N104" s="227">
-        <f>IF(L104="","",$L$44*$L$25*M104)</f>
+        <f>IF(L104="","",$L$48*$L$29*M104)</f>
       </c>
       <c r="O104" s="227">
-        <f>IF(L104="","",$L$44*$L$27)</f>
+        <f>IF(L104="","",$L$48*$L$31)</f>
       </c>
       <c r="P104" s="227">
         <f>IF(L104="","",N104+O104)</f>
@@ -14964,116 +14908,204 @@
         <f>IF(L104="","",O104*(M104-L104))</f>
       </c>
       <c r="S104" s="227">
-        <f>IF(L104="","",(Q104+R104)*$L$32^2/8)</f>
+        <f>IF(L104="","",(Q104+R104)*$L$36^2/8)</f>
       </c>
       <c r="T104" s="227">
-        <f>IF(L104="","",(Q104+R104)*$L$32/2)</f>
+        <f>IF(L104="","",(Q104+R104)*$L$36/2)</f>
+      </c>
+    </row>
+    <row r="105">
+      <c r="K105" s="237">
+        <v>7</v>
+      </c>
+      <c r="L105" s="227">
+        <f>IF((K105-1)*$L$35&gt;=$L$33,"",MAX($L$33-K105*$L$35,0))</f>
+      </c>
+      <c r="M105" s="227">
+        <f>IF(L105="","",$L$33-(K105-1)*$L$35)</f>
+      </c>
+      <c r="N105" s="227">
+        <f>IF(L105="","",$L$48*$L$29*M105)</f>
+      </c>
+      <c r="O105" s="227">
+        <f>IF(L105="","",$L$48*$L$31)</f>
+      </c>
+      <c r="P105" s="227">
+        <f>IF(L105="","",N105+O105)</f>
+      </c>
+      <c r="Q105" s="227">
+        <f>IF(L105="","",N105*(M105-L105))</f>
+      </c>
+      <c r="R105" s="227">
+        <f>IF(L105="","",O105*(M105-L105))</f>
+      </c>
+      <c r="S105" s="227">
+        <f>IF(L105="","",(Q105+R105)*$L$36^2/8)</f>
+      </c>
+      <c r="T105" s="227">
+        <f>IF(L105="","",(Q105+R105)*$L$36/2)</f>
       </c>
     </row>
     <row r="106">
-      <c r="K106" s="221" t="inlineStr">
+      <c r="K106" s="237">
+        <v>8</v>
+      </c>
+      <c r="L106" s="227">
+        <f>IF((K106-1)*$L$35&gt;=$L$33,"",MAX($L$33-K106*$L$35,0))</f>
+      </c>
+      <c r="M106" s="227">
+        <f>IF(L106="","",$L$33-(K106-1)*$L$35)</f>
+      </c>
+      <c r="N106" s="227">
+        <f>IF(L106="","",$L$48*$L$29*M106)</f>
+      </c>
+      <c r="O106" s="227">
+        <f>IF(L106="","",$L$48*$L$31)</f>
+      </c>
+      <c r="P106" s="227">
+        <f>IF(L106="","",N106+O106)</f>
+      </c>
+      <c r="Q106" s="227">
+        <f>IF(L106="","",N106*(M106-L106))</f>
+      </c>
+      <c r="R106" s="227">
+        <f>IF(L106="","",O106*(M106-L106))</f>
+      </c>
+      <c r="S106" s="227">
+        <f>IF(L106="","",(Q106+R106)*$L$36^2/8)</f>
+      </c>
+      <c r="T106" s="227">
+        <f>IF(L106="","",(Q106+R106)*$L$36/2)</f>
+      </c>
+    </row>
+    <row r="107">
+      <c r="K107" s="237">
+        <v>9</v>
+      </c>
+      <c r="L107" s="227">
+        <f>IF((K107-1)*$L$35&gt;=$L$33,"",MAX($L$33-K107*$L$35,0))</f>
+      </c>
+      <c r="M107" s="227">
+        <f>IF(L107="","",$L$33-(K107-1)*$L$35)</f>
+      </c>
+      <c r="N107" s="227">
+        <f>IF(L107="","",$L$48*$L$29*M107)</f>
+      </c>
+      <c r="O107" s="227">
+        <f>IF(L107="","",$L$48*$L$31)</f>
+      </c>
+      <c r="P107" s="227">
+        <f>IF(L107="","",N107+O107)</f>
+      </c>
+      <c r="Q107" s="227">
+        <f>IF(L107="","",N107*(M107-L107))</f>
+      </c>
+      <c r="R107" s="227">
+        <f>IF(L107="","",O107*(M107-L107))</f>
+      </c>
+      <c r="S107" s="227">
+        <f>IF(L107="","",(Q107+R107)*$L$36^2/8)</f>
+      </c>
+      <c r="T107" s="227">
+        <f>IF(L107="","",(Q107+R107)*$L$36/2)</f>
+      </c>
+    </row>
+    <row r="108">
+      <c r="K108" s="237">
+        <v>10</v>
+      </c>
+      <c r="L108" s="227">
+        <f>IF((K108-1)*$L$35&gt;=$L$33,"",MAX($L$33-K108*$L$35,0))</f>
+      </c>
+      <c r="M108" s="227">
+        <f>IF(L108="","",$L$33-(K108-1)*$L$35)</f>
+      </c>
+      <c r="N108" s="227">
+        <f>IF(L108="","",$L$48*$L$29*M108)</f>
+      </c>
+      <c r="O108" s="227">
+        <f>IF(L108="","",$L$48*$L$31)</f>
+      </c>
+      <c r="P108" s="227">
+        <f>IF(L108="","",N108+O108)</f>
+      </c>
+      <c r="Q108" s="227">
+        <f>IF(L108="","",N108*(M108-L108))</f>
+      </c>
+      <c r="R108" s="227">
+        <f>IF(L108="","",O108*(M108-L108))</f>
+      </c>
+      <c r="S108" s="227">
+        <f>IF(L108="","",(Q108+R108)*$L$36^2/8)</f>
+      </c>
+      <c r="T108" s="227">
+        <f>IF(L108="","",(Q108+R108)*$L$36/2)</f>
+      </c>
+    </row>
+    <row r="110">
+      <c r="K110" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">6 . DIAGRAMAS DE CARGA (atualizam automaticamente)</t>
         </is>
       </c>
-      <c r="L106" s="221"/>
-      <c r="M106" s="221"/>
-      <c r="N106" s="221"/>
-      <c r="O106" s="221"/>
-      <c r="P106" s="221"/>
-      <c r="Q106" s="221"/>
-      <c r="R106" s="221"/>
-      <c r="S106" s="221"/>
-      <c r="T106" s="221"/>
-    </row>
-    <row r="108" ht="75" customHeight="1">
-      <c r="K108" s="220" t="inlineStr">
+      <c r="L110" s="221"/>
+      <c r="M110" s="221"/>
+      <c r="N110" s="221"/>
+      <c r="O110" s="221"/>
+      <c r="P110" s="221"/>
+      <c r="Q110" s="221"/>
+      <c r="R110" s="221"/>
+      <c r="S110" s="221"/>
+      <c r="T110" s="221"/>
+    </row>
+    <row r="112" ht="75" customHeight="1">
+      <c r="K112" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Gráficos de dispersão desenhados a partir da tabela de coordenadas do item 6.1. À esquerda: pilar com a carga trapezoidal (kN/m), a resultante E e as reações. À direita: parede de placas alveolares com a pressão real (vermelho) e a pressão adotada em cada painel (azul, constante = valor da borda inferior). O eixo está em PRESSÃO (kN/m²); os rótulos P1, P2… trazem a CARGA NA PLACA (kN/m) = pressão × bw, a mesma da tabela 5.2 (ex.: 23,75 × 1,25 = 29,69 kN/m de solo e 2,64 × 1,25 = 3,30 kN/m de sobrecarga).</t>
         </is>
       </c>
-      <c r="L108" s="220"/>
-      <c r="M108" s="220"/>
-      <c r="N108" s="220"/>
-      <c r="O108" s="220"/>
-      <c r="P108" s="220"/>
-      <c r="Q108" s="220"/>
-      <c r="R108" s="220"/>
-      <c r="S108" s="220"/>
-      <c r="T108" s="220"/>
-    </row>
-    <row r="139">
-      <c r="K139" s="222" t="inlineStr">
+      <c r="L112" s="220"/>
+      <c r="M112" s="220"/>
+      <c r="N112" s="220"/>
+      <c r="O112" s="220"/>
+      <c r="P112" s="220"/>
+      <c r="Q112" s="220"/>
+      <c r="R112" s="220"/>
+      <c r="S112" s="220"/>
+      <c r="T112" s="220"/>
+    </row>
+    <row r="143">
+      <c r="K143" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">6.1 Coordenadas do desenho (não editar)</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="K140" s="235" t="inlineStr">
+    <row r="144">
+      <c r="K144" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">Série</t>
         </is>
       </c>
-      <c r="L140" s="235" t="inlineStr">
+      <c r="L144" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">x</t>
         </is>
       </c>
-      <c r="M140" s="235" t="inlineStr">
+      <c r="M144" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">y (m)</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="K141" s="237" t="inlineStr">
+    <row r="145">
+      <c r="K145" s="237" t="inlineStr">
         <is>
           <t xml:space="preserve">Pilar</t>
         </is>
       </c>
-      <c r="L141" s="227">
-        <v>0</v>
-      </c>
-      <c r="M141" s="227">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="K142" s="237"/>
-      <c r="L142" s="227">
-        <v>0</v>
-      </c>
-      <c r="M142" s="227">
-        <f>$L$29</f>
-      </c>
-    </row>
-    <row r="143">
-      <c r="K143" s="237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga (kN/m)</t>
-        </is>
-      </c>
-      <c r="L143" s="227">
-        <v>0</v>
-      </c>
-      <c r="M143" s="227">
-        <f>$L$29</f>
-      </c>
-    </row>
-    <row r="144">
-      <c r="K144" s="237"/>
-      <c r="L144" s="227">
-        <f>$L$55</f>
-      </c>
-      <c r="M144" s="227">
-        <f>$L$29</f>
-      </c>
-    </row>
-    <row r="145">
-      <c r="K145" s="237"/>
       <c r="L145" s="227">
-        <f>$L$56</f>
+        <v>0</v>
       </c>
       <c r="M145" s="227">
         <v>0</v>
@@ -15085,42 +15117,38 @@
         <v>0</v>
       </c>
       <c r="M146" s="227">
-        <v>0</v>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="147">
       <c r="K147" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sc | solo</t>
+          <t xml:space="preserve">Carga (kN/m)</t>
         </is>
       </c>
       <c r="L147" s="227">
-        <f>$L$55</f>
+        <v>0</v>
       </c>
       <c r="M147" s="227">
-        <f>$L$29</f>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="148">
       <c r="K148" s="237"/>
       <c r="L148" s="227">
-        <f>$L$55</f>
+        <f>$L$59</f>
       </c>
       <c r="M148" s="227">
-        <v>0</v>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="149">
-      <c r="K149" s="237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">seta</t>
-        </is>
-      </c>
+      <c r="K149" s="237"/>
       <c r="L149" s="227">
-        <f>$L$56-$L$57*1/6</f>
+        <f>$L$60</f>
       </c>
       <c r="M149" s="227">
-        <f>$L$29*1/6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -15129,29 +15157,29 @@
         <v>0</v>
       </c>
       <c r="M150" s="227">
-        <f>$L$29*1/6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="K151" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">seta</t>
+          <t xml:space="preserve">Sc | solo</t>
         </is>
       </c>
       <c r="L151" s="227">
-        <f>$L$56-$L$57*2/6</f>
+        <f>$L$59</f>
       </c>
       <c r="M151" s="227">
-        <f>$L$29*2/6</f>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="152">
       <c r="K152" s="237"/>
       <c r="L152" s="227">
-        <v>0</v>
+        <f>$L$59</f>
       </c>
       <c r="M152" s="227">
-        <f>$L$29*2/6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -15161,10 +15189,10 @@
         </is>
       </c>
       <c r="L153" s="227">
-        <f>$L$56-$L$57*3/6</f>
+        <f>$L$60-$L$61*1/6</f>
       </c>
       <c r="M153" s="227">
-        <f>$L$29*3/6</f>
+        <f>$L$33*1/6</f>
       </c>
     </row>
     <row r="154">
@@ -15173,7 +15201,7 @@
         <v>0</v>
       </c>
       <c r="M154" s="227">
-        <f>$L$29*3/6</f>
+        <f>$L$33*1/6</f>
       </c>
     </row>
     <row r="155">
@@ -15183,10 +15211,10 @@
         </is>
       </c>
       <c r="L155" s="227">
-        <f>$L$56-$L$57*4/6</f>
+        <f>$L$60-$L$61*2/6</f>
       </c>
       <c r="M155" s="227">
-        <f>$L$29*4/6</f>
+        <f>$L$33*2/6</f>
       </c>
     </row>
     <row r="156">
@@ -15195,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="M156" s="227">
-        <f>$L$29*4/6</f>
+        <f>$L$33*2/6</f>
       </c>
     </row>
     <row r="157">
@@ -15205,10 +15233,10 @@
         </is>
       </c>
       <c r="L157" s="227">
-        <f>$L$56-$L$57*5/6</f>
+        <f>$L$60-$L$61*3/6</f>
       </c>
       <c r="M157" s="227">
-        <f>$L$29*5/6</f>
+        <f>$L$33*3/6</f>
       </c>
     </row>
     <row r="158">
@@ -15217,20 +15245,20 @@
         <v>0</v>
       </c>
       <c r="M158" s="227">
-        <f>$L$29*5/6</f>
+        <f>$L$33*3/6</f>
       </c>
     </row>
     <row r="159">
       <c r="K159" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">seta</t>
         </is>
       </c>
       <c r="L159" s="227">
-        <f>MAX($L$55,$L$56)*1.15</f>
+        <f>$L$60-$L$61*4/6</f>
       </c>
       <c r="M159" s="227">
-        <f>$L$61</f>
+        <f>$L$33*4/6</f>
       </c>
     </row>
     <row r="160">
@@ -15239,156 +15267,160 @@
         <v>0</v>
       </c>
       <c r="M160" s="227">
-        <f>$L$61</f>
+        <f>$L$33*4/6</f>
       </c>
     </row>
     <row r="161">
       <c r="K161" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">R,topo</t>
+          <t xml:space="preserve">seta</t>
         </is>
       </c>
       <c r="L161" s="227">
-        <f>IF($L$35="Balanço",NA(),0)</f>
+        <f>$L$60-$L$61*5/6</f>
       </c>
       <c r="M161" s="227">
-        <f>$L$29</f>
+        <f>$L$33*5/6</f>
       </c>
     </row>
     <row r="162">
       <c r="K162" s="237"/>
       <c r="L162" s="227">
-        <f>IF($L$35="Balanço",NA(),-0.35*$L$56)</f>
+        <v>0</v>
       </c>
       <c r="M162" s="227">
-        <f>$L$29</f>
+        <f>$L$33*5/6</f>
       </c>
     </row>
     <row r="163">
       <c r="K163" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">R,base</t>
+          <t xml:space="preserve">E</t>
         </is>
       </c>
       <c r="L163" s="227">
-        <v>0</v>
+        <f>MAX($L$59,$L$60)*1.15</f>
       </c>
       <c r="M163" s="227">
-        <v>0</v>
+        <f>$L$65</f>
       </c>
     </row>
     <row r="164">
       <c r="K164" s="237"/>
       <c r="L164" s="227">
-        <f>-0.35*$L$56</f>
+        <v>0</v>
       </c>
       <c r="M164" s="227">
-        <v>0</v>
+        <f>$L$65</f>
       </c>
     </row>
     <row r="165">
-      <c r="K165" s="237">
-        <f>"p,topo = "&amp;FIXED($L$55,2)&amp;" kN/m"</f>
+      <c r="K165" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,topo</t>
+        </is>
       </c>
       <c r="L165" s="227">
-        <f>$L$55</f>
+        <f>IF($L$39="Balanço",NA(),0)</f>
       </c>
       <c r="M165" s="227">
-        <f>$L$29</f>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="166">
-      <c r="K166" s="237">
-        <f>"p,base = "&amp;FIXED($L$56,2)&amp;" kN/m"</f>
-      </c>
+      <c r="K166" s="237"/>
       <c r="L166" s="227">
-        <f>$L$56</f>
+        <f>IF($L$39="Balanço",NA(),-0.35*$L$60)</f>
       </c>
       <c r="M166" s="227">
-        <v>0</v>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="167">
-      <c r="K167" s="237">
-        <f>"E = "&amp;FIXED($L$59,1)&amp;" kN (y = "&amp;FIXED($L$61,2)&amp;" m)"</f>
+      <c r="K167" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R,base</t>
+        </is>
       </c>
       <c r="L167" s="227">
-        <f>MAX($L$55,$L$56)*1.15</f>
+        <v>0</v>
       </c>
       <c r="M167" s="227">
-        <f>$L$61</f>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
-      <c r="K168" s="237">
-        <f>"R,topo = "&amp;FIXED($L$74,1)&amp;" kN → laje"</f>
-      </c>
+      <c r="K168" s="237"/>
       <c r="L168" s="227">
-        <f>IF($L$35="Balanço",NA(),-0.35*$L$56)</f>
+        <f>-0.35*$L$60</f>
       </c>
       <c r="M168" s="227">
-        <f>$L$29</f>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="K169" s="237">
-        <f>"R,base = "&amp;FIXED($L$75,1)&amp;" kN"</f>
+        <f>"p,topo = "&amp;FIXED($L$59,2)&amp;" kN/m"</f>
       </c>
       <c r="L169" s="227">
-        <f>-0.35*$L$56</f>
+        <f>$L$59</f>
       </c>
       <c r="M169" s="227">
-        <v>0</v>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="170">
-      <c r="K170" s="237" t="inlineStr">
+      <c r="K170" s="237">
+        <f>"p,base = "&amp;FIXED($L$60,2)&amp;" kN/m"</f>
+      </c>
+      <c r="L170" s="227">
+        <f>$L$60</f>
+      </c>
+      <c r="M170" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="K171" s="237">
+        <f>"E = "&amp;FIXED($L$63,1)&amp;" kN (y = "&amp;FIXED($L$65,2)&amp;" m)"</f>
+      </c>
+      <c r="L171" s="227">
+        <f>MAX($L$59,$L$60)*1.15</f>
+      </c>
+      <c r="M171" s="227">
+        <f>$L$65</f>
+      </c>
+    </row>
+    <row r="172">
+      <c r="K172" s="237">
+        <f>"R,topo = "&amp;FIXED($L$78,1)&amp;" kN → laje"</f>
+      </c>
+      <c r="L172" s="227">
+        <f>IF($L$39="Balanço",NA(),-0.35*$L$60)</f>
+      </c>
+      <c r="M172" s="227">
+        <f>$L$33</f>
+      </c>
+    </row>
+    <row r="173">
+      <c r="K173" s="237">
+        <f>"R,base = "&amp;FIXED($L$79,1)&amp;" kN"</f>
+      </c>
+      <c r="L173" s="227">
+        <f>-0.35*$L$60</f>
+      </c>
+      <c r="M173" s="227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="K174" s="237" t="inlineStr">
         <is>
           <t xml:space="preserve">Placas</t>
         </is>
       </c>
-      <c r="L170" s="227">
-        <v>0</v>
-      </c>
-      <c r="M170" s="227">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="K171" s="237"/>
-      <c r="L171" s="227">
-        <v>0</v>
-      </c>
-      <c r="M171" s="227">
-        <f>$L$29</f>
-      </c>
-    </row>
-    <row r="172">
-      <c r="K172" s="237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pressão real</t>
-        </is>
-      </c>
-      <c r="L172" s="227">
-        <v>0</v>
-      </c>
-      <c r="M172" s="227">
-        <f>$L$29</f>
-      </c>
-    </row>
-    <row r="173">
-      <c r="K173" s="237"/>
-      <c r="L173" s="227">
-        <f>$L$47</f>
-      </c>
-      <c r="M173" s="227">
-        <f>$L$29</f>
-      </c>
-    </row>
-    <row r="174">
-      <c r="K174" s="237"/>
       <c r="L174" s="227">
-        <f>$L$48</f>
+        <v>0</v>
       </c>
       <c r="M174" s="227">
         <v>0</v>
@@ -15400,42 +15432,38 @@
         <v>0</v>
       </c>
       <c r="M175" s="227">
-        <v>0</v>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="176">
       <c r="K176" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sc | solo</t>
+          <t xml:space="preserve">Pressão real</t>
         </is>
       </c>
       <c r="L176" s="227">
-        <f>$L$47</f>
+        <v>0</v>
       </c>
       <c r="M176" s="227">
-        <f>$L$29</f>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="177">
       <c r="K177" s="237"/>
       <c r="L177" s="227">
-        <f>$L$47</f>
+        <f>$L$51</f>
       </c>
       <c r="M177" s="227">
-        <v>0</v>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="178">
-      <c r="K178" s="237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">seta</t>
-        </is>
-      </c>
+      <c r="K178" s="237"/>
       <c r="L178" s="227">
-        <f>$L$48-($L$48-$L$47)*1/4</f>
+        <f>$L$52</f>
       </c>
       <c r="M178" s="227">
-        <f>$L$29*1/4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -15444,29 +15472,29 @@
         <v>0</v>
       </c>
       <c r="M179" s="227">
-        <f>$L$29*1/4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="K180" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">seta</t>
+          <t xml:space="preserve">Sc | solo</t>
         </is>
       </c>
       <c r="L180" s="227">
-        <f>$L$48-($L$48-$L$47)*2/4</f>
+        <f>$L$51</f>
       </c>
       <c r="M180" s="227">
-        <f>$L$29*2/4</f>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="181">
       <c r="K181" s="237"/>
       <c r="L181" s="227">
-        <v>0</v>
+        <f>$L$51</f>
       </c>
       <c r="M181" s="227">
-        <f>$L$29*2/4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -15476,10 +15504,10 @@
         </is>
       </c>
       <c r="L182" s="227">
-        <f>$L$48-($L$48-$L$47)*3/4</f>
+        <f>$L$52-($L$52-$L$51)*1/4</f>
       </c>
       <c r="M182" s="227">
-        <f>$L$29*3/4</f>
+        <f>$L$33*1/4</f>
       </c>
     </row>
     <row r="183">
@@ -15488,931 +15516,971 @@
         <v>0</v>
       </c>
       <c r="M183" s="227">
-        <f>$L$29*3/4</f>
+        <f>$L$33*1/4</f>
       </c>
     </row>
     <row r="184">
       <c r="K184" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressão adotada por painel</t>
+          <t xml:space="preserve">seta</t>
         </is>
       </c>
       <c r="L184" s="227">
-        <f>P95</f>
+        <f>$L$52-($L$52-$L$51)*2/4</f>
       </c>
       <c r="M184" s="227">
-        <f>$L$29-M95</f>
+        <f>$L$33*2/4</f>
       </c>
     </row>
     <row r="185">
       <c r="K185" s="237"/>
       <c r="L185" s="227">
-        <f>P95</f>
+        <v>0</v>
       </c>
       <c r="M185" s="227">
-        <f>$L$29-L95</f>
+        <f>$L$33*2/4</f>
       </c>
     </row>
     <row r="186">
-      <c r="K186" s="237"/>
+      <c r="K186" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seta</t>
+        </is>
+      </c>
       <c r="L186" s="227">
-        <f>IF(L96="",L185,P96)</f>
+        <f>$L$52-($L$52-$L$51)*3/4</f>
       </c>
       <c r="M186" s="227">
-        <f>IF(L96="",M185,$L$29-M96)</f>
+        <f>$L$33*3/4</f>
       </c>
     </row>
     <row r="187">
       <c r="K187" s="237"/>
       <c r="L187" s="227">
-        <f>IF(L96="",L186,P96)</f>
+        <v>0</v>
       </c>
       <c r="M187" s="227">
-        <f>IF(L96="",M186,$L$29-L96)</f>
+        <f>$L$33*3/4</f>
       </c>
     </row>
     <row r="188">
-      <c r="K188" s="237"/>
+      <c r="K188" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressão adotada por painel</t>
+        </is>
+      </c>
       <c r="L188" s="227">
-        <f>IF(L97="",L187,P97)</f>
+        <f>P99</f>
       </c>
       <c r="M188" s="227">
-        <f>IF(L97="",M187,$L$29-M97)</f>
+        <f>$L$33-M99</f>
       </c>
     </row>
     <row r="189">
       <c r="K189" s="237"/>
       <c r="L189" s="227">
-        <f>IF(L97="",L188,P97)</f>
+        <f>P99</f>
       </c>
       <c r="M189" s="227">
-        <f>IF(L97="",M188,$L$29-L97)</f>
+        <f>$L$33-L99</f>
       </c>
     </row>
     <row r="190">
       <c r="K190" s="237"/>
       <c r="L190" s="227">
-        <f>IF(L98="",L189,P98)</f>
+        <f>IF(L100="",L189,P100)</f>
       </c>
       <c r="M190" s="227">
-        <f>IF(L98="",M189,$L$29-M98)</f>
+        <f>IF(L100="",M189,$L$33-M100)</f>
       </c>
     </row>
     <row r="191">
       <c r="K191" s="237"/>
       <c r="L191" s="227">
-        <f>IF(L98="",L190,P98)</f>
+        <f>IF(L100="",L190,P100)</f>
       </c>
       <c r="M191" s="227">
-        <f>IF(L98="",M190,$L$29-L98)</f>
+        <f>IF(L100="",M190,$L$33-L100)</f>
       </c>
     </row>
     <row r="192">
       <c r="K192" s="237"/>
       <c r="L192" s="227">
-        <f>IF(L99="",L191,P99)</f>
+        <f>IF(L101="",L191,P101)</f>
       </c>
       <c r="M192" s="227">
-        <f>IF(L99="",M191,$L$29-M99)</f>
+        <f>IF(L101="",M191,$L$33-M101)</f>
       </c>
     </row>
     <row r="193">
       <c r="K193" s="237"/>
       <c r="L193" s="227">
-        <f>IF(L99="",L192,P99)</f>
+        <f>IF(L101="",L192,P101)</f>
       </c>
       <c r="M193" s="227">
-        <f>IF(L99="",M192,$L$29-L99)</f>
+        <f>IF(L101="",M192,$L$33-L101)</f>
       </c>
     </row>
     <row r="194">
       <c r="K194" s="237"/>
       <c r="L194" s="227">
-        <f>IF(L100="",L193,P100)</f>
+        <f>IF(L102="",L193,P102)</f>
       </c>
       <c r="M194" s="227">
-        <f>IF(L100="",M193,$L$29-M100)</f>
+        <f>IF(L102="",M193,$L$33-M102)</f>
       </c>
     </row>
     <row r="195">
       <c r="K195" s="237"/>
       <c r="L195" s="227">
-        <f>IF(L100="",L194,P100)</f>
+        <f>IF(L102="",L194,P102)</f>
       </c>
       <c r="M195" s="227">
-        <f>IF(L100="",M194,$L$29-L100)</f>
+        <f>IF(L102="",M194,$L$33-L102)</f>
       </c>
     </row>
     <row r="196">
       <c r="K196" s="237"/>
       <c r="L196" s="227">
-        <f>IF(L101="",L195,P101)</f>
+        <f>IF(L103="",L195,P103)</f>
       </c>
       <c r="M196" s="227">
-        <f>IF(L101="",M195,$L$29-M101)</f>
+        <f>IF(L103="",M195,$L$33-M103)</f>
       </c>
     </row>
     <row r="197">
       <c r="K197" s="237"/>
       <c r="L197" s="227">
-        <f>IF(L101="",L196,P101)</f>
+        <f>IF(L103="",L196,P103)</f>
       </c>
       <c r="M197" s="227">
-        <f>IF(L101="",M196,$L$29-L101)</f>
+        <f>IF(L103="",M196,$L$33-L103)</f>
       </c>
     </row>
     <row r="198">
       <c r="K198" s="237"/>
       <c r="L198" s="227">
-        <f>IF(L102="",L197,P102)</f>
+        <f>IF(L104="",L197,P104)</f>
       </c>
       <c r="M198" s="227">
-        <f>IF(L102="",M197,$L$29-M102)</f>
+        <f>IF(L104="",M197,$L$33-M104)</f>
       </c>
     </row>
     <row r="199">
       <c r="K199" s="237"/>
       <c r="L199" s="227">
-        <f>IF(L102="",L198,P102)</f>
+        <f>IF(L104="",L198,P104)</f>
       </c>
       <c r="M199" s="227">
-        <f>IF(L102="",M198,$L$29-L102)</f>
+        <f>IF(L104="",M198,$L$33-L104)</f>
       </c>
     </row>
     <row r="200">
       <c r="K200" s="237"/>
       <c r="L200" s="227">
-        <f>IF(L103="",L199,P103)</f>
+        <f>IF(L105="",L199,P105)</f>
       </c>
       <c r="M200" s="227">
-        <f>IF(L103="",M199,$L$29-M103)</f>
+        <f>IF(L105="",M199,$L$33-M105)</f>
       </c>
     </row>
     <row r="201">
       <c r="K201" s="237"/>
       <c r="L201" s="227">
-        <f>IF(L103="",L200,P103)</f>
+        <f>IF(L105="",L200,P105)</f>
       </c>
       <c r="M201" s="227">
-        <f>IF(L103="",M200,$L$29-L103)</f>
+        <f>IF(L105="",M200,$L$33-L105)</f>
       </c>
     </row>
     <row r="202">
       <c r="K202" s="237"/>
       <c r="L202" s="227">
-        <f>IF(L104="",L201,P104)</f>
+        <f>IF(L106="",L201,P106)</f>
       </c>
       <c r="M202" s="227">
-        <f>IF(L104="",M201,$L$29-M104)</f>
+        <f>IF(L106="",M201,$L$33-M106)</f>
       </c>
     </row>
     <row r="203">
       <c r="K203" s="237"/>
       <c r="L203" s="227">
-        <f>IF(L104="",L202,P104)</f>
+        <f>IF(L106="",L202,P106)</f>
       </c>
       <c r="M203" s="227">
-        <f>IF(L104="",M202,$L$29-L104)</f>
+        <f>IF(L106="",M202,$L$33-L106)</f>
       </c>
     </row>
     <row r="204">
-      <c r="K204" s="237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">junta 1</t>
-        </is>
-      </c>
+      <c r="K204" s="237"/>
       <c r="L204" s="227">
-        <f>IF($L$31*1&lt;$L$29,0,NA())</f>
+        <f>IF(L107="",L203,P107)</f>
       </c>
       <c r="M204" s="227">
-        <f>$L$31*1</f>
+        <f>IF(L107="",M203,$L$33-M107)</f>
       </c>
     </row>
     <row r="205">
       <c r="K205" s="237"/>
       <c r="L205" s="227">
-        <f>IF($L$31*1&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF(L107="",L204,P107)</f>
       </c>
       <c r="M205" s="227">
-        <f>$L$31*1</f>
+        <f>IF(L107="",M204,$L$33-L107)</f>
       </c>
     </row>
     <row r="206">
-      <c r="K206" s="237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">junta 2</t>
-        </is>
-      </c>
+      <c r="K206" s="237"/>
       <c r="L206" s="227">
-        <f>IF($L$31*2&lt;$L$29,0,NA())</f>
+        <f>IF(L108="",L205,P108)</f>
       </c>
       <c r="M206" s="227">
-        <f>$L$31*2</f>
+        <f>IF(L108="",M205,$L$33-M108)</f>
       </c>
     </row>
     <row r="207">
       <c r="K207" s="237"/>
       <c r="L207" s="227">
-        <f>IF($L$31*2&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF(L108="",L206,P108)</f>
       </c>
       <c r="M207" s="227">
-        <f>$L$31*2</f>
+        <f>IF(L108="",M206,$L$33-L108)</f>
       </c>
     </row>
     <row r="208">
       <c r="K208" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">junta 3</t>
+          <t xml:space="preserve">junta 1</t>
         </is>
       </c>
       <c r="L208" s="227">
-        <f>IF($L$31*3&lt;$L$29,0,NA())</f>
+        <f>IF($L$35*1&lt;$L$33,0,NA())</f>
       </c>
       <c r="M208" s="227">
-        <f>$L$31*3</f>
+        <f>$L$35*1</f>
       </c>
     </row>
     <row r="209">
       <c r="K209" s="237"/>
       <c r="L209" s="227">
-        <f>IF($L$31*3&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF($L$35*1&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M209" s="227">
-        <f>$L$31*3</f>
+        <f>$L$35*1</f>
       </c>
     </row>
     <row r="210">
       <c r="K210" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">junta 4</t>
+          <t xml:space="preserve">junta 2</t>
         </is>
       </c>
       <c r="L210" s="227">
-        <f>IF($L$31*4&lt;$L$29,0,NA())</f>
+        <f>IF($L$35*2&lt;$L$33,0,NA())</f>
       </c>
       <c r="M210" s="227">
-        <f>$L$31*4</f>
+        <f>$L$35*2</f>
       </c>
     </row>
     <row r="211">
       <c r="K211" s="237"/>
       <c r="L211" s="227">
-        <f>IF($L$31*4&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF($L$35*2&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M211" s="227">
-        <f>$L$31*4</f>
+        <f>$L$35*2</f>
       </c>
     </row>
     <row r="212">
       <c r="K212" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">junta 5</t>
+          <t xml:space="preserve">junta 3</t>
         </is>
       </c>
       <c r="L212" s="227">
-        <f>IF($L$31*5&lt;$L$29,0,NA())</f>
+        <f>IF($L$35*3&lt;$L$33,0,NA())</f>
       </c>
       <c r="M212" s="227">
-        <f>$L$31*5</f>
+        <f>$L$35*3</f>
       </c>
     </row>
     <row r="213">
       <c r="K213" s="237"/>
       <c r="L213" s="227">
-        <f>IF($L$31*5&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF($L$35*3&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M213" s="227">
-        <f>$L$31*5</f>
+        <f>$L$35*3</f>
       </c>
     </row>
     <row r="214">
       <c r="K214" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">junta 6</t>
+          <t xml:space="preserve">junta 4</t>
         </is>
       </c>
       <c r="L214" s="227">
-        <f>IF($L$31*6&lt;$L$29,0,NA())</f>
+        <f>IF($L$35*4&lt;$L$33,0,NA())</f>
       </c>
       <c r="M214" s="227">
-        <f>$L$31*6</f>
+        <f>$L$35*4</f>
       </c>
     </row>
     <row r="215">
       <c r="K215" s="237"/>
       <c r="L215" s="227">
-        <f>IF($L$31*6&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF($L$35*4&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M215" s="227">
-        <f>$L$31*6</f>
+        <f>$L$35*4</f>
       </c>
     </row>
     <row r="216">
       <c r="K216" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">junta 7</t>
+          <t xml:space="preserve">junta 5</t>
         </is>
       </c>
       <c r="L216" s="227">
-        <f>IF($L$31*7&lt;$L$29,0,NA())</f>
+        <f>IF($L$35*5&lt;$L$33,0,NA())</f>
       </c>
       <c r="M216" s="227">
-        <f>$L$31*7</f>
+        <f>$L$35*5</f>
       </c>
     </row>
     <row r="217">
       <c r="K217" s="237"/>
       <c r="L217" s="227">
-        <f>IF($L$31*7&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF($L$35*5&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M217" s="227">
-        <f>$L$31*7</f>
+        <f>$L$35*5</f>
       </c>
     </row>
     <row r="218">
       <c r="K218" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">junta 8</t>
+          <t xml:space="preserve">junta 6</t>
         </is>
       </c>
       <c r="L218" s="227">
-        <f>IF($L$31*8&lt;$L$29,0,NA())</f>
+        <f>IF($L$35*6&lt;$L$33,0,NA())</f>
       </c>
       <c r="M218" s="227">
-        <f>$L$31*8</f>
+        <f>$L$35*6</f>
       </c>
     </row>
     <row r="219">
       <c r="K219" s="237"/>
       <c r="L219" s="227">
-        <f>IF($L$31*8&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF($L$35*6&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M219" s="227">
-        <f>$L$31*8</f>
+        <f>$L$35*6</f>
       </c>
     </row>
     <row r="220">
       <c r="K220" s="237" t="inlineStr">
         <is>
-          <t xml:space="preserve">junta 9</t>
+          <t xml:space="preserve">junta 7</t>
         </is>
       </c>
       <c r="L220" s="227">
-        <f>IF($L$31*9&lt;$L$29,0,NA())</f>
+        <f>IF($L$35*7&lt;$L$33,0,NA())</f>
       </c>
       <c r="M220" s="227">
-        <f>$L$31*9</f>
+        <f>$L$35*7</f>
       </c>
     </row>
     <row r="221">
       <c r="K221" s="237"/>
       <c r="L221" s="227">
-        <f>IF($L$31*9&lt;$L$29,$L$48*1.05,NA())</f>
+        <f>IF($L$35*7&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M221" s="227">
-        <f>$L$31*9</f>
+        <f>$L$35*7</f>
       </c>
     </row>
     <row r="222">
-      <c r="K222" s="237">
-        <f>"σq = "&amp;FIXED($L$47,2)&amp;" kN/m² (Sc)"</f>
+      <c r="K222" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 8</t>
+        </is>
       </c>
       <c r="L222" s="227">
-        <f>$L$47</f>
+        <f>IF($L$35*8&lt;$L$33,0,NA())</f>
       </c>
       <c r="M222" s="227">
-        <f>$L$29</f>
+        <f>$L$35*8</f>
       </c>
     </row>
     <row r="223">
-      <c r="K223" s="237">
-        <f>"σ,base = "&amp;FIXED($L$48,2)&amp;" kN/m² = solo "&amp;FIXED($L$49,2)&amp;" + Sc "&amp;FIXED($L$47,2)</f>
-      </c>
+      <c r="K223" s="237"/>
       <c r="L223" s="227">
-        <f>$L$48</f>
+        <f>IF($L$35*8&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M223" s="227">
-        <v>0</v>
+        <f>$L$35*8</f>
       </c>
     </row>
     <row r="224">
-      <c r="K224" s="237">
-        <f>IF(L95="","","P1: g = "&amp;FIXED(Q95,2)&amp;" | q = "&amp;FIXED(R95,2)&amp;" kN/m")</f>
+      <c r="K224" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">junta 9</t>
+        </is>
       </c>
       <c r="L224" s="227">
-        <f>IF(L95="",NA(),P95)</f>
+        <f>IF($L$35*9&lt;$L$33,0,NA())</f>
       </c>
       <c r="M224" s="227">
-        <f>IF(L95="",NA(),$L$29-(L95+M95)/2)</f>
+        <f>$L$35*9</f>
       </c>
     </row>
     <row r="225">
-      <c r="K225" s="237">
-        <f>IF(L96="","","P2: g = "&amp;FIXED(Q96,2)&amp;" | q = "&amp;FIXED(R96,2)&amp;" kN/m")</f>
-      </c>
+      <c r="K225" s="237"/>
       <c r="L225" s="227">
-        <f>IF(L96="",NA(),P96)</f>
+        <f>IF($L$35*9&lt;$L$33,$L$52*1.05,NA())</f>
       </c>
       <c r="M225" s="227">
-        <f>IF(L96="",NA(),$L$29-(L96+M96)/2)</f>
+        <f>$L$35*9</f>
       </c>
     </row>
     <row r="226">
       <c r="K226" s="237">
-        <f>IF(L97="","","P3: g = "&amp;FIXED(Q97,2)&amp;" | q = "&amp;FIXED(R97,2)&amp;" kN/m")</f>
+        <f>"σq = "&amp;FIXED($L$51,2)&amp;" kN/m² (Sc)"</f>
       </c>
       <c r="L226" s="227">
-        <f>IF(L97="",NA(),P97)</f>
+        <f>$L$51</f>
       </c>
       <c r="M226" s="227">
-        <f>IF(L97="",NA(),$L$29-(L97+M97)/2)</f>
+        <f>$L$33</f>
       </c>
     </row>
     <row r="227">
       <c r="K227" s="237">
-        <f>IF(L98="","","P4: g = "&amp;FIXED(Q98,2)&amp;" | q = "&amp;FIXED(R98,2)&amp;" kN/m")</f>
+        <f>"σ,base = "&amp;FIXED($L$52,2)&amp;" kN/m² = solo "&amp;FIXED($L$53,2)&amp;" + Sc "&amp;FIXED($L$51,2)</f>
       </c>
       <c r="L227" s="227">
-        <f>IF(L98="",NA(),P98)</f>
+        <f>$L$52</f>
       </c>
       <c r="M227" s="227">
-        <f>IF(L98="",NA(),$L$29-(L98+M98)/2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="K228" s="237">
-        <f>IF(L99="","","P5: g = "&amp;FIXED(Q99,2)&amp;" | q = "&amp;FIXED(R99,2)&amp;" kN/m")</f>
+        <f>IF(L99="","","P1: g = "&amp;FIXED(Q99,2)&amp;" | q = "&amp;FIXED(R99,2)&amp;" kN/m")</f>
       </c>
       <c r="L228" s="227">
         <f>IF(L99="",NA(),P99)</f>
       </c>
       <c r="M228" s="227">
-        <f>IF(L99="",NA(),$L$29-(L99+M99)/2)</f>
+        <f>IF(L99="",NA(),$L$33-(L99+M99)/2)</f>
       </c>
     </row>
     <row r="229">
       <c r="K229" s="237">
-        <f>IF(L100="","","P6: g = "&amp;FIXED(Q100,2)&amp;" | q = "&amp;FIXED(R100,2)&amp;" kN/m")</f>
+        <f>IF(L100="","","P2: g = "&amp;FIXED(Q100,2)&amp;" | q = "&amp;FIXED(R100,2)&amp;" kN/m")</f>
       </c>
       <c r="L229" s="227">
         <f>IF(L100="",NA(),P100)</f>
       </c>
       <c r="M229" s="227">
-        <f>IF(L100="",NA(),$L$29-(L100+M100)/2)</f>
+        <f>IF(L100="",NA(),$L$33-(L100+M100)/2)</f>
       </c>
     </row>
     <row r="230">
       <c r="K230" s="237">
-        <f>IF(L101="","","P7: g = "&amp;FIXED(Q101,2)&amp;" | q = "&amp;FIXED(R101,2)&amp;" kN/m")</f>
+        <f>IF(L101="","","P3: g = "&amp;FIXED(Q101,2)&amp;" | q = "&amp;FIXED(R101,2)&amp;" kN/m")</f>
       </c>
       <c r="L230" s="227">
         <f>IF(L101="",NA(),P101)</f>
       </c>
       <c r="M230" s="227">
-        <f>IF(L101="",NA(),$L$29-(L101+M101)/2)</f>
+        <f>IF(L101="",NA(),$L$33-(L101+M101)/2)</f>
       </c>
     </row>
     <row r="231">
       <c r="K231" s="237">
-        <f>IF(L102="","","P8: g = "&amp;FIXED(Q102,2)&amp;" | q = "&amp;FIXED(R102,2)&amp;" kN/m")</f>
+        <f>IF(L102="","","P4: g = "&amp;FIXED(Q102,2)&amp;" | q = "&amp;FIXED(R102,2)&amp;" kN/m")</f>
       </c>
       <c r="L231" s="227">
         <f>IF(L102="",NA(),P102)</f>
       </c>
       <c r="M231" s="227">
-        <f>IF(L102="",NA(),$L$29-(L102+M102)/2)</f>
+        <f>IF(L102="",NA(),$L$33-(L102+M102)/2)</f>
       </c>
     </row>
     <row r="232">
       <c r="K232" s="237">
-        <f>IF(L103="","","P9: g = "&amp;FIXED(Q103,2)&amp;" | q = "&amp;FIXED(R103,2)&amp;" kN/m")</f>
+        <f>IF(L103="","","P5: g = "&amp;FIXED(Q103,2)&amp;" | q = "&amp;FIXED(R103,2)&amp;" kN/m")</f>
       </c>
       <c r="L232" s="227">
         <f>IF(L103="",NA(),P103)</f>
       </c>
       <c r="M232" s="227">
-        <f>IF(L103="",NA(),$L$29-(L103+M103)/2)</f>
+        <f>IF(L103="",NA(),$L$33-(L103+M103)/2)</f>
       </c>
     </row>
     <row r="233">
       <c r="K233" s="237">
-        <f>IF(L104="","","P10: g = "&amp;FIXED(Q104,2)&amp;" | q = "&amp;FIXED(R104,2)&amp;" kN/m")</f>
+        <f>IF(L104="","","P6: g = "&amp;FIXED(Q104,2)&amp;" | q = "&amp;FIXED(R104,2)&amp;" kN/m")</f>
       </c>
       <c r="L233" s="227">
         <f>IF(L104="",NA(),P104)</f>
       </c>
       <c r="M233" s="227">
-        <f>IF(L104="",NA(),$L$29-(L104+M104)/2)</f>
+        <f>IF(L104="",NA(),$L$33-(L104+M104)/2)</f>
+      </c>
+    </row>
+    <row r="234">
+      <c r="K234" s="237">
+        <f>IF(L105="","","P7: g = "&amp;FIXED(Q105,2)&amp;" | q = "&amp;FIXED(R105,2)&amp;" kN/m")</f>
+      </c>
+      <c r="L234" s="227">
+        <f>IF(L105="",NA(),P105)</f>
+      </c>
+      <c r="M234" s="227">
+        <f>IF(L105="",NA(),$L$33-(L105+M105)/2)</f>
       </c>
     </row>
     <row r="235">
-      <c r="K235" s="221" t="inlineStr">
+      <c r="K235" s="237">
+        <f>IF(L106="","","P8: g = "&amp;FIXED(Q106,2)&amp;" | q = "&amp;FIXED(R106,2)&amp;" kN/m")</f>
+      </c>
+      <c r="L235" s="227">
+        <f>IF(L106="",NA(),P106)</f>
+      </c>
+      <c r="M235" s="227">
+        <f>IF(L106="",NA(),$L$33-(L106+M106)/2)</f>
+      </c>
+    </row>
+    <row r="236">
+      <c r="K236" s="237">
+        <f>IF(L107="","","P9: g = "&amp;FIXED(Q107,2)&amp;" | q = "&amp;FIXED(R107,2)&amp;" kN/m")</f>
+      </c>
+      <c r="L236" s="227">
+        <f>IF(L107="",NA(),P107)</f>
+      </c>
+      <c r="M236" s="227">
+        <f>IF(L107="",NA(),$L$33-(L107+M107)/2)</f>
+      </c>
+    </row>
+    <row r="237">
+      <c r="K237" s="237">
+        <f>IF(L108="","","P10: g = "&amp;FIXED(Q108,2)&amp;" | q = "&amp;FIXED(R108,2)&amp;" kN/m")</f>
+      </c>
+      <c r="L237" s="227">
+        <f>IF(L108="",NA(),P108)</f>
+      </c>
+      <c r="M237" s="227">
+        <f>IF(L108="",NA(),$L$33-(L108+M108)/2)</f>
+      </c>
+    </row>
+    <row r="239">
+      <c r="K239" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">7 . CONFERÊNCIA DA ABA MURO DE ARRIMO</t>
         </is>
       </c>
-      <c r="L235" s="221"/>
-      <c r="M235" s="221"/>
-      <c r="N235" s="221"/>
-      <c r="O235" s="221"/>
-      <c r="P235" s="221"/>
-      <c r="Q235" s="221"/>
-      <c r="R235" s="221"/>
-      <c r="S235" s="221"/>
-      <c r="T235" s="221"/>
-    </row>
-    <row r="237" ht="18" customHeight="1">
-      <c r="K237" s="220" t="inlineStr">
+      <c r="L239" s="221"/>
+      <c r="M239" s="221"/>
+      <c r="N239" s="221"/>
+      <c r="O239" s="221"/>
+      <c r="P239" s="221"/>
+      <c r="Q239" s="221"/>
+      <c r="R239" s="221"/>
+      <c r="S239" s="221"/>
+      <c r="T239" s="221"/>
+    </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="K241" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Pontos encontrados na aba original (nada foi alterado nela). Esta aba já calcula tudo corrigido.</t>
         </is>
       </c>
-      <c r="L237" s="220"/>
-      <c r="M237" s="220"/>
-      <c r="N237" s="220"/>
-      <c r="O237" s="220"/>
-      <c r="P237" s="220"/>
-      <c r="Q237" s="220"/>
-      <c r="R237" s="220"/>
-      <c r="S237" s="220"/>
-      <c r="T237" s="220"/>
-    </row>
-    <row r="238">
-      <c r="K238" s="222" t="inlineStr">
+      <c r="L241" s="220"/>
+      <c r="M241" s="220"/>
+      <c r="N241" s="220"/>
+      <c r="O241" s="220"/>
+      <c r="P241" s="220"/>
+      <c r="Q241" s="220"/>
+      <c r="R241" s="220"/>
+      <c r="S241" s="220"/>
+      <c r="T241" s="220"/>
+    </row>
+    <row r="242">
+      <c r="K242" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">7.1 Região L2:X40 (a que você usa)</t>
         </is>
       </c>
-    </row>
-    <row r="239" ht="17" customHeight="1">
-      <c r="K239" s="238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M11:M12</t>
-        </is>
-      </c>
-      <c r="L239" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#REF! – referência apagada. São cópias antigas de M22/M23 (corretas). Podem ser apagadas.</t>
-        </is>
-      </c>
-      <c r="M239" s="239"/>
-      <c r="N239" s="239"/>
-      <c r="O239" s="239"/>
-      <c r="P239" s="239"/>
-      <c r="Q239" s="239"/>
-      <c r="R239" s="239"/>
-      <c r="S239" s="239"/>
-      <c r="T239" s="239"/>
-    </row>
-    <row r="240" ht="32" customHeight="1">
-      <c r="K240" s="238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M22:M26</t>
-        </is>
-      </c>
-      <c r="L240" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga no pilar só com o solo, sem a sobrecarga Sc (M30/M31 já incluem). Aqui: E (com Sc) e E,solo (sem Sc) – item 3.2.</t>
-        </is>
-      </c>
-      <c r="M240" s="239"/>
-      <c r="N240" s="239"/>
-      <c r="O240" s="239"/>
-      <c r="P240" s="239"/>
-      <c r="Q240" s="239"/>
-      <c r="R240" s="239"/>
-      <c r="S240" s="239"/>
-      <c r="T240" s="239"/>
-    </row>
-    <row r="241" ht="17" customHeight="1">
-      <c r="K241" s="238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M26</t>
-        </is>
-      </c>
-      <c r="L241" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Momento sem unidade: o resultado é em tf·m (base do pilar em balanço, sem Sc).</t>
-        </is>
-      </c>
-      <c r="M241" s="239"/>
-      <c r="N241" s="239"/>
-      <c r="O241" s="239"/>
-      <c r="P241" s="239"/>
-      <c r="Q241" s="239"/>
-      <c r="R241" s="239"/>
-      <c r="S241" s="239"/>
-      <c r="T241" s="239"/>
-    </row>
-    <row r="242" ht="17" customHeight="1">
-      <c r="K242" s="238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M28</t>
-        </is>
-      </c>
-      <c r="L242" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M25·M24/M27 com M27 = M25 → sempre igual a M24 (redundante, não é erro).</t>
-        </is>
-      </c>
-      <c r="M242" s="239"/>
-      <c r="N242" s="239"/>
-      <c r="O242" s="239"/>
-      <c r="P242" s="239"/>
-      <c r="Q242" s="239"/>
-      <c r="R242" s="239"/>
-      <c r="S242" s="239"/>
-      <c r="T242" s="239"/>
     </row>
     <row r="243" ht="17" customHeight="1">
       <c r="K243" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">M34</t>
-        </is>
-      </c>
-      <c r="L243" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Só vale na cota 0 (usa H² na parcela uniforme). M36 é a fórmula certa para qualquer cota.</t>
-        </is>
-      </c>
-      <c r="M243" s="239"/>
-      <c r="N243" s="239"/>
-      <c r="O243" s="239"/>
-      <c r="P243" s="239"/>
-      <c r="Q243" s="239"/>
-      <c r="R243" s="239"/>
-      <c r="S243" s="239"/>
-      <c r="T243" s="239"/>
+          <t xml:space="preserve">M11:M12</t>
+        </is>
+      </c>
+      <c r="L243" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#REF! – referência apagada. São cópias antigas de M22/M23 (corretas). Podem ser apagadas.</t>
+        </is>
+      </c>
+      <c r="M243" s="241"/>
+      <c r="N243" s="241"/>
+      <c r="O243" s="241"/>
+      <c r="P243" s="241"/>
+      <c r="Q243" s="241"/>
+      <c r="R243" s="241"/>
+      <c r="S243" s="241"/>
+      <c r="T243" s="241"/>
     </row>
     <row r="244" ht="32" customHeight="1">
       <c r="K244" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">M40</t>
-        </is>
-      </c>
-      <c r="L244" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'Biapoiado' é na verdade engastado na base e apoiado no topo. Certo na cota 0 (−78,15 kN·m); para cota ≠ 0 os termos em x estão com sinal trocado e x²·Δp/2 aparece duplicado. Corrigido no item 4.1.</t>
-        </is>
-      </c>
-      <c r="M244" s="239"/>
-      <c r="N244" s="239"/>
-      <c r="O244" s="239"/>
-      <c r="P244" s="239"/>
-      <c r="Q244" s="239"/>
-      <c r="R244" s="239"/>
-      <c r="S244" s="239"/>
-      <c r="T244" s="239"/>
+          <t xml:space="preserve">M22:M26</t>
+        </is>
+      </c>
+      <c r="L244" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga no pilar só com o solo, sem a sobrecarga Sc (M30/M31 já incluem). Aqui: E (com Sc) e E,solo (sem Sc) – item 3.2.</t>
+        </is>
+      </c>
+      <c r="M244" s="241"/>
+      <c r="N244" s="241"/>
+      <c r="O244" s="241"/>
+      <c r="P244" s="241"/>
+      <c r="Q244" s="241"/>
+      <c r="R244" s="241"/>
+      <c r="S244" s="241"/>
+      <c r="T244" s="241"/>
     </row>
     <row r="245" ht="17" customHeight="1">
       <c r="K245" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">P22:R27</t>
-        </is>
-      </c>
-      <c r="L245" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Laje alveolar correta para o painel inferior (pressão na base × bw). O item 5 detalha todos os painéis.</t>
-        </is>
-      </c>
-      <c r="M245" s="239"/>
-      <c r="N245" s="239"/>
-      <c r="O245" s="239"/>
-      <c r="P245" s="239"/>
-      <c r="Q245" s="239"/>
-      <c r="R245" s="239"/>
-      <c r="S245" s="239"/>
-      <c r="T245" s="239"/>
+          <t xml:space="preserve">M26</t>
+        </is>
+      </c>
+      <c r="L245" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento sem unidade: o resultado é em tf·m (base do pilar em balanço, sem Sc).</t>
+        </is>
+      </c>
+      <c r="M245" s="241"/>
+      <c r="N245" s="241"/>
+      <c r="O245" s="241"/>
+      <c r="P245" s="241"/>
+      <c r="Q245" s="241"/>
+      <c r="R245" s="241"/>
+      <c r="S245" s="241"/>
+      <c r="T245" s="241"/>
     </row>
     <row r="246" ht="17" customHeight="1">
       <c r="K246" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">M24</t>
-        </is>
-      </c>
-      <c r="L246" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN → tf por ×0,1 (1 tf = 9,81 kN) fica ~2% abaixo do exato; mantido por ser a convenção usual.</t>
-        </is>
-      </c>
-      <c r="M246" s="239"/>
-      <c r="N246" s="239"/>
-      <c r="O246" s="239"/>
-      <c r="P246" s="239"/>
-      <c r="Q246" s="239"/>
-      <c r="R246" s="239"/>
-      <c r="S246" s="239"/>
-      <c r="T246" s="239"/>
-    </row>
-    <row r="247" ht="32" customHeight="1">
+          <t xml:space="preserve">M28</t>
+        </is>
+      </c>
+      <c r="L246" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M25·M24/M27 com M27 = M25 → sempre igual a M24 (redundante, não é erro).</t>
+        </is>
+      </c>
+      <c r="M246" s="241"/>
+      <c r="N246" s="241"/>
+      <c r="O246" s="241"/>
+      <c r="P246" s="241"/>
+      <c r="Q246" s="241"/>
+      <c r="R246" s="241"/>
+      <c r="S246" s="241"/>
+      <c r="T246" s="241"/>
+    </row>
+    <row r="247" ht="17" customHeight="1">
       <c r="K247" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">M8</t>
-        </is>
-      </c>
-      <c r="L247" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pilar travado no topo quase não se desloca: empuxo em repouso (K0) é mais realista que o ativo. Para φ = 18°: Ka = 0,53 e K0 = 0,69 (+31%). Use a entrada Empuxo (item 1.3).</t>
-        </is>
-      </c>
-      <c r="M247" s="239"/>
-      <c r="N247" s="239"/>
-      <c r="O247" s="239"/>
-      <c r="P247" s="239"/>
-      <c r="Q247" s="239"/>
-      <c r="R247" s="239"/>
-      <c r="S247" s="239"/>
-      <c r="T247" s="239"/>
-    </row>
-    <row r="248">
-      <c r="K248" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.2 Restante da aba (colunas A–C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="32" customHeight="1">
+          <t xml:space="preserve">M34</t>
+        </is>
+      </c>
+      <c r="L247" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Só vale na cota 0 (usa H² na parcela uniforme). M36 é a fórmula certa para qualquer cota.</t>
+        </is>
+      </c>
+      <c r="M247" s="241"/>
+      <c r="N247" s="241"/>
+      <c r="O247" s="241"/>
+      <c r="P247" s="241"/>
+      <c r="Q247" s="241"/>
+      <c r="R247" s="241"/>
+      <c r="S247" s="241"/>
+      <c r="T247" s="241"/>
+    </row>
+    <row r="248" ht="32" customHeight="1">
+      <c r="K248" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M40</t>
+        </is>
+      </c>
+      <c r="L248" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Biapoiado' é na verdade engastado na base e apoiado no topo. Certo na cota 0 (−78,15 kN·m); para cota ≠ 0 os termos em x estão com sinal trocado e x²·Δp/2 aparece duplicado. Corrigido no item 4.1.</t>
+        </is>
+      </c>
+      <c r="M248" s="241"/>
+      <c r="N248" s="241"/>
+      <c r="O248" s="241"/>
+      <c r="P248" s="241"/>
+      <c r="Q248" s="241"/>
+      <c r="R248" s="241"/>
+      <c r="S248" s="241"/>
+      <c r="T248" s="241"/>
+    </row>
+    <row r="249" ht="17" customHeight="1">
       <c r="K249" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">B20 / B28</t>
-        </is>
-      </c>
-      <c r="L249" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#NUM! e #DIV/0!: a alvenaria pede 3,43 cm²/m e Ø8 em todo furo dá só 2,51 cm²/m → espaçamento '0 furos' e divisão por zero. Na prática: Ø8 não basta, usar Ø10 em todo furo (3,93 cm²/m).</t>
-        </is>
-      </c>
-      <c r="M249" s="239"/>
-      <c r="N249" s="239"/>
-      <c r="O249" s="239"/>
-      <c r="P249" s="239"/>
-      <c r="Q249" s="239"/>
-      <c r="R249" s="239"/>
-      <c r="S249" s="239"/>
-      <c r="T249" s="239"/>
+          <t xml:space="preserve">P22:R27</t>
+        </is>
+      </c>
+      <c r="L249" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laje alveolar correta para o painel inferior (pressão na base × bw). O item 5 detalha todos os painéis.</t>
+        </is>
+      </c>
+      <c r="M249" s="241"/>
+      <c r="N249" s="241"/>
+      <c r="O249" s="241"/>
+      <c r="P249" s="241"/>
+      <c r="Q249" s="241"/>
+      <c r="R249" s="241"/>
+      <c r="S249" s="241"/>
+      <c r="T249" s="241"/>
     </row>
     <row r="250" ht="17" customHeight="1">
       <c r="K250" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8 / B9</t>
-        </is>
-      </c>
-      <c r="L250" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coesão e φ dão 0: NSPT (B4) = 0 não existe na tabela DADOS DO SOLO. Sem efeito, pois o Ka de B33 é digitado.</t>
-        </is>
-      </c>
-      <c r="M250" s="239"/>
-      <c r="N250" s="239"/>
-      <c r="O250" s="239"/>
-      <c r="P250" s="239"/>
-      <c r="Q250" s="239"/>
-      <c r="R250" s="239"/>
-      <c r="S250" s="239"/>
-      <c r="T250" s="239"/>
+          <t xml:space="preserve">M24</t>
+        </is>
+      </c>
+      <c r="L250" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN → tf por ×0,1 (1 tf = 9,81 kN) fica ~2% abaixo do exato; mantido por ser a convenção usual.</t>
+        </is>
+      </c>
+      <c r="M250" s="241"/>
+      <c r="N250" s="241"/>
+      <c r="O250" s="241"/>
+      <c r="P250" s="241"/>
+      <c r="Q250" s="241"/>
+      <c r="R250" s="241"/>
+      <c r="S250" s="241"/>
+      <c r="T250" s="241"/>
     </row>
     <row r="251" ht="32" customHeight="1">
       <c r="K251" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">B33</t>
-        </is>
-      </c>
-      <c r="L251" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ka = 0,36 digitado, sem ligação com φ. A aba usa 3 valores diferentes: 0,36 (B33), 0,528 (M8) e 0,75 (CÁLCULO FECHAMENTO).</t>
-        </is>
-      </c>
-      <c r="M251" s="239"/>
-      <c r="N251" s="239"/>
-      <c r="O251" s="239"/>
-      <c r="P251" s="239"/>
-      <c r="Q251" s="239"/>
-      <c r="R251" s="239"/>
-      <c r="S251" s="239"/>
-      <c r="T251" s="239"/>
-    </row>
-    <row r="252" ht="32" customHeight="1">
-      <c r="K252" s="238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B24</t>
-        </is>
-      </c>
-      <c r="L252" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Esbeltez do pilar usa a altura da alvenaria (1,75 m) em vez da do pilar (3,85 m). Com 3,85 m dá ≈ 25,7 &lt; 30 → segue 'Sim', por acaso.</t>
-        </is>
-      </c>
-      <c r="M252" s="239"/>
-      <c r="N252" s="239"/>
-      <c r="O252" s="239"/>
-      <c r="P252" s="239"/>
-      <c r="Q252" s="239"/>
-      <c r="R252" s="239"/>
-      <c r="S252" s="239"/>
-      <c r="T252" s="239"/>
+          <t xml:space="preserve">M8</t>
+        </is>
+      </c>
+      <c r="L251" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar travado no topo quase não se desloca: empuxo em repouso (K0) é mais realista que o ativo. Para φ = 18°: Ka = 0,53 e K0 = 0,69 (+31%). Use a entrada Empuxo (item 1.3).</t>
+        </is>
+      </c>
+      <c r="M251" s="241"/>
+      <c r="N251" s="241"/>
+      <c r="O251" s="241"/>
+      <c r="P251" s="241"/>
+      <c r="Q251" s="241"/>
+      <c r="R251" s="241"/>
+      <c r="S251" s="241"/>
+      <c r="T251" s="241"/>
+    </row>
+    <row r="252">
+      <c r="K252" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.2 Restante da aba (colunas A–C)</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="32" customHeight="1">
       <c r="K253" s="238" t="inlineStr">
         <is>
-          <t xml:space="preserve">B52:B66</t>
-        </is>
-      </c>
-      <c r="L253" s="239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pilar 20×30 não passa: Kc = 0,25 fora de tabela, Ks = 0,028 digitado não corresponde, As = 58 cm² (48 barras). Momento com (H/3 + 0,6) sem origem clara e sem Sc.</t>
-        </is>
-      </c>
-      <c r="M253" s="239"/>
-      <c r="N253" s="239"/>
-      <c r="O253" s="239"/>
-      <c r="P253" s="239"/>
-      <c r="Q253" s="239"/>
-      <c r="R253" s="239"/>
-      <c r="S253" s="239"/>
-      <c r="T253" s="239"/>
+          <t xml:space="preserve">B20 / B28</t>
+        </is>
+      </c>
+      <c r="L253" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#NUM! e #DIV/0!: a alvenaria pede 3,43 cm²/m e Ø8 em todo furo dá só 2,51 cm²/m → espaçamento '0 furos' e divisão por zero. Na prática: Ø8 não basta, usar Ø10 em todo furo (3,93 cm²/m).</t>
+        </is>
+      </c>
+      <c r="M253" s="241"/>
+      <c r="N253" s="241"/>
+      <c r="O253" s="241"/>
+      <c r="P253" s="241"/>
+      <c r="Q253" s="241"/>
+      <c r="R253" s="241"/>
+      <c r="S253" s="241"/>
+      <c r="T253" s="241"/>
     </row>
     <row r="254" ht="17" customHeight="1">
       <c r="K254" s="238" t="inlineStr">
         <is>
+          <t xml:space="preserve">B8 / B9</t>
+        </is>
+      </c>
+      <c r="L254" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coesão e φ dão 0: NSPT (B4) = 0 não existe na tabela DADOS DO SOLO. Sem efeito, pois o Ka de B33 é digitado.</t>
+        </is>
+      </c>
+      <c r="M254" s="241"/>
+      <c r="N254" s="241"/>
+      <c r="O254" s="241"/>
+      <c r="P254" s="241"/>
+      <c r="Q254" s="241"/>
+      <c r="R254" s="241"/>
+      <c r="S254" s="241"/>
+      <c r="T254" s="241"/>
+    </row>
+    <row r="255" ht="32" customHeight="1">
+      <c r="K255" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B33</t>
+        </is>
+      </c>
+      <c r="L255" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ka = 0,36 digitado, sem ligação com φ. A aba usa 3 valores diferentes: 0,36 (B33), 0,528 (M8) e 0,75 (CÁLCULO FECHAMENTO).</t>
+        </is>
+      </c>
+      <c r="M255" s="241"/>
+      <c r="N255" s="241"/>
+      <c r="O255" s="241"/>
+      <c r="P255" s="241"/>
+      <c r="Q255" s="241"/>
+      <c r="R255" s="241"/>
+      <c r="S255" s="241"/>
+      <c r="T255" s="241"/>
+    </row>
+    <row r="256" ht="32" customHeight="1">
+      <c r="K256" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B24</t>
+        </is>
+      </c>
+      <c r="L256" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esbeltez do pilar usa a altura da alvenaria (1,75 m) em vez da do pilar (3,85 m). Com 3,85 m dá ≈ 25,7 &lt; 30 → segue 'Sim', por acaso.</t>
+        </is>
+      </c>
+      <c r="M256" s="241"/>
+      <c r="N256" s="241"/>
+      <c r="O256" s="241"/>
+      <c r="P256" s="241"/>
+      <c r="Q256" s="241"/>
+      <c r="R256" s="241"/>
+      <c r="S256" s="241"/>
+      <c r="T256" s="241"/>
+    </row>
+    <row r="257" ht="32" customHeight="1">
+      <c r="K257" s="238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B52:B66</t>
+        </is>
+      </c>
+      <c r="L257" s="241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar 20×30 não passa: Kc = 0,25 fora de tabela, Ks = 0,028 digitado não corresponde, As = 58 cm² (48 barras). Momento com (H/3 + 0,6) sem origem clara e sem Sc.</t>
+        </is>
+      </c>
+      <c r="M257" s="241"/>
+      <c r="N257" s="241"/>
+      <c r="O257" s="241"/>
+      <c r="P257" s="241"/>
+      <c r="Q257" s="241"/>
+      <c r="R257" s="241"/>
+      <c r="S257" s="241"/>
+      <c r="T257" s="241"/>
+    </row>
+    <row r="258" ht="17" customHeight="1">
+      <c r="K258" s="238" t="inlineStr">
+        <is>
           <t xml:space="preserve">B15</t>
         </is>
       </c>
-      <c r="L254" s="239" t="inlineStr">
+      <c r="L258" s="241" t="inlineStr">
         <is>
           <t xml:space="preserve">TABELAS LÍBANO com μ digitados para La/Lb = 0,91: se mudar H ou D, os coeficientes não se atualizam.</t>
         </is>
       </c>
-      <c r="M254" s="239"/>
-      <c r="N254" s="239"/>
-      <c r="O254" s="239"/>
-      <c r="P254" s="239"/>
-      <c r="Q254" s="239"/>
-      <c r="R254" s="239"/>
-      <c r="S254" s="239"/>
-      <c r="T254" s="239"/>
-    </row>
-    <row r="255" ht="17" customHeight="1">
-      <c r="K255" s="238" t="inlineStr">
+      <c r="M258" s="241"/>
+      <c r="N258" s="241"/>
+      <c r="O258" s="241"/>
+      <c r="P258" s="241"/>
+      <c r="Q258" s="241"/>
+      <c r="R258" s="241"/>
+      <c r="S258" s="241"/>
+      <c r="T258" s="241"/>
+    </row>
+    <row r="259" ht="17" customHeight="1">
+      <c r="K259" s="238" t="inlineStr">
         <is>
           <t xml:space="preserve">B90</t>
         </is>
       </c>
-      <c r="L255" s="239" t="inlineStr">
+      <c r="L259" s="241" t="inlineStr">
         <is>
           <t xml:space="preserve">Peso da sapata fixo (1,2 × 1,0 × 0,5 m).</t>
         </is>
       </c>
-      <c r="M255" s="239"/>
-      <c r="N255" s="239"/>
-      <c r="O255" s="239"/>
-      <c r="P255" s="239"/>
-      <c r="Q255" s="239"/>
-      <c r="R255" s="239"/>
-      <c r="S255" s="239"/>
-      <c r="T255" s="239"/>
+      <c r="M259" s="241"/>
+      <c r="N259" s="241"/>
+      <c r="O259" s="241"/>
+      <c r="P259" s="241"/>
+      <c r="Q259" s="241"/>
+      <c r="R259" s="241"/>
+      <c r="S259" s="241"/>
+      <c r="T259" s="241"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="59">
     <mergeCell ref="K1:T1"/>
-    <mergeCell ref="K2:T2"/>
-    <mergeCell ref="K4:T4"/>
-    <mergeCell ref="K22:T22"/>
-    <mergeCell ref="K38:T38"/>
-    <mergeCell ref="K40:T40"/>
-    <mergeCell ref="K51:T51"/>
-    <mergeCell ref="K53:T53"/>
-    <mergeCell ref="K65:T65"/>
-    <mergeCell ref="K67:T67"/>
-    <mergeCell ref="K81:T81"/>
-    <mergeCell ref="K83:T83"/>
-    <mergeCell ref="K106:T106"/>
-    <mergeCell ref="K108:T108"/>
-    <mergeCell ref="K235:T235"/>
-    <mergeCell ref="K237:T237"/>
-    <mergeCell ref="L239:T239"/>
-    <mergeCell ref="L240:T240"/>
-    <mergeCell ref="L241:T241"/>
-    <mergeCell ref="L242:T242"/>
+    <mergeCell ref="K6:T6"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="K26:T26"/>
+    <mergeCell ref="K42:T42"/>
+    <mergeCell ref="K44:T44"/>
+    <mergeCell ref="K55:T55"/>
+    <mergeCell ref="K57:T57"/>
+    <mergeCell ref="K69:T69"/>
+    <mergeCell ref="K71:T71"/>
+    <mergeCell ref="K85:T85"/>
+    <mergeCell ref="K87:T87"/>
+    <mergeCell ref="K110:T110"/>
+    <mergeCell ref="K112:T112"/>
+    <mergeCell ref="K239:T239"/>
+    <mergeCell ref="K241:T241"/>
     <mergeCell ref="L243:T243"/>
     <mergeCell ref="L244:T244"/>
     <mergeCell ref="L245:T245"/>
     <mergeCell ref="L246:T246"/>
     <mergeCell ref="L247:T247"/>
+    <mergeCell ref="L248:T248"/>
     <mergeCell ref="L249:T249"/>
     <mergeCell ref="L250:T250"/>
     <mergeCell ref="L251:T251"/>
-    <mergeCell ref="L252:T252"/>
     <mergeCell ref="L253:T253"/>
     <mergeCell ref="L254:T254"/>
     <mergeCell ref="L255:T255"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L8:T8"/>
-    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L256:T256"/>
+    <mergeCell ref="L257:T257"/>
+    <mergeCell ref="L258:T258"/>
+    <mergeCell ref="L259:T259"/>
     <mergeCell ref="L10:M10"/>
+    <mergeCell ref="O10:T10"/>
     <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L12:T12"/>
     <mergeCell ref="L13:M13"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="L15:M15"/>
@@ -16420,23 +16488,39 @@
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:T4"/>
   </mergeCells>
-  <conditionalFormatting sqref="N79 N85 N7 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19">
+  <conditionalFormatting sqref="N83 N89 N11 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23">
     <cfRule type="beginsWith" dxfId="6" priority="1" operator="beginsWith" text="Ok">
-      <formula>LEFT(N79,2)="Ok"</formula>
+      <formula>LEFT(N83,2)="Ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N79 N85 N7 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19">
+  <conditionalFormatting sqref="N83 N89 N11 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23">
     <cfRule type="beginsWith" dxfId="5" priority="2" operator="beginsWith" text="Não se aplica">
-      <formula>LEFT(N79,13)="Não se aplica"</formula>
+      <formula>LEFT(N83,13)="Não se aplica"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L34">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L38">
       <formula1>"Ativo,Repouso"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L35">
-      <formula1>$K$70:$K$72</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L39">
+      <formula1>$K$74:$K$76</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
+++ b/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
@@ -14,6 +14,7 @@
   </bookViews>
   <sheets>
     <sheet name="CONTENÇÃO RÁPIDA" sheetId="11" r:id="rId99"/>
+    <sheet name="DIMENSIONAMENTO PILAR" sheetId="12" r:id="rId98"/>
     <sheet name="MURO DE ARRIMO" sheetId="1" r:id="rId1"/>
     <sheet name="DADOS DO SOLO" sheetId="6" r:id="rId2"/>
     <sheet name="ASSENTAMENTO" sheetId="4" r:id="rId3"/>
@@ -24,6 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CONTENÇÃO RÁPIDA'!$K$1:$T$259</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$127</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="1000"/>
   <extLst>
@@ -16527,4 +16529,2012 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="K1:T127"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="10" max="10" width="2.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="K1" s="219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIMENSIONAMENTO DO PILAR COMO VIGA BIAPOIADA – FLEXÃO SIMPLES E ESTRIBOS (NBR 6118)</t>
+        </is>
+      </c>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="K2" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMADURA LONGITUDINAL</t>
+        </is>
+      </c>
+      <c r="L2" s="239"/>
+      <c r="M2" s="240">
+        <f>$L$100&amp;" Ø"&amp;$L$42&amp;" em cada face (simétrica)"</f>
+      </c>
+      <c r="N2" s="240"/>
+      <c r="O2" s="240">
+        <f>"As,ef = "&amp;FIXED($L$101,2)&amp;" cm²/face | total "&amp;FIXED($L$102,2)&amp;" cm²"</f>
+      </c>
+      <c r="P2" s="240"/>
+      <c r="Q2" s="240"/>
+      <c r="R2" s="240">
+        <f>"ρ = "&amp;FIXED($L$103,2)&amp;" % | "&amp;IF($L$105&lt;$L$104,"NÃO CABE","cabe na face")</f>
+      </c>
+      <c r="S2" s="240"/>
+      <c r="T2" s="240"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="K3" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESTRIBOS</t>
+        </is>
+      </c>
+      <c r="L3" s="239"/>
+      <c r="M3" s="240">
+        <f>"Ø"&amp;$L$41&amp;" c/"&amp;$L$125&amp;" ("&amp;$L$43&amp;" ramos)"</f>
+      </c>
+      <c r="N3" s="240"/>
+      <c r="O3" s="240">
+        <f>"Asw = "&amp;FIXED($L$121,2)&amp;" cm²/m"</f>
+      </c>
+      <c r="P3" s="240"/>
+      <c r="Q3" s="240"/>
+      <c r="R3" s="240">
+        <f>"Vsd = "&amp;FIXED($L$111,1)&amp;" kN | VRd2 = "&amp;FIXED($L$112,1)&amp;" kN"</f>
+      </c>
+      <c r="S3" s="240"/>
+      <c r="T3" s="240"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="K4" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESFORÇOS DE CÁLCULO</t>
+        </is>
+      </c>
+      <c r="L4" s="239"/>
+      <c r="M4" s="240">
+        <f>"Md+ = "&amp;FIXED($L$72,2)&amp;" | Md− = "&amp;FIXED($L$83,2)&amp;" kN·m"</f>
+      </c>
+      <c r="N4" s="240"/>
+      <c r="O4" s="240">
+        <f>"Md,lim = "&amp;FIXED($L$67,2)&amp;" kN·m"</f>
+      </c>
+      <c r="P4" s="240"/>
+      <c r="Q4" s="240"/>
+      <c r="R4" s="240">
+        <f>"Modelo: "&amp;$L$45&amp;" | seção "&amp;$L$39&amp;"×"&amp;$L$38</f>
+      </c>
+      <c r="S4" s="240"/>
+      <c r="T4" s="240"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="K6" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Como usar: células CINZA são entradas; os esforços vêm da aba CONTENÇÃO RÁPIDA (pode sobrescrever). Pilar tratado como viga (flexão simples, sem a força normal). Armadura longitudinal SIMÉTRICA: as duas faces recebem a mesma armadura, dimensionada pela pior situação entre a seção do vão (M+) e a da base (M−). Estribos pelo Modelo I (θ = 45°, α = 90°).</t>
+        </is>
+      </c>
+      <c r="L6" s="220"/>
+      <c r="M6" s="220"/>
+      <c r="N6" s="220"/>
+      <c r="O6" s="220"/>
+      <c r="P6" s="220"/>
+      <c r="Q6" s="220"/>
+      <c r="R6" s="220"/>
+      <c r="S6" s="220"/>
+      <c r="T6" s="220"/>
+    </row>
+    <row r="8">
+      <c r="K8" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESUMO DAS VERIFICAÇÕES E ARMADURAS</t>
+        </is>
+      </c>
+      <c r="L8" s="221"/>
+      <c r="M8" s="221"/>
+      <c r="N8" s="221"/>
+      <c r="O8" s="221"/>
+      <c r="P8" s="221"/>
+      <c r="Q8" s="221"/>
+      <c r="R8" s="221"/>
+      <c r="S8" s="221"/>
+      <c r="T8" s="221"/>
+    </row>
+    <row r="10">
+      <c r="K10" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="L10" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resultado</t>
+        </is>
+      </c>
+      <c r="M10" s="235"/>
+      <c r="N10" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="O10" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O que é</t>
+        </is>
+      </c>
+      <c r="P10" s="235"/>
+      <c r="Q10" s="235"/>
+      <c r="R10" s="235"/>
+      <c r="S10" s="235"/>
+      <c r="T10" s="235"/>
+    </row>
+    <row r="11">
+      <c r="K11" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Esforços</t>
+        </is>
+      </c>
+      <c r="L11" s="236">
+        <f>"Md+ = "&amp;FIXED($L$72,1)&amp;" | Md− = "&amp;FIXED($L$83,1)</f>
+      </c>
+      <c r="M11" s="236"/>
+      <c r="N11" s="232">
+        <f>IF(ISNA(MATCH($L$45,'CONTENÇÃO RÁPIDA'!$K$74:$K$76,0)),"Rever: modelo inválido","Ok")</f>
+      </c>
+      <c r="O11" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momentos de cálculo (kN·m) do modelo escolhido – item 1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="K12" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aviso</t>
+        </is>
+      </c>
+      <c r="L12" s="234">
+        <f>IF(MAX($L$72,$L$83)&gt;$L$67,"⚠ Armadura dupla: a seção "&amp;$L$39&amp;"×"&amp;$L$38&amp;" é pequena para Md = "&amp;FIXED(MAX($L$72,$L$83),1)&amp;" kN·m. Para armadura simples use h ≥ "&amp;ROUNDUP($L$68+$L$64,0)&amp;" cm.","Flexão simples (sem a força normal): se o pilar tiver compressão relevante, confira a flexo-compressão no programa.")</f>
+      </c>
+      <c r="M12" s="234"/>
+      <c r="N12" s="234"/>
+      <c r="O12" s="234"/>
+      <c r="P12" s="234"/>
+      <c r="Q12" s="234"/>
+      <c r="R12" s="234"/>
+      <c r="S12" s="234"/>
+      <c r="T12" s="234"/>
+    </row>
+    <row r="13">
+      <c r="K13" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seção do vão</t>
+        </is>
+      </c>
+      <c r="L13" s="236">
+        <f>$L$73</f>
+      </c>
+      <c r="M13" s="236"/>
+      <c r="N13" s="232">
+        <f>IF($L$72=0,"Não se aplica (M = 0)",IF($L$72&lt;=$L$67,"Ok","Arm. dupla – ver d,mín"))</f>
+      </c>
+      <c r="O13" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flexão com M+ – item 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="K14" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seção da base</t>
+        </is>
+      </c>
+      <c r="L14" s="236">
+        <f>$L$84</f>
+      </c>
+      <c r="M14" s="236"/>
+      <c r="N14" s="232">
+        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$67,"Ok","Arm. dupla – ver d,mín"))</f>
+      </c>
+      <c r="O14" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flexão com M− – item 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="K15" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arm. por face</t>
+        </is>
+      </c>
+      <c r="L15" s="236">
+        <f>$L$100&amp;" Ø"&amp;$L$42&amp;" ("&amp;FIXED($L$101,2)&amp;" cm²)"</f>
+      </c>
+      <c r="M15" s="236"/>
+      <c r="N15" s="232">
+        <f>IF($L$105&lt;$L$104,"Não cabe: aumentar b ou Ø,l","Ok")</f>
+      </c>
+      <c r="O15" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mesma armadura nas duas faces (simétrica) – item 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="K16" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taxa total</t>
+        </is>
+      </c>
+      <c r="L16" s="236">
+        <f>FIXED($L$103,2)&amp;" %"</f>
+      </c>
+      <c r="M16" s="236"/>
+      <c r="N16" s="232">
+        <f>IF($L$103&gt;4,"Rever: taxa &gt; 4%",IF($L$103&lt;0.4,"Rever: taxa &lt; 0,4%","Ok"))</f>
+      </c>
+      <c r="O16" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura total / Ac – item 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="K17" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biela</t>
+        </is>
+      </c>
+      <c r="L17" s="236">
+        <f>FIXED($L$111,1)&amp;" ≤ "&amp;FIXED($L$112,1)&amp;" kN"</f>
+      </c>
+      <c r="M17" s="236"/>
+      <c r="N17" s="232">
+        <f>IF($L$111&lt;=$L$112,"Ok","Aumentar seção ou fck")</f>
+      </c>
+      <c r="O17" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vsd ≤ VRd2 – item 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="K18" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estribos</t>
+        </is>
+      </c>
+      <c r="L18" s="236">
+        <f>"Ø"&amp;$L$41&amp;" c/"&amp;$L$125&amp;" ("&amp;$L$43&amp;" ramos)"</f>
+      </c>
+      <c r="M18" s="236"/>
+      <c r="N18" s="232">
+        <f>IF($L$125&lt;5,"s &lt; 5 cm – aumentar Ø,t",IF($L$126&gt;=$L$121,"Ok","Rever"))</f>
+      </c>
+      <c r="O18" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estribos em toda a altura do pilar – item 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="K26" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 . DADOS DE ENTRADA</t>
+        </is>
+      </c>
+      <c r="L26" s="221"/>
+      <c r="M26" s="221"/>
+      <c r="N26" s="221"/>
+      <c r="O26" s="221"/>
+      <c r="P26" s="221"/>
+      <c r="Q26" s="221"/>
+      <c r="R26" s="221"/>
+      <c r="S26" s="221"/>
+      <c r="T26" s="221"/>
+    </row>
+    <row r="28">
+      <c r="K28" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1 Coeficientes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="K29" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">γf</t>
+        </is>
+      </c>
+      <c r="L29" s="224">
+        <v>1.4</v>
+      </c>
+      <c r="M29" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O29" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coeficiente de majoração das cargas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="K30" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">γc</t>
+        </is>
+      </c>
+      <c r="L30" s="224">
+        <v>1.4</v>
+      </c>
+      <c r="M30" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O30" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coeficiente de minoração do concreto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="K31" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">γs</t>
+        </is>
+      </c>
+      <c r="L31" s="224">
+        <v>1.15</v>
+      </c>
+      <c r="M31" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O31" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coeficiente de minoração do aço.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="K32" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2 Materiais</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="K33" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fck</t>
+        </is>
+      </c>
+      <c r="L33" s="224">
+        <v>30</v>
+      </c>
+      <c r="M33" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="N33" s="232">
+        <f>IF(OR($L$33&lt;20,$L$33&gt;50),"Rever: fck entre 20 e 50 MPa","Ok")</f>
+      </c>
+      <c r="O33" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência característica do concreto (até 50 MPa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="K34" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fyk</t>
+        </is>
+      </c>
+      <c r="L34" s="224">
+        <v>500</v>
+      </c>
+      <c r="M34" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O34" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aço da armadura longitudinal (CA-50).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="K35" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fywk</t>
+        </is>
+      </c>
+      <c r="L35" s="224">
+        <v>500</v>
+      </c>
+      <c r="M35" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O35" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aço dos estribos (CA-50 = 500; CA-60 = 600).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="K36" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d,máx</t>
+        </is>
+      </c>
+      <c r="L36" s="224">
+        <v>19</v>
+      </c>
+      <c r="M36" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mm</t>
+        </is>
+      </c>
+      <c r="O36" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diâmetro máximo do agregado (brita 1 = 19 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="K37" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Seção do pilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="K38" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h</t>
+        </is>
+      </c>
+      <c r="L38" s="224">
+        <v>30</v>
+      </c>
+      <c r="M38" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O38" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dimensão na direção do empuxo (altura da seção que resiste à flexão).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="K39" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b</t>
+        </is>
+      </c>
+      <c r="L39" s="224">
+        <v>20</v>
+      </c>
+      <c r="M39" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O39" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dimensão da face onde ficam as barras (largura da 'viga').</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="K40" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c</t>
+        </is>
+      </c>
+      <c r="L40" s="224">
+        <v>3</v>
+      </c>
+      <c r="M40" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O40" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cobrimento (CAA II: pilar 3,0 cm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="K41" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ø,t</t>
+        </is>
+      </c>
+      <c r="L41" s="224">
+        <v>6.3</v>
+      </c>
+      <c r="M41" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mm</t>
+        </is>
+      </c>
+      <c r="O41" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bitola do estribo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="K42" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ø,l</t>
+        </is>
+      </c>
+      <c r="L42" s="224">
+        <v>12.5</v>
+      </c>
+      <c r="M42" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mm</t>
+        </is>
+      </c>
+      <c r="N42" s="232">
+        <f>IF($L$42&lt;10,"Rever: pilar pede Ø ≥ 10 mm",IF($L$42&gt;$L$39*10/8,"Rever: Ø &gt; b/8","Ok"))</f>
+      </c>
+      <c r="O42" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bitola da armadura longitudinal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="K43" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ramos</t>
+        </is>
+      </c>
+      <c r="L43" s="224">
+        <v>2</v>
+      </c>
+      <c r="M43" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O43" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ramos de cada estribo (estribo fechado = 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="K44" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Esforços característicos (da aba CONTENÇÃO RÁPIDA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="K45" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelo</t>
+        </is>
+      </c>
+      <c r="L45" s="224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biapoiado</t>
+        </is>
+      </c>
+      <c r="M45" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N45" s="232">
+        <f>IF(ISNA(MATCH($L$45,'CONTENÇÃO RÁPIDA'!$K$74:$K$76,0)),"Rever: modelo inválido","Ok")</f>
+      </c>
+      <c r="O45" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelo do pilar: Biapoiado (padrão), Engaste-apoio ou Balanço.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="K46" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mk+</t>
+        </is>
+      </c>
+      <c r="L46" s="225">
+        <f>MAX(0,IFERROR(INDEX('CONTENÇÃO RÁPIDA'!$O$74:$O$76,MATCH($L$45,'CONTENÇÃO RÁPIDA'!$K$74:$K$76,0)),0))</f>
+      </c>
+      <c r="M46" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O46" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento positivo máximo (vão) – tração na face externa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="K47" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mk−</t>
+        </is>
+      </c>
+      <c r="L47" s="225">
+        <f>ABS(MIN(0,IFERROR(INDEX('CONTENÇÃO RÁPIDA'!$N$74:$N$76,MATCH($L$45,'CONTENÇÃO RÁPIDA'!$K$74:$K$76,0)),0)))</f>
+      </c>
+      <c r="M47" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O47" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento negativo na base (em módulo) – tração na face do solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="K48" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vk</t>
+        </is>
+      </c>
+      <c r="L48" s="225">
+        <f>MAX(IFERROR(INDEX('CONTENÇÃO RÁPIDA'!$L$74:$L$76,MATCH($L$45,'CONTENÇÃO RÁPIDA'!$K$74:$K$76,0)),0),IFERROR(INDEX('CONTENÇÃO RÁPIDA'!$M$74:$M$76,MATCH($L$45,'CONTENÇÃO RÁPIDA'!$K$74:$K$76,0)),0))</f>
+      </c>
+      <c r="M48" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O48" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maior cortante = maior reação (R,topo ou R,base).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="K49" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nk</t>
+        </is>
+      </c>
+      <c r="L49" s="224">
+        <v>0</v>
+      </c>
+      <c r="M49" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O49" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Força normal no pilar (compressão). Usada só na armadura mínima de pilar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="K50" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Tabela ρ,mín (NBR 6118, tab. 17.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="K51" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fck (MPa)</t>
+        </is>
+      </c>
+      <c r="L51" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ρ,mín (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="K52" s="237">
+        <v>20</v>
+      </c>
+      <c r="L52" s="226">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="K53" s="237">
+        <v>25</v>
+      </c>
+      <c r="L53" s="226">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="K54" s="237">
+        <v>30</v>
+      </c>
+      <c r="L54" s="226">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="K55" s="237">
+        <v>35</v>
+      </c>
+      <c r="L55" s="226">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="K56" s="237">
+        <v>40</v>
+      </c>
+      <c r="L56" s="226">
+        <v>0.179</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="K57" s="237">
+        <v>45</v>
+      </c>
+      <c r="L57" s="226">
+        <v>0.194</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="K58" s="237">
+        <v>50</v>
+      </c>
+      <c r="L58" s="226">
+        <v>0.208</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="K60" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 . PARÂMETROS DE CÁLCULO</t>
+        </is>
+      </c>
+      <c r="L60" s="221"/>
+      <c r="M60" s="221"/>
+      <c r="N60" s="221"/>
+      <c r="O60" s="221"/>
+      <c r="P60" s="221"/>
+      <c r="Q60" s="221"/>
+      <c r="R60" s="221"/>
+      <c r="S60" s="221"/>
+      <c r="T60" s="221"/>
+    </row>
+    <row r="62">
+      <c r="K62" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fcd</t>
+        </is>
+      </c>
+      <c r="L62" s="227">
+        <f>$L$33/$L$30</f>
+      </c>
+      <c r="M62" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O62" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência de cálculo do concreto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="K63" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fyd</t>
+        </is>
+      </c>
+      <c r="L63" s="227">
+        <f>$L$34/$L$31</f>
+      </c>
+      <c r="M63" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O63" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência de cálculo do aço.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="K64" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d'</t>
+        </is>
+      </c>
+      <c r="L64" s="227">
+        <f>$L$40+$L$41/10+$L$42/20</f>
+      </c>
+      <c r="M64" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O64" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distância da face ao eixo das barras (c + Ø,t + Ø,l/2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="K65" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d</t>
+        </is>
+      </c>
+      <c r="L65" s="227">
+        <f>$L$38-$L$64</f>
+      </c>
+      <c r="M65" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O65" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura útil (h − d').</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="K66" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(x/d)lim</t>
+        </is>
+      </c>
+      <c r="L66" s="227">
+        <v>0.45</v>
+      </c>
+      <c r="M66" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O66" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Limite da linha neutra para fck ≤ 50 MPa (ductilidade).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="K67" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Md,lim</t>
+        </is>
+      </c>
+      <c r="L67" s="227">
+        <f>0.68*$L$39*$L$65^2*$L$62/10*$L$66*(1-0.4*$L$66)/100</f>
+      </c>
+      <c r="M67" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O67" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maior momento de cálculo só com armadura simples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="K68" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d,mín</t>
+        </is>
+      </c>
+      <c r="L68" s="227">
+        <f>SQRT(MAX($L$46,$L$47)*$L$29*100/(0.68*$L$39*$L$62/10*$L$66*(1-0.4*$L$66)))</f>
+      </c>
+      <c r="M68" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="N68" s="232">
+        <f>IF($L$65&gt;=$L$68,"Ok","Aumentar h para "&amp;ROUNDUP($L$68+$L$64,0)&amp;" cm (arm. simples)")</f>
+      </c>
+      <c r="O68" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura útil mínima para armadura simples com o maior momento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="K70" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 . FLEXÃO – SEÇÃO DO VÃO (M+)</t>
+        </is>
+      </c>
+      <c r="L70" s="221"/>
+      <c r="M70" s="221"/>
+      <c r="N70" s="221"/>
+      <c r="O70" s="221"/>
+      <c r="P70" s="221"/>
+      <c r="Q70" s="221"/>
+      <c r="R70" s="221"/>
+      <c r="S70" s="221"/>
+      <c r="T70" s="221"/>
+    </row>
+    <row r="72">
+      <c r="K72" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Md</t>
+        </is>
+      </c>
+      <c r="L72" s="227">
+        <f>$L$46*$L$29</f>
+      </c>
+      <c r="M72" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O72" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento de cálculo (γf·Mk).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="K73" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo</t>
+        </is>
+      </c>
+      <c r="L73" s="230">
+        <f>IF($L$72=0,"Não se aplica (M = 0)",IF($L$72&lt;=$L$67,"Armadura simples","Armadura dupla"))</f>
+      </c>
+      <c r="M73" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N73" s="232">
+        <f>IF($L$72=0,"Não se aplica (M = 0)",IF($L$72&lt;=$L$67,"Ok","Arm. dupla – ver d,mín (item 2)"))</f>
+      </c>
+      <c r="O73" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simples se Md ≤ Md,lim; dupla se maior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="K74" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="L74" s="227">
+        <f>IF($L$72&lt;=$L$67,1.25*$L$65*(1-SQRT(MAX(0,1-$L$72*100/(0.425*$L$39*$L$65^2*$L$62/10)))),$L$66*$L$65)</f>
+      </c>
+      <c r="M74" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O74" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Profundidade da linha neutra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="K75" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x/d</t>
+        </is>
+      </c>
+      <c r="L75" s="228">
+        <f>IF($L$65=0,0,$L$74/$L$65)</f>
+      </c>
+      <c r="M75" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O75" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Posição relativa da linha neutra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="K76" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domínio</t>
+        </is>
+      </c>
+      <c r="L76" s="230">
+        <f>IF($L$72=0,"-",IF($L$75&lt;=0.259,"2","3"))</f>
+      </c>
+      <c r="M76" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O76" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domínio de deformação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="K77" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σsc</t>
+        </is>
+      </c>
+      <c r="L77" s="227">
+        <f>MIN($L$63,210000*0.0035*MAX(0,$L$74-$L$64)/MAX($L$74,0.001))</f>
+      </c>
+      <c r="M77" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O77" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tensão na armadura comprimida (Es = 210 GPa, εc = 3,5‰), só na armadura dupla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="K78" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,t</t>
+        </is>
+      </c>
+      <c r="L78" s="227">
+        <f>IF($L$72&lt;=$L$67,$L$72*100/($L$63/10*($L$65-0.4*$L$74)),$L$67*100/($L$63/10*($L$65-0.4*$L$74))+($L$72-$L$67)*100/($L$63/10*($L$65-$L$64)))</f>
+      </c>
+      <c r="M78" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O78" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura tracionada – face externa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="K79" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,c</t>
+        </is>
+      </c>
+      <c r="L79" s="227">
+        <f>IF($L$72&lt;=$L$67,0,($L$72-$L$67)*100/($L$77/10*($L$65-$L$64)))</f>
+      </c>
+      <c r="M79" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O79" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura comprimida – face do solo (0 na armadura simples).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="K81" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 . FLEXÃO – SEÇÃO DA BASE (M−)</t>
+        </is>
+      </c>
+      <c r="L81" s="221"/>
+      <c r="M81" s="221"/>
+      <c r="N81" s="221"/>
+      <c r="O81" s="221"/>
+      <c r="P81" s="221"/>
+      <c r="Q81" s="221"/>
+      <c r="R81" s="221"/>
+      <c r="S81" s="221"/>
+      <c r="T81" s="221"/>
+    </row>
+    <row r="83">
+      <c r="K83" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Md</t>
+        </is>
+      </c>
+      <c r="L83" s="227">
+        <f>$L$47*$L$29</f>
+      </c>
+      <c r="M83" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O83" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento de cálculo (γf·Mk).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="K84" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo</t>
+        </is>
+      </c>
+      <c r="L84" s="230">
+        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$67,"Armadura simples","Armadura dupla"))</f>
+      </c>
+      <c r="M84" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N84" s="232">
+        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$67,"Ok","Arm. dupla – ver d,mín (item 2)"))</f>
+      </c>
+      <c r="O84" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simples se Md ≤ Md,lim; dupla se maior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="K85" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="L85" s="227">
+        <f>IF($L$83&lt;=$L$67,1.25*$L$65*(1-SQRT(MAX(0,1-$L$83*100/(0.425*$L$39*$L$65^2*$L$62/10)))),$L$66*$L$65)</f>
+      </c>
+      <c r="M85" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O85" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Profundidade da linha neutra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="K86" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x/d</t>
+        </is>
+      </c>
+      <c r="L86" s="228">
+        <f>IF($L$65=0,0,$L$85/$L$65)</f>
+      </c>
+      <c r="M86" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O86" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Posição relativa da linha neutra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="K87" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domínio</t>
+        </is>
+      </c>
+      <c r="L87" s="230">
+        <f>IF($L$83=0,"-",IF($L$86&lt;=0.259,"2","3"))</f>
+      </c>
+      <c r="M87" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O87" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domínio de deformação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="K88" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">σsc</t>
+        </is>
+      </c>
+      <c r="L88" s="227">
+        <f>MIN($L$63,210000*0.0035*MAX(0,$L$85-$L$64)/MAX($L$85,0.001))</f>
+      </c>
+      <c r="M88" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O88" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tensão na armadura comprimida (Es = 210 GPa, εc = 3,5‰), só na armadura dupla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="K89" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,t</t>
+        </is>
+      </c>
+      <c r="L89" s="227">
+        <f>IF($L$83&lt;=$L$67,$L$83*100/($L$63/10*($L$65-0.4*$L$85)),$L$67*100/($L$63/10*($L$65-0.4*$L$85))+($L$83-$L$67)*100/($L$63/10*($L$65-$L$64)))</f>
+      </c>
+      <c r="M89" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O89" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura tracionada – face do solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="K90" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,c</t>
+        </is>
+      </c>
+      <c r="L90" s="227">
+        <f>IF($L$83&lt;=$L$67,0,($L$83-$L$67)*100/($L$88/10*($L$65-$L$64)))</f>
+      </c>
+      <c r="M90" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O90" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura comprimida – face externa (0 na armadura simples).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="K92" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 . ARMADURA LONGITUDINAL SIMÉTRICA (mesma nas duas faces)</t>
+        </is>
+      </c>
+      <c r="L92" s="221"/>
+      <c r="M92" s="221"/>
+      <c r="N92" s="221"/>
+      <c r="O92" s="221"/>
+      <c r="P92" s="221"/>
+      <c r="Q92" s="221"/>
+      <c r="R92" s="221"/>
+      <c r="S92" s="221"/>
+      <c r="T92" s="221"/>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="K94" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada face recebe a maior entre: tração do vão, tração da base, compressão da armadura dupla, mínima de viga (por face) e metade da mínima de pilar (0,4% Ac no total). As mesmas barras seguem por toda a altura, cobrindo as duas seções.</t>
+        </is>
+      </c>
+      <c r="L94" s="220"/>
+      <c r="M94" s="220"/>
+      <c r="N94" s="220"/>
+      <c r="O94" s="220"/>
+      <c r="P94" s="220"/>
+      <c r="Q94" s="220"/>
+      <c r="R94" s="220"/>
+      <c r="S94" s="220"/>
+      <c r="T94" s="220"/>
+    </row>
+    <row r="95">
+      <c r="K95" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ρ,mín</t>
+        </is>
+      </c>
+      <c r="L95" s="228">
+        <f>VLOOKUP($L$33,$K$52:$L$58,2,TRUE)</f>
+      </c>
+      <c r="M95" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="O95" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taxa mínima de flexão (tabela 1.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="K96" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,mín,v</t>
+        </is>
+      </c>
+      <c r="L96" s="227">
+        <f>$L$95/100*$L$39*$L$38</f>
+      </c>
+      <c r="M96" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O96" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mínima de viga, por face tracionada: ρ,mín·b·h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="K97" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,mín,p</t>
+        </is>
+      </c>
+      <c r="L97" s="227">
+        <f>MAX(0.15*$L$49*$L$29/($L$63/10),0.004*$L$39*$L$38)</f>
+      </c>
+      <c r="M97" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O97" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mínima de pilar, total: máx(0,15·Nd/fyd; 0,4%·Ac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="K98" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,face</t>
+        </is>
+      </c>
+      <c r="L98" s="227">
+        <f>MAX($L$78,$L$79,$L$89,$L$90,$L$96,$L$97/2)</f>
+      </c>
+      <c r="M98" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O98" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura necessária em cada face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="K99" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A,barra</t>
+        </is>
+      </c>
+      <c r="L99" s="228">
+        <f>PI()*($L$42/10)^2/4</f>
+      </c>
+      <c r="M99" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O99" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de uma barra Ø,l.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="K100" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n</t>
+        </is>
+      </c>
+      <c r="L100" s="229">
+        <f>MAX(2,ROUNDUP($L$98/$L$99,0))</f>
+      </c>
+      <c r="M100" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">un</t>
+        </is>
+      </c>
+      <c r="O100" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barras em cada face (mínimo 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="K101" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,ef</t>
+        </is>
+      </c>
+      <c r="L101" s="227">
+        <f>$L$100*$L$99</f>
+      </c>
+      <c r="M101" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O101" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura efetiva em cada face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="K102" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,total</t>
+        </is>
+      </c>
+      <c r="L102" s="227">
+        <f>2*$L$101</f>
+      </c>
+      <c r="M102" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O102" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura total na seção (duas faces).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="K103" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ρ,total</t>
+        </is>
+      </c>
+      <c r="L103" s="227">
+        <f>$L$102/($L$39*$L$38)*100</f>
+      </c>
+      <c r="M103" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="N103" s="232">
+        <f>IF($L$103&gt;4,"Rever: taxa &gt; 4% – aumentar seção",IF($L$103&lt;0.4,"Rever: taxa &lt; 0,4%","Ok"))</f>
+      </c>
+      <c r="O103" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taxa total (pilar: 0,4% a 4%; 8% na emenda).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="K104" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a,h,mín</t>
+        </is>
+      </c>
+      <c r="L104" s="227">
+        <f>MAX(2,$L$42/10,1.2*$L$36/10)</f>
+      </c>
+      <c r="M104" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O104" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mínimo: 2 cm, Ø,l e 1,2·d,máx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="K105" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a,h</t>
+        </is>
+      </c>
+      <c r="L105" s="227">
+        <f>IF($L$100&lt;=1,0,($L$39-2*$L$40-2*$L$41/10-$L$100*$L$42/10)/($L$100-1))</f>
+      </c>
+      <c r="M105" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="N105" s="232">
+        <f>IF($L$105&lt;$L$104,"Não cabe: aumentar b ou Ø,l",IF($L$105&gt;40,"Rever: espaço &gt; 40 cm","Ok"))</f>
+      </c>
+      <c r="O105" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espaço livre entre barras da mesma face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="K107" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 . ESTRIBOS – FORÇA CORTANTE (Modelo I, NBR 6118)</t>
+        </is>
+      </c>
+      <c r="L107" s="221"/>
+      <c r="M107" s="221"/>
+      <c r="N107" s="221"/>
+      <c r="O107" s="221"/>
+      <c r="P107" s="221"/>
+      <c r="Q107" s="221"/>
+      <c r="R107" s="221"/>
+      <c r="S107" s="221"/>
+      <c r="T107" s="221"/>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="K109" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vsd ≤ VRd2 (biela) e Vsd ≤ Vc0 + Vsw. O espaçamento adotado é o menor entre o calculado, o máximo de viga (0,6·d ≤ 30 cm ou 0,3·d ≤ 20 cm) e o máximo de pilar (20 cm, b, 12·Ø,l).</t>
+        </is>
+      </c>
+      <c r="L109" s="220"/>
+      <c r="M109" s="220"/>
+      <c r="N109" s="220"/>
+      <c r="O109" s="220"/>
+      <c r="P109" s="220"/>
+      <c r="Q109" s="220"/>
+      <c r="R109" s="220"/>
+      <c r="S109" s="220"/>
+      <c r="T109" s="220"/>
+    </row>
+    <row r="110">
+      <c r="K110" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 Biela e parcela do concreto</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="K111" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vsd</t>
+        </is>
+      </c>
+      <c r="L111" s="227">
+        <f>$L$48*$L$29</f>
+      </c>
+      <c r="M111" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O111" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cortante de cálculo (γf·Vk).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="K112" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VRd2</t>
+        </is>
+      </c>
+      <c r="L112" s="227">
+        <f>0.27*(1-$L$33/250)*$L$62/10*$L$39*$L$65</f>
+      </c>
+      <c r="M112" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="N112" s="232">
+        <f>IF($L$111&lt;=$L$112,"Ok","Aumentar seção ou fck")</f>
+      </c>
+      <c r="O112" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência da biela comprimida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="K113" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fctm</t>
+        </is>
+      </c>
+      <c r="L113" s="227">
+        <f>0.3*$L$33^(2/3)</f>
+      </c>
+      <c r="M113" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O113" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência média à tração.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="K114" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fctd</t>
+        </is>
+      </c>
+      <c r="L114" s="227">
+        <f>0.7*$L$113/$L$30</f>
+      </c>
+      <c r="M114" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O114" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência de cálculo à tração (fctk,inf/γc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="K115" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vc0</t>
+        </is>
+      </c>
+      <c r="L115" s="227">
+        <f>0.6*$L$114/10*$L$39*$L$65</f>
+      </c>
+      <c r="M115" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O115" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcela resistida pelo concreto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="K116" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 Armadura transversal</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="K117" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fywd</t>
+        </is>
+      </c>
+      <c r="L117" s="227">
+        <f>MIN($L$35/$L$31,435)</f>
+      </c>
+      <c r="M117" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O117" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência de cálculo do estribo (≤ 435 MPa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="K118" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vsw</t>
+        </is>
+      </c>
+      <c r="L118" s="227">
+        <f>MAX(0,$L$111-$L$115)</f>
+      </c>
+      <c r="M118" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O118" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcela a ser resistida pelos estribos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="K119" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw,calc</t>
+        </is>
+      </c>
+      <c r="L119" s="227">
+        <f>$L$118/(0.9*$L$65*$L$117/10)*100</f>
+      </c>
+      <c r="M119" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²/m</t>
+        </is>
+      </c>
+      <c r="O119" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw/s = Vsw/(0,9·d·fywd).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="K120" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw,mín</t>
+        </is>
+      </c>
+      <c r="L120" s="227">
+        <f>0.2*$L$113/$L$35*$L$39*100</f>
+      </c>
+      <c r="M120" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²/m</t>
+        </is>
+      </c>
+      <c r="O120" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mínima: ρsw = 0,2·fctm/fywk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="K121" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw</t>
+        </is>
+      </c>
+      <c r="L121" s="227">
+        <f>MAX($L$119,$L$120)</f>
+      </c>
+      <c r="M121" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²/m</t>
+        </is>
+      </c>
+      <c r="O121" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura transversal adotada (todos os ramos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="K122" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s,calc</t>
+        </is>
+      </c>
+      <c r="L122" s="227">
+        <f>IF($L$121=0,999,$L$43*PI()*($L$41/10)^2/4/$L$121*100)</f>
+      </c>
+      <c r="M122" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O122" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espaçamento pela armadura calculada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="K123" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s,máx,v</t>
+        </is>
+      </c>
+      <c r="L123" s="227">
+        <f>IF($L$111&lt;=0.67*$L$112,MIN(0.6*$L$65,30),MIN(0.3*$L$65,20))</f>
+      </c>
+      <c r="M123" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O123" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Máximo de viga (NBR 6118, 18.3.3.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="K124" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s,máx,p</t>
+        </is>
+      </c>
+      <c r="L124" s="227">
+        <f>MIN(20,$L$39,$L$38,IF($L$34&gt;=500,12,25)*$L$42/10)</f>
+      </c>
+      <c r="M124" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O124" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Máximo de pilar: 20 cm, menor dimensão, 12·Ø,l (CA-50).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="K125" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="L125" s="229">
+        <f>ROUNDDOWN(MIN($L$122,$L$123,$L$124),0)</f>
+      </c>
+      <c r="M125" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="N125" s="232">
+        <f>IF($L$125&lt;5,"s &lt; 5 cm – aumentar Ø,t ou ramos","Ok")</f>
+      </c>
+      <c r="O125" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espaçamento adotado (arredondado para baixo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="K126" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw,ef</t>
+        </is>
+      </c>
+      <c r="L126" s="227">
+        <f>$L$43*PI()*($L$41/10)^2/4*100/$L$125</f>
+      </c>
+      <c r="M126" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²/m</t>
+        </is>
+      </c>
+      <c r="N126" s="232">
+        <f>IF($L$126&gt;=$L$121,"Ok","Rever")</f>
+      </c>
+      <c r="O126" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura efetiva com o espaçamento adotado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="K127" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ø,t,mín</t>
+        </is>
+      </c>
+      <c r="L127" s="227">
+        <f>MAX(5,$L$42/4)</f>
+      </c>
+      <c r="M127" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mm</t>
+        </is>
+      </c>
+      <c r="N127" s="232">
+        <f>IF($L$41&gt;=$L$127,"Ok","Aumentar Ø,t")</f>
+      </c>
+      <c r="O127" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar: Ø,t ≥ 5 mm e ≥ Ø,l/4.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="K1:T1"/>
+    <mergeCell ref="K6:T6"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="K26:T26"/>
+    <mergeCell ref="K60:T60"/>
+    <mergeCell ref="K70:T70"/>
+    <mergeCell ref="K81:T81"/>
+    <mergeCell ref="K92:T92"/>
+    <mergeCell ref="K94:T94"/>
+    <mergeCell ref="K107:T107"/>
+    <mergeCell ref="K109:T109"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="O10:T10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:T12"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:T4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="N33 N42 N45 N68 N73 N84 N103 N105 N112 N125 N126 N127 N11 N13 N14 N15 N16 N17 N18">
+    <cfRule type="beginsWith" dxfId="6" priority="1" operator="beginsWith" text="Ok">
+      <formula>LEFT(N33,2)="Ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N33 N42 N45 N68 N73 N84 N103 N105 N112 N125 N126 N127 N11 N13 N14 N15 N16 N17 N18">
+    <cfRule type="beginsWith" dxfId="5" priority="2" operator="beginsWith" text="Não se aplica">
+      <formula>LEFT(N33,13)="Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L45">
+      <formula1>'CONTENÇÃO RÁPIDA'!$K$74:$K$76</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+</worksheet>
 </file>
--- a/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
+++ b/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CONTENÇÃO RÁPIDA'!$K$1:$T$259</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$138</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="1000"/>
   <extLst>
@@ -1095,12 +1095,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000%"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="&quot;Ø &quot;0.0&quot; mm&quot;"/>
   </numFmts>
   <fonts count="39" x14ac:knownFonts="1">
     <font>
@@ -2003,7 +2004,7 @@
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2519,6 +2520,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="35" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -16124,19 +16131,19 @@
           <t xml:space="preserve">M11:M12</t>
         </is>
       </c>
-      <c r="L243" s="241" t="inlineStr">
+      <c r="L243" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">#REF! – referência apagada. São cópias antigas de M22/M23 (corretas). Podem ser apagadas.</t>
         </is>
       </c>
-      <c r="M243" s="241"/>
-      <c r="N243" s="241"/>
-      <c r="O243" s="241"/>
-      <c r="P243" s="241"/>
-      <c r="Q243" s="241"/>
-      <c r="R243" s="241"/>
-      <c r="S243" s="241"/>
-      <c r="T243" s="241"/>
+      <c r="M243" s="243"/>
+      <c r="N243" s="243"/>
+      <c r="O243" s="243"/>
+      <c r="P243" s="243"/>
+      <c r="Q243" s="243"/>
+      <c r="R243" s="243"/>
+      <c r="S243" s="243"/>
+      <c r="T243" s="243"/>
     </row>
     <row r="244" ht="32" customHeight="1">
       <c r="K244" s="238" t="inlineStr">
@@ -16144,19 +16151,19 @@
           <t xml:space="preserve">M22:M26</t>
         </is>
       </c>
-      <c r="L244" s="241" t="inlineStr">
+      <c r="L244" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Carga no pilar só com o solo, sem a sobrecarga Sc (M30/M31 já incluem). Aqui: E (com Sc) e E,solo (sem Sc) – item 3.2.</t>
         </is>
       </c>
-      <c r="M244" s="241"/>
-      <c r="N244" s="241"/>
-      <c r="O244" s="241"/>
-      <c r="P244" s="241"/>
-      <c r="Q244" s="241"/>
-      <c r="R244" s="241"/>
-      <c r="S244" s="241"/>
-      <c r="T244" s="241"/>
+      <c r="M244" s="243"/>
+      <c r="N244" s="243"/>
+      <c r="O244" s="243"/>
+      <c r="P244" s="243"/>
+      <c r="Q244" s="243"/>
+      <c r="R244" s="243"/>
+      <c r="S244" s="243"/>
+      <c r="T244" s="243"/>
     </row>
     <row r="245" ht="17" customHeight="1">
       <c r="K245" s="238" t="inlineStr">
@@ -16164,19 +16171,19 @@
           <t xml:space="preserve">M26</t>
         </is>
       </c>
-      <c r="L245" s="241" t="inlineStr">
+      <c r="L245" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Momento sem unidade: o resultado é em tf·m (base do pilar em balanço, sem Sc).</t>
         </is>
       </c>
-      <c r="M245" s="241"/>
-      <c r="N245" s="241"/>
-      <c r="O245" s="241"/>
-      <c r="P245" s="241"/>
-      <c r="Q245" s="241"/>
-      <c r="R245" s="241"/>
-      <c r="S245" s="241"/>
-      <c r="T245" s="241"/>
+      <c r="M245" s="243"/>
+      <c r="N245" s="243"/>
+      <c r="O245" s="243"/>
+      <c r="P245" s="243"/>
+      <c r="Q245" s="243"/>
+      <c r="R245" s="243"/>
+      <c r="S245" s="243"/>
+      <c r="T245" s="243"/>
     </row>
     <row r="246" ht="17" customHeight="1">
       <c r="K246" s="238" t="inlineStr">
@@ -16184,19 +16191,19 @@
           <t xml:space="preserve">M28</t>
         </is>
       </c>
-      <c r="L246" s="241" t="inlineStr">
+      <c r="L246" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">M25·M24/M27 com M27 = M25 → sempre igual a M24 (redundante, não é erro).</t>
         </is>
       </c>
-      <c r="M246" s="241"/>
-      <c r="N246" s="241"/>
-      <c r="O246" s="241"/>
-      <c r="P246" s="241"/>
-      <c r="Q246" s="241"/>
-      <c r="R246" s="241"/>
-      <c r="S246" s="241"/>
-      <c r="T246" s="241"/>
+      <c r="M246" s="243"/>
+      <c r="N246" s="243"/>
+      <c r="O246" s="243"/>
+      <c r="P246" s="243"/>
+      <c r="Q246" s="243"/>
+      <c r="R246" s="243"/>
+      <c r="S246" s="243"/>
+      <c r="T246" s="243"/>
     </row>
     <row r="247" ht="17" customHeight="1">
       <c r="K247" s="238" t="inlineStr">
@@ -16204,19 +16211,19 @@
           <t xml:space="preserve">M34</t>
         </is>
       </c>
-      <c r="L247" s="241" t="inlineStr">
+      <c r="L247" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Só vale na cota 0 (usa H² na parcela uniforme). M36 é a fórmula certa para qualquer cota.</t>
         </is>
       </c>
-      <c r="M247" s="241"/>
-      <c r="N247" s="241"/>
-      <c r="O247" s="241"/>
-      <c r="P247" s="241"/>
-      <c r="Q247" s="241"/>
-      <c r="R247" s="241"/>
-      <c r="S247" s="241"/>
-      <c r="T247" s="241"/>
+      <c r="M247" s="243"/>
+      <c r="N247" s="243"/>
+      <c r="O247" s="243"/>
+      <c r="P247" s="243"/>
+      <c r="Q247" s="243"/>
+      <c r="R247" s="243"/>
+      <c r="S247" s="243"/>
+      <c r="T247" s="243"/>
     </row>
     <row r="248" ht="32" customHeight="1">
       <c r="K248" s="238" t="inlineStr">
@@ -16224,19 +16231,19 @@
           <t xml:space="preserve">M40</t>
         </is>
       </c>
-      <c r="L248" s="241" t="inlineStr">
+      <c r="L248" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">'Biapoiado' é na verdade engastado na base e apoiado no topo. Certo na cota 0 (−78,15 kN·m); para cota ≠ 0 os termos em x estão com sinal trocado e x²·Δp/2 aparece duplicado. Corrigido no item 4.1.</t>
         </is>
       </c>
-      <c r="M248" s="241"/>
-      <c r="N248" s="241"/>
-      <c r="O248" s="241"/>
-      <c r="P248" s="241"/>
-      <c r="Q248" s="241"/>
-      <c r="R248" s="241"/>
-      <c r="S248" s="241"/>
-      <c r="T248" s="241"/>
+      <c r="M248" s="243"/>
+      <c r="N248" s="243"/>
+      <c r="O248" s="243"/>
+      <c r="P248" s="243"/>
+      <c r="Q248" s="243"/>
+      <c r="R248" s="243"/>
+      <c r="S248" s="243"/>
+      <c r="T248" s="243"/>
     </row>
     <row r="249" ht="17" customHeight="1">
       <c r="K249" s="238" t="inlineStr">
@@ -16244,19 +16251,19 @@
           <t xml:space="preserve">P22:R27</t>
         </is>
       </c>
-      <c r="L249" s="241" t="inlineStr">
+      <c r="L249" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Laje alveolar correta para o painel inferior (pressão na base × bw). O item 5 detalha todos os painéis.</t>
         </is>
       </c>
-      <c r="M249" s="241"/>
-      <c r="N249" s="241"/>
-      <c r="O249" s="241"/>
-      <c r="P249" s="241"/>
-      <c r="Q249" s="241"/>
-      <c r="R249" s="241"/>
-      <c r="S249" s="241"/>
-      <c r="T249" s="241"/>
+      <c r="M249" s="243"/>
+      <c r="N249" s="243"/>
+      <c r="O249" s="243"/>
+      <c r="P249" s="243"/>
+      <c r="Q249" s="243"/>
+      <c r="R249" s="243"/>
+      <c r="S249" s="243"/>
+      <c r="T249" s="243"/>
     </row>
     <row r="250" ht="17" customHeight="1">
       <c r="K250" s="238" t="inlineStr">
@@ -16264,19 +16271,19 @@
           <t xml:space="preserve">M24</t>
         </is>
       </c>
-      <c r="L250" s="241" t="inlineStr">
+      <c r="L250" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">kN → tf por ×0,1 (1 tf = 9,81 kN) fica ~2% abaixo do exato; mantido por ser a convenção usual.</t>
         </is>
       </c>
-      <c r="M250" s="241"/>
-      <c r="N250" s="241"/>
-      <c r="O250" s="241"/>
-      <c r="P250" s="241"/>
-      <c r="Q250" s="241"/>
-      <c r="R250" s="241"/>
-      <c r="S250" s="241"/>
-      <c r="T250" s="241"/>
+      <c r="M250" s="243"/>
+      <c r="N250" s="243"/>
+      <c r="O250" s="243"/>
+      <c r="P250" s="243"/>
+      <c r="Q250" s="243"/>
+      <c r="R250" s="243"/>
+      <c r="S250" s="243"/>
+      <c r="T250" s="243"/>
     </row>
     <row r="251" ht="32" customHeight="1">
       <c r="K251" s="238" t="inlineStr">
@@ -16284,19 +16291,19 @@
           <t xml:space="preserve">M8</t>
         </is>
       </c>
-      <c r="L251" s="241" t="inlineStr">
+      <c r="L251" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Pilar travado no topo quase não se desloca: empuxo em repouso (K0) é mais realista que o ativo. Para φ = 18°: Ka = 0,53 e K0 = 0,69 (+31%). Use a entrada Empuxo (item 1.3).</t>
         </is>
       </c>
-      <c r="M251" s="241"/>
-      <c r="N251" s="241"/>
-      <c r="O251" s="241"/>
-      <c r="P251" s="241"/>
-      <c r="Q251" s="241"/>
-      <c r="R251" s="241"/>
-      <c r="S251" s="241"/>
-      <c r="T251" s="241"/>
+      <c r="M251" s="243"/>
+      <c r="N251" s="243"/>
+      <c r="O251" s="243"/>
+      <c r="P251" s="243"/>
+      <c r="Q251" s="243"/>
+      <c r="R251" s="243"/>
+      <c r="S251" s="243"/>
+      <c r="T251" s="243"/>
     </row>
     <row r="252">
       <c r="K252" s="222" t="inlineStr">
@@ -16311,19 +16318,19 @@
           <t xml:space="preserve">B20 / B28</t>
         </is>
       </c>
-      <c r="L253" s="241" t="inlineStr">
+      <c r="L253" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">#NUM! e #DIV/0!: a alvenaria pede 3,43 cm²/m e Ø8 em todo furo dá só 2,51 cm²/m → espaçamento '0 furos' e divisão por zero. Na prática: Ø8 não basta, usar Ø10 em todo furo (3,93 cm²/m).</t>
         </is>
       </c>
-      <c r="M253" s="241"/>
-      <c r="N253" s="241"/>
-      <c r="O253" s="241"/>
-      <c r="P253" s="241"/>
-      <c r="Q253" s="241"/>
-      <c r="R253" s="241"/>
-      <c r="S253" s="241"/>
-      <c r="T253" s="241"/>
+      <c r="M253" s="243"/>
+      <c r="N253" s="243"/>
+      <c r="O253" s="243"/>
+      <c r="P253" s="243"/>
+      <c r="Q253" s="243"/>
+      <c r="R253" s="243"/>
+      <c r="S253" s="243"/>
+      <c r="T253" s="243"/>
     </row>
     <row r="254" ht="17" customHeight="1">
       <c r="K254" s="238" t="inlineStr">
@@ -16331,19 +16338,19 @@
           <t xml:space="preserve">B8 / B9</t>
         </is>
       </c>
-      <c r="L254" s="241" t="inlineStr">
+      <c r="L254" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Coesão e φ dão 0: NSPT (B4) = 0 não existe na tabela DADOS DO SOLO. Sem efeito, pois o Ka de B33 é digitado.</t>
         </is>
       </c>
-      <c r="M254" s="241"/>
-      <c r="N254" s="241"/>
-      <c r="O254" s="241"/>
-      <c r="P254" s="241"/>
-      <c r="Q254" s="241"/>
-      <c r="R254" s="241"/>
-      <c r="S254" s="241"/>
-      <c r="T254" s="241"/>
+      <c r="M254" s="243"/>
+      <c r="N254" s="243"/>
+      <c r="O254" s="243"/>
+      <c r="P254" s="243"/>
+      <c r="Q254" s="243"/>
+      <c r="R254" s="243"/>
+      <c r="S254" s="243"/>
+      <c r="T254" s="243"/>
     </row>
     <row r="255" ht="32" customHeight="1">
       <c r="K255" s="238" t="inlineStr">
@@ -16351,19 +16358,19 @@
           <t xml:space="preserve">B33</t>
         </is>
       </c>
-      <c r="L255" s="241" t="inlineStr">
+      <c r="L255" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Ka = 0,36 digitado, sem ligação com φ. A aba usa 3 valores diferentes: 0,36 (B33), 0,528 (M8) e 0,75 (CÁLCULO FECHAMENTO).</t>
         </is>
       </c>
-      <c r="M255" s="241"/>
-      <c r="N255" s="241"/>
-      <c r="O255" s="241"/>
-      <c r="P255" s="241"/>
-      <c r="Q255" s="241"/>
-      <c r="R255" s="241"/>
-      <c r="S255" s="241"/>
-      <c r="T255" s="241"/>
+      <c r="M255" s="243"/>
+      <c r="N255" s="243"/>
+      <c r="O255" s="243"/>
+      <c r="P255" s="243"/>
+      <c r="Q255" s="243"/>
+      <c r="R255" s="243"/>
+      <c r="S255" s="243"/>
+      <c r="T255" s="243"/>
     </row>
     <row r="256" ht="32" customHeight="1">
       <c r="K256" s="238" t="inlineStr">
@@ -16371,19 +16378,19 @@
           <t xml:space="preserve">B24</t>
         </is>
       </c>
-      <c r="L256" s="241" t="inlineStr">
+      <c r="L256" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Esbeltez do pilar usa a altura da alvenaria (1,75 m) em vez da do pilar (3,85 m). Com 3,85 m dá ≈ 25,7 &lt; 30 → segue 'Sim', por acaso.</t>
         </is>
       </c>
-      <c r="M256" s="241"/>
-      <c r="N256" s="241"/>
-      <c r="O256" s="241"/>
-      <c r="P256" s="241"/>
-      <c r="Q256" s="241"/>
-      <c r="R256" s="241"/>
-      <c r="S256" s="241"/>
-      <c r="T256" s="241"/>
+      <c r="M256" s="243"/>
+      <c r="N256" s="243"/>
+      <c r="O256" s="243"/>
+      <c r="P256" s="243"/>
+      <c r="Q256" s="243"/>
+      <c r="R256" s="243"/>
+      <c r="S256" s="243"/>
+      <c r="T256" s="243"/>
     </row>
     <row r="257" ht="32" customHeight="1">
       <c r="K257" s="238" t="inlineStr">
@@ -16391,19 +16398,19 @@
           <t xml:space="preserve">B52:B66</t>
         </is>
       </c>
-      <c r="L257" s="241" t="inlineStr">
+      <c r="L257" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Pilar 20×30 não passa: Kc = 0,25 fora de tabela, Ks = 0,028 digitado não corresponde, As = 58 cm² (48 barras). Momento com (H/3 + 0,6) sem origem clara e sem Sc.</t>
         </is>
       </c>
-      <c r="M257" s="241"/>
-      <c r="N257" s="241"/>
-      <c r="O257" s="241"/>
-      <c r="P257" s="241"/>
-      <c r="Q257" s="241"/>
-      <c r="R257" s="241"/>
-      <c r="S257" s="241"/>
-      <c r="T257" s="241"/>
+      <c r="M257" s="243"/>
+      <c r="N257" s="243"/>
+      <c r="O257" s="243"/>
+      <c r="P257" s="243"/>
+      <c r="Q257" s="243"/>
+      <c r="R257" s="243"/>
+      <c r="S257" s="243"/>
+      <c r="T257" s="243"/>
     </row>
     <row r="258" ht="17" customHeight="1">
       <c r="K258" s="238" t="inlineStr">
@@ -16411,19 +16418,19 @@
           <t xml:space="preserve">B15</t>
         </is>
       </c>
-      <c r="L258" s="241" t="inlineStr">
+      <c r="L258" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">TABELAS LÍBANO com μ digitados para La/Lb = 0,91: se mudar H ou D, os coeficientes não se atualizam.</t>
         </is>
       </c>
-      <c r="M258" s="241"/>
-      <c r="N258" s="241"/>
-      <c r="O258" s="241"/>
-      <c r="P258" s="241"/>
-      <c r="Q258" s="241"/>
-      <c r="R258" s="241"/>
-      <c r="S258" s="241"/>
-      <c r="T258" s="241"/>
+      <c r="M258" s="243"/>
+      <c r="N258" s="243"/>
+      <c r="O258" s="243"/>
+      <c r="P258" s="243"/>
+      <c r="Q258" s="243"/>
+      <c r="R258" s="243"/>
+      <c r="S258" s="243"/>
+      <c r="T258" s="243"/>
     </row>
     <row r="259" ht="17" customHeight="1">
       <c r="K259" s="238" t="inlineStr">
@@ -16431,19 +16438,19 @@
           <t xml:space="preserve">B90</t>
         </is>
       </c>
-      <c r="L259" s="241" t="inlineStr">
+      <c r="L259" s="243" t="inlineStr">
         <is>
           <t xml:space="preserve">Peso da sapata fixo (1,2 × 1,0 × 0,5 m).</t>
         </is>
       </c>
-      <c r="M259" s="241"/>
-      <c r="N259" s="241"/>
-      <c r="O259" s="241"/>
-      <c r="P259" s="241"/>
-      <c r="Q259" s="241"/>
-      <c r="R259" s="241"/>
-      <c r="S259" s="241"/>
-      <c r="T259" s="241"/>
+      <c r="M259" s="243"/>
+      <c r="N259" s="243"/>
+      <c r="O259" s="243"/>
+      <c r="P259" s="243"/>
+      <c r="Q259" s="243"/>
+      <c r="R259" s="243"/>
+      <c r="S259" s="243"/>
+      <c r="T259" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="59">
@@ -16536,7 +16543,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="K1:T127"/>
+  <dimension ref="K1:T138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="2.7109375" customWidth="1"/>
@@ -16571,63 +16578,67 @@
       </c>
       <c r="L2" s="239"/>
       <c r="M2" s="240">
-        <f>$L$100&amp;" Ø"&amp;$L$42&amp;" em cada face (simétrica)"</f>
+        <f>"As,nec = "&amp;FIXED($L$109,2)&amp;" cm²/face"</f>
       </c>
       <c r="N2" s="240"/>
-      <c r="O2" s="240">
-        <f>"As,ef = "&amp;FIXED($L$101,2)&amp;" cm²/face | total "&amp;FIXED($L$102,2)&amp;" cm²"</f>
-      </c>
-      <c r="P2" s="240"/>
+      <c r="O2" s="241">
+        <v>12.5</v>
+      </c>
+      <c r="P2" s="240">
+        <f>$L$111&amp;" barras em cada face ("&amp;FIXED($L$112,2)&amp;" cm²)"</f>
+      </c>
       <c r="Q2" s="240"/>
-      <c r="R2" s="240">
-        <f>"ρ = "&amp;FIXED($L$103,2)&amp;" % | "&amp;IF($L$105&lt;$L$104,"NÃO CABE","cabe na face")</f>
-      </c>
-      <c r="S2" s="240"/>
-      <c r="T2" s="240"/>
+      <c r="R2" s="240"/>
+      <c r="S2" s="242">
+        <f>IF($L$116&lt;$L$115,"NÃO OK – não cabe na face",IF($L$114&gt;4,"NÃO OK – taxa &gt; 4%",IF($L$42&lt;10,"NÃO OK – Ø &lt; 10 mm",IF($L$42&gt;$L$39*10/8,"NÃO OK – Ø &gt; b/8","OK"))))</f>
+      </c>
+      <c r="T2" s="242"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="K3" s="239" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTRIBOS</t>
+          <t xml:space="preserve">ARMADURA TRANSVERSAL</t>
         </is>
       </c>
       <c r="L3" s="239"/>
       <c r="M3" s="240">
-        <f>"Ø"&amp;$L$41&amp;" c/"&amp;$L$125&amp;" ("&amp;$L$43&amp;" ramos)"</f>
+        <f>"Asw,nec = "&amp;FIXED($L$132,2)&amp;" cm²/m"</f>
       </c>
       <c r="N3" s="240"/>
-      <c r="O3" s="240">
-        <f>"Asw = "&amp;FIXED($L$121,2)&amp;" cm²/m"</f>
-      </c>
-      <c r="P3" s="240"/>
+      <c r="O3" s="241">
+        <v>6.3</v>
+      </c>
+      <c r="P3" s="240">
+        <f>"c/ "&amp;$L$136&amp;" cm ("&amp;$L$43&amp;" ramos) = "&amp;FIXED($L$137,2)&amp;" cm²/m"</f>
+      </c>
       <c r="Q3" s="240"/>
-      <c r="R3" s="240">
-        <f>"Vsd = "&amp;FIXED($L$111,1)&amp;" kN | VRd2 = "&amp;FIXED($L$112,1)&amp;" kN"</f>
-      </c>
-      <c r="S3" s="240"/>
-      <c r="T3" s="240"/>
+      <c r="R3" s="240"/>
+      <c r="S3" s="242">
+        <f>IF($L$122&gt;$L$123,"NÃO OK – biela: aumentar seção",IF($L$136&lt;5,"NÃO OK – s &lt; 5 cm: aumentar Ø",IF($L$41&lt;$L$138,"NÃO OK – Ø,t &lt; Ø,l/4","OK")))</f>
+      </c>
+      <c r="T3" s="242"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="K4" s="239" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESFORÇOS DE CÁLCULO</t>
+          <t xml:space="preserve">FLEXÃO / ESFORÇOS</t>
         </is>
       </c>
       <c r="L4" s="239"/>
       <c r="M4" s="240">
-        <f>"Md+ = "&amp;FIXED($L$72,2)&amp;" | Md− = "&amp;FIXED($L$83,2)&amp;" kN·m"</f>
+        <f>"Md+ = "&amp;FIXED($L$83,1)&amp;" | Md− = "&amp;FIXED($L$94,1)&amp;" kN·m"</f>
       </c>
       <c r="N4" s="240"/>
       <c r="O4" s="240">
-        <f>"Md,lim = "&amp;FIXED($L$67,2)&amp;" kN·m"</f>
+        <f>"Md,lim = "&amp;FIXED($L$78,1)&amp;" kN·m | Vsd = "&amp;FIXED($L$122,1)&amp;" kN ("&amp;$L$45&amp;")"</f>
       </c>
       <c r="P4" s="240"/>
       <c r="Q4" s="240"/>
-      <c r="R4" s="240">
-        <f>"Modelo: "&amp;$L$45&amp;" | seção "&amp;$L$39&amp;"×"&amp;$L$38</f>
-      </c>
-      <c r="S4" s="240"/>
-      <c r="T4" s="240"/>
+      <c r="R4" s="240"/>
+      <c r="S4" s="242">
+        <f>IF(MAX($L$83,$L$94)&gt;$L$78,"NÃO OK – arm. dupla: h ≥ "&amp;ROUNDUP($L$79+$L$75,0)&amp;" cm","OK – arm. simples")</f>
+      </c>
+      <c r="T4" s="242"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="K6" s="220" t="inlineStr">
@@ -16696,7 +16707,7 @@
         </is>
       </c>
       <c r="L11" s="236">
-        <f>"Md+ = "&amp;FIXED($L$72,1)&amp;" | Md− = "&amp;FIXED($L$83,1)</f>
+        <f>"Md+ = "&amp;FIXED($L$83,1)&amp;" | Md− = "&amp;FIXED($L$94,1)</f>
       </c>
       <c r="M11" s="236"/>
       <c r="N11" s="232">
@@ -16715,7 +16726,7 @@
         </is>
       </c>
       <c r="L12" s="234">
-        <f>IF(MAX($L$72,$L$83)&gt;$L$67,"⚠ Armadura dupla: a seção "&amp;$L$39&amp;"×"&amp;$L$38&amp;" é pequena para Md = "&amp;FIXED(MAX($L$72,$L$83),1)&amp;" kN·m. Para armadura simples use h ≥ "&amp;ROUNDUP($L$68+$L$64,0)&amp;" cm.","Flexão simples (sem a força normal): se o pilar tiver compressão relevante, confira a flexo-compressão no programa.")</f>
+        <f>IF(MAX($L$83,$L$94)&gt;$L$78,"⚠ Armadura dupla: a seção "&amp;$L$39&amp;"×"&amp;$L$38&amp;" é pequena para Md = "&amp;FIXED(MAX($L$83,$L$94),1)&amp;" kN·m. Para armadura simples use h ≥ "&amp;ROUNDUP($L$79+$L$75,0)&amp;" cm.","Flexão simples (sem a força normal): se o pilar tiver compressão relevante, confira a flexo-compressão no programa.")</f>
       </c>
       <c r="M12" s="234"/>
       <c r="N12" s="234"/>
@@ -16733,11 +16744,11 @@
         </is>
       </c>
       <c r="L13" s="236">
-        <f>$L$73</f>
+        <f>$L$84</f>
       </c>
       <c r="M13" s="236"/>
       <c r="N13" s="232">
-        <f>IF($L$72=0,"Não se aplica (M = 0)",IF($L$72&lt;=$L$67,"Ok","Arm. dupla – ver d,mín"))</f>
+        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$78,"Ok","Arm. dupla – ver d,mín"))</f>
       </c>
       <c r="O13" s="233" t="inlineStr">
         <is>
@@ -16752,11 +16763,11 @@
         </is>
       </c>
       <c r="L14" s="236">
-        <f>$L$84</f>
+        <f>$L$95</f>
       </c>
       <c r="M14" s="236"/>
       <c r="N14" s="232">
-        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$67,"Ok","Arm. dupla – ver d,mín"))</f>
+        <f>IF($L$94=0,"Não se aplica (M = 0)",IF($L$94&lt;=$L$78,"Ok","Arm. dupla – ver d,mín"))</f>
       </c>
       <c r="O14" s="233" t="inlineStr">
         <is>
@@ -16771,11 +16782,11 @@
         </is>
       </c>
       <c r="L15" s="236">
-        <f>$L$100&amp;" Ø"&amp;$L$42&amp;" ("&amp;FIXED($L$101,2)&amp;" cm²)"</f>
+        <f>$L$111&amp;" Ø"&amp;$L$42&amp;" ("&amp;FIXED($L$112,2)&amp;" cm²)"</f>
       </c>
       <c r="M15" s="236"/>
       <c r="N15" s="232">
-        <f>IF($L$105&lt;$L$104,"Não cabe: aumentar b ou Ø,l","Ok")</f>
+        <f>IF($L$116&lt;$L$115,"Não cabe: aumentar b ou Ø,l","Ok")</f>
       </c>
       <c r="O15" s="233" t="inlineStr">
         <is>
@@ -16790,11 +16801,11 @@
         </is>
       </c>
       <c r="L16" s="236">
-        <f>FIXED($L$103,2)&amp;" %"</f>
+        <f>FIXED($L$114,2)&amp;" %"</f>
       </c>
       <c r="M16" s="236"/>
       <c r="N16" s="232">
-        <f>IF($L$103&gt;4,"Rever: taxa &gt; 4%",IF($L$103&lt;0.4,"Rever: taxa &lt; 0,4%","Ok"))</f>
+        <f>IF($L$114&gt;4,"Rever: taxa &gt; 4%",IF($L$114&lt;0.4,"Rever: taxa &lt; 0,4%","Ok"))</f>
       </c>
       <c r="O16" s="233" t="inlineStr">
         <is>
@@ -16809,11 +16820,11 @@
         </is>
       </c>
       <c r="L17" s="236">
-        <f>FIXED($L$111,1)&amp;" ≤ "&amp;FIXED($L$112,1)&amp;" kN"</f>
+        <f>FIXED($L$122,1)&amp;" ≤ "&amp;FIXED($L$123,1)&amp;" kN"</f>
       </c>
       <c r="M17" s="236"/>
       <c r="N17" s="232">
-        <f>IF($L$111&lt;=$L$112,"Ok","Aumentar seção ou fck")</f>
+        <f>IF($L$122&lt;=$L$123,"Ok","Aumentar seção ou fck")</f>
       </c>
       <c r="O17" s="233" t="inlineStr">
         <is>
@@ -16828,11 +16839,11 @@
         </is>
       </c>
       <c r="L18" s="236">
-        <f>"Ø"&amp;$L$41&amp;" c/"&amp;$L$125&amp;" ("&amp;$L$43&amp;" ramos)"</f>
+        <f>"Ø"&amp;$L$41&amp;" c/"&amp;$L$136&amp;" ("&amp;$L$43&amp;" ramos)"</f>
       </c>
       <c r="M18" s="236"/>
       <c r="N18" s="232">
-        <f>IF($L$125&lt;5,"s &lt; 5 cm – aumentar Ø,t",IF($L$126&gt;=$L$121,"Ok","Rever"))</f>
+        <f>IF($L$136&lt;5,"s &lt; 5 cm – aumentar Ø,t",IF($L$137&gt;=$L$132,"Ok","Rever"))</f>
       </c>
       <c r="O18" s="233" t="inlineStr">
         <is>
@@ -17086,8 +17097,8 @@
           <t xml:space="preserve">Ø,t</t>
         </is>
       </c>
-      <c r="L41" s="224">
-        <v>6.3</v>
+      <c r="L41" s="227">
+        <f>$O$3</f>
       </c>
       <c r="M41" s="231" t="inlineStr">
         <is>
@@ -17096,7 +17107,7 @@
       </c>
       <c r="O41" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bitola do estribo.</t>
+          <t xml:space="preserve">Bitola do estribo – escolha no painel do topo (linha 3).</t>
         </is>
       </c>
     </row>
@@ -17106,8 +17117,8 @@
           <t xml:space="preserve">Ø,l</t>
         </is>
       </c>
-      <c r="L42" s="224">
-        <v>12.5</v>
+      <c r="L42" s="227">
+        <f>$O$2</f>
       </c>
       <c r="M42" s="231" t="inlineStr">
         <is>
@@ -17119,7 +17130,7 @@
       </c>
       <c r="O42" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bitola da armadura longitudinal.</t>
+          <t xml:space="preserve">Bitola longitudinal – escolha no painel do topo (linha 2).</t>
         </is>
       </c>
     </row>
@@ -17258,420 +17269,332 @@
     <row r="50">
       <c r="K50" s="222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Tabela ρ,mín (NBR 6118, tab. 17.3)</t>
+          <t xml:space="preserve">1.6 Bitolas disponíveis (lista do painel do topo)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="K51" s="235" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ø (mm)</t>
+        </is>
+      </c>
+      <c r="L51" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área (cm²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="K52" s="224">
+        <v>5</v>
+      </c>
+      <c r="L52" s="228">
+        <f>PI()*(K52/10)^2/4</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="K53" s="224">
+        <v>6.3</v>
+      </c>
+      <c r="L53" s="228">
+        <f>PI()*(K53/10)^2/4</f>
+      </c>
+    </row>
+    <row r="54">
+      <c r="K54" s="224">
+        <v>8</v>
+      </c>
+      <c r="L54" s="228">
+        <f>PI()*(K54/10)^2/4</f>
+      </c>
+    </row>
+    <row r="55">
+      <c r="K55" s="224">
+        <v>10</v>
+      </c>
+      <c r="L55" s="228">
+        <f>PI()*(K55/10)^2/4</f>
+      </c>
+    </row>
+    <row r="56">
+      <c r="K56" s="224">
+        <v>12.5</v>
+      </c>
+      <c r="L56" s="228">
+        <f>PI()*(K56/10)^2/4</f>
+      </c>
+    </row>
+    <row r="57">
+      <c r="K57" s="224">
+        <v>16</v>
+      </c>
+      <c r="L57" s="228">
+        <f>PI()*(K57/10)^2/4</f>
+      </c>
+    </row>
+    <row r="58">
+      <c r="K58" s="224">
+        <v>20</v>
+      </c>
+      <c r="L58" s="228">
+        <f>PI()*(K58/10)^2/4</f>
+      </c>
+    </row>
+    <row r="59">
+      <c r="K59" s="224">
+        <v>25</v>
+      </c>
+      <c r="L59" s="228">
+        <f>PI()*(K59/10)^2/4</f>
+      </c>
+    </row>
+    <row r="60">
+      <c r="K60" s="224">
+        <v>32</v>
+      </c>
+      <c r="L60" s="228">
+        <f>PI()*(K60/10)^2/4</f>
+      </c>
+    </row>
+    <row r="61">
+      <c r="K61" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Tabela ρ,mín (NBR 6118, tab. 17.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="K62" s="235" t="inlineStr">
+        <is>
           <t xml:space="preserve">fck (MPa)</t>
         </is>
       </c>
-      <c r="L51" s="235" t="inlineStr">
+      <c r="L62" s="235" t="inlineStr">
         <is>
           <t xml:space="preserve">ρ,mín (%)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="K52" s="237">
+    <row r="63">
+      <c r="K63" s="237">
         <v>20</v>
       </c>
-      <c r="L52" s="226">
+      <c r="L63" s="226">
         <v>0.15</v>
       </c>
     </row>
-    <row r="53">
-      <c r="K53" s="237">
+    <row r="64">
+      <c r="K64" s="237">
         <v>25</v>
       </c>
-      <c r="L53" s="226">
+      <c r="L64" s="226">
         <v>0.15</v>
       </c>
     </row>
-    <row r="54">
-      <c r="K54" s="237">
+    <row r="65">
+      <c r="K65" s="237">
         <v>30</v>
       </c>
-      <c r="L54" s="226">
+      <c r="L65" s="226">
         <v>0.15</v>
       </c>
     </row>
-    <row r="55">
-      <c r="K55" s="237">
+    <row r="66">
+      <c r="K66" s="237">
         <v>35</v>
       </c>
-      <c r="L55" s="226">
+      <c r="L66" s="226">
         <v>0.164</v>
       </c>
     </row>
-    <row r="56">
-      <c r="K56" s="237">
+    <row r="67">
+      <c r="K67" s="237">
         <v>40</v>
       </c>
-      <c r="L56" s="226">
+      <c r="L67" s="226">
         <v>0.179</v>
       </c>
     </row>
-    <row r="57">
-      <c r="K57" s="237">
+    <row r="68">
+      <c r="K68" s="237">
         <v>45</v>
       </c>
-      <c r="L57" s="226">
+      <c r="L68" s="226">
         <v>0.194</v>
       </c>
     </row>
-    <row r="58">
-      <c r="K58" s="237">
+    <row r="69">
+      <c r="K69" s="237">
         <v>50</v>
       </c>
-      <c r="L58" s="226">
+      <c r="L69" s="226">
         <v>0.208</v>
       </c>
     </row>
-    <row r="60">
-      <c r="K60" s="221" t="inlineStr">
+    <row r="71">
+      <c r="K71" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">2 . PARÂMETROS DE CÁLCULO</t>
         </is>
       </c>
-      <c r="L60" s="221"/>
-      <c r="M60" s="221"/>
-      <c r="N60" s="221"/>
-      <c r="O60" s="221"/>
-      <c r="P60" s="221"/>
-      <c r="Q60" s="221"/>
-      <c r="R60" s="221"/>
-      <c r="S60" s="221"/>
-      <c r="T60" s="221"/>
-    </row>
-    <row r="62">
-      <c r="K62" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fcd</t>
-        </is>
-      </c>
-      <c r="L62" s="227">
-        <f>$L$33/$L$30</f>
-      </c>
-      <c r="M62" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPa</t>
-        </is>
-      </c>
-      <c r="O62" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resistência de cálculo do concreto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="K63" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fyd</t>
-        </is>
-      </c>
-      <c r="L63" s="227">
-        <f>$L$34/$L$31</f>
-      </c>
-      <c r="M63" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPa</t>
-        </is>
-      </c>
-      <c r="O63" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resistência de cálculo do aço.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="K64" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">d'</t>
-        </is>
-      </c>
-      <c r="L64" s="227">
-        <f>$L$40+$L$41/10+$L$42/20</f>
-      </c>
-      <c r="M64" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cm</t>
-        </is>
-      </c>
-      <c r="O64" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Distância da face ao eixo das barras (c + Ø,t + Ø,l/2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="K65" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">d</t>
-        </is>
-      </c>
-      <c r="L65" s="227">
-        <f>$L$38-$L$64</f>
-      </c>
-      <c r="M65" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cm</t>
-        </is>
-      </c>
-      <c r="O65" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Altura útil (h − d').</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="K66" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(x/d)lim</t>
-        </is>
-      </c>
-      <c r="L66" s="227">
-        <v>0.45</v>
-      </c>
-      <c r="M66" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O66" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Limite da linha neutra para fck ≤ 50 MPa (ductilidade).</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="K67" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Md,lim</t>
-        </is>
-      </c>
-      <c r="L67" s="227">
-        <f>0.68*$L$39*$L$65^2*$L$62/10*$L$66*(1-0.4*$L$66)/100</f>
-      </c>
-      <c r="M67" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN·m</t>
-        </is>
-      </c>
-      <c r="O67" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Maior momento de cálculo só com armadura simples.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="K68" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">d,mín</t>
-        </is>
-      </c>
-      <c r="L68" s="227">
-        <f>SQRT(MAX($L$46,$L$47)*$L$29*100/(0.68*$L$39*$L$62/10*$L$66*(1-0.4*$L$66)))</f>
-      </c>
-      <c r="M68" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cm</t>
-        </is>
-      </c>
-      <c r="N68" s="232">
-        <f>IF($L$65&gt;=$L$68,"Ok","Aumentar h para "&amp;ROUNDUP($L$68+$L$64,0)&amp;" cm (arm. simples)")</f>
-      </c>
-      <c r="O68" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Altura útil mínima para armadura simples com o maior momento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="K70" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 . FLEXÃO – SEÇÃO DO VÃO (M+)</t>
-        </is>
-      </c>
-      <c r="L70" s="221"/>
-      <c r="M70" s="221"/>
-      <c r="N70" s="221"/>
-      <c r="O70" s="221"/>
-      <c r="P70" s="221"/>
-      <c r="Q70" s="221"/>
-      <c r="R70" s="221"/>
-      <c r="S70" s="221"/>
-      <c r="T70" s="221"/>
-    </row>
-    <row r="72">
-      <c r="K72" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Md</t>
-        </is>
-      </c>
-      <c r="L72" s="227">
-        <f>$L$46*$L$29</f>
-      </c>
-      <c r="M72" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN·m</t>
-        </is>
-      </c>
-      <c r="O72" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Momento de cálculo (γf·Mk).</t>
-        </is>
-      </c>
+      <c r="L71" s="221"/>
+      <c r="M71" s="221"/>
+      <c r="N71" s="221"/>
+      <c r="O71" s="221"/>
+      <c r="P71" s="221"/>
+      <c r="Q71" s="221"/>
+      <c r="R71" s="221"/>
+      <c r="S71" s="221"/>
+      <c r="T71" s="221"/>
     </row>
     <row r="73">
       <c r="K73" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo</t>
-        </is>
-      </c>
-      <c r="L73" s="230">
-        <f>IF($L$72=0,"Não se aplica (M = 0)",IF($L$72&lt;=$L$67,"Armadura simples","Armadura dupla"))</f>
+          <t xml:space="preserve">fcd</t>
+        </is>
+      </c>
+      <c r="L73" s="227">
+        <f>$L$33/$L$30</f>
       </c>
       <c r="M73" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N73" s="232">
-        <f>IF($L$72=0,"Não se aplica (M = 0)",IF($L$72&lt;=$L$67,"Ok","Arm. dupla – ver d,mín (item 2)"))</f>
+          <t xml:space="preserve">MPa</t>
+        </is>
       </c>
       <c r="O73" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simples se Md ≤ Md,lim; dupla se maior.</t>
+          <t xml:space="preserve">Resistência de cálculo do concreto.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="K74" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">x</t>
+          <t xml:space="preserve">fyd</t>
         </is>
       </c>
       <c r="L74" s="227">
-        <f>IF($L$72&lt;=$L$67,1.25*$L$65*(1-SQRT(MAX(0,1-$L$72*100/(0.425*$L$39*$L$65^2*$L$62/10)))),$L$66*$L$65)</f>
+        <f>$L$34/$L$31</f>
       </c>
       <c r="M74" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm</t>
+          <t xml:space="preserve">MPa</t>
         </is>
       </c>
       <c r="O74" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Profundidade da linha neutra.</t>
+          <t xml:space="preserve">Resistência de cálculo do aço.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="K75" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">x/d</t>
-        </is>
-      </c>
-      <c r="L75" s="228">
-        <f>IF($L$65=0,0,$L$74/$L$65)</f>
+          <t xml:space="preserve">d'</t>
+        </is>
+      </c>
+      <c r="L75" s="227">
+        <f>$L$40+$L$41/10+$L$42/20</f>
       </c>
       <c r="M75" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">cm</t>
         </is>
       </c>
       <c r="O75" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posição relativa da linha neutra.</t>
+          <t xml:space="preserve">Distância da face ao eixo das barras (c + Ø,t + Ø,l/2).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="K76" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domínio</t>
-        </is>
-      </c>
-      <c r="L76" s="230">
-        <f>IF($L$72=0,"-",IF($L$75&lt;=0.259,"2","3"))</f>
+          <t xml:space="preserve">d</t>
+        </is>
+      </c>
+      <c r="L76" s="227">
+        <f>$L$38-$L$75</f>
       </c>
       <c r="M76" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">cm</t>
         </is>
       </c>
       <c r="O76" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domínio de deformação.</t>
+          <t xml:space="preserve">Altura útil (h − d').</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="K77" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">σsc</t>
+          <t xml:space="preserve">(x/d)lim</t>
         </is>
       </c>
       <c r="L77" s="227">
-        <f>MIN($L$63,210000*0.0035*MAX(0,$L$74-$L$64)/MAX($L$74,0.001))</f>
+        <v>0.45</v>
       </c>
       <c r="M77" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">MPa</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O77" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tensão na armadura comprimida (Es = 210 GPa, εc = 3,5‰), só na armadura dupla.</t>
+          <t xml:space="preserve">Limite da linha neutra para fck ≤ 50 MPa (ductilidade).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="K78" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">As,t</t>
+          <t xml:space="preserve">Md,lim</t>
         </is>
       </c>
       <c r="L78" s="227">
-        <f>IF($L$72&lt;=$L$67,$L$72*100/($L$63/10*($L$65-0.4*$L$74)),$L$67*100/($L$63/10*($L$65-0.4*$L$74))+($L$72-$L$67)*100/($L$63/10*($L$65-$L$64)))</f>
+        <f>0.68*$L$39*$L$76^2*$L$73/10*$L$77*(1-0.4*$L$77)/100</f>
       </c>
       <c r="M78" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm²</t>
+          <t xml:space="preserve">kN·m</t>
         </is>
       </c>
       <c r="O78" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura tracionada – face externa.</t>
+          <t xml:space="preserve">Maior momento de cálculo só com armadura simples.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="K79" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">As,c</t>
+          <t xml:space="preserve">d,mín</t>
         </is>
       </c>
       <c r="L79" s="227">
-        <f>IF($L$72&lt;=$L$67,0,($L$72-$L$67)*100/($L$77/10*($L$65-$L$64)))</f>
+        <f>SQRT(MAX($L$46,$L$47)*$L$29*100/(0.68*$L$39*$L$73/10*$L$77*(1-0.4*$L$77)))</f>
       </c>
       <c r="M79" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm²</t>
-        </is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="N79" s="232">
+        <f>IF($L$76&gt;=$L$79,"Ok","Aumentar h para "&amp;ROUNDUP($L$79+$L$75,0)&amp;" cm (arm. simples)")</f>
       </c>
       <c r="O79" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura comprimida – face do solo (0 na armadura simples).</t>
+          <t xml:space="preserve">Altura útil mínima para armadura simples com o maior momento.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="K81" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 . FLEXÃO – SEÇÃO DA BASE (M−)</t>
+          <t xml:space="preserve">3 . FLEXÃO – SEÇÃO DO VÃO (M+)</t>
         </is>
       </c>
       <c r="L81" s="221"/>
@@ -17691,7 +17614,7 @@
         </is>
       </c>
       <c r="L83" s="227">
-        <f>$L$47*$L$29</f>
+        <f>$L$46*$L$29</f>
       </c>
       <c r="M83" s="231" t="inlineStr">
         <is>
@@ -17711,7 +17634,7 @@
         </is>
       </c>
       <c r="L84" s="230">
-        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$67,"Armadura simples","Armadura dupla"))</f>
+        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$78,"Armadura simples","Armadura dupla"))</f>
       </c>
       <c r="M84" s="231" t="inlineStr">
         <is>
@@ -17719,7 +17642,7 @@
         </is>
       </c>
       <c r="N84" s="232">
-        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$67,"Ok","Arm. dupla – ver d,mín (item 2)"))</f>
+        <f>IF($L$83=0,"Não se aplica (M = 0)",IF($L$83&lt;=$L$78,"Ok","Arm. dupla – ver d,mín (item 2)"))</f>
       </c>
       <c r="O84" s="233" t="inlineStr">
         <is>
@@ -17734,7 +17657,7 @@
         </is>
       </c>
       <c r="L85" s="227">
-        <f>IF($L$83&lt;=$L$67,1.25*$L$65*(1-SQRT(MAX(0,1-$L$83*100/(0.425*$L$39*$L$65^2*$L$62/10)))),$L$66*$L$65)</f>
+        <f>IF($L$83&lt;=$L$78,1.25*$L$76*(1-SQRT(MAX(0,1-$L$83*100/(0.425*$L$39*$L$76^2*$L$73/10)))),$L$77*$L$76)</f>
       </c>
       <c r="M85" s="231" t="inlineStr">
         <is>
@@ -17754,7 +17677,7 @@
         </is>
       </c>
       <c r="L86" s="228">
-        <f>IF($L$65=0,0,$L$85/$L$65)</f>
+        <f>IF($L$76=0,0,$L$85/$L$76)</f>
       </c>
       <c r="M86" s="231" t="inlineStr">
         <is>
@@ -17794,7 +17717,7 @@
         </is>
       </c>
       <c r="L88" s="227">
-        <f>MIN($L$63,210000*0.0035*MAX(0,$L$85-$L$64)/MAX($L$85,0.001))</f>
+        <f>MIN($L$74,210000*0.0035*MAX(0,$L$85-$L$75)/MAX($L$85,0.001))</f>
       </c>
       <c r="M88" s="231" t="inlineStr">
         <is>
@@ -17814,7 +17737,7 @@
         </is>
       </c>
       <c r="L89" s="227">
-        <f>IF($L$83&lt;=$L$67,$L$83*100/($L$63/10*($L$65-0.4*$L$85)),$L$67*100/($L$63/10*($L$65-0.4*$L$85))+($L$83-$L$67)*100/($L$63/10*($L$65-$L$64)))</f>
+        <f>IF($L$83&lt;=$L$78,$L$83*100/($L$74/10*($L$76-0.4*$L$85)),$L$78*100/($L$74/10*($L$76-0.4*$L$85))+($L$83-$L$78)*100/($L$74/10*($L$76-$L$75)))</f>
       </c>
       <c r="M89" s="231" t="inlineStr">
         <is>
@@ -17823,7 +17746,7 @@
       </c>
       <c r="O89" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura tracionada – face do solo.</t>
+          <t xml:space="preserve">Armadura tracionada – face externa.</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17757,7 @@
         </is>
       </c>
       <c r="L90" s="227">
-        <f>IF($L$83&lt;=$L$67,0,($L$83-$L$67)*100/($L$88/10*($L$65-$L$64)))</f>
+        <f>IF($L$83&lt;=$L$78,0,($L$83-$L$78)*100/($L$88/10*($L$76-$L$75)))</f>
       </c>
       <c r="M90" s="231" t="inlineStr">
         <is>
@@ -17843,14 +17766,14 @@
       </c>
       <c r="O90" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura comprimida – face externa (0 na armadura simples).</t>
+          <t xml:space="preserve">Armadura comprimida – face do solo (0 na armadura simples).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="K92" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 . ARMADURA LONGITUDINAL SIMÉTRICA (mesma nas duas faces)</t>
+          <t xml:space="preserve">4 . FLEXÃO – SEÇÃO DA BASE (M−)</t>
         </is>
       </c>
       <c r="L92" s="221"/>
@@ -17863,150 +17786,157 @@
       <c r="S92" s="221"/>
       <c r="T92" s="221"/>
     </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="K94" s="220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cada face recebe a maior entre: tração do vão, tração da base, compressão da armadura dupla, mínima de viga (por face) e metade da mínima de pilar (0,4% Ac no total). As mesmas barras seguem por toda a altura, cobrindo as duas seções.</t>
-        </is>
-      </c>
-      <c r="L94" s="220"/>
-      <c r="M94" s="220"/>
-      <c r="N94" s="220"/>
-      <c r="O94" s="220"/>
-      <c r="P94" s="220"/>
-      <c r="Q94" s="220"/>
-      <c r="R94" s="220"/>
-      <c r="S94" s="220"/>
-      <c r="T94" s="220"/>
+    <row r="94">
+      <c r="K94" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Md</t>
+        </is>
+      </c>
+      <c r="L94" s="227">
+        <f>$L$47*$L$29</f>
+      </c>
+      <c r="M94" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN·m</t>
+        </is>
+      </c>
+      <c r="O94" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momento de cálculo (γf·Mk).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="K95" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">ρ,mín</t>
-        </is>
-      </c>
-      <c r="L95" s="228">
-        <f>VLOOKUP($L$33,$K$52:$L$58,2,TRUE)</f>
+          <t xml:space="preserve">Tipo</t>
+        </is>
+      </c>
+      <c r="L95" s="230">
+        <f>IF($L$94=0,"Não se aplica (M = 0)",IF($L$94&lt;=$L$78,"Armadura simples","Armadura dupla"))</f>
       </c>
       <c r="M95" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
-        </is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N95" s="232">
+        <f>IF($L$94=0,"Não se aplica (M = 0)",IF($L$94&lt;=$L$78,"Ok","Arm. dupla – ver d,mín (item 2)"))</f>
       </c>
       <c r="O95" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxa mínima de flexão (tabela 1.5).</t>
+          <t xml:space="preserve">Simples se Md ≤ Md,lim; dupla se maior.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="K96" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">As,mín,v</t>
+          <t xml:space="preserve">x</t>
         </is>
       </c>
       <c r="L96" s="227">
-        <f>$L$95/100*$L$39*$L$38</f>
+        <f>IF($L$94&lt;=$L$78,1.25*$L$76*(1-SQRT(MAX(0,1-$L$94*100/(0.425*$L$39*$L$76^2*$L$73/10)))),$L$77*$L$76)</f>
       </c>
       <c r="M96" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm²</t>
+          <t xml:space="preserve">cm</t>
         </is>
       </c>
       <c r="O96" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mínima de viga, por face tracionada: ρ,mín·b·h.</t>
+          <t xml:space="preserve">Profundidade da linha neutra.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="K97" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">As,mín,p</t>
-        </is>
-      </c>
-      <c r="L97" s="227">
-        <f>MAX(0.15*$L$49*$L$29/($L$63/10),0.004*$L$39*$L$38)</f>
+          <t xml:space="preserve">x/d</t>
+        </is>
+      </c>
+      <c r="L97" s="228">
+        <f>IF($L$76=0,0,$L$96/$L$76)</f>
       </c>
       <c r="M97" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm²</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O97" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mínima de pilar, total: máx(0,15·Nd/fyd; 0,4%·Ac).</t>
+          <t xml:space="preserve">Posição relativa da linha neutra.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="K98" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">As,face</t>
-        </is>
-      </c>
-      <c r="L98" s="227">
-        <f>MAX($L$78,$L$79,$L$89,$L$90,$L$96,$L$97/2)</f>
+          <t xml:space="preserve">Domínio</t>
+        </is>
+      </c>
+      <c r="L98" s="230">
+        <f>IF($L$94=0,"-",IF($L$97&lt;=0.259,"2","3"))</f>
       </c>
       <c r="M98" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm²</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O98" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura necessária em cada face.</t>
+          <t xml:space="preserve">Domínio de deformação.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="K99" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">A,barra</t>
-        </is>
-      </c>
-      <c r="L99" s="228">
-        <f>PI()*($L$42/10)^2/4</f>
+          <t xml:space="preserve">σsc</t>
+        </is>
+      </c>
+      <c r="L99" s="227">
+        <f>MIN($L$74,210000*0.0035*MAX(0,$L$96-$L$75)/MAX($L$96,0.001))</f>
       </c>
       <c r="M99" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm²</t>
+          <t xml:space="preserve">MPa</t>
         </is>
       </c>
       <c r="O99" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Área de uma barra Ø,l.</t>
+          <t xml:space="preserve">Tensão na armadura comprimida (Es = 210 GPa, εc = 3,5‰), só na armadura dupla.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="K100" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">n</t>
-        </is>
-      </c>
-      <c r="L100" s="229">
-        <f>MAX(2,ROUNDUP($L$98/$L$99,0))</f>
+          <t xml:space="preserve">As,t</t>
+        </is>
+      </c>
+      <c r="L100" s="227">
+        <f>IF($L$94&lt;=$L$78,$L$94*100/($L$74/10*($L$76-0.4*$L$96)),$L$78*100/($L$74/10*($L$76-0.4*$L$96))+($L$94-$L$78)*100/($L$74/10*($L$76-$L$75)))</f>
       </c>
       <c r="M100" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">un</t>
+          <t xml:space="preserve">cm²</t>
         </is>
       </c>
       <c r="O100" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barras em cada face (mínimo 2).</t>
+          <t xml:space="preserve">Armadura tracionada – face do solo.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="K101" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">As,ef</t>
+          <t xml:space="preserve">As,c</t>
         </is>
       </c>
       <c r="L101" s="227">
-        <f>$L$100*$L$99</f>
+        <f>IF($L$94&lt;=$L$78,0,($L$94-$L$78)*100/($L$99/10*($L$76-$L$75)))</f>
       </c>
       <c r="M101" s="231" t="inlineStr">
         <is>
@@ -18015,469 +17945,641 @@
       </c>
       <c r="O101" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura efetiva em cada face.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="K102" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As,total</t>
-        </is>
-      </c>
-      <c r="L102" s="227">
-        <f>2*$L$101</f>
-      </c>
-      <c r="M102" s="231" t="inlineStr">
+          <t xml:space="preserve">Armadura comprimida – face externa (0 na armadura simples).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="K103" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 . ARMADURA LONGITUDINAL SIMÉTRICA (mesma nas duas faces)</t>
+        </is>
+      </c>
+      <c r="L103" s="221"/>
+      <c r="M103" s="221"/>
+      <c r="N103" s="221"/>
+      <c r="O103" s="221"/>
+      <c r="P103" s="221"/>
+      <c r="Q103" s="221"/>
+      <c r="R103" s="221"/>
+      <c r="S103" s="221"/>
+      <c r="T103" s="221"/>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="K105" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada face recebe a maior entre: tração do vão, tração da base, compressão da armadura dupla, mínima de viga (por face) e metade da mínima de pilar (0,4% Ac no total). As mesmas barras seguem por toda a altura, cobrindo as duas seções.</t>
+        </is>
+      </c>
+      <c r="L105" s="220"/>
+      <c r="M105" s="220"/>
+      <c r="N105" s="220"/>
+      <c r="O105" s="220"/>
+      <c r="P105" s="220"/>
+      <c r="Q105" s="220"/>
+      <c r="R105" s="220"/>
+      <c r="S105" s="220"/>
+      <c r="T105" s="220"/>
+    </row>
+    <row r="106">
+      <c r="K106" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ρ,mín</t>
+        </is>
+      </c>
+      <c r="L106" s="228">
+        <f>VLOOKUP($L$33,$K$63:$L$69,2,TRUE)</f>
+      </c>
+      <c r="M106" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="O106" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taxa mínima de flexão (tabela 1.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="K107" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,mín,v</t>
+        </is>
+      </c>
+      <c r="L107" s="227">
+        <f>$L$106/100*$L$39*$L$38</f>
+      </c>
+      <c r="M107" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">cm²</t>
         </is>
       </c>
-      <c r="O102" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Armadura total na seção (duas faces).</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="K103" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ρ,total</t>
-        </is>
-      </c>
-      <c r="L103" s="227">
-        <f>$L$102/($L$39*$L$38)*100</f>
-      </c>
-      <c r="M103" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">%</t>
-        </is>
-      </c>
-      <c r="N103" s="232">
-        <f>IF($L$103&gt;4,"Rever: taxa &gt; 4% – aumentar seção",IF($L$103&lt;0.4,"Rever: taxa &lt; 0,4%","Ok"))</f>
-      </c>
-      <c r="O103" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Taxa total (pilar: 0,4% a 4%; 8% na emenda).</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="K104" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a,h,mín</t>
-        </is>
-      </c>
-      <c r="L104" s="227">
-        <f>MAX(2,$L$42/10,1.2*$L$36/10)</f>
-      </c>
-      <c r="M104" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cm</t>
-        </is>
-      </c>
-      <c r="O104" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mínimo: 2 cm, Ø,l e 1,2·d,máx.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="K105" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a,h</t>
-        </is>
-      </c>
-      <c r="L105" s="227">
-        <f>IF($L$100&lt;=1,0,($L$39-2*$L$40-2*$L$41/10-$L$100*$L$42/10)/($L$100-1))</f>
-      </c>
-      <c r="M105" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cm</t>
-        </is>
-      </c>
-      <c r="N105" s="232">
-        <f>IF($L$105&lt;$L$104,"Não cabe: aumentar b ou Ø,l",IF($L$105&gt;40,"Rever: espaço &gt; 40 cm","Ok"))</f>
-      </c>
-      <c r="O105" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Espaço livre entre barras da mesma face.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="K107" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 . ESTRIBOS – FORÇA CORTANTE (Modelo I, NBR 6118)</t>
-        </is>
-      </c>
-      <c r="L107" s="221"/>
-      <c r="M107" s="221"/>
-      <c r="N107" s="221"/>
-      <c r="O107" s="221"/>
-      <c r="P107" s="221"/>
-      <c r="Q107" s="221"/>
-      <c r="R107" s="221"/>
-      <c r="S107" s="221"/>
-      <c r="T107" s="221"/>
-    </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="K109" s="220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vsd ≤ VRd2 (biela) e Vsd ≤ Vc0 + Vsw. O espaçamento adotado é o menor entre o calculado, o máximo de viga (0,6·d ≤ 30 cm ou 0,3·d ≤ 20 cm) e o máximo de pilar (20 cm, b, 12·Ø,l).</t>
-        </is>
-      </c>
-      <c r="L109" s="220"/>
-      <c r="M109" s="220"/>
-      <c r="N109" s="220"/>
-      <c r="O109" s="220"/>
-      <c r="P109" s="220"/>
-      <c r="Q109" s="220"/>
-      <c r="R109" s="220"/>
-      <c r="S109" s="220"/>
-      <c r="T109" s="220"/>
+      <c r="O107" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mínima de viga, por face tracionada: ρ,mín·b·h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="K108" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,mín,p</t>
+        </is>
+      </c>
+      <c r="L108" s="227">
+        <f>MAX(0.15*$L$49*$L$29/($L$74/10),0.004*$L$39*$L$38)</f>
+      </c>
+      <c r="M108" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O108" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mínima de pilar, total: máx(0,15·Nd/fyd; 0,4%·Ac).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="K109" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As,face</t>
+        </is>
+      </c>
+      <c r="L109" s="227">
+        <f>MAX($L$89,$L$90,$L$100,$L$101,$L$107,$L$108/2)</f>
+      </c>
+      <c r="M109" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O109" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura necessária em cada face.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="K110" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.1 Biela e parcela do concreto</t>
+      <c r="K110" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A,barra</t>
+        </is>
+      </c>
+      <c r="L110" s="228">
+        <f>PI()*($L$42/10)^2/4</f>
+      </c>
+      <c r="M110" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²</t>
+        </is>
+      </c>
+      <c r="O110" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de uma barra Ø,l.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="K111" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vsd</t>
-        </is>
-      </c>
-      <c r="L111" s="227">
-        <f>$L$48*$L$29</f>
+          <t xml:space="preserve">n</t>
+        </is>
+      </c>
+      <c r="L111" s="229">
+        <f>MAX(2,ROUNDUP($L$109/$L$110,0))</f>
       </c>
       <c r="M111" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN</t>
+          <t xml:space="preserve">un</t>
         </is>
       </c>
       <c r="O111" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cortante de cálculo (γf·Vk).</t>
+          <t xml:space="preserve">Barras em cada face (mínimo 2).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="K112" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">VRd2</t>
+          <t xml:space="preserve">As,ef</t>
         </is>
       </c>
       <c r="L112" s="227">
-        <f>0.27*(1-$L$33/250)*$L$62/10*$L$39*$L$65</f>
+        <f>$L$111*$L$110</f>
       </c>
       <c r="M112" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN</t>
-        </is>
-      </c>
-      <c r="N112" s="232">
-        <f>IF($L$111&lt;=$L$112,"Ok","Aumentar seção ou fck")</f>
+          <t xml:space="preserve">cm²</t>
+        </is>
       </c>
       <c r="O112" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistência da biela comprimida.</t>
+          <t xml:space="preserve">Armadura efetiva em cada face.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="K113" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">fctm</t>
+          <t xml:space="preserve">As,total</t>
         </is>
       </c>
       <c r="L113" s="227">
-        <f>0.3*$L$33^(2/3)</f>
+        <f>2*$L$112</f>
       </c>
       <c r="M113" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">MPa</t>
+          <t xml:space="preserve">cm²</t>
         </is>
       </c>
       <c r="O113" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistência média à tração.</t>
+          <t xml:space="preserve">Armadura total na seção (duas faces).</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="K114" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">fctd</t>
+          <t xml:space="preserve">ρ,total</t>
         </is>
       </c>
       <c r="L114" s="227">
-        <f>0.7*$L$113/$L$30</f>
+        <f>$L$113/($L$39*$L$38)*100</f>
       </c>
       <c r="M114" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">MPa</t>
-        </is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="N114" s="232">
+        <f>IF($L$114&gt;4,"Rever: taxa &gt; 4% – aumentar seção",IF($L$114&lt;0.4,"Rever: taxa &lt; 0,4%","Ok"))</f>
       </c>
       <c r="O114" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistência de cálculo à tração (fctk,inf/γc).</t>
+          <t xml:space="preserve">Taxa total (pilar: 0,4% a 4%; 8% na emenda).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="K115" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vc0</t>
+          <t xml:space="preserve">a,h,mín</t>
         </is>
       </c>
       <c r="L115" s="227">
-        <f>0.6*$L$114/10*$L$39*$L$65</f>
+        <f>MAX(2,$L$42/10,1.2*$L$36/10)</f>
       </c>
       <c r="M115" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN</t>
+          <t xml:space="preserve">cm</t>
         </is>
       </c>
       <c r="O115" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcela resistida pelo concreto.</t>
+          <t xml:space="preserve">Mínimo: 2 cm, Ø,l e 1,2·d,máx.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="K116" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2 Armadura transversal</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="K117" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fywd</t>
-        </is>
-      </c>
-      <c r="L117" s="227">
-        <f>MIN($L$35/$L$31,435)</f>
-      </c>
-      <c r="M117" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPa</t>
-        </is>
-      </c>
-      <c r="O117" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resistência de cálculo do estribo (≤ 435 MPa).</t>
+      <c r="K116" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a,h</t>
+        </is>
+      </c>
+      <c r="L116" s="227">
+        <f>IF($L$111&lt;=1,0,($L$39-2*$L$40-2*$L$41/10-$L$111*$L$42/10)/($L$111-1))</f>
+      </c>
+      <c r="M116" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="N116" s="232">
+        <f>IF($L$116&lt;$L$115,"Não cabe: aumentar b ou Ø,l",IF($L$116&gt;40,"Rever: espaço &gt; 40 cm","Ok"))</f>
+      </c>
+      <c r="O116" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espaço livre entre barras da mesma face.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="K118" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vsw</t>
-        </is>
-      </c>
-      <c r="L118" s="227">
-        <f>MAX(0,$L$111-$L$115)</f>
-      </c>
-      <c r="M118" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN</t>
-        </is>
-      </c>
-      <c r="O118" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parcela a ser resistida pelos estribos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="K119" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asw,calc</t>
-        </is>
-      </c>
-      <c r="L119" s="227">
-        <f>$L$118/(0.9*$L$65*$L$117/10)*100</f>
-      </c>
-      <c r="M119" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cm²/m</t>
-        </is>
-      </c>
-      <c r="O119" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asw/s = Vsw/(0,9·d·fywd).</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="K120" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asw,mín</t>
-        </is>
-      </c>
-      <c r="L120" s="227">
-        <f>0.2*$L$113/$L$35*$L$39*100</f>
-      </c>
-      <c r="M120" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cm²/m</t>
-        </is>
-      </c>
-      <c r="O120" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mínima: ρsw = 0,2·fctm/fywk.</t>
-        </is>
-      </c>
+      <c r="K118" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 . ESTRIBOS – FORÇA CORTANTE (Modelo I, NBR 6118)</t>
+        </is>
+      </c>
+      <c r="L118" s="221"/>
+      <c r="M118" s="221"/>
+      <c r="N118" s="221"/>
+      <c r="O118" s="221"/>
+      <c r="P118" s="221"/>
+      <c r="Q118" s="221"/>
+      <c r="R118" s="221"/>
+      <c r="S118" s="221"/>
+      <c r="T118" s="221"/>
+    </row>
+    <row r="120" ht="32" customHeight="1">
+      <c r="K120" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vsd ≤ VRd2 (biela) e Vsd ≤ Vc0 + Vsw. O espaçamento adotado é o menor entre o calculado, o máximo de viga (0,6·d ≤ 30 cm ou 0,3·d ≤ 20 cm) e o máximo de pilar (20 cm, b, 12·Ø,l).</t>
+        </is>
+      </c>
+      <c r="L120" s="220"/>
+      <c r="M120" s="220"/>
+      <c r="N120" s="220"/>
+      <c r="O120" s="220"/>
+      <c r="P120" s="220"/>
+      <c r="Q120" s="220"/>
+      <c r="R120" s="220"/>
+      <c r="S120" s="220"/>
+      <c r="T120" s="220"/>
     </row>
     <row r="121">
-      <c r="K121" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asw</t>
-        </is>
-      </c>
-      <c r="L121" s="227">
-        <f>MAX($L$119,$L$120)</f>
-      </c>
-      <c r="M121" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cm²/m</t>
-        </is>
-      </c>
-      <c r="O121" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Armadura transversal adotada (todos os ramos).</t>
+      <c r="K121" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 Biela e parcela do concreto</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="K122" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s,calc</t>
+          <t xml:space="preserve">Vsd</t>
         </is>
       </c>
       <c r="L122" s="227">
-        <f>IF($L$121=0,999,$L$43*PI()*($L$41/10)^2/4/$L$121*100)</f>
+        <f>$L$48*$L$29</f>
       </c>
       <c r="M122" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm</t>
+          <t xml:space="preserve">kN</t>
         </is>
       </c>
       <c r="O122" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espaçamento pela armadura calculada.</t>
+          <t xml:space="preserve">Cortante de cálculo (γf·Vk).</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="K123" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s,máx,v</t>
+          <t xml:space="preserve">VRd2</t>
         </is>
       </c>
       <c r="L123" s="227">
-        <f>IF($L$111&lt;=0.67*$L$112,MIN(0.6*$L$65,30),MIN(0.3*$L$65,20))</f>
+        <f>0.27*(1-$L$33/250)*$L$73/10*$L$39*$L$76</f>
       </c>
       <c r="M123" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm</t>
-        </is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="N123" s="232">
+        <f>IF($L$122&lt;=$L$123,"Ok","Aumentar seção ou fck")</f>
       </c>
       <c r="O123" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Máximo de viga (NBR 6118, 18.3.3.2).</t>
+          <t xml:space="preserve">Resistência da biela comprimida.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="K124" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s,máx,p</t>
+          <t xml:space="preserve">fctm</t>
         </is>
       </c>
       <c r="L124" s="227">
-        <f>MIN(20,$L$39,$L$38,IF($L$34&gt;=500,12,25)*$L$42/10)</f>
+        <f>0.3*$L$33^(2/3)</f>
       </c>
       <c r="M124" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm</t>
+          <t xml:space="preserve">MPa</t>
         </is>
       </c>
       <c r="O124" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Máximo de pilar: 20 cm, menor dimensão, 12·Ø,l (CA-50).</t>
+          <t xml:space="preserve">Resistência média à tração.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="K125" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="L125" s="229">
-        <f>ROUNDDOWN(MIN($L$122,$L$123,$L$124),0)</f>
+          <t xml:space="preserve">fctd</t>
+        </is>
+      </c>
+      <c r="L125" s="227">
+        <f>0.7*$L$124/$L$30</f>
       </c>
       <c r="M125" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm</t>
-        </is>
-      </c>
-      <c r="N125" s="232">
-        <f>IF($L$125&lt;5,"s &lt; 5 cm – aumentar Ø,t ou ramos","Ok")</f>
+          <t xml:space="preserve">MPa</t>
+        </is>
       </c>
       <c r="O125" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espaçamento adotado (arredondado para baixo).</t>
+          <t xml:space="preserve">Resistência de cálculo à tração (fctk,inf/γc).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="K126" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vc0</t>
+        </is>
+      </c>
+      <c r="L126" s="227">
+        <f>0.6*$L$125/10*$L$39*$L$76</f>
+      </c>
+      <c r="M126" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O126" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcela resistida pelo concreto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="K127" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2 Armadura transversal</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="K128" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fywd</t>
+        </is>
+      </c>
+      <c r="L128" s="227">
+        <f>MIN($L$35/$L$31,435)</f>
+      </c>
+      <c r="M128" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O128" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência de cálculo do estribo (≤ 435 MPa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="K129" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vsw</t>
+        </is>
+      </c>
+      <c r="L129" s="227">
+        <f>MAX(0,$L$122-$L$126)</f>
+      </c>
+      <c r="M129" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="O129" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcela a ser resistida pelos estribos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="K130" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw,calc</t>
+        </is>
+      </c>
+      <c r="L130" s="227">
+        <f>$L$129/(0.9*$L$76*$L$128/10)*100</f>
+      </c>
+      <c r="M130" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²/m</t>
+        </is>
+      </c>
+      <c r="O130" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw/s = Vsw/(0,9·d·fywd).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="K131" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw,mín</t>
+        </is>
+      </c>
+      <c r="L131" s="227">
+        <f>0.2*$L$124/$L$35*$L$39*100</f>
+      </c>
+      <c r="M131" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²/m</t>
+        </is>
+      </c>
+      <c r="O131" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mínima: ρsw = 0,2·fctm/fywk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="K132" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw</t>
+        </is>
+      </c>
+      <c r="L132" s="227">
+        <f>MAX($L$130,$L$131)</f>
+      </c>
+      <c r="M132" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²/m</t>
+        </is>
+      </c>
+      <c r="O132" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura transversal adotada (todos os ramos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="K133" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s,calc</t>
+        </is>
+      </c>
+      <c r="L133" s="227">
+        <f>IF($L$132=0,999,$L$43*PI()*($L$41/10)^2/4/$L$132*100)</f>
+      </c>
+      <c r="M133" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O133" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espaçamento pela armadura calculada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="K134" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s,máx,v</t>
+        </is>
+      </c>
+      <c r="L134" s="227">
+        <f>IF($L$122&lt;=0.67*$L$123,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20))</f>
+      </c>
+      <c r="M134" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O134" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Máximo de viga (NBR 6118, 18.3.3.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="K135" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s,máx,p</t>
+        </is>
+      </c>
+      <c r="L135" s="227">
+        <f>MIN(20,$L$39,$L$38,IF($L$34&gt;=500,12,25)*$L$42/10)</f>
+      </c>
+      <c r="M135" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O135" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Máximo de pilar: 20 cm, menor dimensão, 12·Ø,l (CA-50).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="K136" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="L136" s="229">
+        <f>ROUNDDOWN(MIN($L$133,$L$134,$L$135),0)</f>
+      </c>
+      <c r="M136" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="N136" s="232">
+        <f>IF($L$136&lt;5,"s &lt; 5 cm – aumentar Ø,t ou ramos","Ok")</f>
+      </c>
+      <c r="O136" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espaçamento adotado (arredondado para baixo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="K137" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">Asw,ef</t>
         </is>
       </c>
-      <c r="L126" s="227">
-        <f>$L$43*PI()*($L$41/10)^2/4*100/$L$125</f>
-      </c>
-      <c r="M126" s="231" t="inlineStr">
+      <c r="L137" s="227">
+        <f>$L$43*PI()*($L$41/10)^2/4*100/$L$136</f>
+      </c>
+      <c r="M137" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">cm²/m</t>
         </is>
       </c>
-      <c r="N126" s="232">
-        <f>IF($L$126&gt;=$L$121,"Ok","Rever")</f>
-      </c>
-      <c r="O126" s="233" t="inlineStr">
+      <c r="N137" s="232">
+        <f>IF($L$137&gt;=$L$132,"Ok","Rever")</f>
+      </c>
+      <c r="O137" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Armadura efetiva com o espaçamento adotado.</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="K127" s="223" t="inlineStr">
+    <row r="138">
+      <c r="K138" s="223" t="inlineStr">
         <is>
           <t xml:space="preserve">Ø,t,mín</t>
         </is>
       </c>
-      <c r="L127" s="227">
+      <c r="L138" s="227">
         <f>MAX(5,$L$42/4)</f>
       </c>
-      <c r="M127" s="231" t="inlineStr">
+      <c r="M138" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">mm</t>
         </is>
       </c>
-      <c r="N127" s="232">
-        <f>IF($L$41&gt;=$L$127,"Ok","Aumentar Ø,t")</f>
-      </c>
-      <c r="O127" s="233" t="inlineStr">
+      <c r="N138" s="232">
+        <f>IF($L$41&gt;=$L$138,"Ok","Aumentar Ø,t")</f>
+      </c>
+      <c r="O138" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Pilar: Ø,t ≥ 5 mm e ≥ Ø,l/4.</t>
         </is>
@@ -18489,13 +18591,13 @@
     <mergeCell ref="K6:T6"/>
     <mergeCell ref="K8:T8"/>
     <mergeCell ref="K26:T26"/>
-    <mergeCell ref="K60:T60"/>
-    <mergeCell ref="K70:T70"/>
+    <mergeCell ref="K71:T71"/>
     <mergeCell ref="K81:T81"/>
     <mergeCell ref="K92:T92"/>
-    <mergeCell ref="K94:T94"/>
-    <mergeCell ref="K107:T107"/>
-    <mergeCell ref="K109:T109"/>
+    <mergeCell ref="K103:T103"/>
+    <mergeCell ref="K105:T105"/>
+    <mergeCell ref="K118:T118"/>
+    <mergeCell ref="K120:T120"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="O10:T10"/>
     <mergeCell ref="L11:M11"/>
@@ -18508,30 +18610,33 @@
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="S2:T2"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:T3"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="S4:T4"/>
   </mergeCells>
-  <conditionalFormatting sqref="N33 N42 N45 N68 N73 N84 N103 N105 N112 N125 N126 N127 N11 N13 N14 N15 N16 N17 N18">
+  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N116 N123 N136 N137 N138 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4">
     <cfRule type="beginsWith" dxfId="6" priority="1" operator="beginsWith" text="Ok">
       <formula>LEFT(N33,2)="Ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N33 N42 N45 N68 N73 N84 N103 N105 N112 N125 N126 N127 N11 N13 N14 N15 N16 N17 N18">
+  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N116 N123 N136 N137 N138 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4">
     <cfRule type="beginsWith" dxfId="5" priority="2" operator="beginsWith" text="Não se aplica">
       <formula>LEFT(N33,13)="Não se aplica"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L45">
       <formula1>'CONTENÇÃO RÁPIDA'!$K$74:$K$76</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O3">
+      <formula1>$K$52:$K$60</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
+++ b/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CONTENÇÃO RÁPIDA'!$K$1:$T$259</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$138</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$146</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="1000"/>
   <extLst>
@@ -16543,7 +16543,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="K1:T138"/>
+  <dimension ref="K1:T146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="2.7109375" customWidth="1"/>
@@ -16640,6 +16640,28 @@
       </c>
       <c r="T4" s="242"/>
     </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="K5" s="239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAXA DE AÇO</t>
+        </is>
+      </c>
+      <c r="L5" s="239"/>
+      <c r="M5" s="240">
+        <f>"ρ,long = "&amp;FIXED($L$114,2)&amp;" % (0,4% a 4%)"</f>
+      </c>
+      <c r="N5" s="240"/>
+      <c r="O5" s="240">
+        <f>"Longit. "&amp;FIXED($L$143,1)&amp;" + estribos "&amp;FIXED($L$145,1)&amp;" = "&amp;FIXED($L$146,1)&amp;" kg/m³"</f>
+      </c>
+      <c r="P5" s="240"/>
+      <c r="Q5" s="240"/>
+      <c r="R5" s="240"/>
+      <c r="S5" s="242">
+        <f>IF($L$114&gt;4,"NÃO OK – ρ &gt; 4%",IF($L$114&lt;0.4,"NÃO OK – ρ &lt; 0,4%","OK"))</f>
+      </c>
+      <c r="T5" s="242"/>
+    </row>
     <row r="6" ht="60" customHeight="1">
       <c r="K6" s="220" t="inlineStr">
         <is>
@@ -18585,8 +18607,124 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="K140" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 . TAXA DE AÇO</t>
+        </is>
+      </c>
+      <c r="L140" s="221"/>
+      <c r="M140" s="221"/>
+      <c r="N140" s="221"/>
+      <c r="O140" s="221"/>
+      <c r="P140" s="221"/>
+      <c r="Q140" s="221"/>
+      <c r="R140" s="221"/>
+      <c r="S140" s="221"/>
+      <c r="T140" s="221"/>
+    </row>
+    <row r="142">
+      <c r="K142" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ρ,aço</t>
+        </is>
+      </c>
+      <c r="L142" s="224">
+        <v>0.785</v>
+      </c>
+      <c r="M142" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg/m/cm²</t>
+        </is>
+      </c>
+      <c r="O142" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peso por metro de 1 cm² de barra (7850 kg/m³).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="K143" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Longit.</t>
+        </is>
+      </c>
+      <c r="L143" s="227">
+        <f>$L$113*$L$142/($L$39*$L$38/10000)</f>
+      </c>
+      <c r="M143" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg/m³</t>
+        </is>
+      </c>
+      <c r="O143" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura longitudinal (duas faces) por m³ de concreto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="K144" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">l,est</t>
+        </is>
+      </c>
+      <c r="L144" s="227">
+        <f>2*($L$39+$L$38)-8*$L$40+12</f>
+      </c>
+      <c r="M144" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O144" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comprimento de cada estribo (perímetro − cobrimentos + ganchos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="K145" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estribos</t>
+        </is>
+      </c>
+      <c r="L145" s="227">
+        <f>100/$L$136*$L$144/100*PI()*($L$41/10)^2/4*$L$142*$L$43/2/($L$39*$L$38/10000)</f>
+      </c>
+      <c r="M145" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg/m³</t>
+        </is>
+      </c>
+      <c r="O145" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estribos por m³ de concreto (100/s estribos por metro).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="K146" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total</t>
+        </is>
+      </c>
+      <c r="L146" s="227">
+        <f>$L$143+$L$145</f>
+      </c>
+      <c r="M146" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg/m³</t>
+        </is>
+      </c>
+      <c r="O146" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taxa total de aço do pilar.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="38">
     <mergeCell ref="K1:T1"/>
     <mergeCell ref="K6:T6"/>
     <mergeCell ref="K8:T8"/>
@@ -18598,6 +18736,7 @@
     <mergeCell ref="K105:T105"/>
     <mergeCell ref="K118:T118"/>
     <mergeCell ref="K120:T120"/>
+    <mergeCell ref="K140:T140"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="O10:T10"/>
     <mergeCell ref="L11:M11"/>
@@ -18620,13 +18759,17 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:R4"/>
     <mergeCell ref="S4:T4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="S5:T5"/>
   </mergeCells>
-  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N116 N123 N136 N137 N138 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4">
+  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N116 N123 N136 N137 N138 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
     <cfRule type="beginsWith" dxfId="6" priority="1" operator="beginsWith" text="Ok">
       <formula>LEFT(N33,2)="Ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N116 N123 N136 N137 N138 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4">
+  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N116 N123 N136 N137 N138 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
     <cfRule type="beginsWith" dxfId="5" priority="2" operator="beginsWith" text="Não se aplica">
       <formula>LEFT(N33,13)="Não se aplica"</formula>
     </cfRule>

--- a/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
+++ b/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CONTENÇÃO RÁPIDA'!$K$1:$T$259</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$146</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$147</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="1000"/>
   <extLst>
@@ -16543,7 +16543,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="K1:T146"/>
+  <dimension ref="K1:T147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="2.7109375" customWidth="1"/>
@@ -16585,12 +16585,12 @@
         <v>12.5</v>
       </c>
       <c r="P2" s="240">
-        <f>$L$111&amp;" barras em cada face ("&amp;FIXED($L$112,2)&amp;" cm²)"</f>
+        <f>$L$111&amp;" barras em cada face ("&amp;FIXED($L$112,2)&amp;" cm²) | espaço livre "&amp;FIXED($L$117,2)&amp;" cm"</f>
       </c>
       <c r="Q2" s="240"/>
       <c r="R2" s="240"/>
       <c r="S2" s="242">
-        <f>IF($L$116&lt;$L$115,"NÃO OK – não cabe na face",IF($L$114&gt;4,"NÃO OK – taxa &gt; 4%",IF($L$42&lt;10,"NÃO OK – Ø &lt; 10 mm",IF($L$42&gt;$L$39*10/8,"NÃO OK – Ø &gt; b/8","OK"))))</f>
+        <f>IF($L$117&lt;$L$115,"NÃO OK – "&amp;"Espaço livre "&amp;FIXED($L$117,2)&amp;" &lt; "&amp;FIXED($L$115,2)&amp;" cm ("&amp;$L$116&amp;")",IF($L$114&gt;4,"NÃO OK – taxa &gt; 4%",IF($L$42&lt;10,"NÃO OK – Ø &lt; 10 mm",IF($L$42&gt;$L$39*10/8,"NÃO OK – Ø &gt; b/8","OK"))))</f>
       </c>
       <c r="T2" s="242"/>
     </row>
@@ -16602,19 +16602,19 @@
       </c>
       <c r="L3" s="239"/>
       <c r="M3" s="240">
-        <f>"Asw,nec = "&amp;FIXED($L$132,2)&amp;" cm²/m"</f>
+        <f>"Asw,nec = "&amp;FIXED($L$133,2)&amp;" cm²/m"</f>
       </c>
       <c r="N3" s="240"/>
       <c r="O3" s="241">
         <v>6.3</v>
       </c>
       <c r="P3" s="240">
-        <f>"c/ "&amp;$L$136&amp;" cm ("&amp;$L$43&amp;" ramos) = "&amp;FIXED($L$137,2)&amp;" cm²/m"</f>
+        <f>"c/ "&amp;$L$137&amp;" cm ("&amp;$L$43&amp;" ramos) = "&amp;FIXED($L$138,2)&amp;" cm²/m"</f>
       </c>
       <c r="Q3" s="240"/>
       <c r="R3" s="240"/>
       <c r="S3" s="242">
-        <f>IF($L$122&gt;$L$123,"NÃO OK – biela: aumentar seção",IF($L$136&lt;5,"NÃO OK – s &lt; 5 cm: aumentar Ø",IF($L$41&lt;$L$138,"NÃO OK – Ø,t &lt; Ø,l/4","OK")))</f>
+        <f>IF($L$123&gt;$L$124,"NÃO OK – biela: aumentar seção",IF($L$137&lt;5,"NÃO OK – s &lt; 5 cm: aumentar Ø",IF($L$41&lt;$L$139,"NÃO OK – Ø,t &lt; Ø,l/4","OK")))</f>
       </c>
       <c r="T3" s="242"/>
     </row>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="N4" s="240"/>
       <c r="O4" s="240">
-        <f>"Md,lim = "&amp;FIXED($L$78,1)&amp;" kN·m | Vsd = "&amp;FIXED($L$122,1)&amp;" kN ("&amp;$L$45&amp;")"</f>
+        <f>"Md,lim = "&amp;FIXED($L$78,1)&amp;" kN·m | Vsd = "&amp;FIXED($L$123,1)&amp;" kN ("&amp;$L$45&amp;")"</f>
       </c>
       <c r="P4" s="240"/>
       <c r="Q4" s="240"/>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="N5" s="240"/>
       <c r="O5" s="240">
-        <f>"Longit. "&amp;FIXED($L$143,1)&amp;" + estribos "&amp;FIXED($L$145,1)&amp;" = "&amp;FIXED($L$146,1)&amp;" kg/m³"</f>
+        <f>"Longit. "&amp;FIXED($L$144,1)&amp;" + estribos "&amp;FIXED($L$146,1)&amp;" = "&amp;FIXED($L$147,1)&amp;" kg/m³"</f>
       </c>
       <c r="P5" s="240"/>
       <c r="Q5" s="240"/>
@@ -16808,7 +16808,7 @@
       </c>
       <c r="M15" s="236"/>
       <c r="N15" s="232">
-        <f>IF($L$116&lt;$L$115,"Não cabe: aumentar b ou Ø,l","Ok")</f>
+        <f>IF($L$117&lt;$L$115,"Espaço livre "&amp;FIXED($L$117,2)&amp;" &lt; "&amp;FIXED($L$115,2)&amp;" cm ("&amp;$L$116&amp;")","Ok")</f>
       </c>
       <c r="O15" s="233" t="inlineStr">
         <is>
@@ -16842,11 +16842,11 @@
         </is>
       </c>
       <c r="L17" s="236">
-        <f>FIXED($L$122,1)&amp;" ≤ "&amp;FIXED($L$123,1)&amp;" kN"</f>
+        <f>FIXED($L$123,1)&amp;" ≤ "&amp;FIXED($L$124,1)&amp;" kN"</f>
       </c>
       <c r="M17" s="236"/>
       <c r="N17" s="232">
-        <f>IF($L$122&lt;=$L$123,"Ok","Aumentar seção ou fck")</f>
+        <f>IF($L$123&lt;=$L$124,"Ok","Aumentar seção ou fck")</f>
       </c>
       <c r="O17" s="233" t="inlineStr">
         <is>
@@ -16861,11 +16861,11 @@
         </is>
       </c>
       <c r="L18" s="236">
-        <f>"Ø"&amp;$L$41&amp;" c/"&amp;$L$136&amp;" ("&amp;$L$43&amp;" ramos)"</f>
+        <f>"Ø"&amp;$L$41&amp;" c/"&amp;$L$137&amp;" ("&amp;$L$43&amp;" ramos)"</f>
       </c>
       <c r="M18" s="236"/>
       <c r="N18" s="232">
-        <f>IF($L$136&lt;5,"s &lt; 5 cm – aumentar Ø,t",IF($L$137&gt;=$L$132,"Ok","Rever"))</f>
+        <f>IF($L$137&lt;5,"s &lt; 5 cm – aumentar Ø,t",IF($L$138&gt;=$L$133,"Ok","Rever"))</f>
       </c>
       <c r="O18" s="233" t="inlineStr">
         <is>
@@ -18202,143 +18202,143 @@
       </c>
       <c r="O115" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mínimo: 2 cm, Ø,l e 1,2·d,máx.</t>
+          <t xml:space="preserve">NBR 6118, 18.4.2.2: maior entre 2 cm, Ø,l e 1,2·d,máx.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="K116" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">governa</t>
+        </is>
+      </c>
+      <c r="L116" s="230">
+        <f>IF($L$115=$L$42/10,"≥ Ø da barra",IF($L$115=2,"≥ 2 cm","≥ 1,2·d,máx"))</f>
+      </c>
+      <c r="M116" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O116" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critério que define o espaço mínimo (brita 0: d,máx = 9,5 mm; brita 1: 19 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="K117" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">a,h</t>
         </is>
       </c>
-      <c r="L116" s="227">
+      <c r="L117" s="227">
         <f>IF($L$111&lt;=1,0,($L$39-2*$L$40-2*$L$41/10-$L$111*$L$42/10)/($L$111-1))</f>
       </c>
-      <c r="M116" s="231" t="inlineStr">
+      <c r="M117" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">cm</t>
         </is>
       </c>
-      <c r="N116" s="232">
-        <f>IF($L$116&lt;$L$115,"Não cabe: aumentar b ou Ø,l",IF($L$116&gt;40,"Rever: espaço &gt; 40 cm","Ok"))</f>
-      </c>
-      <c r="O116" s="233" t="inlineStr">
+      <c r="N117" s="232">
+        <f>IF($L$117&lt;$L$115,"Espaço livre "&amp;FIXED($L$117,2)&amp;" &lt; "&amp;FIXED($L$115,2)&amp;" cm ("&amp;$L$116&amp;")",IF($L$117&gt;40,"Rever: espaço &gt; 40 cm","Ok"))</f>
+      </c>
+      <c r="O117" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Espaço livre entre barras da mesma face.</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="K118" s="221" t="inlineStr">
+    <row r="119">
+      <c r="K119" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">6 . ESTRIBOS – FORÇA CORTANTE (Modelo I, NBR 6118)</t>
         </is>
       </c>
-      <c r="L118" s="221"/>
-      <c r="M118" s="221"/>
-      <c r="N118" s="221"/>
-      <c r="O118" s="221"/>
-      <c r="P118" s="221"/>
-      <c r="Q118" s="221"/>
-      <c r="R118" s="221"/>
-      <c r="S118" s="221"/>
-      <c r="T118" s="221"/>
-    </row>
-    <row r="120" ht="32" customHeight="1">
-      <c r="K120" s="220" t="inlineStr">
+      <c r="L119" s="221"/>
+      <c r="M119" s="221"/>
+      <c r="N119" s="221"/>
+      <c r="O119" s="221"/>
+      <c r="P119" s="221"/>
+      <c r="Q119" s="221"/>
+      <c r="R119" s="221"/>
+      <c r="S119" s="221"/>
+      <c r="T119" s="221"/>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="K121" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Vsd ≤ VRd2 (biela) e Vsd ≤ Vc0 + Vsw. O espaçamento adotado é o menor entre o calculado, o máximo de viga (0,6·d ≤ 30 cm ou 0,3·d ≤ 20 cm) e o máximo de pilar (20 cm, b, 12·Ø,l).</t>
         </is>
       </c>
-      <c r="L120" s="220"/>
-      <c r="M120" s="220"/>
-      <c r="N120" s="220"/>
-      <c r="O120" s="220"/>
-      <c r="P120" s="220"/>
-      <c r="Q120" s="220"/>
-      <c r="R120" s="220"/>
-      <c r="S120" s="220"/>
-      <c r="T120" s="220"/>
-    </row>
-    <row r="121">
-      <c r="K121" s="222" t="inlineStr">
+      <c r="L121" s="220"/>
+      <c r="M121" s="220"/>
+      <c r="N121" s="220"/>
+      <c r="O121" s="220"/>
+      <c r="P121" s="220"/>
+      <c r="Q121" s="220"/>
+      <c r="R121" s="220"/>
+      <c r="S121" s="220"/>
+      <c r="T121" s="220"/>
+    </row>
+    <row r="122">
+      <c r="K122" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">6.1 Biela e parcela do concreto</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="K122" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vsd</t>
-        </is>
-      </c>
-      <c r="L122" s="227">
-        <f>$L$48*$L$29</f>
-      </c>
-      <c r="M122" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kN</t>
-        </is>
-      </c>
-      <c r="O122" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cortante de cálculo (γf·Vk).</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="K123" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">VRd2</t>
+          <t xml:space="preserve">Vsd</t>
         </is>
       </c>
       <c r="L123" s="227">
-        <f>0.27*(1-$L$33/250)*$L$73/10*$L$39*$L$76</f>
+        <f>$L$48*$L$29</f>
       </c>
       <c r="M123" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN</t>
         </is>
       </c>
-      <c r="N123" s="232">
-        <f>IF($L$122&lt;=$L$123,"Ok","Aumentar seção ou fck")</f>
-      </c>
       <c r="O123" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistência da biela comprimida.</t>
+          <t xml:space="preserve">Cortante de cálculo (γf·Vk).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="K124" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">fctm</t>
+          <t xml:space="preserve">VRd2</t>
         </is>
       </c>
       <c r="L124" s="227">
-        <f>0.3*$L$33^(2/3)</f>
+        <f>0.27*(1-$L$33/250)*$L$73/10*$L$39*$L$76</f>
       </c>
       <c r="M124" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">MPa</t>
-        </is>
+          <t xml:space="preserve">kN</t>
+        </is>
+      </c>
+      <c r="N124" s="232">
+        <f>IF($L$123&lt;=$L$124,"Ok","Aumentar seção ou fck")</f>
       </c>
       <c r="O124" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistência média à tração.</t>
+          <t xml:space="preserve">Resistência da biela comprimida.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="K125" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">fctd</t>
+          <t xml:space="preserve">fctm</t>
         </is>
       </c>
       <c r="L125" s="227">
-        <f>0.7*$L$124/$L$30</f>
+        <f>0.3*$L$33^(2/3)</f>
       </c>
       <c r="M125" s="231" t="inlineStr">
         <is>
@@ -18347,105 +18347,105 @@
       </c>
       <c r="O125" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistência de cálculo à tração (fctk,inf/γc).</t>
+          <t xml:space="preserve">Resistência média à tração.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="K126" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">fctd</t>
+        </is>
+      </c>
+      <c r="L126" s="227">
+        <f>0.7*$L$125/$L$30</f>
+      </c>
+      <c r="M126" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPa</t>
+        </is>
+      </c>
+      <c r="O126" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resistência de cálculo à tração (fctk,inf/γc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="K127" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vc0</t>
         </is>
       </c>
-      <c r="L126" s="227">
-        <f>0.6*$L$125/10*$L$39*$L$76</f>
-      </c>
-      <c r="M126" s="231" t="inlineStr">
+      <c r="L127" s="227">
+        <f>0.6*$L$126/10*$L$39*$L$76</f>
+      </c>
+      <c r="M127" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kN</t>
         </is>
       </c>
-      <c r="O126" s="233" t="inlineStr">
+      <c r="O127" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcela resistida pelo concreto.</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="K127" s="222" t="inlineStr">
+    <row r="128">
+      <c r="K128" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">6.2 Armadura transversal</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="K128" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fywd</t>
-        </is>
-      </c>
-      <c r="L128" s="227">
-        <f>MIN($L$35/$L$31,435)</f>
-      </c>
-      <c r="M128" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPa</t>
-        </is>
-      </c>
-      <c r="O128" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resistência de cálculo do estribo (≤ 435 MPa).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="K129" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vsw</t>
+          <t xml:space="preserve">fywd</t>
         </is>
       </c>
       <c r="L129" s="227">
-        <f>MAX(0,$L$122-$L$126)</f>
+        <f>MIN($L$35/$L$31,435)</f>
       </c>
       <c r="M129" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kN</t>
+          <t xml:space="preserve">MPa</t>
         </is>
       </c>
       <c r="O129" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcela a ser resistida pelos estribos.</t>
+          <t xml:space="preserve">Resistência de cálculo do estribo (≤ 435 MPa).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="K130" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asw,calc</t>
+          <t xml:space="preserve">Vsw</t>
         </is>
       </c>
       <c r="L130" s="227">
-        <f>$L$129/(0.9*$L$76*$L$128/10)*100</f>
+        <f>MAX(0,$L$123-$L$127)</f>
       </c>
       <c r="M130" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm²/m</t>
+          <t xml:space="preserve">kN</t>
         </is>
       </c>
       <c r="O130" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asw/s = Vsw/(0,9·d·fywd).</t>
+          <t xml:space="preserve">Parcela a ser resistida pelos estribos.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="K131" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asw,mín</t>
+          <t xml:space="preserve">Asw,calc</t>
         </is>
       </c>
       <c r="L131" s="227">
-        <f>0.2*$L$124/$L$35*$L$39*100</f>
+        <f>$L$130/(0.9*$L$76*$L$129/10)*100</f>
       </c>
       <c r="M131" s="231" t="inlineStr">
         <is>
@@ -18454,18 +18454,18 @@
       </c>
       <c r="O131" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mínima: ρsw = 0,2·fctm/fywk.</t>
+          <t xml:space="preserve">Asw/s = Vsw/(0,9·d·fywd).</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="K132" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asw</t>
+          <t xml:space="preserve">Asw,mín</t>
         </is>
       </c>
       <c r="L132" s="227">
-        <f>MAX($L$130,$L$131)</f>
+        <f>0.2*$L$125/$L$35*$L$39*100</f>
       </c>
       <c r="M132" s="231" t="inlineStr">
         <is>
@@ -18474,38 +18474,38 @@
       </c>
       <c r="O132" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura transversal adotada (todos os ramos).</t>
+          <t xml:space="preserve">Mínima: ρsw = 0,2·fctm/fywk.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="K133" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s,calc</t>
+          <t xml:space="preserve">Asw</t>
         </is>
       </c>
       <c r="L133" s="227">
-        <f>IF($L$132=0,999,$L$43*PI()*($L$41/10)^2/4/$L$132*100)</f>
+        <f>MAX($L$131,$L$132)</f>
       </c>
       <c r="M133" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm</t>
+          <t xml:space="preserve">cm²/m</t>
         </is>
       </c>
       <c r="O133" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espaçamento pela armadura calculada.</t>
+          <t xml:space="preserve">Armadura transversal adotada (todos os ramos).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="K134" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s,máx,v</t>
+          <t xml:space="preserve">s,calc</t>
         </is>
       </c>
       <c r="L134" s="227">
-        <f>IF($L$122&lt;=0.67*$L$123,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20))</f>
+        <f>IF($L$133=0,999,$L$43*PI()*($L$41/10)^2/4/$L$133*100)</f>
       </c>
       <c r="M134" s="231" t="inlineStr">
         <is>
@@ -18514,18 +18514,18 @@
       </c>
       <c r="O134" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Máximo de viga (NBR 6118, 18.3.3.2).</t>
+          <t xml:space="preserve">Espaçamento pela armadura calculada.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="K135" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s,máx,p</t>
+          <t xml:space="preserve">s,máx,v</t>
         </is>
       </c>
       <c r="L135" s="227">
-        <f>MIN(20,$L$39,$L$38,IF($L$34&gt;=500,12,25)*$L$42/10)</f>
+        <f>IF($L$123&lt;=0.67*$L$124,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20))</f>
       </c>
       <c r="M135" s="231" t="inlineStr">
         <is>
@@ -18534,190 +18534,210 @@
       </c>
       <c r="O135" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Máximo de pilar: 20 cm, menor dimensão, 12·Ø,l (CA-50).</t>
+          <t xml:space="preserve">Máximo de viga (NBR 6118, 18.3.3.2).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="K136" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="L136" s="229">
-        <f>ROUNDDOWN(MIN($L$133,$L$134,$L$135),0)</f>
+          <t xml:space="preserve">s,máx,p</t>
+        </is>
+      </c>
+      <c r="L136" s="227">
+        <f>MIN(20,$L$39,$L$38,IF($L$34&gt;=500,12,25)*$L$42/10)</f>
       </c>
       <c r="M136" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">cm</t>
         </is>
       </c>
-      <c r="N136" s="232">
-        <f>IF($L$136&lt;5,"s &lt; 5 cm – aumentar Ø,t ou ramos","Ok")</f>
-      </c>
       <c r="O136" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espaçamento adotado (arredondado para baixo).</t>
+          <t xml:space="preserve">Máximo de pilar: 20 cm, menor dimensão, 12·Ø,l (CA-50).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="K137" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asw,ef</t>
-        </is>
-      </c>
-      <c r="L137" s="227">
-        <f>$L$43*PI()*($L$41/10)^2/4*100/$L$136</f>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="L137" s="229">
+        <f>ROUNDDOWN(MIN($L$134,$L$135,$L$136),0)</f>
       </c>
       <c r="M137" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm²/m</t>
+          <t xml:space="preserve">cm</t>
         </is>
       </c>
       <c r="N137" s="232">
-        <f>IF($L$137&gt;=$L$132,"Ok","Rever")</f>
+        <f>IF($L$137&lt;5,"s &lt; 5 cm – aumentar Ø,t ou ramos","Ok")</f>
       </c>
       <c r="O137" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura efetiva com o espaçamento adotado.</t>
+          <t xml:space="preserve">Espaçamento adotado (arredondado para baixo).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="K138" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Asw,ef</t>
+        </is>
+      </c>
+      <c r="L138" s="227">
+        <f>$L$43*PI()*($L$41/10)^2/4*100/$L$137</f>
+      </c>
+      <c r="M138" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm²/m</t>
+        </is>
+      </c>
+      <c r="N138" s="232">
+        <f>IF($L$138&gt;=$L$133,"Ok","Rever")</f>
+      </c>
+      <c r="O138" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura efetiva com o espaçamento adotado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="K139" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ø,t,mín</t>
         </is>
       </c>
-      <c r="L138" s="227">
+      <c r="L139" s="227">
         <f>MAX(5,$L$42/4)</f>
       </c>
-      <c r="M138" s="231" t="inlineStr">
+      <c r="M139" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">mm</t>
         </is>
       </c>
-      <c r="N138" s="232">
-        <f>IF($L$41&gt;=$L$138,"Ok","Aumentar Ø,t")</f>
-      </c>
-      <c r="O138" s="233" t="inlineStr">
+      <c r="N139" s="232">
+        <f>IF($L$41&gt;=$L$139,"Ok","Aumentar Ø,t")</f>
+      </c>
+      <c r="O139" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Pilar: Ø,t ≥ 5 mm e ≥ Ø,l/4.</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="K140" s="221" t="inlineStr">
+    <row r="141">
+      <c r="K141" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">7 . TAXA DE AÇO</t>
         </is>
       </c>
-      <c r="L140" s="221"/>
-      <c r="M140" s="221"/>
-      <c r="N140" s="221"/>
-      <c r="O140" s="221"/>
-      <c r="P140" s="221"/>
-      <c r="Q140" s="221"/>
-      <c r="R140" s="221"/>
-      <c r="S140" s="221"/>
-      <c r="T140" s="221"/>
-    </row>
-    <row r="142">
-      <c r="K142" s="223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ρ,aço</t>
-        </is>
-      </c>
-      <c r="L142" s="224">
-        <v>0.785</v>
-      </c>
-      <c r="M142" s="231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg/m/cm²</t>
-        </is>
-      </c>
-      <c r="O142" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peso por metro de 1 cm² de barra (7850 kg/m³).</t>
-        </is>
-      </c>
+      <c r="L141" s="221"/>
+      <c r="M141" s="221"/>
+      <c r="N141" s="221"/>
+      <c r="O141" s="221"/>
+      <c r="P141" s="221"/>
+      <c r="Q141" s="221"/>
+      <c r="R141" s="221"/>
+      <c r="S141" s="221"/>
+      <c r="T141" s="221"/>
     </row>
     <row r="143">
       <c r="K143" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Longit.</t>
-        </is>
-      </c>
-      <c r="L143" s="227">
-        <f>$L$113*$L$142/($L$39*$L$38/10000)</f>
+          <t xml:space="preserve">ρ,aço</t>
+        </is>
+      </c>
+      <c r="L143" s="224">
+        <v>0.785</v>
       </c>
       <c r="M143" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kg/m³</t>
+          <t xml:space="preserve">kg/m/cm²</t>
         </is>
       </c>
       <c r="O143" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura longitudinal (duas faces) por m³ de concreto.</t>
+          <t xml:space="preserve">Peso por metro de 1 cm² de barra (7850 kg/m³).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="K144" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">l,est</t>
+          <t xml:space="preserve">Longit.</t>
         </is>
       </c>
       <c r="L144" s="227">
-        <f>2*($L$39+$L$38)-8*$L$40+12</f>
+        <f>$L$113*$L$143/($L$39*$L$38/10000)</f>
       </c>
       <c r="M144" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm</t>
+          <t xml:space="preserve">kg/m³</t>
         </is>
       </c>
       <c r="O144" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comprimento de cada estribo (perímetro − cobrimentos + ganchos).</t>
+          <t xml:space="preserve">Armadura longitudinal (duas faces) por m³ de concreto.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="K145" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estribos</t>
+          <t xml:space="preserve">l,est</t>
         </is>
       </c>
       <c r="L145" s="227">
-        <f>100/$L$136*$L$144/100*PI()*($L$41/10)^2/4*$L$142*$L$43/2/($L$39*$L$38/10000)</f>
+        <f>2*($L$39+$L$38)-8*$L$40+12</f>
       </c>
       <c r="M145" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kg/m³</t>
+          <t xml:space="preserve">cm</t>
         </is>
       </c>
       <c r="O145" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estribos por m³ de concreto (100/s estribos por metro).</t>
+          <t xml:space="preserve">Comprimento de cada estribo (perímetro − cobrimentos + ganchos).</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="K146" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Estribos</t>
+        </is>
+      </c>
+      <c r="L146" s="227">
+        <f>100/$L$137*$L$145/100*PI()*($L$41/10)^2/4*$L$143*$L$43/2/($L$39*$L$38/10000)</f>
+      </c>
+      <c r="M146" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg/m³</t>
+        </is>
+      </c>
+      <c r="O146" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estribos por m³ de concreto (100/s estribos por metro).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="K147" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="L146" s="227">
-        <f>$L$143+$L$145</f>
-      </c>
-      <c r="M146" s="231" t="inlineStr">
+      <c r="L147" s="227">
+        <f>$L$144+$L$146</f>
+      </c>
+      <c r="M147" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kg/m³</t>
         </is>
       </c>
-      <c r="O146" s="233" t="inlineStr">
+      <c r="O147" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Taxa total de aço do pilar.</t>
         </is>
@@ -18734,9 +18754,9 @@
     <mergeCell ref="K92:T92"/>
     <mergeCell ref="K103:T103"/>
     <mergeCell ref="K105:T105"/>
-    <mergeCell ref="K118:T118"/>
-    <mergeCell ref="K120:T120"/>
-    <mergeCell ref="K140:T140"/>
+    <mergeCell ref="K119:T119"/>
+    <mergeCell ref="K121:T121"/>
+    <mergeCell ref="K141:T141"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="O10:T10"/>
     <mergeCell ref="L11:M11"/>
@@ -18764,12 +18784,12 @@
     <mergeCell ref="O5:R5"/>
     <mergeCell ref="S5:T5"/>
   </mergeCells>
-  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N116 N123 N136 N137 N138 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
+  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N117 N124 N137 N138 N139 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
     <cfRule type="beginsWith" dxfId="6" priority="1" operator="beginsWith" text="Ok">
       <formula>LEFT(N33,2)="Ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N116 N123 N136 N137 N138 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
+  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N117 N124 N137 N138 N139 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
     <cfRule type="beginsWith" dxfId="5" priority="2" operator="beginsWith" text="Não se aplica">
       <formula>LEFT(N33,13)="Não se aplica"</formula>
     </cfRule>

--- a/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
+++ b/3 - EMPUXO DE MUROS DE ARRIMO.xlsx
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CONTENÇÃO RÁPIDA'!$K$1:$T$259</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$147</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'DIMENSIONAMENTO PILAR'!$K$1:$T$165</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" iterateCount="1000"/>
   <extLst>
@@ -2689,7 +2689,7 @@
                   <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2723,10 +2723,10 @@
                   <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.247957670388743</c:v>
+                  <c:v>12.167266237259694</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>172.47957670388743</c:v>
+                  <c:v>187.3759000537993</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.0</c:v>
@@ -2741,10 +2741,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.0</c:v>
@@ -2782,10 +2782,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>17.247957670388743</c:v>
+                  <c:v>12.167266237259694</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.247957670388743</c:v>
+                  <c:v>12.167266237259694</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2797,7 +2797,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -2832,7 +2832,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>146.60764019830432</c:v>
+                  <c:v>158.17446108437605</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -2847,10 +2847,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.4166666666666667</c:v>
+                  <c:v>0.6666666666666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4166666666666667</c:v>
+                  <c:v>0.6666666666666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2882,7 +2882,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>120.73570369272119</c:v>
+                  <c:v>128.97302211495278</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -2897,10 +2897,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.8333333333333334</c:v>
+                  <c:v>1.3333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8333333333333334</c:v>
+                  <c:v>1.3333333333333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2932,7 +2932,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>94.86376718713808</c:v>
+                  <c:v>99.7715831455295</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -2947,10 +2947,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1.25</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.25</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2982,7 +2982,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>68.99183068155496</c:v>
+                  <c:v>70.57014417610624</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -2997,10 +2997,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1.6666666666666667</c:v>
+                  <c:v>2.6666666666666665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6666666666666667</c:v>
+                  <c:v>2.6666666666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3032,7 +3032,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>43.119894175971865</c:v>
+                  <c:v>41.36870520668296</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -3047,10 +3047,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2.0833333333333335</c:v>
+                  <c:v>3.3333333333333335</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0833333333333335</c:v>
+                  <c:v>3.3333333333333335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3082,7 +3082,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>198.35151320947054</c:v>
+                  <c:v>215.4822850618692</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -3097,10 +3097,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.9090909090909092</c:v>
+                  <c:v>1.4146341463414631</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9090909090909092</c:v>
+                  <c:v>1.4146341463414631</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3135,7 +3135,7 @@
                   <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-60.367851846360594</c:v>
+                  <c:v>-65.58156501882975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3147,10 +3147,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3185,7 +3185,7 @@
                   <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-60.367851846360594</c:v>
+                  <c:v>-65.58156501882975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3216,7 +3216,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>p,topo = 17,25 kN/m</c:v>
+                  <c:v>p,topo = 12,17 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3260,7 +3260,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>17.247957670388743</c:v>
+                  <c:v>12.167266237259694</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3272,7 +3272,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3288,7 +3288,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>p,base = 172,48 kN/m</c:v>
+                  <c:v>p,base = 187,38 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3332,7 +3332,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>172.47957670388743</c:v>
+                  <c:v>187.3759000537993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3360,7 +3360,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>E = 237,2 kN (y = 0,91 m)</c:v>
+                  <c:v>E = 399,1 kN (y = 1,41 m)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3404,7 +3404,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>198.35151320947054</c:v>
+                  <c:v>215.4822850618692</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3416,7 +3416,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.9090909090909092</c:v>
+                  <c:v>1.4146341463414631</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3432,7 +3432,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>R,topo = 55,0 kN → laje</c:v>
+                  <c:v>R,topo = 88,3 kN → laje</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3476,7 +3476,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>-60.367851846360594</c:v>
+                  <c:v>-65.58156501882975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3488,7 +3488,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3504,7 +3504,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>R,base = 182,2 kN</c:v>
+                  <c:v>R,base = 310,8 kN</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3548,7 +3548,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>-60.367851846360594</c:v>
+                  <c:v>-65.58156501882975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3793,7 +3793,7 @@
                   <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3830,7 +3830,7 @@
                   <c:v>2.639320225002103</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26.39320225002103</c:v>
+                  <c:v>40.645531465032384</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.0</c:v>
@@ -3845,10 +3845,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.0</c:v>
@@ -3901,7 +3901,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -3936,7 +3936,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>20.4547317437663</c:v>
+                  <c:v>31.143978655024814</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -3951,10 +3951,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.625</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.625</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3986,7 +3986,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>14.516261237511566</c:v>
+                  <c:v>21.642425845017243</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -4001,10 +4001,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1.25</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.25</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4036,7 +4036,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>8.577790731256833</c:v>
+                  <c:v>12.140873035009673</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.0</c:v>
@@ -4051,10 +4051,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1.875</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.875</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4085,64 +4085,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>26.393202250021027</c:v>
+                  <c:v>40.645531465032384</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.393202250021027</c:v>
+                  <c:v>40.645531465032384</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>28.768590452522922</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>28.768590452522922</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>16.89164944001346</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>16.89164944001346</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>5.0147084275039955</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4169,49 +4169,49 @@
                   <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.5</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.5</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4246,7 +4246,7 @@
                   <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.71286236252208</c:v>
+                  <c:v>42.677808038284006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4292,6 +4292,12 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42.677808038284006</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4336,6 +4342,12 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42.677808038284006</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4685,7 +4697,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4701,7 +4713,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>σ,base = 26,39 kN/m² = solo 23,75 + Sc 2,64</c:v>
+                  <c:v>σ,base = 40,65 kN/m² = solo 38,01 + Sc 2,64</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4745,7 +4757,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>26.39320225002103</c:v>
+                  <c:v>40.645531465032384</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4773,7 +4785,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>P1: g = 29,69 | q = 3,30 kN/m</c:v>
+                  <c:v>P1: g = 47,51 | q = 3,30 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4817,7 +4829,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>26.393202250021027</c:v>
+                  <c:v>40.645531465032384</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4845,7 +4857,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>P2: g = 14,85 | q = 3,30 kN/m</c:v>
+                  <c:v>P2: g = 32,66 | q = 3,30 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4889,7 +4901,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>14.516261237511564</c:v>
+                  <c:v>28.768590452522922</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4917,7 +4929,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v/>
+                  <c:v>P3: g = 17,82 | q = 3,30 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4960,6 +4972,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>16.89164944001346</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4969,6 +4984,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4983,7 +5001,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v/>
+                  <c:v>P4: g = 0,59 | q = 0,66 kN/m</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5026,6 +5044,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.0147084275039955</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -5035,6 +5056,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.875</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -13651,7 +13675,7 @@
         </is>
       </c>
       <c r="L33" s="224">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="M33" s="231" t="inlineStr">
         <is>
@@ -13671,7 +13695,7 @@
         </is>
       </c>
       <c r="L34" s="226">
-        <f>13.07/2</f>
+        <f>9.22/2</f>
       </c>
       <c r="M34" s="231" t="inlineStr">
         <is>
@@ -16543,7 +16567,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="K1:T147"/>
+  <dimension ref="K1:T165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="2.7109375" customWidth="1"/>
@@ -16582,7 +16606,7 @@
       </c>
       <c r="N2" s="240"/>
       <c r="O2" s="241">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="P2" s="240">
         <f>$L$111&amp;" barras em cada face ("&amp;FIXED($L$112,2)&amp;" cm²) | espaço livre "&amp;FIXED($L$117,2)&amp;" cm"</f>
@@ -16602,19 +16626,19 @@
       </c>
       <c r="L3" s="239"/>
       <c r="M3" s="240">
-        <f>"Asw,nec = "&amp;FIXED($L$133,2)&amp;" cm²/m"</f>
+        <f>"Asw,nec = "&amp;FIXED($L$133,2)&amp;" cm²/m (máx.)"</f>
       </c>
       <c r="N3" s="240"/>
       <c r="O3" s="241">
         <v>6.3</v>
       </c>
       <c r="P3" s="240">
-        <f>"c/ "&amp;$L$137&amp;" cm ("&amp;$L$43&amp;" ramos) = "&amp;FIXED($L$138,2)&amp;" cm²/m"</f>
+        <f>("Ø"&amp;$L$41&amp;": "&amp;IF(N148&lt;=0,"","c/"&amp;S148&amp;" ("&amp;FIXED(L148,1)&amp;"–"&amp;FIXED(M148,1)&amp;" m)")&amp;IF(N149&lt;=0,""," | "&amp;"c/"&amp;S149&amp;" ("&amp;FIXED(L149,1)&amp;"–"&amp;FIXED(M149,1)&amp;" m)")&amp;IF(N150&lt;=0,""," | "&amp;"c/"&amp;S150&amp;" ("&amp;FIXED(L150,1)&amp;"–"&amp;FIXED(M150,1)&amp;" m)")&amp;IF(N151&lt;=0,""," | "&amp;"c/"&amp;S151&amp;" ("&amp;FIXED(L151,1)&amp;"–"&amp;FIXED(M151,1)&amp;" m)")&amp;IF(N152&lt;=0,""," | "&amp;"c/"&amp;S152&amp;" ("&amp;FIXED(L152,1)&amp;"–"&amp;FIXED(M152,1)&amp;" m)")&amp;IF(N153&lt;=0,""," | "&amp;"c/"&amp;S153&amp;" ("&amp;FIXED(L153,1)&amp;"–"&amp;FIXED(M153,1)&amp;" m)"))</f>
       </c>
       <c r="Q3" s="240"/>
       <c r="R3" s="240"/>
       <c r="S3" s="242">
-        <f>IF($L$123&gt;$L$124,"NÃO OK – biela: aumentar seção",IF($L$137&lt;5,"NÃO OK – s &lt; 5 cm: aumentar Ø",IF($L$41&lt;$L$139,"NÃO OK – Ø,t &lt; Ø,l/4","OK")))</f>
+        <f>IF($L$123&gt;$L$124,"NÃO OK – biela: aumentar seção",IF($L$41&lt;$L$139,"NÃO OK – Ø,t &lt; Ø,l/4",(IF(ABS($L$155-$L$142)&gt;0.01,"NÃO OK – soma das zonas ≠ H",IF($L$156&lt;5,"NÃO OK – s &lt; 5 cm: aumentar Ø","OK")))))</f>
       </c>
       <c r="T3" s="242"/>
     </row>
@@ -16652,7 +16676,7 @@
       </c>
       <c r="N5" s="240"/>
       <c r="O5" s="240">
-        <f>"Longit. "&amp;FIXED($L$144,1)&amp;" + estribos "&amp;FIXED($L$146,1)&amp;" = "&amp;FIXED($L$147,1)&amp;" kg/m³"</f>
+        <f>"Longit. "&amp;FIXED($L$161,1)&amp;" + estribos "&amp;FIXED($L$163,1)&amp;" = "&amp;FIXED($L$165,1)&amp;" kg/m³"</f>
       </c>
       <c r="P5" s="240"/>
       <c r="Q5" s="240"/>
@@ -16861,11 +16885,11 @@
         </is>
       </c>
       <c r="L18" s="236">
-        <f>"Ø"&amp;$L$41&amp;" c/"&amp;$L$137&amp;" ("&amp;$L$43&amp;" ramos)"</f>
+        <f>"Ø"&amp;$L$41&amp;" – "&amp;$L$154&amp;" estribos"</f>
       </c>
       <c r="M18" s="236"/>
       <c r="N18" s="232">
-        <f>IF($L$137&lt;5,"s &lt; 5 cm – aumentar Ø,t",IF($L$138&gt;=$L$133,"Ok","Rever"))</f>
+        <f>(IF(ABS($L$155-$L$142)&gt;0.01,"NÃO OK – soma das zonas ≠ H",IF($L$156&lt;5,"NÃO OK – s &lt; 5 cm: aumentar Ø","OK")))</f>
       </c>
       <c r="O18" s="233" t="inlineStr">
         <is>
@@ -16923,7 +16947,7 @@
         </is>
       </c>
       <c r="L30" s="224">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M30" s="231" t="inlineStr">
         <is>
@@ -16943,7 +16967,7 @@
         </is>
       </c>
       <c r="L31" s="224">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="M31" s="231" t="inlineStr">
         <is>
@@ -16970,7 +16994,7 @@
         </is>
       </c>
       <c r="L33" s="224">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M33" s="231" t="inlineStr">
         <is>
@@ -17060,7 +17084,7 @@
         </is>
       </c>
       <c r="L38" s="224">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M38" s="231" t="inlineStr">
         <is>
@@ -17080,7 +17104,7 @@
         </is>
       </c>
       <c r="L39" s="224">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M39" s="231" t="inlineStr">
         <is>
@@ -18561,7 +18585,7 @@
     <row r="137">
       <c r="K137" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">s</t>
+          <t xml:space="preserve">s,unif</t>
         </is>
       </c>
       <c r="L137" s="229">
@@ -18577,7 +18601,7 @@
       </c>
       <c r="O137" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espaçamento adotado (arredondado para baixo).</t>
+          <t xml:space="preserve">Espaçamento se usar o Vsd máximo em toda a altura (sem escalonamento).</t>
         </is>
       </c>
     </row>
@@ -18627,124 +18651,577 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="K141" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 . TAXA DE AÇO</t>
-        </is>
-      </c>
-      <c r="L141" s="221"/>
-      <c r="M141" s="221"/>
-      <c r="N141" s="221"/>
-      <c r="O141" s="221"/>
-      <c r="P141" s="221"/>
-      <c r="Q141" s="221"/>
-      <c r="R141" s="221"/>
-      <c r="S141" s="221"/>
-      <c r="T141" s="221"/>
+    <row r="140">
+      <c r="K140" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.3 Estribos por zonas (escalonamento ao longo da altura)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="32" customHeight="1">
+      <c r="K141" s="220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O cortante cai da base para o topo, então cada zona usa o maior |V| do seu trecho (e não o Vsd máximo em toda a altura). V(z) = R,base − p,base·z + Δp·z²/(2H), com z medido da base. Os comprimentos das zonas são cinza: pode editar.</t>
+        </is>
+      </c>
+      <c r="L141" s="220"/>
+      <c r="M141" s="220"/>
+      <c r="N141" s="220"/>
+      <c r="O141" s="220"/>
+      <c r="P141" s="220"/>
+      <c r="Q141" s="220"/>
+      <c r="R141" s="220"/>
+      <c r="S141" s="220"/>
+      <c r="T141" s="220"/>
+    </row>
+    <row r="142">
+      <c r="K142" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="L142" s="227">
+        <f>'CONTENÇÃO RÁPIDA'!$L$33</f>
+      </c>
+      <c r="M142" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="O142" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Altura do pilar carregada (aba CONTENÇÃO RÁPIDA).</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="K143" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">ρ,aço</t>
-        </is>
-      </c>
-      <c r="L143" s="224">
-        <v>0.785</v>
+          <t xml:space="preserve">p,base</t>
+        </is>
+      </c>
+      <c r="L143" s="227">
+        <f>'CONTENÇÃO RÁPIDA'!$L$60</f>
       </c>
       <c r="M143" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kg/m/cm²</t>
+          <t xml:space="preserve">kN/m</t>
         </is>
       </c>
       <c r="O143" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peso por metro de 1 cm² de barra (7850 kg/m³).</t>
+          <t xml:space="preserve">Carga na base (aba CONTENÇÃO RÁPIDA).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="K144" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Longit.</t>
+          <t xml:space="preserve">Δp</t>
         </is>
       </c>
       <c r="L144" s="227">
-        <f>$L$113*$L$143/($L$39*$L$38/10000)</f>
+        <f>'CONTENÇÃO RÁPIDA'!$L$61</f>
       </c>
       <c r="M144" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">kg/m³</t>
+          <t xml:space="preserve">kN/m</t>
         </is>
       </c>
       <c r="O144" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadura longitudinal (duas faces) por m³ de concreto.</t>
+          <t xml:space="preserve">Parcela triangular (aba CONTENÇÃO RÁPIDA).</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="K145" s="223" t="inlineStr">
         <is>
-          <t xml:space="preserve">l,est</t>
+          <t xml:space="preserve">R,base</t>
         </is>
       </c>
       <c r="L145" s="227">
-        <f>2*($L$39+$L$38)-8*$L$40+12</f>
+        <f>IFERROR(INDEX('CONTENÇÃO RÁPIDA'!$M$74:$M$76,MATCH($L$45,'CONTENÇÃO RÁPIDA'!$K$74:$K$76,0)),0)</f>
       </c>
       <c r="M145" s="231" t="inlineStr">
         <is>
-          <t xml:space="preserve">cm</t>
+          <t xml:space="preserve">kN</t>
         </is>
       </c>
       <c r="O145" s="233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comprimento de cada estribo (perímetro − cobrimentos + ganchos).</t>
+          <t xml:space="preserve">Reação na base do modelo escolhido.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="K146" s="223" t="inlineStr">
         <is>
+          <t xml:space="preserve">zonas</t>
+        </is>
+      </c>
+      <c r="L146" s="224">
+        <v>3</v>
+      </c>
+      <c r="M146" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">un</t>
+        </is>
+      </c>
+      <c r="N146" s="232">
+        <f>IF(OR($L$146&lt;1,$L$146&gt;6),"Rever: 1 a 6 zonas","Ok")</f>
+      </c>
+      <c r="O146" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Número de zonas de mesmo comprimento (1 a 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="K147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zona</t>
+        </is>
+      </c>
+      <c r="L147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z,início (m)</t>
+        </is>
+      </c>
+      <c r="M147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z,fim (m)</t>
+        </is>
+      </c>
+      <c r="N147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compr. (m)</t>
+        </is>
+      </c>
+      <c r="O147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vk,máx (kN)</t>
+        </is>
+      </c>
+      <c r="P147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vsd (kN)</t>
+        </is>
+      </c>
+      <c r="Q147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asw (cm²/m)</t>
+        </is>
+      </c>
+      <c r="R147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s,calc (cm)</t>
+        </is>
+      </c>
+      <c r="S147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s (cm)</t>
+        </is>
+      </c>
+      <c r="T147" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nº estribos</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="K148" s="237">
+        <v>1</v>
+      </c>
+      <c r="L148" s="227">
+        <v>0</v>
+      </c>
+      <c r="M148" s="227">
+        <f>L148+N148</f>
+      </c>
+      <c r="N148" s="225">
+        <f>IF(1&lt;=$L$146,$L$142/$L$146,0)</f>
+      </c>
+      <c r="O148" s="227">
+        <f>IF(N148&lt;=0,"",MAX(ABS(($L$145-$L$143*L148+$L$144*L148^2/(2*$L$142))),ABS(($L$145-$L$143*M148+$L$144*M148^2/(2*$L$142)))))</f>
+      </c>
+      <c r="P148" s="227">
+        <f>IF(N148&lt;=0,"",O148*$L$29)</f>
+      </c>
+      <c r="Q148" s="227">
+        <f>IF(N148&lt;=0,"",MAX(MAX(0,P148-$L$127)/(0.9*$L$76*$L$129/10)*100,$L$132))</f>
+      </c>
+      <c r="R148" s="227">
+        <f>IF(N148&lt;=0,"",$L$43*PI()*($L$41/10)^2/4/Q148*100)</f>
+      </c>
+      <c r="S148" s="229">
+        <f>IF(N148&lt;=0,"",ROUNDDOWN(MIN(R148,IF(P148&lt;=0.67*$L$124,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20)),$L$136),0))</f>
+      </c>
+      <c r="T148" s="229">
+        <f>IF(N148&lt;=0,"",ROUNDUP(N148*100/S148,0))</f>
+      </c>
+    </row>
+    <row r="149">
+      <c r="K149" s="237">
+        <v>2</v>
+      </c>
+      <c r="L149" s="227">
+        <f>M148</f>
+      </c>
+      <c r="M149" s="227">
+        <f>L149+N149</f>
+      </c>
+      <c r="N149" s="225">
+        <f>IF(2&lt;=$L$146,$L$142/$L$146,0)</f>
+      </c>
+      <c r="O149" s="227">
+        <f>IF(N149&lt;=0,"",MAX(ABS(($L$145-$L$143*L149+$L$144*L149^2/(2*$L$142))),ABS(($L$145-$L$143*M149+$L$144*M149^2/(2*$L$142)))))</f>
+      </c>
+      <c r="P149" s="227">
+        <f>IF(N149&lt;=0,"",O149*$L$29)</f>
+      </c>
+      <c r="Q149" s="227">
+        <f>IF(N149&lt;=0,"",MAX(MAX(0,P149-$L$127)/(0.9*$L$76*$L$129/10)*100,$L$132))</f>
+      </c>
+      <c r="R149" s="227">
+        <f>IF(N149&lt;=0,"",$L$43*PI()*($L$41/10)^2/4/Q149*100)</f>
+      </c>
+      <c r="S149" s="229">
+        <f>IF(N149&lt;=0,"",ROUNDDOWN(MIN(R149,IF(P149&lt;=0.67*$L$124,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20)),$L$136),0))</f>
+      </c>
+      <c r="T149" s="229">
+        <f>IF(N149&lt;=0,"",ROUNDUP(N149*100/S149,0))</f>
+      </c>
+    </row>
+    <row r="150">
+      <c r="K150" s="237">
+        <v>3</v>
+      </c>
+      <c r="L150" s="227">
+        <f>M149</f>
+      </c>
+      <c r="M150" s="227">
+        <f>L150+N150</f>
+      </c>
+      <c r="N150" s="225">
+        <f>IF(3&lt;=$L$146,$L$142/$L$146,0)</f>
+      </c>
+      <c r="O150" s="227">
+        <f>IF(N150&lt;=0,"",MAX(ABS(($L$145-$L$143*L150+$L$144*L150^2/(2*$L$142))),ABS(($L$145-$L$143*M150+$L$144*M150^2/(2*$L$142)))))</f>
+      </c>
+      <c r="P150" s="227">
+        <f>IF(N150&lt;=0,"",O150*$L$29)</f>
+      </c>
+      <c r="Q150" s="227">
+        <f>IF(N150&lt;=0,"",MAX(MAX(0,P150-$L$127)/(0.9*$L$76*$L$129/10)*100,$L$132))</f>
+      </c>
+      <c r="R150" s="227">
+        <f>IF(N150&lt;=0,"",$L$43*PI()*($L$41/10)^2/4/Q150*100)</f>
+      </c>
+      <c r="S150" s="229">
+        <f>IF(N150&lt;=0,"",ROUNDDOWN(MIN(R150,IF(P150&lt;=0.67*$L$124,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20)),$L$136),0))</f>
+      </c>
+      <c r="T150" s="229">
+        <f>IF(N150&lt;=0,"",ROUNDUP(N150*100/S150,0))</f>
+      </c>
+    </row>
+    <row r="151">
+      <c r="K151" s="237">
+        <v>4</v>
+      </c>
+      <c r="L151" s="227">
+        <f>M150</f>
+      </c>
+      <c r="M151" s="227">
+        <f>L151+N151</f>
+      </c>
+      <c r="N151" s="225">
+        <f>IF(4&lt;=$L$146,$L$142/$L$146,0)</f>
+      </c>
+      <c r="O151" s="227">
+        <f>IF(N151&lt;=0,"",MAX(ABS(($L$145-$L$143*L151+$L$144*L151^2/(2*$L$142))),ABS(($L$145-$L$143*M151+$L$144*M151^2/(2*$L$142)))))</f>
+      </c>
+      <c r="P151" s="227">
+        <f>IF(N151&lt;=0,"",O151*$L$29)</f>
+      </c>
+      <c r="Q151" s="227">
+        <f>IF(N151&lt;=0,"",MAX(MAX(0,P151-$L$127)/(0.9*$L$76*$L$129/10)*100,$L$132))</f>
+      </c>
+      <c r="R151" s="227">
+        <f>IF(N151&lt;=0,"",$L$43*PI()*($L$41/10)^2/4/Q151*100)</f>
+      </c>
+      <c r="S151" s="229">
+        <f>IF(N151&lt;=0,"",ROUNDDOWN(MIN(R151,IF(P151&lt;=0.67*$L$124,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20)),$L$136),0))</f>
+      </c>
+      <c r="T151" s="229">
+        <f>IF(N151&lt;=0,"",ROUNDUP(N151*100/S151,0))</f>
+      </c>
+    </row>
+    <row r="152">
+      <c r="K152" s="237">
+        <v>5</v>
+      </c>
+      <c r="L152" s="227">
+        <f>M151</f>
+      </c>
+      <c r="M152" s="227">
+        <f>L152+N152</f>
+      </c>
+      <c r="N152" s="225">
+        <f>IF(5&lt;=$L$146,$L$142/$L$146,0)</f>
+      </c>
+      <c r="O152" s="227">
+        <f>IF(N152&lt;=0,"",MAX(ABS(($L$145-$L$143*L152+$L$144*L152^2/(2*$L$142))),ABS(($L$145-$L$143*M152+$L$144*M152^2/(2*$L$142)))))</f>
+      </c>
+      <c r="P152" s="227">
+        <f>IF(N152&lt;=0,"",O152*$L$29)</f>
+      </c>
+      <c r="Q152" s="227">
+        <f>IF(N152&lt;=0,"",MAX(MAX(0,P152-$L$127)/(0.9*$L$76*$L$129/10)*100,$L$132))</f>
+      </c>
+      <c r="R152" s="227">
+        <f>IF(N152&lt;=0,"",$L$43*PI()*($L$41/10)^2/4/Q152*100)</f>
+      </c>
+      <c r="S152" s="229">
+        <f>IF(N152&lt;=0,"",ROUNDDOWN(MIN(R152,IF(P152&lt;=0.67*$L$124,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20)),$L$136),0))</f>
+      </c>
+      <c r="T152" s="229">
+        <f>IF(N152&lt;=0,"",ROUNDUP(N152*100/S152,0))</f>
+      </c>
+    </row>
+    <row r="153">
+      <c r="K153" s="237">
+        <v>6</v>
+      </c>
+      <c r="L153" s="227">
+        <f>M152</f>
+      </c>
+      <c r="M153" s="227">
+        <f>L153+N153</f>
+      </c>
+      <c r="N153" s="225">
+        <f>IF(6&lt;=$L$146,$L$142/$L$146,0)</f>
+      </c>
+      <c r="O153" s="227">
+        <f>IF(N153&lt;=0,"",MAX(ABS(($L$145-$L$143*L153+$L$144*L153^2/(2*$L$142))),ABS(($L$145-$L$143*M153+$L$144*M153^2/(2*$L$142)))))</f>
+      </c>
+      <c r="P153" s="227">
+        <f>IF(N153&lt;=0,"",O153*$L$29)</f>
+      </c>
+      <c r="Q153" s="227">
+        <f>IF(N153&lt;=0,"",MAX(MAX(0,P153-$L$127)/(0.9*$L$76*$L$129/10)*100,$L$132))</f>
+      </c>
+      <c r="R153" s="227">
+        <f>IF(N153&lt;=0,"",$L$43*PI()*($L$41/10)^2/4/Q153*100)</f>
+      </c>
+      <c r="S153" s="229">
+        <f>IF(N153&lt;=0,"",ROUNDDOWN(MIN(R153,IF(P153&lt;=0.67*$L$124,MIN(0.6*$L$76,30),MIN(0.3*$L$76,20)),$L$136),0))</f>
+      </c>
+      <c r="T153" s="229">
+        <f>IF(N153&lt;=0,"",ROUNDUP(N153*100/S153,0))</f>
+      </c>
+    </row>
+    <row r="154">
+      <c r="K154" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total</t>
+        </is>
+      </c>
+      <c r="L154" s="229">
+        <f>SUM(T148:T153)</f>
+      </c>
+      <c r="M154" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estr.</t>
+        </is>
+      </c>
+      <c r="O154" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Número total de estribos no pilar (escalonados).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="K155" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣL</t>
+        </is>
+      </c>
+      <c r="L155" s="227">
+        <f>SUM(N148:N153)</f>
+      </c>
+      <c r="M155" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="N155" s="232">
+        <f>IF(ABS($L$155-$L$142)&gt;0.01,"Rever: soma ≠ H","Ok")</f>
+      </c>
+      <c r="O155" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soma dos comprimentos das zonas (deve ser igual a H).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="K156" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s,mín</t>
+        </is>
+      </c>
+      <c r="L156" s="229">
+        <f>MIN(S148:S153)</f>
+      </c>
+      <c r="M156" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O156" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Menor espaçamento entre as zonas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="K158" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 . TAXA DE AÇO</t>
+        </is>
+      </c>
+      <c r="L158" s="221"/>
+      <c r="M158" s="221"/>
+      <c r="N158" s="221"/>
+      <c r="O158" s="221"/>
+      <c r="P158" s="221"/>
+      <c r="Q158" s="221"/>
+      <c r="R158" s="221"/>
+      <c r="S158" s="221"/>
+      <c r="T158" s="221"/>
+    </row>
+    <row r="160">
+      <c r="K160" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ρ,aço</t>
+        </is>
+      </c>
+      <c r="L160" s="224">
+        <v>0.785</v>
+      </c>
+      <c r="M160" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg/m/cm²</t>
+        </is>
+      </c>
+      <c r="O160" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peso por metro de 1 cm² de barra (7850 kg/m³).</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="K161" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Longit.</t>
+        </is>
+      </c>
+      <c r="L161" s="227">
+        <f>$L$113*$L$160/($L$39*$L$38/10000)</f>
+      </c>
+      <c r="M161" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg/m³</t>
+        </is>
+      </c>
+      <c r="O161" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armadura longitudinal (duas faces) por m³ de concreto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="K162" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">l,est</t>
+        </is>
+      </c>
+      <c r="L162" s="227">
+        <f>2*($L$39+$L$38)-8*$L$40+12</f>
+      </c>
+      <c r="M162" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cm</t>
+        </is>
+      </c>
+      <c r="O162" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comprimento de cada estribo (perímetro − cobrimentos + ganchos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="K163" s="223" t="inlineStr">
+        <is>
           <t xml:space="preserve">Estribos</t>
         </is>
       </c>
-      <c r="L146" s="227">
-        <f>100/$L$137*$L$145/100*PI()*($L$41/10)^2/4*$L$143*$L$43/2/($L$39*$L$38/10000)</f>
-      </c>
-      <c r="M146" s="231" t="inlineStr">
+      <c r="L163" s="227">
+        <f>$L$154*$L$162/100*PI()*($L$41/10)^2/4*$L$160*$L$43/2/($L$39*$L$38/10000*$L$142)</f>
+      </c>
+      <c r="M163" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kg/m³</t>
         </is>
       </c>
-      <c r="O146" s="233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estribos por m³ de concreto (100/s estribos por metro).</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="K147" s="223" t="inlineStr">
+      <c r="O163" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estribos escalonados (item 6.3) por m³ de concreto do pilar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="K164" s="223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estr. unif.</t>
+        </is>
+      </c>
+      <c r="L164" s="227">
+        <f>100/$L$137*$L$162/100*PI()*($L$41/10)^2/4*$L$160*$L$43/2/($L$39*$L$38/10000)</f>
+      </c>
+      <c r="M164" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg/m³</t>
+        </is>
+      </c>
+      <c r="O164" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparação: estribos com s,unif em toda a altura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="K165" s="223" t="inlineStr">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="L147" s="227">
-        <f>$L$144+$L$146</f>
-      </c>
-      <c r="M147" s="231" t="inlineStr">
+      <c r="L165" s="227">
+        <f>$L$161+$L$163</f>
+      </c>
+      <c r="M165" s="231" t="inlineStr">
         <is>
           <t xml:space="preserve">kg/m³</t>
         </is>
       </c>
-      <c r="O147" s="233" t="inlineStr">
+      <c r="O165" s="233" t="inlineStr">
         <is>
           <t xml:space="preserve">Taxa total de aço do pilar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="K1:T1"/>
     <mergeCell ref="K6:T6"/>
     <mergeCell ref="K8:T8"/>
@@ -18757,6 +19234,7 @@
     <mergeCell ref="K119:T119"/>
     <mergeCell ref="K121:T121"/>
     <mergeCell ref="K141:T141"/>
+    <mergeCell ref="K158:T158"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="O10:T10"/>
     <mergeCell ref="L11:M11"/>
@@ -18784,12 +19262,12 @@
     <mergeCell ref="O5:R5"/>
     <mergeCell ref="S5:T5"/>
   </mergeCells>
-  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N117 N124 N137 N138 N139 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
+  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N117 N124 N137 N138 N139 N146 N155 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
     <cfRule type="beginsWith" dxfId="6" priority="1" operator="beginsWith" text="Ok">
       <formula>LEFT(N33,2)="Ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N117 N124 N137 N138 N139 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
+  <conditionalFormatting sqref="N33 N42 N45 N79 N84 N95 N114 N117 N124 N137 N138 N139 N146 N155 N11 N13 N14 N15 N16 N17 N18 S2 S3 S4 S5">
     <cfRule type="beginsWith" dxfId="5" priority="2" operator="beginsWith" text="Não se aplica">
       <formula>LEFT(N33,13)="Não se aplica"</formula>
     </cfRule>
